--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
     <t xml:space="preserve">4.40775871276855</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643571853638</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702157974243</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539794921875</t>
@@ -89,55 +89,55 @@
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422574996948</t>
+    <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
     <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819520950317</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
     <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054127693176</t>
+    <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142753601074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628540039062</t>
+    <t xml:space="preserve">4.28628492355347</t>
   </si>
   <si>
     <t xml:space="preserve">4.06936836242676</t>
@@ -146,67 +146,67 @@
     <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127721786499</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789433479309</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171347618103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
     <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230076789856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421010017395</t>
+    <t xml:space="preserve">3.64420962333679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657062530518</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201530456543</t>
+    <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524810791016</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
     <t xml:space="preserve">3.89583420753479</t>
@@ -215,49 +215,49 @@
     <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833083152771</t>
+    <t xml:space="preserve">3.74833059310913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273631095886</t>
+    <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375938415527</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037530899048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052610397339</t>
+    <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714226722717</t>
+    <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596935272217</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302248954773</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363981246948</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216229438782</t>
+    <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
     <t xml:space="preserve">3.29552412033081</t>
@@ -314,49 +314,49 @@
     <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404660224915</t>
+    <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
     <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0135543346405</t>
+    <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97830772399902</t>
+    <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9430615901947</t>
+    <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207681655884</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912154197693</t>
+    <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100608825684</t>
@@ -371,52 +371,52 @@
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477470397949</t>
+    <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239765167236</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854379653931</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567447662354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805081367493</t>
+    <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002131462097</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
@@ -425,19 +425,19 @@
     <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535316467285</t>
+    <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248312950134</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -452,16 +452,16 @@
     <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445363044739</t>
@@ -473,16 +473,16 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929249763489</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740818977356</t>
+    <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027798652649</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369161605835</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674734115601</t>
+    <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562651634216</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48130798339844</t>
+    <t xml:space="preserve">4.4813084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537424087524</t>
+    <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.39168262481689</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790636062622</t>
+    <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056108474731</t>
+    <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525211334229</t>
+    <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732685089111</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579414367676</t>
+    <t xml:space="preserve">3.40579438209534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334619522095</t>
+    <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147680282593</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -42784,7 +42784,7 @@
     </row>
     <row r="1589">
       <c r="A1589" s="1" t="n">
-        <v>45940.5910185185</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B1589" t="n">
         <v>10750</v>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849632263184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4077582359314</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526256561279</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999391555786</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643619537354</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966804504395</t>
   </si>
   <si>
     <t xml:space="preserve">4.21687173843384</t>
@@ -86,28 +86,28 @@
     <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745903015137</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1648120880127</t>
+    <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054056167603</t>
+    <t xml:space="preserve">3.93054151535034</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628540039062</t>
+    <t xml:space="preserve">4.28628492355347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936836242676</t>
+    <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
     <t xml:space="preserve">3.99127793312073</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436017990112</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759393692017</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
     <t xml:space="preserve">3.60082674026489</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392439842224</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804441452026</t>
@@ -197,34 +197,34 @@
     <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201530456543</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186450958252</t>
+    <t xml:space="preserve">3.92186379432678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258599281311</t>
+    <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684163093567</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -245,16 +245,16 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596982955933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978920936584</t>
+    <t xml:space="preserve">3.27978897094727</t>
   </si>
   <si>
     <t xml:space="preserve">3.19302225112915</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4541323184967</t>
+    <t xml:space="preserve">3.45413208007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22503161430359</t>
+    <t xml:space="preserve">3.22503185272217</t>
   </si>
   <si>
     <t xml:space="preserve">3.43650913238525</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.471755027771</t>
+    <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273980140686</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552435874939</t>
+    <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
     <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207633972168</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346837997437</t>
@@ -350,16 +350,16 @@
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387516975403</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
@@ -371,28 +371,28 @@
     <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16764426231384</t>
+    <t xml:space="preserve">2.16764402389526</t>
   </si>
   <si>
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903606414795</t>
+    <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854379653931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567411899567</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -413,28 +413,28 @@
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535316467285</t>
+    <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,22 +446,22 @@
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059906005859</t>
+    <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445363044739</t>
+    <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
     <t xml:space="preserve">2.69633769989014</t>
@@ -470,22 +470,22 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
     <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978500366211</t>
+    <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239252090454</t>
+    <t xml:space="preserve">3.26239275932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -515,28 +515,28 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297179222107</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072942733765</t>
+    <t xml:space="preserve">4.14072895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168262481689</t>
+    <t xml:space="preserve">4.39168214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695363998413</t>
+    <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612209320068</t>
+    <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280321121216</t>
+    <t xml:space="preserve">4.12280416488647</t>
   </si>
   <si>
     <t xml:space="preserve">4.26620626449585</t>
@@ -611,25 +611,25 @@
     <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902742385864</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9794020652771</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147656440735</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -785,22 +785,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -42958,6 +42958,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1596">
+      <c r="A1596" s="1" t="n">
+        <v>45951.2916666667</v>
+      </c>
+      <c r="B1596" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1596" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D1596" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="F1596" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="G1596" t="s">
+        <v>374</v>
+      </c>
+      <c r="H1596" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="1" t="n">
+        <v>45952.4288773148</v>
+      </c>
+      <c r="B1597" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1597" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D1597" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="G1597" t="s">
+        <v>374</v>
+      </c>
+      <c r="H1597" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849632263184</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415710449219</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3730525970459</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.37999296188354</t>
@@ -71,25 +71,25 @@
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966804504395</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539747238159</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
@@ -101,37 +101,37 @@
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613508224487</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819520950317</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
     <t xml:space="preserve">4.1214280128479</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0693678855896</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995470046997</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789433479309</t>
@@ -158,40 +158,40 @@
     <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509731292725</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77435994148254</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759322166443</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082650184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7656843662262</t>
+    <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392392158508</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
@@ -203,46 +203,46 @@
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186379432678</t>
+    <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524834632874</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583373069763</t>
+    <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833035469055</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273654937744</t>
+    <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258646965027</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345850944519</t>
+    <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714250564575</t>
+    <t xml:space="preserve">3.29714226722717</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596959114075</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978897094727</t>
+    <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302225112915</t>
+    <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650889396667</t>
+    <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207681655884</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912130355835</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22051382064819</t>
+    <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
@@ -383,34 +383,34 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854379653931</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
     <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158431053162</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822200775146</t>
+    <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674496650696</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633769989014</t>
+    <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929249763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027774810791</t>
+    <t xml:space="preserve">3.26027798652649</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674757957458</t>
+    <t xml:space="preserve">3.65674734115601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297179222107</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562651634216</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
     <t xml:space="preserve">4.17657947540283</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056060791016</t>
+    <t xml:space="preserve">4.66056108474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280416488647</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525259017944</t>
+    <t xml:space="preserve">4.01525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732685089111</t>
   </si>
   <si>
     <t xml:space="preserve">3.97940158843994</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579438209534</t>
+    <t xml:space="preserve">3.40579414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334595680237</t>
+    <t xml:space="preserve">3.51334619522095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147680282593</t>
@@ -43018,7 +43018,7 @@
     </row>
     <row r="1598">
       <c r="A1598" s="1" t="n">
-        <v>45953.3920601852</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B1598" t="n">
         <v>3000</v>
@@ -43039,6 +43039,32 @@
         <v>376</v>
       </c>
       <c r="H1598" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="1" t="n">
+        <v>45954.544212963</v>
+      </c>
+      <c r="B1599" t="n">
+        <v>14500</v>
+      </c>
+      <c r="C1599" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="D1599" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F1599" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G1599" t="s">
+        <v>365</v>
+      </c>
+      <c r="H1599" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -56,34 +56,34 @@
     <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305164337158</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
     <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539842605591</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1648120880127</t>
+    <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613460540771</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451049804688</t>
+    <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9305408000946</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142753601074</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -143,40 +143,40 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995493888855</t>
+    <t xml:space="preserve">3.99995470046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789433479309</t>
+    <t xml:space="preserve">3.94789385795593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171419143677</t>
   </si>
   <si>
     <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436017990112</t>
+    <t xml:space="preserve">3.77436089515686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
     <t xml:space="preserve">3.60082674026489</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657062530518</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392416000366</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201530456543</t>
+    <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598476409912</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524810791016</t>
+    <t xml:space="preserve">3.96524739265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833035469055</t>
+    <t xml:space="preserve">3.74833059310913</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714226722717</t>
+    <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363933563232</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126252174377</t>
+    <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
     <t xml:space="preserve">3.43650937080383</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.471755027771</t>
+    <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
     <t xml:space="preserve">3.61274003982544</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.348393201828</t>
+    <t xml:space="preserve">3.34839344024658</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.46723699569702</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387516975403</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22051334381104</t>
+    <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
     <t xml:space="preserve">2.20289039611816</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239812850952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.9561665058136</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805081367493</t>
+    <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002107620239</t>
+    <t xml:space="preserve">2.15002083778381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575971603394</t>
+    <t xml:space="preserve">2.25575995445251</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010655403137</t>
+    <t xml:space="preserve">2.52010631561279</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961428642273</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
     <t xml:space="preserve">3.11929273605347</t>
@@ -43096,7 +43096,7 @@
     </row>
     <row r="1601">
       <c r="A1601" s="1" t="n">
-        <v>45958.406412037</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B1601" t="n">
         <v>1750</v>
@@ -43117,6 +43117,32 @@
         <v>366</v>
       </c>
       <c r="H1601" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="1" t="n">
+        <v>45959.6864583333</v>
+      </c>
+      <c r="B1602" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C1602" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D1602" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="E1602" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F1602" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="G1602" t="s">
+        <v>372</v>
+      </c>
+      <c r="H1602" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -47,43 +47,43 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187944412231</t>
+    <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
     <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216872215271</t>
+    <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702157974243</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539842605591</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
     <t xml:space="preserve">4.2255482673645</t>
@@ -101,40 +101,40 @@
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.16481113433838</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995470046997</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
     <t xml:space="preserve">3.99127769470215</t>
@@ -152,25 +152,25 @@
     <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789385795593</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171419143677</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
     <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436089515686</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72229981422424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
@@ -179,64 +179,64 @@
     <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672189712524</t>
+    <t xml:space="preserve">4.08672094345093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583420753479</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273654937744</t>
+    <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684210777283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037530899048</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596911430359</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390970230103</t>
+    <t xml:space="preserve">3.38390922546387</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4541323184967</t>
+    <t xml:space="preserve">3.45413255691528</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363933563232</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650937080383</t>
+    <t xml:space="preserve">3.43650889396667</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077025413513</t>
+    <t xml:space="preserve">3.33077001571655</t>
   </si>
   <si>
     <t xml:space="preserve">3.34839344024658</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216205596924</t>
+    <t xml:space="preserve">3.17216229438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
     <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -332,34 +332,34 @@
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81970000267029</t>
+    <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9430615901947</t>
+    <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346837997437</t>
+    <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
     <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46723699569702</t>
+    <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
     <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100584983826</t>
+    <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387540817261</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289039611816</t>
+    <t xml:space="preserve">2.20289015769958</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239812850952</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -404,28 +404,28 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518161296844</t>
+    <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002083778381</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
     <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575995445251</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
     <t xml:space="preserve">2.73158407211304</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822224617004</t>
+    <t xml:space="preserve">2.60822200775146</t>
   </si>
   <si>
     <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010631561279</t>
+    <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445363044739</t>
@@ -470,16 +470,16 @@
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
     <t xml:space="preserve">3.26027774810791</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239252090454</t>
+    <t xml:space="preserve">3.26239275932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3520188331604</t>
+    <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616830825806</t>
+    <t xml:space="preserve">3.31616806983948</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168262481689</t>
+    <t xml:space="preserve">4.39168214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -551,43 +551,43 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574792861938</t>
+    <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753267288208</t>
+    <t xml:space="preserve">4.42753314971924</t>
   </si>
   <si>
     <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413105010986</t>
+    <t xml:space="preserve">4.28413057327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998205184937</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -617,31 +617,31 @@
     <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902837753296</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824280738831</t>
+    <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -43122,7 +43122,7 @@
     </row>
     <row r="1602">
       <c r="A1602" s="1" t="n">
-        <v>45959.6864583333</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B1602" t="n">
         <v>3250</v>
@@ -43143,6 +43143,32 @@
         <v>372</v>
       </c>
       <c r="H1602" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="1" t="n">
+        <v>45960.6846527778</v>
+      </c>
+      <c r="B1603" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1603" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D1603" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E1603" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="F1603" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G1603" t="s">
+        <v>364</v>
+      </c>
+      <c r="H1603" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849489212036</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415710449219</t>
@@ -53,16 +53,16 @@
     <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526256561279</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187944412231</t>
+    <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3730525970459</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.3799934387207</t>
@@ -77,40 +77,40 @@
     <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157928466797</t>
+    <t xml:space="preserve">4.25157785415649</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613460540771</t>
@@ -119,103 +119,103 @@
     <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819425582886</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451121330261</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
     <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.01730728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.12142848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936836242676</t>
+    <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995470046997</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127793312073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921732902527</t>
+    <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230052947998</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420962333679</t>
+    <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759393692017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568388938904</t>
+    <t xml:space="preserve">3.7656843662262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672189712524</t>
+    <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583444595337</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596982955933</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363933563232</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47175526618958</t>
+    <t xml:space="preserve">3.471755027771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274027824402</t>
+    <t xml:space="preserve">3.61273980140686</t>
   </si>
   <si>
     <t xml:space="preserve">3.33077025413513</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552388191223</t>
+    <t xml:space="preserve">3.29552435874939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81970000267029</t>
+    <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
     <t xml:space="preserve">2.85494613647461</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207633972168</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387540817261</t>
+    <t xml:space="preserve">2.34387516975403</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
@@ -383,43 +383,43 @@
     <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239812850952</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903630256653</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854343891144</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8328047990799</t>
+    <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518161296844</t>
+    <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042774677277</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002083778381</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575995445251</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
@@ -428,13 +428,13 @@
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822248458862</t>
+    <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
     <t xml:space="preserve">2.5024836063385</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48486018180847</t>
+    <t xml:space="preserve">2.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633793830872</t>
+    <t xml:space="preserve">2.69633769989014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
     <t xml:space="preserve">3.11929297447205</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978524208069</t>
+    <t xml:space="preserve">3.18978500366211</t>
   </si>
   <si>
     <t xml:space="preserve">3.13691568374634</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072942733765</t>
+    <t xml:space="preserve">4.14072895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695363998413</t>
+    <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612209320068</t>
+    <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -605,25 +605,25 @@
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280321121216</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902742385864</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9794020652771</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147656440735</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -43223,7 +43223,7 @@
     </row>
     <row r="1606">
       <c r="A1606" s="1" t="n">
-        <v>45965.6625462963</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B1606" t="n">
         <v>9500</v>
@@ -43244,6 +43244,32 @@
         <v>363</v>
       </c>
       <c r="H1606" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="1" t="n">
+        <v>45966.6673148148</v>
+      </c>
+      <c r="B1607" t="n">
+        <v>9250</v>
+      </c>
+      <c r="C1607" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D1607" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E1607" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F1607" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1607" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1607" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -53,22 +53,22 @@
     <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526304244995</t>
+    <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187944412231</t>
+    <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
     <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.32966899871826</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539794921875</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745903015137</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216514587402</t>
+    <t xml:space="preserve">4.18216562271118</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054127693176</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628492355347</t>
@@ -143,112 +143,112 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921732902527</t>
+    <t xml:space="preserve">3.93921709060669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230052947998</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494675636292</t>
+    <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
     <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082721710205</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
     <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392439842224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804393768311</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201482772827</t>
+    <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186379432678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.965247631073</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833083152771</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273654937744</t>
+    <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258575439453</t>
+    <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345850944519</t>
+    <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052610397339</t>
+    <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596935272217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -299,28 +299,28 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216205596924</t>
+    <t xml:space="preserve">3.17216229438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404636383057</t>
+    <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
     <t xml:space="preserve">2.96068453788757</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100608825684</t>
+    <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387540817261</t>
@@ -380,25 +380,25 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
     <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567447662354</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -407,16 +407,16 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042774677277</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059906005859</t>
+    <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445363044739</t>
@@ -473,16 +473,16 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929249763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027774810791</t>
+    <t xml:space="preserve">3.26027798652649</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674757957458</t>
+    <t xml:space="preserve">3.65674734115601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297226905823</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562651634216</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.39168262481689</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056060791016</t>
+    <t xml:space="preserve">4.66056108474731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545841217041</t>
+    <t xml:space="preserve">4.44545793533325</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525259017944</t>
+    <t xml:space="preserve">4.01525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732685089111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579438209534</t>
+    <t xml:space="preserve">3.40579414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334595680237</t>
+    <t xml:space="preserve">3.51334619522095</t>
   </si>
   <si>
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -43434,7 +43434,7 @@
     </row>
     <row r="1614">
       <c r="A1614" s="1" t="n">
-        <v>45975.5936458333</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B1614" t="n">
         <v>500</v>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849632263184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
     <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526304244995</t>
+    <t xml:space="preserve">4.55526351928711</t>
   </si>
   <si>
     <t xml:space="preserve">4.51187896728516</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.37999391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643619537354</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.32966899871826</t>
@@ -77,25 +77,25 @@
     <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702301025391</t>
+    <t xml:space="preserve">4.34702157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539842605591</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010549545288</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -107,22 +107,22 @@
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613555908203</t>
+    <t xml:space="preserve">4.15613412857056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216514587402</t>
+    <t xml:space="preserve">4.18216466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819568634033</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451049804688</t>
+    <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
     <t xml:space="preserve">3.93054056167603</t>
@@ -140,55 +140,55 @@
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0693678855896</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995422363281</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
     <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921756744385</t>
+    <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789433479309</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171347618103</t>
+    <t xml:space="preserve">3.79171419143677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509707450867</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436065673828</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421010017395</t>
+    <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759322166443</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568388938904</t>
+    <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392392158508</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.02598524093628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583373069763</t>
+    <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333686828613</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273631095886</t>
@@ -230,22 +230,22 @@
     <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037602424622</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714274406433</t>
+    <t xml:space="preserve">3.29714226722717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596935272217</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978920936584</t>
+    <t xml:space="preserve">3.27978944778442</t>
   </si>
   <si>
     <t xml:space="preserve">3.19302225112915</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45413208007812</t>
+    <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363981246948</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22503161430359</t>
+    <t xml:space="preserve">3.22503137588501</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126276016235</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
     <t xml:space="preserve">3.1016697883606</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068429946899</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0135543346405</t>
+    <t xml:space="preserve">3.01355385780334</t>
   </si>
   <si>
     <t xml:space="preserve">2.9783079624176</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207681655884</t>
@@ -350,70 +350,70 @@
     <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4672372341156</t>
+    <t xml:space="preserve">2.46723699569702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912130355835</t>
+    <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100584983826</t>
+    <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
+    <t xml:space="preserve">2.34387516975403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625246047974</t>
+    <t xml:space="preserve">2.32625198364258</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477470397949</t>
+    <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239765167236</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854379653931</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002131462097</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
     <t xml:space="preserve">2.04428219795227</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010679244995</t>
+    <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
@@ -449,46 +449,46 @@
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059929847717</t>
+    <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633769989014</t>
+    <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929249763489</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027798652649</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978524208069</t>
+    <t xml:space="preserve">3.18978548049927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369161605835</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35201859474182</t>
+    <t xml:space="preserve">3.3520188331604</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297179222107</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48130798339844</t>
+    <t xml:space="preserve">4.4813084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537424087524</t>
+    <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
     <t xml:space="preserve">4.17657947540283</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
     <t xml:space="preserve">4.5709342956543</t>
@@ -572,22 +572,22 @@
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574745178223</t>
+    <t xml:space="preserve">4.61574792861938</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790636062622</t>
+    <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280416488647</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317785263062</t>
+    <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
     <t xml:space="preserve">3.97940158843994</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824304580688</t>
+    <t xml:space="preserve">3.29824280738831</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147680282593</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -43538,7 +43538,7 @@
     </row>
     <row r="1618">
       <c r="A1618" s="1" t="n">
-        <v>45981.5171759259</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B1618" t="n">
         <v>5500</v>
@@ -43559,6 +43559,32 @@
         <v>368</v>
       </c>
       <c r="H1618" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="1" t="n">
+        <v>45982.45125</v>
+      </c>
+      <c r="B1619" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1619" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1619" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G1619" t="s">
+        <v>369</v>
+      </c>
+      <c r="H1619" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849632263184</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
     <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526351928711</t>
+    <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999391555786</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643571853638</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702157974243</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745855331421</t>
@@ -101,31 +101,31 @@
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613412857056</t>
+    <t xml:space="preserve">4.15613555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216562271118</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054056167603</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863075256348</t>
@@ -143,31 +143,31 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
     <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171419143677</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436065673828</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494699478149</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392439842224</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
@@ -200,49 +200,49 @@
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598524093628</t>
+    <t xml:space="preserve">4.0259838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.96524739265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833083152771</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258646965027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714226722717</t>
+    <t xml:space="preserve">3.29714274406433</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596935272217</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978944778442</t>
+    <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
     <t xml:space="preserve">3.19302225112915</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22503137588501</t>
+    <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126276016235</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.17216229438782</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355385780334</t>
+    <t xml:space="preserve">3.0135543346405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783079624176</t>
+    <t xml:space="preserve">2.97830772399902</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
@@ -350,49 +350,49 @@
     <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46723699569702</t>
+    <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387516975403</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625198364258</t>
+    <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289039611816</t>
+    <t xml:space="preserve">2.20289015769958</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477494239807</t>
+    <t xml:space="preserve">2.11477470397949</t>
   </si>
   <si>
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903606414795</t>
+    <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
     <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854379653931</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518161296844</t>
+    <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002107620239</t>
+    <t xml:space="preserve">2.15002131462097</t>
   </si>
   <si>
     <t xml:space="preserve">2.04428219795227</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53772974014282</t>
+    <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
     <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248312950134</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059906005859</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929249763489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740842819214</t>
+    <t xml:space="preserve">3.20740818977356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027774810791</t>
+    <t xml:space="preserve">3.26027798652649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978548049927</t>
+    <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3520188331604</t>
+    <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674757957458</t>
+    <t xml:space="preserve">3.65674734115601</t>
   </si>
   <si>
     <t xml:space="preserve">3.60297203063965</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.92562651634216</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.39168262481689</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.5709342956543</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574792861938</t>
+    <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056060791016</t>
+    <t xml:space="preserve">4.66056108474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035526275635</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525259017944</t>
+    <t xml:space="preserve">4.01525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732685089111</t>
   </si>
   <si>
     <t xml:space="preserve">3.97940158843994</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824280738831</t>
+    <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579438209534</t>
+    <t xml:space="preserve">3.40579414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334595680237</t>
+    <t xml:space="preserve">3.51334619522095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -43564,7 +43564,7 @@
     </row>
     <row r="1619">
       <c r="A1619" s="1" t="n">
-        <v>45982.45125</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B1619" t="n">
         <v>6000</v>
@@ -43585,6 +43585,32 @@
         <v>369</v>
       </c>
       <c r="H1619" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="1" t="n">
+        <v>45985.6911226852</v>
+      </c>
+      <c r="B1620" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1620" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1620" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1620" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F1620" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G1620" t="s">
+        <v>373</v>
+      </c>
+      <c r="H1620" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -47,31 +47,31 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
     <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526256561279</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
     <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3799934387207</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
     <t xml:space="preserve">4.21687173843384</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
@@ -101,19 +101,19 @@
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1648120880127</t>
+    <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613555908203</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216562271118</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863075256348</t>
@@ -140,31 +140,31 @@
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936836242676</t>
+    <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995422363281</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127745628357</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921756744385</t>
+    <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789433479309</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436017990112</t>
+    <t xml:space="preserve">3.77435994148254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
     <t xml:space="preserve">3.72230005264282</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420986175537</t>
+    <t xml:space="preserve">3.64421033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568365097046</t>
+    <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657110214233</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392439842224</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804393768311</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672189712524</t>
@@ -200,34 +200,34 @@
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0259838104248</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
     <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833035469055</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273631095886</t>
+    <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258646965027</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684163093567</t>
+    <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
     <t xml:space="preserve">3.25375890731812</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037530899048</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714274406433</t>
+    <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596935272217</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302225112915</t>
+    <t xml:space="preserve">3.19302248954773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390946388245</t>
+    <t xml:space="preserve">3.38390922546387</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650913238525</t>
+    <t xml:space="preserve">3.43650889396667</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216229438782</t>
+    <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
     <t xml:space="preserve">3.29552412033081</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -326,19 +326,19 @@
     <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0135543346405</t>
+    <t xml:space="preserve">3.01355385780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97830772399902</t>
+    <t xml:space="preserve">2.97830820083618</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9430615901947</t>
+    <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207681655884</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912154197693</t>
+    <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100608825684</t>
@@ -371,73 +371,73 @@
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477470397949</t>
+    <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239765167236</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854379653931</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805081367493</t>
+    <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002131462097</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535316467285</t>
+    <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248312950134</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,22 +446,22 @@
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445363044739</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929249763489</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740818977356</t>
+    <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027798652649</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239252090454</t>
+    <t xml:space="preserve">3.26239275932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369161605835</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616830825806</t>
+    <t xml:space="preserve">3.31616806983948</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674734115601</t>
+    <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
     <t xml:space="preserve">3.60297203063965</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562651634216</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48130798339844</t>
+    <t xml:space="preserve">4.4813084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537424087524</t>
+    <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168262481689</t>
+    <t xml:space="preserve">4.39168214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753267288208</t>
+    <t xml:space="preserve">4.42753314971924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790636062622</t>
+    <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413105010986</t>
+    <t xml:space="preserve">4.28413057327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998205184937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056108474731</t>
+    <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317785263062</t>
+    <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902837753296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525211334229</t>
+    <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732685089111</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579414367676</t>
+    <t xml:space="preserve">3.40579438209534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334619522095</t>
+    <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147680282593</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -43590,7 +43590,7 @@
     </row>
     <row r="1620">
       <c r="A1620" s="1" t="n">
-        <v>45985.6911226852</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B1620" t="n">
         <v>500</v>
@@ -43599,7 +43599,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="D1620" t="n">
-        <v>2.27999997138977</v>
+        <v>2.25999999046326</v>
       </c>
       <c r="E1620" t="n">
         <v>2.27999997138977</v>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
     <t xml:space="preserve">4.40775871276855</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3730525970459</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.37999391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
     <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702253341675</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745903015137</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010549545288</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -104,16 +104,16 @@
     <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613555908203</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216514587402</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451121330261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9305408000946</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863027572632</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730728149414</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142848968506</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -143,52 +143,52 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995398521423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127721786499</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921732902527</t>
+    <t xml:space="preserve">3.93921685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789505004883</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171347618103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509731292725</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230076789856</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420986175537</t>
+    <t xml:space="preserve">3.64420962333679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
     <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
@@ -203,40 +203,40 @@
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.965247631073</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833083152771</t>
+    <t xml:space="preserve">3.74833011627197</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -245,37 +245,37 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596935272217</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978920936584</t>
+    <t xml:space="preserve">3.27978944778442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302248954773</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126299858093</t>
+    <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363933563232</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22503185272217</t>
+    <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126276016235</t>
+    <t xml:space="preserve">3.40126252174377</t>
   </si>
   <si>
     <t xml:space="preserve">3.43650913238525</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61273980140686</t>
+    <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077001571655</t>
+    <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
     <t xml:space="preserve">3.34839344024658</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
@@ -341,46 +341,46 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207633972168</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100608825684</t>
+    <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387516975403</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22051334381104</t>
+    <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
     <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16764402389526</t>
+    <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239789009094</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854343891144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567411899567</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -404,25 +404,25 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48486042022705</t>
+    <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445363044739</t>
+    <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
     <t xml:space="preserve">2.69633793830872</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740842819214</t>
+    <t xml:space="preserve">3.20740818977356</t>
   </si>
   <si>
     <t xml:space="preserve">3.24265480041504</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616806983948</t>
+    <t xml:space="preserve">3.31616830825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072895050049</t>
+    <t xml:space="preserve">4.14072942733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
@@ -557,34 +557,34 @@
     <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695316314697</t>
+    <t xml:space="preserve">4.08695363998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612161636353</t>
+    <t xml:space="preserve">4.52612209320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753314971924</t>
+    <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
     <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413057327271</t>
+    <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998205184937</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
@@ -599,31 +599,31 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280368804932</t>
+    <t xml:space="preserve">4.12280321121216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620578765869</t>
+    <t xml:space="preserve">4.26620626449585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902837753296</t>
+    <t xml:space="preserve">4.06902742385864</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.9794020652771</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147656440735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -43769,7 +43769,7 @@
     </row>
     <row r="1627">
       <c r="A1627" s="1" t="n">
-        <v>45994.6558912037</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B1627" t="n">
         <v>750</v>
@@ -43790,6 +43790,32 @@
         <v>367</v>
       </c>
       <c r="H1627" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="1" t="n">
+        <v>45995.5740162037</v>
+      </c>
+      <c r="B1628" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1628" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1628" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E1628" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F1628" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G1628" t="s">
+        <v>369</v>
+      </c>
+      <c r="H1628" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -44,49 +44,49 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849536895752</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526256561279</t>
+    <t xml:space="preserve">4.55526208877563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3730525970459</t>
+    <t xml:space="preserve">4.37305164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216872215271</t>
+    <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745855331421</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451121330261</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
     <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863170623779</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142753601074</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -143,31 +143,31 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995422363281</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127721786499</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921685218811</t>
+    <t xml:space="preserve">3.93921828269958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789528846741</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
     <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436065673828</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230052947998</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494675636292</t>
@@ -176,28 +176,28 @@
     <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568365097046</t>
+    <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657134056091</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804393768311</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
@@ -206,28 +206,28 @@
     <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333829879761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273631095886</t>
+    <t xml:space="preserve">3.52273678779602</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684163093567</t>
+    <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
     <t xml:space="preserve">3.25375890731812</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390946388245</t>
+    <t xml:space="preserve">3.38390970230103</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126276016235</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363933563232</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -281,10 +281,10 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47175526618958</t>
+    <t xml:space="preserve">3.471755027771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274027824402</t>
+    <t xml:space="preserve">3.61273980140686</t>
   </si>
   <si>
     <t xml:space="preserve">3.33077025413513</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552388191223</t>
+    <t xml:space="preserve">3.29552435874939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81970000267029</t>
+    <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
     <t xml:space="preserve">2.85494613647461</t>
@@ -338,19 +338,19 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207633972168</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387540817261</t>
+    <t xml:space="preserve">2.34387516975403</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
@@ -380,43 +380,43 @@
     <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239812850952</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903630256653</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854343891144</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8328047990799</t>
+    <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518161296844</t>
+    <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042774677277</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002083778381</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575995445251</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822248458862</t>
+    <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
     <t xml:space="preserve">2.5024836063385</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48486018180847</t>
+    <t xml:space="preserve">2.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633793830872</t>
+    <t xml:space="preserve">2.69633769989014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
     <t xml:space="preserve">3.11929297447205</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978524208069</t>
+    <t xml:space="preserve">3.18978500366211</t>
   </si>
   <si>
     <t xml:space="preserve">3.13691568374634</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072942733765</t>
+    <t xml:space="preserve">4.14072895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695363998413</t>
+    <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612209320068</t>
+    <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
@@ -581,13 +581,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -602,25 +602,25 @@
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280321121216</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902742385864</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9794020652771</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147656440735</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -43949,6 +43949,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1634">
+      <c r="A1634" s="1" t="n">
+        <v>46003.3333333333</v>
+      </c>
+      <c r="B1634" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1634" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1634" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1634" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G1634" t="s">
+        <v>371</v>
+      </c>
+      <c r="H1634" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="1" t="n">
+        <v>46006.6909837963</v>
+      </c>
+      <c r="B1635" t="n">
+        <v>17250</v>
+      </c>
+      <c r="C1635" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1635" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1635" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1635" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G1635" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1635" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="384">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4077582359314</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526304244995</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539794921875</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010549545288</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481113433838</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
@@ -113,43 +113,43 @@
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613555908203</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216562271118</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819520950317</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0693678855896</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995470046997</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789433479309</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436017990112</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494699478149</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082650184631</t>
   </si>
   <si>
     <t xml:space="preserve">3.76568388938904</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392439842224</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
@@ -206,25 +206,25 @@
     <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833035469055</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273654937744</t>
+    <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258646965027</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684186935425</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714274406433</t>
+    <t xml:space="preserve">3.29714226722717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596935272217</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45413208007812</t>
+    <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363981246948</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
     <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068429946899</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0135543346405</t>
+    <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
     <t xml:space="preserve">2.9783079624176</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
     <t xml:space="preserve">2.62584519386292</t>
@@ -353,67 +353,67 @@
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912130355835</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625246047974</t>
+    <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477470397949</t>
+    <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854379653931</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
     <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002131462097</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
     <t xml:space="preserve">2.04428219795227</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010679244995</t>
+    <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633769989014</t>
+    <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
     <t xml:space="preserve">3.04880046844482</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674757957458</t>
+    <t xml:space="preserve">3.65674734115601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297179222107</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562651634216</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
     <t xml:space="preserve">4.17657947540283</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056060791016</t>
+    <t xml:space="preserve">4.66056108474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280416488647</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525259017944</t>
+    <t xml:space="preserve">4.01525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732685089111</t>
   </si>
   <si>
     <t xml:space="preserve">3.97940158843994</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579438209534</t>
+    <t xml:space="preserve">3.40579414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334595680237</t>
+    <t xml:space="preserve">3.51334619522095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147680282593</t>
@@ -1162,6 +1162,9 @@
   <si>
     <t xml:space="preserve">2.22000002861023</t>
   </si>
+  <si>
+    <t xml:space="preserve">2.16000008583069</t>
+  </si>
 </sst>
 </file>
 
@@ -44009,7 +44012,7 @@
     </row>
     <row r="1636">
       <c r="A1636" s="1" t="n">
-        <v>46007.6191087963</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B1636" t="n">
         <v>1250</v>
@@ -44030,6 +44033,32 @@
         <v>369</v>
       </c>
       <c r="H1636" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="1" t="n">
+        <v>46008.6868287037</v>
+      </c>
+      <c r="B1637" t="n">
+        <v>12750</v>
+      </c>
+      <c r="C1637" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="D1637" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1637" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G1637" t="s">
+        <v>383</v>
+      </c>
+      <c r="H1637" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">4.46849536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775918960571</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526256561279</t>
@@ -74,22 +74,22 @@
     <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010549545288</t>
@@ -101,64 +101,64 @@
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290227890015</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613508224487</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
     <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936883926392</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
     <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127721786499</t>
+    <t xml:space="preserve">3.99127793312073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921732902527</t>
+    <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789505004883</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
     <t xml:space="preserve">3.77436017990112</t>
@@ -167,25 +167,25 @@
     <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230076789856</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494675636292</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420962333679</t>
+    <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759393692017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082721710205</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568365097046</t>
+    <t xml:space="preserve">3.7656843662262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392416000366</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672094345093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186450958252</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">3.89583420753479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833035469055</t>
+    <t xml:space="preserve">3.74833059310913</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345850944519</t>
+    <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
     <t xml:space="preserve">3.21037554740906</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302248954773</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126276016235</t>
+    <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
     <t xml:space="preserve">3.4541323184967</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126252174377</t>
+    <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
     <t xml:space="preserve">3.43650913238525</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47175526618958</t>
+    <t xml:space="preserve">3.471755027771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274003982544</t>
+    <t xml:space="preserve">3.61273980140686</t>
   </si>
   <si>
     <t xml:space="preserve">3.33077025413513</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552435874939</t>
   </si>
   <si>
     <t xml:space="preserve">3.15453886985779</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207633972168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387540817261</t>
+    <t xml:space="preserve">2.34387516975403</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854331970215</t>
+    <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518161296844</t>
+    <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042774677277</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48486018180847</t>
+    <t xml:space="preserve">2.48486042022705</t>
   </si>
   <si>
     <t xml:space="preserve">2.43199110031128</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633793830872</t>
+    <t xml:space="preserve">2.69633769989014</t>
   </si>
   <si>
     <t xml:space="preserve">3.04880046844482</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740818977356</t>
+    <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
     <t xml:space="preserve">3.24265480041504</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978524208069</t>
+    <t xml:space="preserve">3.18978500366211</t>
   </si>
   <si>
     <t xml:space="preserve">3.13691568374634</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297226905823</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072895050049</t>
+    <t xml:space="preserve">4.14072942733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695316314697</t>
+    <t xml:space="preserve">4.08695363998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612161636353</t>
+    <t xml:space="preserve">4.52612209320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545841217041</t>
+    <t xml:space="preserve">4.44545793533325</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -605,25 +605,25 @@
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280368804932</t>
+    <t xml:space="preserve">4.12280321121216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620578765869</t>
+    <t xml:space="preserve">4.26620626449585</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902742385864</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.9794020652771</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147656440735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -44148,7 +44148,7 @@
     </row>
     <row r="1641">
       <c r="A1641" s="1" t="n">
-        <v>46014.6868171296</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B1641" t="n">
         <v>8000</v>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849536895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39214086532593</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702205657959</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216514587402</t>
+    <t xml:space="preserve">4.18216466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451049804688</t>
+    <t xml:space="preserve">3.90451121330261</t>
   </si>
   <si>
     <t xml:space="preserve">3.93054127693176</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
     <t xml:space="preserve">4.1214280128479</t>
@@ -158,31 +158,31 @@
     <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
     <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
     <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421010017395</t>
+    <t xml:space="preserve">3.64421033859253</t>
   </si>
   <si>
     <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082650184631</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568388938904</t>
+    <t xml:space="preserve">3.7656843662262</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657110214233</t>
@@ -194,19 +194,19 @@
     <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201482772827</t>
+    <t xml:space="preserve">4.05201530456543</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.965247631073</t>
+    <t xml:space="preserve">3.96524810791016</t>
   </si>
   <si>
     <t xml:space="preserve">3.89583396911621</t>
@@ -218,28 +218,28 @@
     <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273631095886</t>
+    <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258646965027</t>
+    <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684210777283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375938415527</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052586555481</t>
+    <t xml:space="preserve">3.34052610397339</t>
   </si>
   <si>
     <t xml:space="preserve">3.29714226722717</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978920936584</t>
+    <t xml:space="preserve">3.27978944778442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126299858093</t>
+    <t xml:space="preserve">3.40126323699951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4541323184967</t>
+    <t xml:space="preserve">3.45413255691528</t>
   </si>
   <si>
     <t xml:space="preserve">3.3836395740509</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274003982544</t>
+    <t xml:space="preserve">3.61274027824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077025413513</t>
+    <t xml:space="preserve">3.33077049255371</t>
   </si>
   <si>
     <t xml:space="preserve">3.348393201828</t>
@@ -299,37 +299,37 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216229438782</t>
+    <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552388191223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
     <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593091011047</t>
+    <t xml:space="preserve">2.99593114852905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404660224915</t>
+    <t xml:space="preserve">3.08404684066772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783079624176</t>
+    <t xml:space="preserve">2.97830772399902</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207681655884</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912154197693</t>
+    <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100584983826</t>
+    <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387540817261</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289039611816</t>
+    <t xml:space="preserve">2.20289015769958</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239765167236</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903606414795</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805081367493</t>
+    <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952857017517</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575947761536</t>
+    <t xml:space="preserve">2.25575971603394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53772974014282</t>
+    <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
     <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535316467285</t>
+    <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
@@ -440,25 +440,25 @@
     <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010655403137</t>
+    <t xml:space="preserve">2.52010631561279</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059929847717</t>
+    <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.66109156608582</t>
@@ -470,25 +470,25 @@
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929249763489</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027798652649</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.4077582359314</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526256561279</t>
@@ -59,28 +59,28 @@
     <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.37999391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643619537354</t>
   </si>
   <si>
     <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216872215271</t>
+    <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539747238159</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613460540771</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054127693176</t>
+    <t xml:space="preserve">3.93054056167603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995398521423</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
     <t xml:space="preserve">3.99127793312073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921732902527</t>
+    <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789433479309</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171371459961</t>
@@ -161,31 +161,31 @@
     <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759393692017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082650184631</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.7656843662262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657062530518</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392463684082</t>
@@ -194,19 +194,19 @@
     <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672094345093</t>
+    <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.05201530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524810791016</t>
+    <t xml:space="preserve">3.96524739265442</t>
   </si>
   <si>
     <t xml:space="preserve">3.89583396911621</t>
@@ -215,31 +215,31 @@
     <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833083152771</t>
+    <t xml:space="preserve">3.74833059310913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273631095886</t>
+    <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375938415527</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052610397339</t>
+    <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.29714250564575</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45413208007812</t>
+    <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363933563232</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22503185272217</t>
+    <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
     <t xml:space="preserve">3.43650913238525</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47175526618958</t>
+    <t xml:space="preserve">3.471755027771</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273980140686</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552435874939</t>
   </si>
   <si>
     <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207633972168</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346837997437</t>
@@ -350,16 +350,16 @@
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912154197693</t>
+    <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387540817261</t>
+    <t xml:space="preserve">2.34387516975403</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
@@ -371,28 +371,28 @@
     <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16764402389526</t>
+    <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854379653931</t>
+    <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567411899567</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -413,28 +413,28 @@
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,22 +446,22 @@
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059929847717</t>
+    <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.69633769989014</t>
@@ -470,22 +470,22 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
     <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978524208069</t>
+    <t xml:space="preserve">3.18978500366211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369161605835</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -515,28 +515,28 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297179222107</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072895050049</t>
+    <t xml:space="preserve">4.14072942733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48130798339844</t>
+    <t xml:space="preserve">4.4813084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537424087524</t>
+    <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695316314697</t>
+    <t xml:space="preserve">4.08695363998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612161636353</t>
+    <t xml:space="preserve">4.52612209320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790636062622</t>
+    <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280416488647</t>
+    <t xml:space="preserve">4.12280321121216</t>
   </si>
   <si>
     <t xml:space="preserve">4.26620626449585</t>
@@ -611,25 +611,25 @@
     <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902742385864</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.9794020652771</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147680282593</t>
+    <t xml:space="preserve">3.96147656440735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -785,22 +785,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -44197,7 +44197,7 @@
     </row>
     <row r="1643">
       <c r="A1643" s="1" t="n">
-        <v>46021.4003703704</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B1643" t="n">
         <v>250</v>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849536895752</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415758132935</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
     <t xml:space="preserve">4.216872215271</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539747238159</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745759963989</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422527313232</t>
+    <t xml:space="preserve">4.23422479629517</t>
   </si>
   <si>
     <t xml:space="preserve">4.1648120880127</t>
@@ -110,37 +110,37 @@
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216562271118</t>
+    <t xml:space="preserve">4.18216466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819520950317</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
     <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054127693176</t>
+    <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
     <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628587722778</t>
+    <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936740875244</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
     <t xml:space="preserve">3.99995446205139</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
     <t xml:space="preserve">3.83509755134583</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421033859253</t>
+    <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
     <t xml:space="preserve">3.68759369850159</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
     <t xml:space="preserve">4.05201482772827</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186450958252</t>
+    <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524810791016</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
     <t xml:space="preserve">3.74833059310913</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258623123169</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037530899048</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -254,13 +254,13 @@
     <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978944778442</t>
+    <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302225112915</t>
+    <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390922546387</t>
+    <t xml:space="preserve">3.38390970230103</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363933563232</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650889396667</t>
+    <t xml:space="preserve">3.43650937080383</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274027824402</t>
+    <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077049255371</t>
+    <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
     <t xml:space="preserve">3.34839344024658</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552388191223</t>
+    <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
     <t xml:space="preserve">3.15453910827637</t>
@@ -314,34 +314,34 @@
     <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593114852905</t>
+    <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355385780334</t>
+    <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97830820083618</t>
+    <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81969976425171</t>
+    <t xml:space="preserve">2.81970000267029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207681655884</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346837997437</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4672372341156</t>
+    <t xml:space="preserve">2.46723699569702</t>
   </si>
   <si>
     <t xml:space="preserve">2.36149859428406</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625246047974</t>
+    <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616662502289</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854343891144</t>
+    <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805105209351</t>
+    <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -407,28 +407,28 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002107620239</t>
+    <t xml:space="preserve">2.15002083778381</t>
   </si>
   <si>
     <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575971603394</t>
+    <t xml:space="preserve">2.25575995445251</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53772974014282</t>
+    <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158431053162</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010655403137</t>
+    <t xml:space="preserve">2.52010631561279</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
@@ -449,40 +449,40 @@
     <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059929847717</t>
+    <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633769989014</t>
+    <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
     <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740866661072</t>
+    <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027750968933</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35201859474182</t>
+    <t xml:space="preserve">3.3520188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616806983948</t>
+    <t xml:space="preserve">3.31616830825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -551,43 +551,43 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574745178223</t>
+    <t xml:space="preserve">4.61574792861938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753314971924</t>
+    <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
     <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413057327271</t>
+    <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998205184937</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -617,31 +617,31 @@
     <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902837753296</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824304580688</t>
+    <t xml:space="preserve">3.29824280738831</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -44227,6 +44227,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1644">
+      <c r="A1644" s="1" t="n">
+        <v>46024.381875</v>
+      </c>
+      <c r="B1644" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1644" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1644" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1644" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G1644" t="s">
+        <v>385</v>
+      </c>
+      <c r="H1644" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -50,16 +50,16 @@
     <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526256561279</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214134216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
@@ -71,67 +71,67 @@
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
     <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834600448608</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539842605591</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422479629517</t>
+    <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1648120880127</t>
+    <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216562271118</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
     <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863027572632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
     <t xml:space="preserve">4.1214280128479</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127745628357</t>
+    <t xml:space="preserve">3.99127721786499</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789433479309</t>
+    <t xml:space="preserve">3.94789409637451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171347618103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436017990112</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627022743225</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
@@ -182,34 +182,34 @@
     <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657110214233</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201482772827</t>
+    <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524810791016</t>
+    <t xml:space="preserve">3.96524715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
     <t xml:space="preserve">3.25375914573669</t>
@@ -248,19 +248,19 @@
     <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302248954773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390970230103</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363933563232</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650937080383</t>
+    <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404660224915</t>
+    <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -332,25 +332,25 @@
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81970000267029</t>
+    <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9430615901947</t>
+    <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346837997437</t>
+    <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
     <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46723699569702</t>
+    <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
     <t xml:space="preserve">2.36149859428406</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100584983826</t>
+    <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387540817261</t>
@@ -380,22 +380,22 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239812850952</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903606414795</t>
+    <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567447662354</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -407,25 +407,25 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002083778381</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575995445251</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
     <t xml:space="preserve">2.73158407211304</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010631561279</t>
+    <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445363044739</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
     <t xml:space="preserve">3.11929273605347</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
     <t xml:space="preserve">3.26027774810791</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3520188331604</t>
+    <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574792861938</t>
+    <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
@@ -623,25 +623,25 @@
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824280738831</t>
+    <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -44229,7 +44229,7 @@
     </row>
     <row r="1644">
       <c r="A1644" s="1" t="n">
-        <v>46024.381875</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B1644" t="n">
         <v>1000</v>
@@ -44250,6 +44250,32 @@
         <v>385</v>
       </c>
       <c r="H1644" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="1" t="n">
+        <v>46027.5645138889</v>
+      </c>
+      <c r="B1645" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1645" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="D1645" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1645" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G1645" t="s">
+        <v>385</v>
+      </c>
+      <c r="H1645" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -44,58 +44,58 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849632263184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775918960571</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187944412231</t>
+    <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214134216309</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216872215271</t>
+    <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834600448608</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539842605591</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010454177856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -107,28 +107,28 @@
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613555908203</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216562271118</t>
+    <t xml:space="preserve">4.18216466903687</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451049804688</t>
+    <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9305408000946</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863027572632</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
@@ -140,85 +140,85 @@
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936836242676</t>
+    <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
     <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127721786499</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921732902527</t>
+    <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789409637451</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171347618103</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509731292725</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
     <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494675636292</t>
+    <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568365097046</t>
+    <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524715423584</t>
+    <t xml:space="preserve">3.96524834632874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583373069763</t>
+    <t xml:space="preserve">3.89583349227905</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273654937744</t>
+    <t xml:space="preserve">3.52273678779602</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670648574829</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684163093567</t>
+    <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
     <t xml:space="preserve">3.25375914573669</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596982955933</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861605644226</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302248954773</t>
+    <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390946388245</t>
+    <t xml:space="preserve">3.38390970230103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126299858093</t>
+    <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
     <t xml:space="preserve">3.4541323184967</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126276016235</t>
+    <t xml:space="preserve">3.40126252174377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650913238525</t>
+    <t xml:space="preserve">3.43650937080383</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47175526618958</t>
+    <t xml:space="preserve">3.471755027771</t>
   </si>
   <si>
     <t xml:space="preserve">3.61274003982544</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404636383057</t>
+    <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81969976425171</t>
+    <t xml:space="preserve">2.81970000267029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207657814026</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4672372341156</t>
+    <t xml:space="preserve">2.46723699569702</t>
   </si>
   <si>
     <t xml:space="preserve">2.36149859428406</t>
@@ -359,16 +359,16 @@
     <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100608825684</t>
+    <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387540817261</t>
+    <t xml:space="preserve">2.34387516975403</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22051358222961</t>
+    <t xml:space="preserve">2.22051334381104</t>
   </si>
   <si>
     <t xml:space="preserve">2.20289039611816</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239789009094</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567447662354</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042774677277</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575947761536</t>
+    <t xml:space="preserve">2.25575971603394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53772974014282</t>
+    <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445363044739</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
     <t xml:space="preserve">3.26027774810791</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35201859474182</t>
+    <t xml:space="preserve">3.3520188331604</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297226905823</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574745178223</t>
+    <t xml:space="preserve">4.61574792861938</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545841217041</t>
+    <t xml:space="preserve">4.44545793533325</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317785263062</t>
+    <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
@@ -623,25 +623,25 @@
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824304580688</t>
+    <t xml:space="preserve">3.29824280738831</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -44255,7 +44255,7 @@
     </row>
     <row r="1645">
       <c r="A1645" s="1" t="n">
-        <v>46027.5645138889</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B1645" t="n">
         <v>500</v>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,61 +44,61 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849632263184</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39213991165161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3799934387207</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.32966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010454177856</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
     <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422527313232</t>
+    <t xml:space="preserve">4.23422574996948</t>
   </si>
   <si>
     <t xml:space="preserve">4.16481161117554</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">4.18216466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
     <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995470046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127745628357</t>
+    <t xml:space="preserve">3.99127817153931</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171395301819</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494699478149</t>
@@ -176,82 +176,82 @@
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759322166443</t>
   </si>
   <si>
     <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657062530518</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672189712524</t>
+    <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524834632874</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583349227905</t>
+    <t xml:space="preserve">3.89583420753479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
     <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273678779602</t>
+    <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345850944519</t>
+    <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052586555481</t>
+    <t xml:space="preserve">3.34052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596982955933</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390970230103</t>
+    <t xml:space="preserve">3.38390922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126276016235</t>
+    <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
     <t xml:space="preserve">3.4541323184967</t>
@@ -275,37 +275,37 @@
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126252174377</t>
+    <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650937080383</t>
+    <t xml:space="preserve">3.43650889396667</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.471755027771</t>
+    <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274003982544</t>
+    <t xml:space="preserve">3.61274027824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077025413513</t>
+    <t xml:space="preserve">3.33077049255371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.348393201828</t>
+    <t xml:space="preserve">3.34839344024658</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552388191223</t>
   </si>
   <si>
     <t xml:space="preserve">3.15453910827637</t>
@@ -317,40 +317,40 @@
     <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593091011047</t>
+    <t xml:space="preserve">2.99593114852905</t>
   </si>
   <si>
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355409622192</t>
+    <t xml:space="preserve">3.01355385780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783079624176</t>
+    <t xml:space="preserve">2.97830820083618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81970000267029</t>
+    <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46723699569702</t>
+    <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
     <t xml:space="preserve">2.36149859428406</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387516975403</t>
+    <t xml:space="preserve">2.34387564659119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625222206116</t>
+    <t xml:space="preserve">2.32625246047974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22051334381104</t>
+    <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
     <t xml:space="preserve">2.20289039611816</t>
@@ -383,22 +383,22 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239812850952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616662502289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854343891144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805081367493</t>
+    <t xml:space="preserve">1.86805105209351</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -407,16 +407,16 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575971603394</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158431053162</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,43 +446,43 @@
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059906005859</t>
+    <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445363044739</t>
+    <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633793830872</t>
+    <t xml:space="preserve">2.69633769989014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740842819214</t>
+    <t xml:space="preserve">3.20740866661072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027774810791</t>
+    <t xml:space="preserve">3.26027750968933</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239252090454</t>
+    <t xml:space="preserve">3.26239275932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3520188331604</t>
+    <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616830825806</t>
+    <t xml:space="preserve">3.31616806983948</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168262481689</t>
+    <t xml:space="preserve">4.39168214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -551,43 +551,43 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574792861938</t>
+    <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753267288208</t>
+    <t xml:space="preserve">4.42753314971924</t>
   </si>
   <si>
     <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413105010986</t>
+    <t xml:space="preserve">4.28413057327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998205184937</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -617,31 +617,31 @@
     <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902837753296</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824280738831</t>
+    <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -1174,6 +1174,9 @@
   <si>
     <t xml:space="preserve">2.09999990463257</t>
   </si>
+  <si>
+    <t xml:space="preserve">2.07999992370605</t>
+  </si>
 </sst>
 </file>
 
@@ -44279,6 +44282,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1646">
+      <c r="A1646" s="1" t="n">
+        <v>46028.3333333333</v>
+      </c>
+      <c r="B1646" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1646" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1646" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1646" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1646" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G1646" t="s">
+        <v>385</v>
+      </c>
+      <c r="H1646" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="1" t="n">
+        <v>46029.6017824074</v>
+      </c>
+      <c r="B1647" t="n">
+        <v>7250</v>
+      </c>
+      <c r="C1647" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D1647" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E1647" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1647" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G1647" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1647" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775918960571</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526304244995</t>
@@ -59,37 +59,37 @@
     <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39213991165161</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3730525970459</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.37999391555786</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966804504395</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
     <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010549545288</t>
@@ -98,37 +98,37 @@
     <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422574996948</t>
+    <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819520950317</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054127693176</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
@@ -137,19 +137,19 @@
     <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628540039062</t>
+    <t xml:space="preserve">4.28628492355347</t>
   </si>
   <si>
     <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995470046997</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127817153931</t>
+    <t xml:space="preserve">3.99127793312073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789433479309</t>
@@ -161,37 +161,37 @@
     <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436017990112</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421010017395</t>
+    <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759322166443</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568388938904</t>
+    <t xml:space="preserve">3.76568341255188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.96524810791016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583444595337</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333734512329</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345827102661</t>
@@ -239,10 +239,10 @@
     <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052562713623</t>
+    <t xml:space="preserve">3.34052610397339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714250564575</t>
+    <t xml:space="preserve">3.29714226722717</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596959114075</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390922546387</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650889396667</t>
+    <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -287,49 +287,49 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274027824402</t>
+    <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077049255371</t>
+    <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552388191223</t>
+    <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
     <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593114852905</t>
+    <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404660224915</t>
+    <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
     <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355385780334</t>
+    <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97830820083618</t>
+    <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9430615901947</t>
+    <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207681655884</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346837997437</t>
+    <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
     <t xml:space="preserve">2.62584543228149</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100584983826</t>
+    <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625246047974</t>
+    <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
@@ -380,25 +380,25 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239812850952</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903606414795</t>
+    <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616662502289</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854343891144</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567447662354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805105209351</t>
+    <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952833175659</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575971603394</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158431053162</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436767578125</t>
@@ -458,37 +458,37 @@
     <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059929847717</t>
+    <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633769989014</t>
+    <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740866661072</t>
+    <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
     <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027750968933</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616806983948</t>
+    <t xml:space="preserve">3.31616830825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -578,22 +578,22 @@
     <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753314971924</t>
+    <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
     <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413057327271</t>
+    <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998205184937</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035478591919</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902837753296</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
@@ -44310,7 +44310,7 @@
     </row>
     <row r="1647">
       <c r="A1647" s="1" t="n">
-        <v>46029.6017824074</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B1647" t="n">
         <v>7250</v>
@@ -44331,6 +44331,32 @@
         <v>387</v>
       </c>
       <c r="H1647" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="1" t="n">
+        <v>46030.5883680556</v>
+      </c>
+      <c r="B1648" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C1648" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1648" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E1648" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F1648" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G1648" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1648" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849536895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526304244995</t>
@@ -59,31 +59,31 @@
     <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999391555786</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
     <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834457397461</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539747238159</t>
+    <t xml:space="preserve">4.09539842605591</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010549545288</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
     <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422527313232</t>
+    <t xml:space="preserve">4.23422574996948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1648120880127</t>
+    <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275100708008</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216514587402</t>
+    <t xml:space="preserve">4.18216466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451121330261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
@@ -137,85 +137,85 @@
     <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628492355347</t>
+    <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0693678855896</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789433479309</t>
+    <t xml:space="preserve">3.94789481163025</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436065673828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
     <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494675636292</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420986175537</t>
+    <t xml:space="preserve">3.64421033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568341255188</t>
+    <t xml:space="preserve">3.7656843662262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657062530518</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524810791016</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583444595337</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833035469055</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
@@ -224,10 +224,10 @@
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258599281311</t>
+    <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684163093567</t>
+    <t xml:space="preserve">3.03684210777283</t>
   </si>
   <si>
     <t xml:space="preserve">3.25375914573669</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052610397339</t>
+    <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.29714226722717</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4541323184967</t>
+    <t xml:space="preserve">3.45413255691528</t>
   </si>
   <si>
     <t xml:space="preserve">3.3836395740509</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274003982544</t>
+    <t xml:space="preserve">3.61274027824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077025413513</t>
+    <t xml:space="preserve">3.33077049255371</t>
   </si>
   <si>
     <t xml:space="preserve">3.348393201828</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552388191223</t>
   </si>
   <si>
     <t xml:space="preserve">3.15453910827637</t>
@@ -314,37 +314,37 @@
     <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593091011047</t>
+    <t xml:space="preserve">2.99593114852905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404636383057</t>
+    <t xml:space="preserve">3.08404684066772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783079624176</t>
+    <t xml:space="preserve">2.97830772399902</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
     <t xml:space="preserve">2.62584543228149</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289039611816</t>
+    <t xml:space="preserve">2.20289015769958</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
@@ -380,22 +380,22 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567447662354</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -407,28 +407,28 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042774677277</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575947761536</t>
+    <t xml:space="preserve">2.25575971603394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53772974014282</t>
+    <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010655403137</t>
+    <t xml:space="preserve">2.52010631561279</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445363044739</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
     <t xml:space="preserve">3.11929273605347</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674757957458</t>
+    <t xml:space="preserve">3.65674734115601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297226905823</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562651634216</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.39168262481689</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056060791016</t>
+    <t xml:space="preserve">4.66056108474731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545841217041</t>
+    <t xml:space="preserve">4.44545793533325</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525259017944</t>
+    <t xml:space="preserve">4.01525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732685089111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579438209534</t>
+    <t xml:space="preserve">3.40579414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334595680237</t>
+    <t xml:space="preserve">3.51334619522095</t>
   </si>
   <si>
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -44336,7 +44336,7 @@
     </row>
     <row r="1648">
       <c r="A1648" s="1" t="n">
-        <v>46030.5883680556</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B1648" t="n">
         <v>6500</v>
@@ -44357,6 +44357,32 @@
         <v>387</v>
       </c>
       <c r="H1648" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="1" t="n">
+        <v>46031.6124305556</v>
+      </c>
+      <c r="B1649" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1649" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1649" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E1649" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1649" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G1649" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1649" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39214038848877</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
     <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702205657959</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010549545288</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481113433838</t>
+    <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
@@ -113,85 +113,85 @@
     <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613555908203</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216562271118</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819520950317</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
     <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142753601074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628540039062</t>
+    <t xml:space="preserve">4.28628492355347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936740875244</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995422363281</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921756744385</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789481163025</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436017990112</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.72230052947998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421010017395</t>
+    <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
     <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568365097046</t>
+    <t xml:space="preserve">3.76568341255188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657062530518</t>
+    <t xml:space="preserve">3.9565703868866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392439842224</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.96524810791016</t>
   </si>
   <si>
     <t xml:space="preserve">3.89583420753479</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833035469055</t>
+    <t xml:space="preserve">3.74833059310913</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
@@ -224,40 +224,40 @@
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052586555481</t>
+    <t xml:space="preserve">3.34052610397339</t>
   </si>
   <si>
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596935272217</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45413208007812</t>
+    <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363981246948</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216229438782</t>
+    <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
     <t xml:space="preserve">3.29552412033081</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404660224915</t>
+    <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068429946899</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0135543346405</t>
+    <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
     <t xml:space="preserve">2.9783079624176</t>
@@ -338,61 +338,61 @@
     <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207681655884</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912130355835</t>
+    <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100584983826</t>
+    <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625246047974</t>
+    <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477470397949</t>
+    <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
     <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239765167236</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854379653931</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567447662354</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -401,19 +401,19 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002131462097</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010679244995</t>
+    <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
@@ -446,40 +446,40 @@
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059929847717</t>
+    <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633769989014</t>
+    <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929249763489</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027798652649</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369161605835</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297179222107</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48130798339844</t>
+    <t xml:space="preserve">4.4813084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537424087524</t>
+    <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790636062622</t>
+    <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -599,16 +599,16 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280416488647</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147680282593</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -44385,7 +44385,7 @@
     </row>
     <row r="1650">
       <c r="A1650" s="1" t="n">
-        <v>46034.586712963</v>
+        <v>46034.3333333333</v>
       </c>
       <c r="B1650" t="n">
         <v>13750</v>
@@ -44406,6 +44406,32 @@
         <v>381</v>
       </c>
       <c r="H1650" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="1" t="n">
+        <v>46035.6772685185</v>
+      </c>
+      <c r="B1651" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1651" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="D1651" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G1651" t="s">
+        <v>384</v>
+      </c>
+      <c r="H1651" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
     <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526256561279</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187944412231</t>
+    <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3799934387207</t>
+    <t xml:space="preserve">4.37999391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.32966899871826</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539747238159</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010549545288</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
     <t xml:space="preserve">4.2255482673645</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613508224487</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216514587402</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451121330261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9305408000946</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
@@ -134,46 +134,46 @@
     <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628492355347</t>
+    <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995398521423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921732902527</t>
+    <t xml:space="preserve">3.93921685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789505004883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171347618103</t>
   </si>
   <si>
     <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230052947998</t>
+    <t xml:space="preserve">3.72230076789856</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420986175537</t>
+    <t xml:space="preserve">3.64420962333679</t>
   </si>
   <si>
     <t xml:space="preserve">3.68759369850159</t>
@@ -182,55 +182,55 @@
     <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568341255188</t>
+    <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9565703868866</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524810791016</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833011627197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273654937744</t>
+    <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258599281311</t>
+    <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345850944519</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052610397339</t>
+    <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.29714250564575</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978920936584</t>
+    <t xml:space="preserve">3.27978944778442</t>
   </si>
   <si>
     <t xml:space="preserve">3.19302225112915</t>
@@ -275,6 +275,9 @@
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
+    <t xml:space="preserve">3.40126252174377</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
@@ -290,7 +293,7 @@
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.348393201828</t>
+    <t xml:space="preserve">3.34839344024658</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -305,7 +308,7 @@
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
     <t xml:space="preserve">3.10166954994202</t>
@@ -335,7 +338,7 @@
     <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207657814026</t>
@@ -350,13 +353,13 @@
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100608825684</t>
+    <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387540817261</t>
@@ -383,16 +386,16 @@
     <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854343891144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567447662354</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -407,7 +410,7 @@
     <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
@@ -419,13 +422,13 @@
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -434,7 +437,7 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -449,7 +452,7 @@
     <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
@@ -461,7 +464,7 @@
     <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445363044739</t>
+    <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
     <t xml:space="preserve">2.69633793830872</t>
@@ -470,10 +473,10 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740842819214</t>
+    <t xml:space="preserve">3.20740818977356</t>
   </si>
   <si>
     <t xml:space="preserve">3.24265480041504</t>
@@ -485,7 +488,7 @@
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -498,9 +501,6 @@
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297226905823</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072895050049</t>
+    <t xml:space="preserve">4.14072942733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695316314697</t>
+    <t xml:space="preserve">4.08695363998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612161636353</t>
+    <t xml:space="preserve">4.52612209320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545841217041</t>
+    <t xml:space="preserve">4.44545793533325</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -605,25 +605,25 @@
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280368804932</t>
+    <t xml:space="preserve">4.12280321121216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620578765869</t>
+    <t xml:space="preserve">4.26620626449585</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902742385864</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.9794020652771</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147656440735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -7093,7 +7093,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -7119,7 +7119,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -7145,7 +7145,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -7171,7 +7171,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -7197,7 +7197,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -7223,7 +7223,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7249,7 +7249,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -7275,7 +7275,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -7301,7 +7301,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G223" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -7327,7 +7327,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -7353,7 +7353,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -7379,7 +7379,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -7405,7 +7405,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -7431,7 +7431,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -7457,7 +7457,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7483,7 +7483,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -7509,7 +7509,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -7535,7 +7535,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -7561,7 +7561,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7587,7 +7587,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -7613,7 +7613,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7639,7 +7639,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -7665,7 +7665,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -7691,7 +7691,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -7717,7 +7717,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -7743,7 +7743,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -7769,7 +7769,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -7795,7 +7795,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -7821,7 +7821,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -7847,7 +7847,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -7873,7 +7873,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -7899,7 +7899,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -7951,7 +7951,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -7977,7 +7977,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8003,7 +8003,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8029,7 +8029,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8055,7 +8055,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G252" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -8107,7 +8107,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -8133,7 +8133,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -8159,7 +8159,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -8185,7 +8185,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -8211,7 +8211,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G258" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -8237,7 +8237,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -8263,7 +8263,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -8289,7 +8289,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -8315,7 +8315,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8341,7 +8341,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -8367,7 +8367,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8393,7 +8393,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -8419,7 +8419,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -8445,7 +8445,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8471,7 +8471,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8497,7 +8497,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -8523,7 +8523,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8549,7 +8549,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8575,7 +8575,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8601,7 +8601,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8627,7 +8627,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8653,7 +8653,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -8679,7 +8679,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -8705,7 +8705,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8731,7 +8731,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -8757,7 +8757,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8783,7 +8783,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8809,7 +8809,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -8835,7 +8835,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -8861,7 +8861,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -8887,7 +8887,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -8913,7 +8913,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -8939,7 +8939,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -8965,7 +8965,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -8991,7 +8991,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -9017,7 +9017,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -9043,7 +9043,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -9069,7 +9069,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -9095,7 +9095,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9121,7 +9121,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -9147,7 +9147,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9173,7 +9173,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -9199,7 +9199,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -9225,7 +9225,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -9251,7 +9251,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9277,7 +9277,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -9303,7 +9303,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -9329,7 +9329,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9355,7 +9355,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -9381,7 +9381,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -9407,7 +9407,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -9433,7 +9433,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9459,7 +9459,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -9485,7 +9485,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9511,7 +9511,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9537,7 +9537,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -9563,7 +9563,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9589,7 +9589,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -9615,7 +9615,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -9641,7 +9641,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -9667,7 +9667,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G314" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -9693,7 +9693,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G315" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -9719,7 +9719,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G316" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -9745,7 +9745,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9771,7 +9771,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -9797,7 +9797,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -9823,7 +9823,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -9849,7 +9849,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -9875,7 +9875,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -9901,7 +9901,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G323" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -9927,7 +9927,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -9953,7 +9953,7 @@
         <v>2.5</v>
       </c>
       <c r="G325" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9979,7 +9979,7 @@
         <v>2.5</v>
       </c>
       <c r="G326" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -10005,7 +10005,7 @@
         <v>2.5</v>
       </c>
       <c r="G327" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -10031,7 +10031,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -10057,7 +10057,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -10083,7 +10083,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -10109,7 +10109,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -10135,7 +10135,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -10161,7 +10161,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -10187,7 +10187,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -10213,7 +10213,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10239,7 +10239,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -10265,7 +10265,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10291,7 +10291,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10317,7 +10317,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -10343,7 +10343,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10369,7 +10369,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10395,7 +10395,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -10421,7 +10421,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10447,7 +10447,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10473,7 +10473,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10499,7 +10499,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G346" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10525,7 +10525,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10551,7 +10551,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G348" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10577,7 +10577,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10603,7 +10603,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G350" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10629,7 +10629,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10655,7 +10655,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -10681,7 +10681,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -10707,7 +10707,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -10733,7 +10733,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10759,7 +10759,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -10785,7 +10785,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10811,7 +10811,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -10837,7 +10837,7 @@
         <v>2.5</v>
       </c>
       <c r="G359" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10863,7 +10863,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -10889,7 +10889,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -10915,7 +10915,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -10941,7 +10941,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10967,7 +10967,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -10993,7 +10993,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11019,7 +11019,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11045,7 +11045,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11071,7 +11071,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11097,7 +11097,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G369" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11123,7 +11123,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11149,7 +11149,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11175,7 +11175,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11201,7 +11201,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11227,7 +11227,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G374" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11253,7 +11253,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11279,7 +11279,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11305,7 +11305,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11331,7 +11331,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11357,7 +11357,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G379" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11383,7 +11383,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G380" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11409,7 +11409,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G381" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11435,7 +11435,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G382" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11461,7 +11461,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G383" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11487,7 +11487,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11513,7 +11513,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G385" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11539,7 +11539,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11565,7 +11565,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G387" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11591,7 +11591,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G388" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11617,7 +11617,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G389" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11643,7 +11643,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G390" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11669,7 +11669,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11695,7 +11695,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11721,7 +11721,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G393" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11747,7 +11747,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11773,7 +11773,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G395" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -11799,7 +11799,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -11825,7 +11825,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -11851,7 +11851,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -11877,7 +11877,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -11903,7 +11903,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -11929,7 +11929,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -11955,7 +11955,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -11981,7 +11981,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12007,7 +12007,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12033,7 +12033,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12059,7 +12059,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12085,7 +12085,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12111,7 +12111,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12137,7 +12137,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12163,7 +12163,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12189,7 +12189,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12215,7 +12215,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G412" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12241,7 +12241,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G413" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12267,7 +12267,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G414" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12293,7 +12293,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G415" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12319,7 +12319,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G416" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12345,7 +12345,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12371,7 +12371,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12397,7 +12397,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G419" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12423,7 +12423,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G420" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12449,7 +12449,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12475,7 +12475,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12501,7 +12501,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12527,7 +12527,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12553,7 +12553,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12579,7 +12579,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12605,7 +12605,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12631,7 +12631,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12657,7 +12657,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12683,7 +12683,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G430" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12709,7 +12709,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G431" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12735,7 +12735,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12761,7 +12761,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -12787,7 +12787,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -12813,7 +12813,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -12839,7 +12839,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -12865,7 +12865,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -12891,7 +12891,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -12917,7 +12917,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -12943,7 +12943,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -12969,7 +12969,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -12995,7 +12995,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13021,7 +13021,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13047,7 +13047,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13073,7 +13073,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13125,7 +13125,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13151,7 +13151,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13177,7 +13177,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13203,7 +13203,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13229,7 +13229,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13255,7 +13255,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13281,7 +13281,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13307,7 +13307,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13333,7 +13333,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13359,7 +13359,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13385,7 +13385,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G457" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13411,7 +13411,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13437,7 +13437,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13463,7 +13463,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G460" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13489,7 +13489,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13515,7 +13515,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G462" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13541,7 +13541,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13567,7 +13567,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G464" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13593,7 +13593,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G465" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13619,7 +13619,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13645,7 +13645,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G467" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13671,7 +13671,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G468" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -44411,7 +44411,7 @@
     </row>
     <row r="1651">
       <c r="A1651" s="1" t="n">
-        <v>46035.6772685185</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B1651" t="n">
         <v>7000</v>
@@ -44432,6 +44432,32 @@
         <v>384</v>
       </c>
       <c r="H1651" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="1" t="n">
+        <v>46036.6815509259</v>
+      </c>
+      <c r="B1652" t="n">
+        <v>19750</v>
+      </c>
+      <c r="C1652" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="D1652" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1652" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G1652" t="s">
+        <v>382</v>
+      </c>
+      <c r="H1652" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775918960571</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526256561279</t>
@@ -59,31 +59,31 @@
     <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3799934387207</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966804504395</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539842605591</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010549545288</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613508224487</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819425582886</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
     <t xml:space="preserve">3.9305408000946</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -143,46 +143,46 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
     <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789481163025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509731292725</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436065673828</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
     <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494675636292</t>
+    <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420962333679</t>
+    <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082721710205</t>
+    <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568365097046</t>
+    <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657086372375</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
     <t xml:space="preserve">4.05201435089111</t>
@@ -206,25 +206,25 @@
     <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.965247631073</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833083152771</t>
+    <t xml:space="preserve">3.74833059310913</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258599281311</t>
+    <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684186935425</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052586555481</t>
+    <t xml:space="preserve">3.34052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">3.29714250564575</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978897094727</t>
+    <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302248954773</t>
+    <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390946388245</t>
+    <t xml:space="preserve">3.38390970230103</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126276016235</t>
@@ -269,16 +269,13 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363933563232</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126252174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43650913238525</t>
+    <t xml:space="preserve">3.43650937080383</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -308,22 +305,22 @@
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404636383057</t>
+    <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -332,10 +329,10 @@
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81969976425171</t>
+    <t xml:space="preserve">2.81970000267029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
     <t xml:space="preserve">2.9430615901947</t>
@@ -344,16 +341,16 @@
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
     <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4672372341156</t>
+    <t xml:space="preserve">2.46723699569702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
@@ -380,22 +377,22 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239812850952</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854331970215</t>
+    <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -407,28 +404,28 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042774677277</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002107620239</t>
+    <t xml:space="preserve">2.15002083778381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575947761536</t>
+    <t xml:space="preserve">2.25575995445251</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53772974014282</t>
+    <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -440,13 +437,13 @@
     <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010655403137</t>
+    <t xml:space="preserve">2.52010631561279</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961428642273</t>
@@ -455,31 +452,31 @@
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740818977356</t>
+    <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
     <t xml:space="preserve">3.26027774810791</t>
@@ -503,7 +500,10 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35201859474182</t>
+    <t xml:space="preserve">3.13691592216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3520188331604</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297226905823</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -548,31 +548,31 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574745178223</t>
+    <t xml:space="preserve">4.61574792861938</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545841217041</t>
+    <t xml:space="preserve">4.44545793533325</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317785263062</t>
+    <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
@@ -620,25 +620,25 @@
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824304580688</t>
+    <t xml:space="preserve">3.29824280738831</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -7096,7 +7096,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -7122,7 +7122,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -7148,7 +7148,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -7174,7 +7174,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -7200,7 +7200,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -7226,7 +7226,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7252,7 +7252,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -7278,7 +7278,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -7304,7 +7304,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G223" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -7330,7 +7330,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -7356,7 +7356,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -7382,7 +7382,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -7408,7 +7408,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -7434,7 +7434,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -7460,7 +7460,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7486,7 +7486,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -7512,7 +7512,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -7538,7 +7538,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -7564,7 +7564,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7590,7 +7590,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -7616,7 +7616,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7642,7 +7642,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -7668,7 +7668,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -7694,7 +7694,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -7720,7 +7720,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -7746,7 +7746,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -7772,7 +7772,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -7798,7 +7798,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -7824,7 +7824,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -7850,7 +7850,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -7876,7 +7876,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -7902,7 +7902,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -7954,7 +7954,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -7980,7 +7980,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8006,7 +8006,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8032,7 +8032,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8058,7 +8058,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G252" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -8110,7 +8110,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -8136,7 +8136,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -8162,7 +8162,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -8188,7 +8188,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -8214,7 +8214,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G258" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -8240,7 +8240,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -8266,7 +8266,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -8292,7 +8292,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -8318,7 +8318,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8344,7 +8344,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -8370,7 +8370,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8396,7 +8396,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -8422,7 +8422,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -8448,7 +8448,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8474,7 +8474,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8500,7 +8500,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -8526,7 +8526,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8552,7 +8552,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8578,7 +8578,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8604,7 +8604,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8630,7 +8630,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8656,7 +8656,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -8682,7 +8682,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -8708,7 +8708,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8734,7 +8734,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -8760,7 +8760,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8786,7 +8786,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8812,7 +8812,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -8838,7 +8838,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -8864,7 +8864,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -8890,7 +8890,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -8916,7 +8916,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -8942,7 +8942,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -8968,7 +8968,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -8994,7 +8994,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -9020,7 +9020,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -9046,7 +9046,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -9072,7 +9072,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -9098,7 +9098,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9124,7 +9124,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -9150,7 +9150,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9176,7 +9176,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -9202,7 +9202,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -9228,7 +9228,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -9254,7 +9254,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9280,7 +9280,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -9306,7 +9306,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -9332,7 +9332,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9358,7 +9358,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -9384,7 +9384,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -9410,7 +9410,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -9436,7 +9436,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9462,7 +9462,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -9488,7 +9488,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9514,7 +9514,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9540,7 +9540,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -9566,7 +9566,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9592,7 +9592,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -9618,7 +9618,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -9644,7 +9644,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -9670,7 +9670,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G314" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -9696,7 +9696,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G315" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -9722,7 +9722,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G316" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -9748,7 +9748,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9774,7 +9774,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -9800,7 +9800,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -9826,7 +9826,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -9852,7 +9852,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -9878,7 +9878,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -9904,7 +9904,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G323" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -9930,7 +9930,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -9956,7 +9956,7 @@
         <v>2.5</v>
       </c>
       <c r="G325" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9982,7 +9982,7 @@
         <v>2.5</v>
       </c>
       <c r="G326" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -10008,7 +10008,7 @@
         <v>2.5</v>
       </c>
       <c r="G327" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -10034,7 +10034,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -10060,7 +10060,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -10086,7 +10086,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -10112,7 +10112,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -10138,7 +10138,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -10164,7 +10164,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -10190,7 +10190,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -10216,7 +10216,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10242,7 +10242,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -10268,7 +10268,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10294,7 +10294,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10320,7 +10320,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -10346,7 +10346,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10372,7 +10372,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10398,7 +10398,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -10424,7 +10424,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10450,7 +10450,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10476,7 +10476,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10502,7 +10502,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G346" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10528,7 +10528,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10554,7 +10554,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G348" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10580,7 +10580,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10606,7 +10606,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G350" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10632,7 +10632,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10658,7 +10658,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -10684,7 +10684,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -10710,7 +10710,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -10736,7 +10736,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10762,7 +10762,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -10788,7 +10788,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10814,7 +10814,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -10840,7 +10840,7 @@
         <v>2.5</v>
       </c>
       <c r="G359" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10866,7 +10866,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -10892,7 +10892,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -10918,7 +10918,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -10944,7 +10944,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10970,7 +10970,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -10996,7 +10996,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11022,7 +11022,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11048,7 +11048,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11074,7 +11074,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11100,7 +11100,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G369" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11126,7 +11126,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11152,7 +11152,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11178,7 +11178,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11204,7 +11204,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11230,7 +11230,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G374" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11256,7 +11256,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11282,7 +11282,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11308,7 +11308,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11334,7 +11334,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11360,7 +11360,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G379" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11386,7 +11386,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G380" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11412,7 +11412,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G381" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11438,7 +11438,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G382" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11464,7 +11464,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G383" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11490,7 +11490,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11516,7 +11516,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G385" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11542,7 +11542,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11568,7 +11568,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G387" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11594,7 +11594,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G388" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11620,7 +11620,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G389" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11646,7 +11646,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G390" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11672,7 +11672,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11698,7 +11698,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11724,7 +11724,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G393" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11750,7 +11750,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11776,7 +11776,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G395" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -11802,7 +11802,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -11828,7 +11828,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -11854,7 +11854,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -11880,7 +11880,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -11906,7 +11906,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -11932,7 +11932,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -11958,7 +11958,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -11984,7 +11984,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12010,7 +12010,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12036,7 +12036,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12062,7 +12062,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12088,7 +12088,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12114,7 +12114,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12140,7 +12140,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12166,7 +12166,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12192,7 +12192,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12218,7 +12218,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G412" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12244,7 +12244,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G413" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12270,7 +12270,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G414" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12296,7 +12296,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G415" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12322,7 +12322,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G416" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12348,7 +12348,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12374,7 +12374,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12400,7 +12400,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G419" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12426,7 +12426,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G420" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12452,7 +12452,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12478,7 +12478,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12504,7 +12504,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12530,7 +12530,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12556,7 +12556,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12582,7 +12582,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12608,7 +12608,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12634,7 +12634,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12660,7 +12660,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12686,7 +12686,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G430" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12712,7 +12712,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G431" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12738,7 +12738,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12764,7 +12764,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -12790,7 +12790,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -12816,7 +12816,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -12842,7 +12842,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -12868,7 +12868,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -12894,7 +12894,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -12920,7 +12920,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -12946,7 +12946,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -12972,7 +12972,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -12998,7 +12998,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13024,7 +13024,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13050,7 +13050,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13128,7 +13128,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13154,7 +13154,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13180,7 +13180,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13206,7 +13206,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13232,7 +13232,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13258,7 +13258,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13284,7 +13284,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13310,7 +13310,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13336,7 +13336,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13362,7 +13362,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13388,7 +13388,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G457" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13414,7 +13414,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13440,7 +13440,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13466,7 +13466,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G460" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13492,7 +13492,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13518,7 +13518,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G462" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13544,7 +13544,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13570,7 +13570,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G464" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13596,7 +13596,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G465" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13622,7 +13622,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13648,7 +13648,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G467" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13674,7 +13674,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G468" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -44492,7 +44492,7 @@
     </row>
     <row r="1654">
       <c r="A1654" s="1" t="n">
-        <v>46038.6476736111</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B1654" t="n">
         <v>11250</v>
@@ -44513,6 +44513,32 @@
         <v>368</v>
       </c>
       <c r="H1654" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="1" t="n">
+        <v>46041.676875</v>
+      </c>
+      <c r="B1655" t="n">
+        <v>7750</v>
+      </c>
+      <c r="C1655" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1655" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G1655" t="s">
+        <v>368</v>
+      </c>
+      <c r="H1655" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -47,49 +47,49 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
     <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526256561279</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
     <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
     <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.37999391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216872215271</t>
+    <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539842605591</t>
+    <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
@@ -104,16 +104,16 @@
     <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216466903687</t>
@@ -122,16 +122,16 @@
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451121330261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9305408000946</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
     <t xml:space="preserve">4.1214280128479</t>
@@ -140,52 +140,52 @@
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936836242676</t>
+    <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995422363281</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127697944641</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789481163025</t>
+    <t xml:space="preserve">3.94789505004883</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230052947998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421010017395</t>
+    <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392416000366</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672189712524</t>
+    <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.96524834632874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583373069763</t>
+    <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
@@ -227,40 +227,40 @@
     <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052562713623</t>
+    <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596982955933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390970230103</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126276016235</t>
@@ -269,28 +269,31 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363933563232</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650937080383</t>
+    <t xml:space="preserve">3.40126252174377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47175526618958</t>
+    <t xml:space="preserve">3.471755027771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274003982544</t>
+    <t xml:space="preserve">3.61274027824402</t>
   </si>
   <si>
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -302,7 +305,7 @@
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552388191223</t>
   </si>
   <si>
     <t xml:space="preserve">3.15453910827637</t>
@@ -311,16 +314,16 @@
     <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404660224915</t>
+    <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -332,7 +335,7 @@
     <t xml:space="preserve">2.81970000267029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
     <t xml:space="preserve">2.9430615901947</t>
@@ -341,13 +344,13 @@
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346837997437</t>
+    <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46723699569702</t>
+    <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
     <t xml:space="preserve">2.36149859428406</t>
@@ -377,76 +380,76 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239812850952</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854343891144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83280467987061</t>
+    <t xml:space="preserve">1.8328047990799</t>
   </si>
   <si>
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002083778381</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575995445251</t>
+    <t xml:space="preserve">2.25575971603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822224617004</t>
+    <t xml:space="preserve">2.60822248458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010631561279</t>
+    <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
@@ -461,22 +464,22 @@
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445363044739</t>
+    <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
     <t xml:space="preserve">3.26027774810791</t>
@@ -500,10 +503,7 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3520188331604</t>
+    <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072895050049</t>
+    <t xml:space="preserve">4.14072942733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -551,28 +551,28 @@
     <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695316314697</t>
+    <t xml:space="preserve">4.08695363998413</t>
   </si>
   <si>
     <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612161636353</t>
+    <t xml:space="preserve">4.52612209320068</t>
   </si>
   <si>
     <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574792861938</t>
+    <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280368804932</t>
+    <t xml:space="preserve">4.12280321121216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620578765869</t>
+    <t xml:space="preserve">4.26620626449585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902742385864</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.9794020652771</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770149230957</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824280738831</t>
+    <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147656440735</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686899185181</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -7096,7 +7096,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -7122,7 +7122,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -7148,7 +7148,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -7174,7 +7174,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -7200,7 +7200,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -7226,7 +7226,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7252,7 +7252,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -7278,7 +7278,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -7304,7 +7304,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G223" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -7330,7 +7330,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -7356,7 +7356,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -7382,7 +7382,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -7408,7 +7408,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -7434,7 +7434,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -7460,7 +7460,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7486,7 +7486,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -7512,7 +7512,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -7538,7 +7538,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -7564,7 +7564,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7590,7 +7590,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -7616,7 +7616,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7642,7 +7642,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -7668,7 +7668,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -7694,7 +7694,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -7720,7 +7720,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -7746,7 +7746,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -7772,7 +7772,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -7798,7 +7798,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -7824,7 +7824,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -7850,7 +7850,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -7876,7 +7876,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -7902,7 +7902,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -7954,7 +7954,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -7980,7 +7980,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8006,7 +8006,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8032,7 +8032,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8058,7 +8058,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G252" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -8110,7 +8110,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -8136,7 +8136,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -8162,7 +8162,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -8188,7 +8188,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -8214,7 +8214,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G258" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -8240,7 +8240,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -8266,7 +8266,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -8292,7 +8292,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -8318,7 +8318,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8344,7 +8344,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -8370,7 +8370,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8396,7 +8396,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -8422,7 +8422,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -8448,7 +8448,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8474,7 +8474,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8500,7 +8500,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -8526,7 +8526,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8552,7 +8552,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8578,7 +8578,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8604,7 +8604,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8630,7 +8630,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8656,7 +8656,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -8682,7 +8682,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -8708,7 +8708,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8734,7 +8734,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -8760,7 +8760,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8786,7 +8786,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8812,7 +8812,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -8838,7 +8838,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -8864,7 +8864,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -8890,7 +8890,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -8916,7 +8916,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -8942,7 +8942,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -8968,7 +8968,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -8994,7 +8994,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -9020,7 +9020,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -9046,7 +9046,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -9072,7 +9072,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -9098,7 +9098,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9124,7 +9124,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -9150,7 +9150,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9176,7 +9176,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -9202,7 +9202,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -9228,7 +9228,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -9254,7 +9254,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9280,7 +9280,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -9306,7 +9306,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -9332,7 +9332,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9358,7 +9358,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -9384,7 +9384,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -9410,7 +9410,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -9436,7 +9436,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9462,7 +9462,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -9488,7 +9488,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9514,7 +9514,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9540,7 +9540,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -9566,7 +9566,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9592,7 +9592,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -9618,7 +9618,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -9644,7 +9644,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -9670,7 +9670,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G314" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -9696,7 +9696,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G315" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -9722,7 +9722,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G316" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -9748,7 +9748,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9774,7 +9774,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -9800,7 +9800,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -9826,7 +9826,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -9852,7 +9852,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -9878,7 +9878,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -9904,7 +9904,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G323" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -9930,7 +9930,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -9956,7 +9956,7 @@
         <v>2.5</v>
       </c>
       <c r="G325" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9982,7 +9982,7 @@
         <v>2.5</v>
       </c>
       <c r="G326" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -10008,7 +10008,7 @@
         <v>2.5</v>
       </c>
       <c r="G327" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -10034,7 +10034,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -10060,7 +10060,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -10086,7 +10086,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -10112,7 +10112,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -10138,7 +10138,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -10164,7 +10164,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -10190,7 +10190,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -10216,7 +10216,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10242,7 +10242,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -10268,7 +10268,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10294,7 +10294,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10320,7 +10320,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -10346,7 +10346,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10372,7 +10372,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10398,7 +10398,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -10424,7 +10424,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10450,7 +10450,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10476,7 +10476,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10502,7 +10502,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G346" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10528,7 +10528,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10554,7 +10554,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G348" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10580,7 +10580,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10606,7 +10606,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G350" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10632,7 +10632,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10658,7 +10658,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -10684,7 +10684,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -10710,7 +10710,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -10736,7 +10736,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10762,7 +10762,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -10788,7 +10788,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10814,7 +10814,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -10840,7 +10840,7 @@
         <v>2.5</v>
       </c>
       <c r="G359" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10866,7 +10866,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -10892,7 +10892,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -10918,7 +10918,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -10944,7 +10944,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10970,7 +10970,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -10996,7 +10996,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11022,7 +11022,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11048,7 +11048,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11074,7 +11074,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11100,7 +11100,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G369" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11126,7 +11126,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11152,7 +11152,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11178,7 +11178,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11204,7 +11204,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11230,7 +11230,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G374" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11256,7 +11256,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11282,7 +11282,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11308,7 +11308,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11334,7 +11334,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11360,7 +11360,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G379" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11386,7 +11386,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G380" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11412,7 +11412,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G381" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11438,7 +11438,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G382" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11464,7 +11464,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G383" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11490,7 +11490,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11516,7 +11516,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G385" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11542,7 +11542,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11568,7 +11568,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G387" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11594,7 +11594,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G388" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11620,7 +11620,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G389" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11646,7 +11646,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G390" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11672,7 +11672,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11698,7 +11698,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11724,7 +11724,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G393" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11750,7 +11750,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11776,7 +11776,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G395" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -11802,7 +11802,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -11828,7 +11828,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -11854,7 +11854,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -11880,7 +11880,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -11906,7 +11906,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -11932,7 +11932,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -11958,7 +11958,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -11984,7 +11984,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12010,7 +12010,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12036,7 +12036,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12062,7 +12062,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12088,7 +12088,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12114,7 +12114,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12140,7 +12140,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12166,7 +12166,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12192,7 +12192,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12218,7 +12218,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G412" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12244,7 +12244,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G413" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12270,7 +12270,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G414" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12296,7 +12296,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G415" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12322,7 +12322,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G416" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12348,7 +12348,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12374,7 +12374,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12400,7 +12400,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G419" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12426,7 +12426,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G420" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12452,7 +12452,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12478,7 +12478,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12504,7 +12504,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12530,7 +12530,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12556,7 +12556,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12582,7 +12582,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12608,7 +12608,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12634,7 +12634,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12660,7 +12660,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12686,7 +12686,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G430" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12712,7 +12712,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G431" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12738,7 +12738,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12764,7 +12764,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -12790,7 +12790,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -12816,7 +12816,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -12842,7 +12842,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -12868,7 +12868,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -12894,7 +12894,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -12920,7 +12920,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -12946,7 +12946,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -12972,7 +12972,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -12998,7 +12998,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13024,7 +13024,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13050,7 +13050,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13076,7 +13076,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13128,7 +13128,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13154,7 +13154,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13180,7 +13180,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13206,7 +13206,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13232,7 +13232,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13258,7 +13258,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13284,7 +13284,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13310,7 +13310,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13336,7 +13336,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13362,7 +13362,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13388,7 +13388,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G457" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13414,7 +13414,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13440,7 +13440,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13466,7 +13466,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G460" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13492,7 +13492,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13518,7 +13518,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G462" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13544,7 +13544,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13570,7 +13570,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G464" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13596,7 +13596,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G465" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13622,7 +13622,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13648,7 +13648,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G467" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13674,7 +13674,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G468" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -44518,7 +44518,7 @@
     </row>
     <row r="1655">
       <c r="A1655" s="1" t="n">
-        <v>46041.676875</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B1655" t="n">
         <v>7750</v>
@@ -44539,6 +44539,32 @@
         <v>368</v>
       </c>
       <c r="H1655" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="1" t="n">
+        <v>46042.6751736111</v>
+      </c>
+      <c r="B1656" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1656" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D1656" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1656" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1656" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G1656" t="s">
+        <v>368</v>
+      </c>
+      <c r="H1656" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849632263184</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415710449219</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39214086532593</t>
@@ -71,28 +71,28 @@
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539842605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010454177856</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
     <t xml:space="preserve">4.2255482673645</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819473266602</t>
@@ -131,37 +131,37 @@
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142753601074</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0693678855896</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995470046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127745628357</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789385795593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171419143677</t>
   </si>
   <si>
     <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436017990112</t>
+    <t xml:space="preserve">3.77436089515686</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657062530518</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392416000366</t>
@@ -197,28 +197,28 @@
     <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201482772827</t>
+    <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524834632874</t>
+    <t xml:space="preserve">3.96524739265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583349227905</t>
+    <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833035469055</t>
+    <t xml:space="preserve">3.74833059310913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273678779602</t>
+    <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670648574829</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345850944519</t>
+    <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596982955933</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -263,19 +263,19 @@
     <t xml:space="preserve">3.38390970230103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126276016235</t>
+    <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363933563232</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126252174377</t>
+    <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
     <t xml:space="preserve">3.43650937080383</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.471755027771</t>
+    <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
     <t xml:space="preserve">3.61274003982544</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.348393201828</t>
+    <t xml:space="preserve">3.34839344024658</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.46723699569702</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387516975403</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22051334381104</t>
+    <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
     <t xml:space="preserve">2.20289039611816</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239812850952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.9561665058136</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805081367493</t>
+    <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002107620239</t>
+    <t xml:space="preserve">2.15002083778381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575971603394</t>
+    <t xml:space="preserve">2.25575995445251</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010655403137</t>
+    <t xml:space="preserve">2.52010631561279</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961428642273</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
     <t xml:space="preserve">3.11929273605347</t>
@@ -44810,7 +44810,7 @@
     </row>
     <row r="1666">
       <c r="A1666" s="1" t="n">
-        <v>46056.6480902778</v>
+        <v>46056.3333333333</v>
       </c>
       <c r="B1666" t="n">
         <v>2500</v>
@@ -44831,6 +44831,32 @@
         <v>370</v>
       </c>
       <c r="H1666" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="1" t="n">
+        <v>46057.4835185185</v>
+      </c>
+      <c r="B1667" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C1667" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D1667" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E1667" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F1667" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G1667" t="s">
+        <v>364</v>
+      </c>
+      <c r="H1667" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
     <t xml:space="preserve">4.40775871276855</t>
@@ -77,19 +77,19 @@
     <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702157974243</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539842605591</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216514587402</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.01730823516846</t>
@@ -137,61 +137,61 @@
     <t xml:space="preserve">4.12142753601074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628540039062</t>
+    <t xml:space="preserve">4.28628492355347</t>
   </si>
   <si>
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995470046997</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789385795593</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171419143677</t>
+    <t xml:space="preserve">3.79171347618103</t>
   </si>
   <si>
     <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436089515686</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230076789856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421010017395</t>
+    <t xml:space="preserve">3.64420962333679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082721710205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672189712524</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583420753479</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
     <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037530899048</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302248954773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390970230103</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363933563232</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650937080383</t>
+    <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404660224915</t>
+    <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -332,25 +332,25 @@
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81970000267029</t>
+    <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9430615901947</t>
+    <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346837997437</t>
+    <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
     <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46723699569702</t>
+    <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
     <t xml:space="preserve">2.36149859428406</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100584983826</t>
+    <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387540817261</t>
@@ -380,22 +380,22 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239812850952</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903606414795</t>
+    <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567447662354</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -407,25 +407,25 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002083778381</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575995445251</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
     <t xml:space="preserve">2.73158407211304</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010631561279</t>
+    <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445363044739</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
     <t xml:space="preserve">3.11929273605347</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
     <t xml:space="preserve">3.26027774810791</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3520188331604</t>
+    <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574792861938</t>
+    <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
@@ -623,25 +623,25 @@
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824280738831</t>
+    <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -44836,7 +44836,7 @@
     </row>
     <row r="1667">
       <c r="A1667" s="1" t="n">
-        <v>46057.4835185185</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B1667" t="n">
         <v>2250</v>
@@ -44857,6 +44857,32 @@
         <v>364</v>
       </c>
       <c r="H1667" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="1" t="n">
+        <v>46058.6847106481</v>
+      </c>
+      <c r="B1668" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1668" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D1668" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F1668" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G1668" t="s">
+        <v>369</v>
+      </c>
+      <c r="H1668" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849536895752</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526304244995</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3799934387207</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643571853638</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834600448608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539794921875</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275148391724</t>
@@ -119,67 +119,67 @@
     <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
     <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863027572632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628492355347</t>
+    <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995398521423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127721786499</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789409637451</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171347618103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77435994148254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230076789856</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420962333679</t>
+    <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082721710205</t>
+    <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
     <t xml:space="preserve">3.76568365097046</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804441452026</t>
@@ -197,46 +197,46 @@
     <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186450958252</t>
+    <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.965247631073</t>
+    <t xml:space="preserve">3.96524715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684163093567</t>
+    <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037530899048</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363981246948</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650913238525</t>
+    <t xml:space="preserve">3.43650889396667</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
     <t xml:space="preserve">3.17216205596924</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
@@ -320,16 +320,16 @@
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404636383057</t>
+    <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
     <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355409622192</t>
+    <t xml:space="preserve">3.01355385780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783079624176</t>
+    <t xml:space="preserve">2.97830820083618</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207681655884</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346861839294</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567447662354</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042774677277</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952833175659</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961428642273</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239252090454</t>
+    <t xml:space="preserve">3.26239275932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616830825806</t>
+    <t xml:space="preserve">3.31616806983948</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297226905823</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168262481689</t>
+    <t xml:space="preserve">4.39168214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -578,22 +578,22 @@
     <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753267288208</t>
+    <t xml:space="preserve">4.42753314971924</t>
   </si>
   <si>
     <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413105010986</t>
+    <t xml:space="preserve">4.28413057327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998205184937</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545841217041</t>
+    <t xml:space="preserve">4.44545793533325</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035478591919</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317785263062</t>
+    <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902837753296</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
@@ -44862,7 +44862,7 @@
     </row>
     <row r="1668">
       <c r="A1668" s="1" t="n">
-        <v>46058.6847106481</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B1668" t="n">
         <v>6000</v>
@@ -44883,6 +44883,32 @@
         <v>369</v>
       </c>
       <c r="H1668" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="1" t="n">
+        <v>46059.6330439815</v>
+      </c>
+      <c r="B1669" t="n">
+        <v>5750</v>
+      </c>
+      <c r="C1669" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D1669" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1669" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F1669" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G1669" t="s">
+        <v>382</v>
+      </c>
+      <c r="H1669" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -44,40 +44,40 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849536895752</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3730525970459</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966804504395</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216872215271</t>
+    <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702253341675</t>
@@ -86,49 +86,49 @@
     <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422574996948</t>
+    <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216562271118</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819520950317</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054127693176</t>
+    <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
@@ -140,46 +140,46 @@
     <t xml:space="preserve">4.28628587722778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936740875244</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995422363281</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127721786499</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789481163025</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509683609009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436065673828</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421033859253</t>
+    <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
     <t xml:space="preserve">3.76568412780762</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804441452026</t>
@@ -197,25 +197,25 @@
     <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186450958252</t>
+    <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
     <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
@@ -233,37 +233,37 @@
     <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052562713623</t>
+    <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714250564575</t>
+    <t xml:space="preserve">3.29714274406433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596935272217</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302225112915</t>
+    <t xml:space="preserve">3.19302248954773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390922546387</t>
+    <t xml:space="preserve">3.38390970230103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126276016235</t>
+    <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
     <t xml:space="preserve">3.4541323184967</t>
@@ -275,19 +275,22 @@
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650889396667</t>
+    <t xml:space="preserve">3.40126276016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47175526618958</t>
+    <t xml:space="preserve">3.471755027771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274027824402</t>
+    <t xml:space="preserve">3.61273980140686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077049255371</t>
+    <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
     <t xml:space="preserve">3.34839344024658</t>
@@ -296,37 +299,37 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552388191223</t>
+    <t xml:space="preserve">3.29552435874939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593114852905</t>
+    <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404660224915</t>
+    <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355385780334</t>
+    <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97830820083618</t>
+    <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
@@ -338,19 +341,19 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207681655884</t>
+    <t xml:space="preserve">2.80207633972168</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
@@ -359,10 +362,10 @@
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
+    <t xml:space="preserve">2.34387516975403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625246047974</t>
+    <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
@@ -377,34 +380,34 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239812850952</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616662502289</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854343891144</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805105209351</t>
+    <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518161296844</t>
+    <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952833175659</t>
@@ -413,10 +416,10 @@
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575971603394</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
@@ -425,10 +428,10 @@
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158431053162</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
@@ -440,49 +443,49 @@
     <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48486018180847</t>
+    <t xml:space="preserve">2.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059929847717</t>
+    <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.69633769989014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
     <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740866661072</t>
+    <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
     <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027750968933</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978524208069</t>
+    <t xml:space="preserve">3.18978500366211</t>
   </si>
   <si>
     <t xml:space="preserve">3.13691568374634</t>
@@ -494,19 +497,16 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616806983948</t>
+    <t xml:space="preserve">3.31616830825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -575,22 +575,22 @@
     <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753314971924</t>
+    <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
     <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413057327271</t>
+    <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998205184937</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035478591919</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902837753296</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
@@ -7099,7 +7099,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -7125,7 +7125,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -7151,7 +7151,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -7177,7 +7177,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -7203,7 +7203,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -7229,7 +7229,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7255,7 +7255,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -7281,7 +7281,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -7307,7 +7307,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G223" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -7333,7 +7333,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -7359,7 +7359,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -7385,7 +7385,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -7411,7 +7411,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -7437,7 +7437,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -7463,7 +7463,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7489,7 +7489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -7515,7 +7515,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -7541,7 +7541,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -7567,7 +7567,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7593,7 +7593,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -7619,7 +7619,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7645,7 +7645,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -7671,7 +7671,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -7697,7 +7697,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -7723,7 +7723,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -7749,7 +7749,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -7775,7 +7775,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -7801,7 +7801,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -7827,7 +7827,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -7853,7 +7853,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -7879,7 +7879,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -7905,7 +7905,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -7957,7 +7957,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -7983,7 +7983,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8009,7 +8009,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8035,7 +8035,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8061,7 +8061,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G252" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -8113,7 +8113,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -8139,7 +8139,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -8165,7 +8165,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -8191,7 +8191,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -8217,7 +8217,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G258" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -8243,7 +8243,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -8269,7 +8269,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -8295,7 +8295,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -8321,7 +8321,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8347,7 +8347,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -8373,7 +8373,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8399,7 +8399,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -8425,7 +8425,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -8451,7 +8451,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8477,7 +8477,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8503,7 +8503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -8529,7 +8529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8555,7 +8555,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8581,7 +8581,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8607,7 +8607,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8633,7 +8633,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8659,7 +8659,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -8685,7 +8685,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -8711,7 +8711,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8737,7 +8737,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -8763,7 +8763,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8789,7 +8789,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8815,7 +8815,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -8841,7 +8841,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -8867,7 +8867,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -8893,7 +8893,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -8919,7 +8919,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -8945,7 +8945,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -8971,7 +8971,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -8997,7 +8997,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -9023,7 +9023,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -9049,7 +9049,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -9075,7 +9075,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -9101,7 +9101,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9127,7 +9127,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -9153,7 +9153,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9179,7 +9179,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -9205,7 +9205,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -9231,7 +9231,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -9257,7 +9257,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9283,7 +9283,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -9309,7 +9309,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -9335,7 +9335,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9361,7 +9361,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -9387,7 +9387,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -9413,7 +9413,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -9439,7 +9439,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9465,7 +9465,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -9491,7 +9491,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9517,7 +9517,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9543,7 +9543,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -9569,7 +9569,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9595,7 +9595,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -9621,7 +9621,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -9647,7 +9647,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -9673,7 +9673,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G314" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -9699,7 +9699,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G315" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -9725,7 +9725,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G316" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -9751,7 +9751,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9777,7 +9777,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -9803,7 +9803,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -9829,7 +9829,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -9855,7 +9855,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -9881,7 +9881,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -9907,7 +9907,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G323" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -9933,7 +9933,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -9959,7 +9959,7 @@
         <v>2.5</v>
       </c>
       <c r="G325" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9985,7 +9985,7 @@
         <v>2.5</v>
       </c>
       <c r="G326" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -10011,7 +10011,7 @@
         <v>2.5</v>
       </c>
       <c r="G327" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -10037,7 +10037,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -10063,7 +10063,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -10089,7 +10089,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -10115,7 +10115,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -10141,7 +10141,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -10167,7 +10167,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -10193,7 +10193,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -10219,7 +10219,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10245,7 +10245,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -10271,7 +10271,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10297,7 +10297,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10323,7 +10323,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -10349,7 +10349,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10375,7 +10375,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10401,7 +10401,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -10427,7 +10427,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10453,7 +10453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10479,7 +10479,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10505,7 +10505,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G346" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10531,7 +10531,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10557,7 +10557,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G348" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10583,7 +10583,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10609,7 +10609,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G350" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10635,7 +10635,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10661,7 +10661,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -10687,7 +10687,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -10713,7 +10713,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -10739,7 +10739,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10765,7 +10765,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -10791,7 +10791,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10817,7 +10817,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -10843,7 +10843,7 @@
         <v>2.5</v>
       </c>
       <c r="G359" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10869,7 +10869,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -10895,7 +10895,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -10921,7 +10921,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -10947,7 +10947,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10973,7 +10973,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -10999,7 +10999,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11025,7 +11025,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11051,7 +11051,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11077,7 +11077,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11103,7 +11103,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G369" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11129,7 +11129,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11155,7 +11155,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11181,7 +11181,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11207,7 +11207,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11233,7 +11233,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G374" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11259,7 +11259,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11285,7 +11285,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11311,7 +11311,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11337,7 +11337,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11363,7 +11363,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G379" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11389,7 +11389,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G380" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11415,7 +11415,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G381" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11441,7 +11441,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G382" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11467,7 +11467,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G383" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11493,7 +11493,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11519,7 +11519,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G385" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11545,7 +11545,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11571,7 +11571,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G387" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11597,7 +11597,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G388" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11623,7 +11623,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G389" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11649,7 +11649,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G390" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11675,7 +11675,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11701,7 +11701,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11727,7 +11727,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G393" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11753,7 +11753,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11779,7 +11779,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G395" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -11805,7 +11805,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -11831,7 +11831,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -11857,7 +11857,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -11883,7 +11883,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -11909,7 +11909,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -11935,7 +11935,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -11961,7 +11961,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -11987,7 +11987,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12013,7 +12013,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12039,7 +12039,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12065,7 +12065,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12091,7 +12091,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12117,7 +12117,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12143,7 +12143,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12169,7 +12169,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12195,7 +12195,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12221,7 +12221,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G412" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12247,7 +12247,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G413" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12273,7 +12273,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G414" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12299,7 +12299,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G415" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12325,7 +12325,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G416" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12351,7 +12351,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12377,7 +12377,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12403,7 +12403,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G419" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12429,7 +12429,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G420" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12455,7 +12455,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12481,7 +12481,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12507,7 +12507,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12533,7 +12533,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12559,7 +12559,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12585,7 +12585,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12611,7 +12611,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12637,7 +12637,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12663,7 +12663,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12689,7 +12689,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G430" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12715,7 +12715,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G431" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12741,7 +12741,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12767,7 +12767,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -12793,7 +12793,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -12819,7 +12819,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -12845,7 +12845,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -12871,7 +12871,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -12897,7 +12897,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -12923,7 +12923,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -12949,7 +12949,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -12975,7 +12975,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -13001,7 +13001,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13027,7 +13027,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13053,7 +13053,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13079,7 +13079,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13131,7 +13131,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13157,7 +13157,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13183,7 +13183,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13209,7 +13209,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13235,7 +13235,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13261,7 +13261,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13287,7 +13287,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13313,7 +13313,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13339,7 +13339,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13365,7 +13365,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13391,7 +13391,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G457" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13417,7 +13417,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13443,7 +13443,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13469,7 +13469,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G460" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13495,7 +13495,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13521,7 +13521,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G462" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13547,7 +13547,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13573,7 +13573,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G464" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13599,7 +13599,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G465" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13625,7 +13625,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13651,7 +13651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G467" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13677,7 +13677,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G468" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -44937,7 +44937,7 @@
     </row>
     <row r="1671">
       <c r="A1671" s="1" t="n">
-        <v>46063.6667824074</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B1671" t="n">
         <v>4500</v>
@@ -44958,6 +44958,32 @@
         <v>367</v>
       </c>
       <c r="H1671" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="1" t="n">
+        <v>46064.5740972222</v>
+      </c>
+      <c r="B1672" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1672" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1672" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G1672" t="s">
+        <v>368</v>
+      </c>
+      <c r="H1672" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -45018,7 +45018,7 @@
     </row>
     <row r="1674">
       <c r="A1674" s="1" t="n">
-        <v>46066.3805787037</v>
+        <v>46066.3333333333</v>
       </c>
       <c r="B1674" t="n">
         <v>1000</v>
@@ -45039,6 +45039,32 @@
         <v>389</v>
       </c>
       <c r="H1674" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="1" t="n">
+        <v>46069.5479050926</v>
+      </c>
+      <c r="B1675" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1675" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1675" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="G1675" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1675" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187944412231</t>
+    <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
     <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.3296685218811</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539842605591</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157833099365</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216562271118</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819520950317</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054127693176</t>
+    <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863075256348</t>
@@ -134,79 +134,79 @@
     <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0693678855896</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995398521423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171347618103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77435994148254</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.72229981422424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421033859253</t>
+    <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082721710205</t>
+    <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804393768311</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672189712524</t>
+    <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.965247631073</t>
+    <t xml:space="preserve">3.96524715423584</t>
   </si>
   <si>
     <t xml:space="preserve">3.89583373069763</t>
@@ -218,16 +218,16 @@
     <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273654937744</t>
+    <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684210777283</t>
   </si>
   <si>
     <t xml:space="preserve">3.25375890731812</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037530899048</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596935272217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">3.19302248954773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390922546387</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4541323184967</t>
+    <t xml:space="preserve">3.45413255691528</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363981246948</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077025413513</t>
+    <t xml:space="preserve">3.33077001571655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.348393201828</t>
+    <t xml:space="preserve">3.34839344024658</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216205596924</t>
+    <t xml:space="preserve">3.17216229438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
     <t xml:space="preserve">3.1016697883606</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355385780334</t>
+    <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97830820083618</t>
+    <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207681655884</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346861839294</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100608825684</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289039611816</t>
+    <t xml:space="preserve">2.20289015769958</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.95616674423218</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518161296844</t>
+    <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
     <t xml:space="preserve">1.85042798519135</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822224617004</t>
+    <t xml:space="preserve">2.60822200775146</t>
   </si>
   <si>
     <t xml:space="preserve">2.5024836063385</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
@@ -45044,7 +45044,7 @@
     </row>
     <row r="1675">
       <c r="A1675" s="1" t="n">
-        <v>46069.5479050926</v>
+        <v>46069.3333333333</v>
       </c>
       <c r="B1675" t="n">
         <v>7000</v>
@@ -45065,6 +45065,32 @@
         <v>367</v>
       </c>
       <c r="H1675" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="1" t="n">
+        <v>46070.4217013889</v>
+      </c>
+      <c r="B1676" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C1676" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D1676" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F1676" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="G1676" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1676" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231594085693</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -50,25 +50,25 @@
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4077582359314</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526256561279</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187944412231</t>
+    <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
     <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3799934387207</t>
+    <t xml:space="preserve">4.37999391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.32966899871826</t>
@@ -83,28 +83,28 @@
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010454177856</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1648120880127</t>
+    <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290132522583</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216514587402</t>
+    <t xml:space="preserve">4.18216466903687</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451121330261</t>
   </si>
   <si>
     <t xml:space="preserve">3.93054103851318</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
     <t xml:space="preserve">4.1214280128479</t>
@@ -140,100 +140,100 @@
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936836242676</t>
+    <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
     <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127745628357</t>
+    <t xml:space="preserve">3.99127697944641</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789505004883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436065673828</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230052947998</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421033859253</t>
+    <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
     <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568388938904</t>
+    <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672189712524</t>
+    <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186450958252</t>
+    <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.96524834632874</t>
   </si>
   <si>
     <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258646965027</t>
+    <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
     <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
     <t xml:space="preserve">3.21037578582764</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714226722717</t>
+    <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596982955933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
@@ -272,7 +272,10 @@
     <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22503137588501</t>
+    <t xml:space="preserve">3.22503161430359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40126252174377</t>
   </si>
   <si>
     <t xml:space="preserve">3.43650913238525</t>
@@ -281,10 +284,10 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47175526618958</t>
+    <t xml:space="preserve">3.471755027771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274003982544</t>
+    <t xml:space="preserve">3.61274027824402</t>
   </si>
   <si>
     <t xml:space="preserve">3.33077025413513</t>
@@ -296,16 +299,16 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216229438782</t>
+    <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552388191223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
     <t xml:space="preserve">3.1016697883606</t>
@@ -317,28 +320,28 @@
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404660224915</t>
+    <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355385780334</t>
+    <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81969976425171</t>
+    <t xml:space="preserve">2.81970000267029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207681655884</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346861839294</t>
@@ -347,7 +350,7 @@
     <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46723699569702</t>
+    <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
     <t xml:space="preserve">2.36149859428406</t>
@@ -356,13 +359,13 @@
     <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100608825684</t>
+    <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387516975403</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625198364258</t>
+    <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
@@ -377,7 +380,7 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239789009094</t>
@@ -386,10 +389,10 @@
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854343891144</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
@@ -398,25 +401,25 @@
     <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83280467987061</t>
+    <t xml:space="preserve">1.8328047990799</t>
   </si>
   <si>
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575947761536</t>
+    <t xml:space="preserve">2.25575971603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
@@ -431,10 +434,10 @@
     <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822224617004</t>
+    <t xml:space="preserve">2.60822248458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,7 +449,7 @@
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
@@ -461,7 +464,7 @@
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445363044739</t>
+    <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
     <t xml:space="preserve">2.69633793830872</t>
@@ -470,7 +473,7 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
@@ -482,7 +485,7 @@
     <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978548049927</t>
+    <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
     <t xml:space="preserve">3.13691568374634</t>
@@ -500,10 +503,7 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3520188331604</t>
+    <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072895050049</t>
+    <t xml:space="preserve">4.14072942733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -551,28 +551,28 @@
     <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695316314697</t>
+    <t xml:space="preserve">4.08695363998413</t>
   </si>
   <si>
     <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612161636353</t>
+    <t xml:space="preserve">4.52612209320068</t>
   </si>
   <si>
     <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574792861938</t>
+    <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280368804932</t>
+    <t xml:space="preserve">4.12280321121216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620578765869</t>
+    <t xml:space="preserve">4.26620626449585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902742385864</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.9794020652771</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770149230957</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824280738831</t>
+    <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147656440735</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686899185181</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -7099,7 +7099,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -7125,7 +7125,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -7151,7 +7151,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -7177,7 +7177,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -7203,7 +7203,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -7229,7 +7229,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7255,7 +7255,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -7281,7 +7281,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -7307,7 +7307,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G223" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -7333,7 +7333,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -7359,7 +7359,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -7385,7 +7385,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -7411,7 +7411,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -7437,7 +7437,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -7463,7 +7463,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7489,7 +7489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -7515,7 +7515,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -7541,7 +7541,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -7567,7 +7567,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7593,7 +7593,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -7619,7 +7619,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7645,7 +7645,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -7671,7 +7671,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -7697,7 +7697,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -7723,7 +7723,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -7749,7 +7749,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -7775,7 +7775,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -7801,7 +7801,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -7827,7 +7827,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -7853,7 +7853,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -7879,7 +7879,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -7905,7 +7905,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -7957,7 +7957,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -7983,7 +7983,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8009,7 +8009,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8035,7 +8035,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8061,7 +8061,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G252" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -8113,7 +8113,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -8139,7 +8139,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -8165,7 +8165,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -8191,7 +8191,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -8217,7 +8217,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G258" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -8243,7 +8243,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -8269,7 +8269,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -8295,7 +8295,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -8321,7 +8321,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8347,7 +8347,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -8373,7 +8373,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8399,7 +8399,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -8425,7 +8425,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -8451,7 +8451,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8477,7 +8477,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8503,7 +8503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -8529,7 +8529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8555,7 +8555,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8581,7 +8581,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8607,7 +8607,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8633,7 +8633,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8659,7 +8659,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -8685,7 +8685,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -8711,7 +8711,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8737,7 +8737,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -8763,7 +8763,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8789,7 +8789,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8815,7 +8815,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -8841,7 +8841,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -8867,7 +8867,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -8893,7 +8893,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -8919,7 +8919,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -8945,7 +8945,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -8971,7 +8971,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -8997,7 +8997,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -9023,7 +9023,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -9049,7 +9049,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -9075,7 +9075,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -9101,7 +9101,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9127,7 +9127,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -9153,7 +9153,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9179,7 +9179,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -9205,7 +9205,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -9231,7 +9231,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -9257,7 +9257,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9283,7 +9283,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -9309,7 +9309,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -9335,7 +9335,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9361,7 +9361,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -9387,7 +9387,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -9413,7 +9413,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -9439,7 +9439,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9465,7 +9465,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -9491,7 +9491,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9517,7 +9517,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9543,7 +9543,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -9569,7 +9569,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9595,7 +9595,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -9621,7 +9621,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -9647,7 +9647,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -9673,7 +9673,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G314" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -9699,7 +9699,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G315" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -9725,7 +9725,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G316" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -9751,7 +9751,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9777,7 +9777,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -9803,7 +9803,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -9829,7 +9829,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -9855,7 +9855,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -9881,7 +9881,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -9907,7 +9907,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G323" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -9933,7 +9933,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -9959,7 +9959,7 @@
         <v>2.5</v>
       </c>
       <c r="G325" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9985,7 +9985,7 @@
         <v>2.5</v>
       </c>
       <c r="G326" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -10011,7 +10011,7 @@
         <v>2.5</v>
       </c>
       <c r="G327" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -10037,7 +10037,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -10063,7 +10063,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -10089,7 +10089,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -10115,7 +10115,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -10141,7 +10141,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -10167,7 +10167,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -10193,7 +10193,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -10219,7 +10219,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10245,7 +10245,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -10271,7 +10271,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10297,7 +10297,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10323,7 +10323,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -10349,7 +10349,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10375,7 +10375,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10401,7 +10401,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -10427,7 +10427,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10453,7 +10453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10479,7 +10479,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10505,7 +10505,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G346" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10531,7 +10531,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10557,7 +10557,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G348" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10583,7 +10583,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10609,7 +10609,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G350" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10635,7 +10635,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10661,7 +10661,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -10687,7 +10687,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -10713,7 +10713,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -10739,7 +10739,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10765,7 +10765,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -10791,7 +10791,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10817,7 +10817,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -10843,7 +10843,7 @@
         <v>2.5</v>
       </c>
       <c r="G359" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10869,7 +10869,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -10895,7 +10895,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -10921,7 +10921,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -10947,7 +10947,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10973,7 +10973,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -10999,7 +10999,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11025,7 +11025,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11051,7 +11051,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11077,7 +11077,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11103,7 +11103,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G369" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11129,7 +11129,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11155,7 +11155,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11181,7 +11181,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11207,7 +11207,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11233,7 +11233,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G374" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11259,7 +11259,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11285,7 +11285,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11311,7 +11311,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11337,7 +11337,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11363,7 +11363,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G379" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11389,7 +11389,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G380" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11415,7 +11415,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G381" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11441,7 +11441,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G382" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11467,7 +11467,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G383" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11493,7 +11493,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11519,7 +11519,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G385" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11545,7 +11545,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11571,7 +11571,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G387" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11597,7 +11597,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G388" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11623,7 +11623,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G389" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11649,7 +11649,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G390" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11675,7 +11675,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11701,7 +11701,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11727,7 +11727,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G393" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11753,7 +11753,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11779,7 +11779,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G395" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -11805,7 +11805,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -11831,7 +11831,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -11857,7 +11857,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -11883,7 +11883,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -11909,7 +11909,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -11935,7 +11935,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -11961,7 +11961,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -11987,7 +11987,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12013,7 +12013,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12039,7 +12039,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12065,7 +12065,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12091,7 +12091,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12117,7 +12117,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12143,7 +12143,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12169,7 +12169,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12195,7 +12195,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12221,7 +12221,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G412" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12247,7 +12247,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G413" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12273,7 +12273,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G414" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12299,7 +12299,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G415" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12325,7 +12325,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G416" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12351,7 +12351,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12377,7 +12377,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12403,7 +12403,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G419" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12429,7 +12429,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G420" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12455,7 +12455,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12481,7 +12481,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12507,7 +12507,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12533,7 +12533,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12559,7 +12559,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12585,7 +12585,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12611,7 +12611,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12637,7 +12637,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12663,7 +12663,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12689,7 +12689,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G430" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12715,7 +12715,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G431" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12741,7 +12741,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12767,7 +12767,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -12793,7 +12793,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -12819,7 +12819,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -12845,7 +12845,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -12871,7 +12871,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -12897,7 +12897,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -12923,7 +12923,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -12949,7 +12949,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -12975,7 +12975,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -13001,7 +13001,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13027,7 +13027,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13053,7 +13053,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13079,7 +13079,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13131,7 +13131,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13157,7 +13157,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13183,7 +13183,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13209,7 +13209,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13235,7 +13235,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13261,7 +13261,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13287,7 +13287,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13313,7 +13313,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13339,7 +13339,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13365,7 +13365,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13391,7 +13391,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G457" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13417,7 +13417,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13443,7 +13443,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13469,7 +13469,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G460" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13495,7 +13495,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13521,7 +13521,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G462" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13547,7 +13547,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13573,7 +13573,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G464" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13599,7 +13599,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G465" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13625,7 +13625,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13651,7 +13651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G467" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13677,7 +13677,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G468" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -45093,7 +45093,7 @@
     </row>
     <row r="1677">
       <c r="A1677" s="1" t="n">
-        <v>46071.5928125</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B1677" t="n">
         <v>8000</v>
@@ -45114,6 +45114,32 @@
         <v>372</v>
       </c>
       <c r="H1677" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="1" t="n">
+        <v>46072.6156481481</v>
+      </c>
+      <c r="B1678" t="n">
+        <v>5750</v>
+      </c>
+      <c r="C1678" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1678" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G1678" t="s">
+        <v>381</v>
+      </c>
+      <c r="H1678" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849536895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526304244995</t>
+    <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
     <t xml:space="preserve">4.51187896728516</t>
@@ -62,37 +62,37 @@
     <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3730525970459</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999391555786</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
     <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539747238159</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
     <t xml:space="preserve">4.2255482673645</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
@@ -116,37 +116,37 @@
     <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451121330261</t>
+    <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142753601074</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0693678855896</t>
+    <t xml:space="preserve">4.06936883926392</t>
   </si>
   <si>
     <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127697944641</t>
+    <t xml:space="preserve">3.99127721786499</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921732902527</t>
@@ -155,64 +155,64 @@
     <t xml:space="preserve">3.94789505004883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
     <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230052947998</t>
+    <t xml:space="preserve">3.72230076789856</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420986175537</t>
+    <t xml:space="preserve">3.64420962333679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082721710205</t>
   </si>
   <si>
     <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657110214233</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201482772827</t>
+    <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524834632874</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583420753479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
     <t xml:space="preserve">3.74833035469055</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684163093567</t>
+    <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596982955933</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302225112915</t>
+    <t xml:space="preserve">3.19302248954773</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.471755027771</t>
+    <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274027824402</t>
+    <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.348393201828</t>
+    <t xml:space="preserve">3.34839344024658</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552388191223</t>
+    <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81970000267029</t>
+    <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
     <t xml:space="preserve">2.85494613647461</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
@@ -392,16 +392,16 @@
     <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854343891144</t>
+    <t xml:space="preserve">1.93854331970215</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805081367493</t>
+    <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8328047990799</t>
+    <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
     <t xml:space="preserve">1.81518161296844</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575971603394</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822248458862</t>
+    <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445339202881</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740842819214</t>
+    <t xml:space="preserve">3.20740818977356</t>
   </si>
   <si>
     <t xml:space="preserve">3.24265480041504</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072942733765</t>
+    <t xml:space="preserve">4.14072895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695363998413</t>
+    <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612209320068</t>
+    <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -605,25 +605,25 @@
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280321121216</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902742385864</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9794020652771</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147656440735</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -45119,7 +45119,7 @@
     </row>
     <row r="1678">
       <c r="A1678" s="1" t="n">
-        <v>46072.6156481481</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B1678" t="n">
         <v>5750</v>
@@ -45140,6 +45140,32 @@
         <v>381</v>
       </c>
       <c r="H1678" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="1" t="n">
+        <v>46073.6242939815</v>
+      </c>
+      <c r="B1679" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1679" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D1679" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1679" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F1679" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G1679" t="s">
+        <v>368</v>
+      </c>
+      <c r="H1679" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -53,19 +53,19 @@
     <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526256561279</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
     <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3799934387207</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643571853638</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539794921875</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422527313232</t>
+    <t xml:space="preserve">4.23422574996948</t>
   </si>
   <si>
     <t xml:space="preserve">4.16481161117554</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613508224487</t>
@@ -119,70 +119,70 @@
     <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451121330261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9305408000946</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936883926392</t>
+    <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127721786499</t>
+    <t xml:space="preserve">3.99127817153931</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789505004883</t>
+    <t xml:space="preserve">3.94789481163025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436017990112</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230076789856</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494675636292</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420962333679</t>
+    <t xml:space="preserve">3.64421033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082721710205</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568365097046</t>
+    <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657086372375</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.965247631073</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
@@ -224,16 +224,16 @@
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258599281311</t>
+    <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684210777283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345850944519</t>
+    <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
     <t xml:space="preserve">3.21037554740906</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302248954773</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
@@ -275,9 +275,6 @@
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126252174377</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
@@ -287,10 +284,10 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274003982544</t>
+    <t xml:space="preserve">3.61274027824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077025413513</t>
+    <t xml:space="preserve">3.33077049255371</t>
   </si>
   <si>
     <t xml:space="preserve">3.34839344024658</t>
@@ -299,28 +296,28 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552388191223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593091011047</t>
+    <t xml:space="preserve">2.99593114852905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404636383057</t>
+    <t xml:space="preserve">3.08404684066772</t>
   </si>
   <si>
     <t xml:space="preserve">2.96068453788757</t>
@@ -338,13 +335,13 @@
     <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9430615901947</t>
+    <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
     <t xml:space="preserve">2.62584543228149</t>
@@ -356,22 +353,22 @@
     <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387540817261</t>
+    <t xml:space="preserve">2.34387564659119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625222206116</t>
+    <t xml:space="preserve">2.32625246047974</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289039611816</t>
+    <t xml:space="preserve">2.20289015769958</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
@@ -389,16 +386,16 @@
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854331970215</t>
+    <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567411899567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805105209351</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -407,19 +404,19 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042774677277</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575947761536</t>
+    <t xml:space="preserve">2.25575971603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
@@ -428,10 +425,10 @@
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535268783569</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
@@ -446,37 +443,37 @@
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059906005859</t>
+    <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633793830872</t>
+    <t xml:space="preserve">2.69633769989014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740818977356</t>
+    <t xml:space="preserve">3.20740866661072</t>
   </si>
   <si>
     <t xml:space="preserve">3.24265480041504</t>
@@ -497,10 +494,13 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239252090454</t>
+    <t xml:space="preserve">3.26239275932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297226905823</t>
+    <t xml:space="preserve">3.60297179222107</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168262481689</t>
+    <t xml:space="preserve">4.39168214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545841217041</t>
+    <t xml:space="preserve">4.44545793533325</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -599,16 +599,16 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280368804932</t>
+    <t xml:space="preserve">4.12280416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620578765869</t>
+    <t xml:space="preserve">4.26620626449585</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -7099,7 +7099,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -7125,7 +7125,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -7151,7 +7151,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -7177,7 +7177,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -7203,7 +7203,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -7229,7 +7229,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7255,7 +7255,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -7281,7 +7281,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -7307,7 +7307,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G223" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -7333,7 +7333,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -7359,7 +7359,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -7385,7 +7385,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -7411,7 +7411,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -7437,7 +7437,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -7463,7 +7463,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7489,7 +7489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -7515,7 +7515,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -7541,7 +7541,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -7567,7 +7567,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7593,7 +7593,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -7619,7 +7619,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7645,7 +7645,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -7671,7 +7671,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -7697,7 +7697,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -7723,7 +7723,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -7749,7 +7749,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -7775,7 +7775,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -7801,7 +7801,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -7827,7 +7827,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -7853,7 +7853,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -7879,7 +7879,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -7905,7 +7905,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -7957,7 +7957,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -7983,7 +7983,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8009,7 +8009,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8035,7 +8035,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8061,7 +8061,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G252" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -8113,7 +8113,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -8139,7 +8139,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -8165,7 +8165,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -8191,7 +8191,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -8217,7 +8217,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G258" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -8243,7 +8243,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -8269,7 +8269,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -8295,7 +8295,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -8321,7 +8321,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8347,7 +8347,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -8373,7 +8373,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8399,7 +8399,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -8425,7 +8425,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -8451,7 +8451,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8477,7 +8477,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8503,7 +8503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -8529,7 +8529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8555,7 +8555,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8581,7 +8581,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8607,7 +8607,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8633,7 +8633,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8659,7 +8659,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -8685,7 +8685,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -8711,7 +8711,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8737,7 +8737,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -8763,7 +8763,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8789,7 +8789,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8815,7 +8815,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -8841,7 +8841,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -8867,7 +8867,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -8893,7 +8893,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -8919,7 +8919,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -8945,7 +8945,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -8971,7 +8971,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -8997,7 +8997,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -9023,7 +9023,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -9049,7 +9049,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -9075,7 +9075,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -9101,7 +9101,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9127,7 +9127,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -9153,7 +9153,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9179,7 +9179,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -9205,7 +9205,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -9231,7 +9231,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -9257,7 +9257,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9283,7 +9283,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -9309,7 +9309,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -9335,7 +9335,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9361,7 +9361,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -9387,7 +9387,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -9413,7 +9413,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -9439,7 +9439,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9465,7 +9465,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -9491,7 +9491,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9517,7 +9517,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9543,7 +9543,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -9569,7 +9569,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9595,7 +9595,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -9621,7 +9621,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -9647,7 +9647,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -9673,7 +9673,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G314" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -9699,7 +9699,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G315" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -9725,7 +9725,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G316" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -9751,7 +9751,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9777,7 +9777,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -9803,7 +9803,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -9829,7 +9829,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -9855,7 +9855,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -9881,7 +9881,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -9907,7 +9907,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G323" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -9933,7 +9933,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -9959,7 +9959,7 @@
         <v>2.5</v>
       </c>
       <c r="G325" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9985,7 +9985,7 @@
         <v>2.5</v>
       </c>
       <c r="G326" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -10011,7 +10011,7 @@
         <v>2.5</v>
       </c>
       <c r="G327" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -10037,7 +10037,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -10063,7 +10063,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -10089,7 +10089,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -10115,7 +10115,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -10141,7 +10141,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -10167,7 +10167,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -10193,7 +10193,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -10219,7 +10219,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10245,7 +10245,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -10271,7 +10271,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10297,7 +10297,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10323,7 +10323,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -10349,7 +10349,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10375,7 +10375,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10401,7 +10401,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -10427,7 +10427,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10453,7 +10453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10479,7 +10479,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10505,7 +10505,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G346" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10531,7 +10531,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10557,7 +10557,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G348" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10583,7 +10583,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10609,7 +10609,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G350" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10635,7 +10635,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10661,7 +10661,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -10687,7 +10687,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -10713,7 +10713,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -10739,7 +10739,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10765,7 +10765,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -10791,7 +10791,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10817,7 +10817,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -10843,7 +10843,7 @@
         <v>2.5</v>
       </c>
       <c r="G359" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10869,7 +10869,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -10895,7 +10895,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -10921,7 +10921,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -10947,7 +10947,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10973,7 +10973,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -10999,7 +10999,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11025,7 +11025,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11051,7 +11051,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11077,7 +11077,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11103,7 +11103,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G369" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11129,7 +11129,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11155,7 +11155,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11181,7 +11181,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11207,7 +11207,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11233,7 +11233,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G374" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11259,7 +11259,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11285,7 +11285,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11311,7 +11311,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11337,7 +11337,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11363,7 +11363,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G379" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11389,7 +11389,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G380" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11415,7 +11415,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G381" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11441,7 +11441,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G382" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11467,7 +11467,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G383" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11493,7 +11493,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11519,7 +11519,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G385" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11545,7 +11545,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11571,7 +11571,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G387" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11597,7 +11597,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G388" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11623,7 +11623,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G389" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11649,7 +11649,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G390" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11675,7 +11675,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11701,7 +11701,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11727,7 +11727,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G393" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11753,7 +11753,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11779,7 +11779,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G395" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -11805,7 +11805,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -11831,7 +11831,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -11857,7 +11857,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -11883,7 +11883,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -11909,7 +11909,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -11935,7 +11935,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -11961,7 +11961,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -11987,7 +11987,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12013,7 +12013,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12039,7 +12039,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12065,7 +12065,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12091,7 +12091,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12117,7 +12117,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12143,7 +12143,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12169,7 +12169,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12195,7 +12195,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12221,7 +12221,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G412" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12247,7 +12247,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G413" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12273,7 +12273,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G414" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12299,7 +12299,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G415" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12325,7 +12325,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G416" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12351,7 +12351,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12377,7 +12377,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12403,7 +12403,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G419" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12429,7 +12429,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G420" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12455,7 +12455,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12481,7 +12481,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12507,7 +12507,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12533,7 +12533,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12559,7 +12559,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12585,7 +12585,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12611,7 +12611,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12637,7 +12637,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12663,7 +12663,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12689,7 +12689,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G430" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12715,7 +12715,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G431" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12741,7 +12741,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12767,7 +12767,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -12793,7 +12793,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -12819,7 +12819,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -12845,7 +12845,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -12871,7 +12871,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -12897,7 +12897,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -12923,7 +12923,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -12949,7 +12949,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -12975,7 +12975,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -13001,7 +13001,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13027,7 +13027,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13053,7 +13053,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13079,7 +13079,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13131,7 +13131,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13157,7 +13157,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13183,7 +13183,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13209,7 +13209,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13235,7 +13235,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13261,7 +13261,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13287,7 +13287,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13313,7 +13313,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13339,7 +13339,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13365,7 +13365,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13391,7 +13391,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G457" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13417,7 +13417,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13443,7 +13443,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13469,7 +13469,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G460" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13495,7 +13495,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13521,7 +13521,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G462" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13547,7 +13547,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13573,7 +13573,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G464" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13599,7 +13599,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G465" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13625,7 +13625,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13651,7 +13651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G467" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13677,7 +13677,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G468" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -45145,7 +45145,7 @@
     </row>
     <row r="1679">
       <c r="A1679" s="1" t="n">
-        <v>46073.6242939815</v>
+        <v>46073.3333333333</v>
       </c>
       <c r="B1679" t="n">
         <v>1500</v>
@@ -45166,6 +45166,32 @@
         <v>368</v>
       </c>
       <c r="H1679" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="1" t="n">
+        <v>46076.4471064815</v>
+      </c>
+      <c r="B1680" t="n">
+        <v>4250</v>
+      </c>
+      <c r="C1680" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1680" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G1680" t="s">
+        <v>381</v>
+      </c>
+      <c r="H1680" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849536895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4077582359314</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39214086532593</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999391555786</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643619537354</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
     <t xml:space="preserve">4.33834552764893</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157785415649</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613460540771</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054056167603</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995493888855</t>
   </si>
   <si>
     <t xml:space="preserve">3.99127793312073</t>
@@ -152,43 +152,43 @@
     <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.83509707450867</t>
   </si>
   <si>
     <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759393692017</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
     <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7656843662262</t>
+    <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804441452026</t>
@@ -197,19 +197,19 @@
     <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201530456543</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583420753479</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333734512329</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258599281311</t>
+    <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684163093567</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052586555481</t>
+    <t xml:space="preserve">3.34052610397339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714250564575</t>
+    <t xml:space="preserve">3.29714226722717</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4541323184967</t>
+    <t xml:space="preserve">3.45413208007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363933563232</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -281,34 +281,34 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.471755027771</t>
+    <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61273980140686</t>
+    <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27790093421936</t>
+    <t xml:space="preserve">3.27790069580078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216205596924</t>
+    <t xml:space="preserve">3.17216229438782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552435874939</t>
+    <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
     <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355409622192</t>
+    <t xml:space="preserve">3.01355385780334</t>
   </si>
   <si>
     <t xml:space="preserve">2.9783079624176</t>
@@ -338,10 +338,10 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207633972168</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346837997437</t>
+    <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
     <t xml:space="preserve">2.62584519386292</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100584983826</t>
+    <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387516975403</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16764426231384</t>
+    <t xml:space="preserve">2.16764402389526</t>
   </si>
   <si>
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239789009094</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535316467285</t>
+    <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
@@ -440,16 +440,16 @@
     <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48486042022705</t>
+    <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978500366211</t>
+    <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35201859474182</t>
+    <t xml:space="preserve">3.3520188331604</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072942733765</t>
+    <t xml:space="preserve">4.14072895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695363998413</t>
+    <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
     <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612209320068</t>
+    <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
     <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574745178223</t>
+    <t xml:space="preserve">4.61574792861938</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
@@ -599,19 +599,19 @@
     <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280321121216</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317785263062</t>
+    <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902742385864</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9794020652771</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770149230957</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824304580688</t>
+    <t xml:space="preserve">3.29824280738831</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147656440735</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686899185181</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -785,22 +785,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -45350,7 +45350,7 @@
     </row>
     <row r="1687">
       <c r="A1687" s="1" t="n">
-        <v>46085.6909953704</v>
+        <v>46085.3333333333</v>
       </c>
       <c r="B1687" t="n">
         <v>2500</v>
@@ -45371,6 +45371,32 @@
         <v>371</v>
       </c>
       <c r="H1687" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="1" t="n">
+        <v>46086.4037847222</v>
+      </c>
+      <c r="B1688" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1688" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1688" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F1688" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="G1688" t="s">
+        <v>365</v>
+      </c>
+      <c r="H1688" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -44,34 +44,34 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849632263184</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526304244995</t>
+    <t xml:space="preserve">4.55526208877563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.37305164337158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999391555786</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966804504395</t>
   </si>
   <si>
     <t xml:space="preserve">4.21687173843384</t>
@@ -80,19 +80,19 @@
     <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
     <t xml:space="preserve">4.22554874420166</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216514587402</t>
@@ -122,115 +122,115 @@
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142753601074</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0693678855896</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995398521423</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921828269958</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171347618103</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436017990112</t>
+    <t xml:space="preserve">3.77436065673828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
     <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
     <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759393692017</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7656843662262</t>
+    <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657110214233</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804393768311</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201530456543</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333829879761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273654937744</t>
+    <t xml:space="preserve">3.52273678779602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684163093567</t>
+    <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345850944519</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390946388245</t>
+    <t xml:space="preserve">3.38390970230103</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126276016235</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072942733765</t>
+    <t xml:space="preserve">4.14072895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695363998413</t>
+    <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612209320068</t>
+    <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
@@ -581,13 +581,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -602,25 +602,25 @@
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280321121216</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902742385864</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9794020652771</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147656440735</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849632263184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775918960571</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526208877563</t>
+    <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187944412231</t>
+    <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305164337158</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3799934387207</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643571853638</t>
@@ -80,19 +80,19 @@
     <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745903015137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010549545288</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
     <t xml:space="preserve">4.22554874420166</t>
@@ -107,25 +107,25 @@
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613508224487</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451049804688</t>
+    <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9305408000946</t>
+    <t xml:space="preserve">3.93054151535034</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
@@ -134,34 +134,34 @@
     <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628540039062</t>
+    <t xml:space="preserve">4.28628492355347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936836242676</t>
+    <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127793312073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921828269958</t>
+    <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
     <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436065673828</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
@@ -170,28 +170,28 @@
     <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494675636292</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420986175537</t>
+    <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
     <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.7656843662262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392439842224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804393768311</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
@@ -203,34 +203,34 @@
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186379432678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.965247631073</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
     <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333829879761</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
     <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273678779602</t>
+    <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258599281311</t>
+    <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345850944519</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596982955933</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
@@ -254,25 +254,25 @@
     <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978920936584</t>
+    <t xml:space="preserve">3.27978897094727</t>
   </si>
   <si>
     <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390970230103</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4541323184967</t>
+    <t xml:space="preserve">3.45413208007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363933563232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22503161430359</t>
+    <t xml:space="preserve">3.22503185272217</t>
   </si>
   <si>
     <t xml:space="preserve">3.43650913238525</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.471755027771</t>
+    <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273980140686</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552435874939</t>
+    <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
     <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207633972168</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346837997437</t>
@@ -350,16 +350,16 @@
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387516975403</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
@@ -371,28 +371,28 @@
     <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16764426231384</t>
+    <t xml:space="preserve">2.16764402389526</t>
   </si>
   <si>
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903606414795</t>
+    <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854379653931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567411899567</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -413,28 +413,28 @@
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535316467285</t>
+    <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,22 +446,22 @@
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059906005859</t>
+    <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445363044739</t>
+    <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
     <t xml:space="preserve">2.69633769989014</t>
@@ -470,22 +470,22 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
     <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978500366211</t>
+    <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239252090454</t>
+    <t xml:space="preserve">3.26239275932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297226905823</t>
+    <t xml:space="preserve">3.60297179222107</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168262481689</t>
+    <t xml:space="preserve">4.39168214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545841217041</t>
+    <t xml:space="preserve">4.44545793533325</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280368804932</t>
+    <t xml:space="preserve">4.12280416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620578765869</t>
+    <t xml:space="preserve">4.26620626449585</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -785,22 +785,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -45454,7 +45454,7 @@
     </row>
     <row r="1691">
       <c r="A1691" s="1" t="n">
-        <v>46091.5629513889</v>
+        <v>46091.3333333333</v>
       </c>
       <c r="B1691" t="n">
         <v>750</v>
@@ -45475,6 +45475,58 @@
         <v>366</v>
       </c>
       <c r="H1691" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="1" t="n">
+        <v>46092.3333333333</v>
+      </c>
+      <c r="B1692" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1692" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1692" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1692" t="s">
+        <v>366</v>
+      </c>
+      <c r="H1692" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="1" t="n">
+        <v>46093.6540972222</v>
+      </c>
+      <c r="B1693" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1693" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D1693" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1693" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F1693" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G1693" t="s">
+        <v>387</v>
+      </c>
+      <c r="H1693" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,121 +38,121 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231594085693</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849536895752</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.4077582359314</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3730525970459</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966804504395</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216872215271</t>
+    <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010454177856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422574996948</t>
+    <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216562271118</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819520950317</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
     <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054127693176</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
     <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628587722778</t>
+    <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936740875244</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995422363281</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789481163025</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171371459961</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436065673828</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421033859253</t>
@@ -179,25 +179,25 @@
     <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.96524739265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583373069763</t>
+    <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
     <t xml:space="preserve">3.74833059310913</t>
@@ -224,25 +224,25 @@
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258646965027</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052562713623</t>
+    <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714250564575</t>
+    <t xml:space="preserve">3.29714226722717</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596959114075</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390922546387</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126276016235</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22503161430359</t>
+    <t xml:space="preserve">3.22503137588501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650889396667</t>
+    <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274027824402</t>
+    <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077049255371</t>
+    <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216205596924</t>
+    <t xml:space="preserve">3.17216229438782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552388191223</t>
+    <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
     <t xml:space="preserve">3.1016697883606</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593114852905</t>
+    <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355385780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97830820083618</t>
+    <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
     <t xml:space="preserve">2.9430615901947</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">2.80207681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346837997437</t>
+    <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4672372341156</t>
+    <t xml:space="preserve">2.46723699569702</t>
   </si>
   <si>
     <t xml:space="preserve">2.36149859428406</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100584983826</t>
+    <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
+    <t xml:space="preserve">2.34387516975403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625246047974</t>
+    <t xml:space="preserve">2.32625198364258</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
@@ -380,22 +380,22 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239812850952</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616662502289</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854343891144</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805105209351</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575971603394</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158431053162</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -443,46 +443,46 @@
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059929847717</t>
+    <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633769989014</t>
+    <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740866661072</t>
+    <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
     <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027750968933</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978524208069</t>
+    <t xml:space="preserve">3.18978548049927</t>
   </si>
   <si>
     <t xml:space="preserve">3.13691568374634</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35201859474182</t>
+    <t xml:space="preserve">3.3520188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616806983948</t>
+    <t xml:space="preserve">3.31616830825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -548,43 +548,43 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574745178223</t>
+    <t xml:space="preserve">4.61574792861938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753314971924</t>
+    <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
     <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413057327271</t>
+    <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998205184937</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
@@ -599,10 +599,10 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -614,31 +614,31 @@
     <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902837753296</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824304580688</t>
+    <t xml:space="preserve">3.29824280738831</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -45552,9 +45552,11 @@
       <c r="E1694" t="n">
         <v>2.20000004768372</v>
       </c>
-      <c r="F1694"/>
+      <c r="F1694" t="n">
+        <v>2.20000004768372</v>
+      </c>
       <c r="G1694" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45562,27 +45564,51 @@
     </row>
     <row r="1695">
       <c r="A1695" s="1" t="n">
-        <v>46094.5450115741</v>
+        <v>46097.3333333333</v>
       </c>
       <c r="B1695" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="C1695" t="n">
-        <v>2.20000004768372</v>
+        <v>2.16000008583069</v>
       </c>
       <c r="D1695" t="n">
-        <v>2.20000004768372</v>
+        <v>2.16000008583069</v>
       </c>
       <c r="E1695" t="n">
-        <v>2.20000004768372</v>
-      </c>
-      <c r="F1695" t="n">
-        <v>2.20000004768372</v>
-      </c>
+        <v>2.16000008583069</v>
+      </c>
+      <c r="F1695"/>
       <c r="G1695" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1695" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="1" t="n">
+        <v>46097.4624189815</v>
+      </c>
+      <c r="B1696" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1696" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D1696" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="F1696" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G1696" t="s">
+        <v>382</v>
+      </c>
+      <c r="H1696" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775918960571</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526304244995</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3730525970459</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999296188354</t>
+    <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643524169922</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966804504395</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
     <t xml:space="preserve">4.21687173843384</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539747238159</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745855331421</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.16481113433838</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275148391724</t>
@@ -110,25 +110,25 @@
     <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613508224487</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9305408000946</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
@@ -137,112 +137,112 @@
     <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628540039062</t>
+    <t xml:space="preserve">4.28628492355347</t>
   </si>
   <si>
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995493888855</t>
+    <t xml:space="preserve">3.99995470046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171419143677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509731292725</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77435994148254</t>
+    <t xml:space="preserve">3.77436065673828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72229981422424</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421010017395</t>
+    <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
     <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7656843662262</t>
+    <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392439842224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201482772827</t>
+    <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524810791016</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833035469055</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684210777283</t>
+    <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345850944519</t>
+    <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037530899048</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714250564575</t>
+    <t xml:space="preserve">3.29714226722717</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596935272217</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978897094727</t>
+    <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
     <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390922546387</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45413255691528</t>
+    <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
     <t xml:space="preserve">3.3836395740509</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650889396667</t>
+    <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077001571655</t>
+    <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207681655884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100608825684</t>
+    <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387540817261</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239765167236</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
     <t xml:space="preserve">1.93854355812073</t>
@@ -398,19 +398,19 @@
     <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822200775146</t>
+    <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,22 +446,22 @@
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059906005859</t>
+    <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445363044739</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929249763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027774810791</t>
+    <t xml:space="preserve">3.26027798652649</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616806983948</t>
+    <t xml:space="preserve">3.31616830825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674757957458</t>
+    <t xml:space="preserve">3.65674734115601</t>
   </si>
   <si>
     <t xml:space="preserve">3.60297203063965</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562651634216</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753314971924</t>
+    <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413057327271</t>
+    <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998205184937</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056060791016</t>
+    <t xml:space="preserve">4.66056108474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902837753296</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525259017944</t>
+    <t xml:space="preserve">4.01525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732685089111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579438209534</t>
+    <t xml:space="preserve">3.40579414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334595680237</t>
+    <t xml:space="preserve">3.51334619522095</t>
   </si>
   <si>
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -45607,9 +45607,11 @@
       <c r="E1696" t="n">
         <v>2.16000008583069</v>
       </c>
-      <c r="F1696"/>
+      <c r="F1696" t="n">
+        <v>2.09999990463257</v>
+      </c>
       <c r="G1696" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45617,27 +45619,51 @@
     </row>
     <row r="1697">
       <c r="A1697" s="1" t="n">
-        <v>46098.6872453704</v>
+        <v>46099.3333333333</v>
       </c>
       <c r="B1697" t="n">
-        <v>5250</v>
+        <v>4750</v>
       </c>
       <c r="C1697" t="n">
-        <v>2.16000008583069</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="D1697" t="n">
-        <v>2.05999994277954</v>
+        <v>2.09999990463257</v>
       </c>
       <c r="E1697" t="n">
-        <v>2.16000008583069</v>
-      </c>
-      <c r="F1697" t="n">
         <v>2.09999990463257</v>
       </c>
+      <c r="F1697"/>
       <c r="G1697" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H1697" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="1" t="n">
+        <v>46099.5688773148</v>
+      </c>
+      <c r="B1698" t="n">
+        <v>4750</v>
+      </c>
+      <c r="C1698" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D1698" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1698" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G1698" t="s">
+        <v>384</v>
+      </c>
+      <c r="H1698" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
     <t xml:space="preserve">4.40775871276855</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3799934387207</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.32966804504395</t>
   </si>
   <si>
     <t xml:space="preserve">4.21687173843384</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539794921875</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422527313232</t>
+    <t xml:space="preserve">4.23422574996948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481113433838</t>
+    <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275148391724</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613460540771</t>
@@ -122,88 +122,88 @@
     <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451049804688</t>
+    <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142848968506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628492355347</t>
+    <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936836242676</t>
+    <t xml:space="preserve">4.06936740875244</t>
   </si>
   <si>
     <t xml:space="preserve">3.99995470046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127745628357</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921756744385</t>
+    <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789433479309</t>
+    <t xml:space="preserve">3.94789481163025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171419143677</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
     <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436065673828</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420986175537</t>
+    <t xml:space="preserve">3.64421033859253</t>
   </si>
   <si>
     <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.7656843662262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657110214233</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392439842224</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201435089111</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524786949158</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
     <t xml:space="preserve">3.74833083152771</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345827102661</t>
@@ -239,19 +239,19 @@
     <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052586555481</t>
+    <t xml:space="preserve">3.34052562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714226722717</t>
+    <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596935272217</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390946388245</t>
+    <t xml:space="preserve">3.38390922546387</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650913238525</t>
+    <t xml:space="preserve">3.43650889396667</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274003982544</t>
+    <t xml:space="preserve">3.61274027824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077025413513</t>
+    <t xml:space="preserve">3.33077049255371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.348393201828</t>
+    <t xml:space="preserve">3.34839344024658</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216229438782</t>
+    <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552388191223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
     <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593091011047</t>
+    <t xml:space="preserve">2.99593114852905</t>
   </si>
   <si>
     <t xml:space="preserve">3.08404660224915</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355409622192</t>
+    <t xml:space="preserve">3.01355385780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783079624176</t>
+    <t xml:space="preserve">2.97830820083618</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
     <t xml:space="preserve">2.9430615901947</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912154197693</t>
+    <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387540817261</t>
+    <t xml:space="preserve">2.34387564659119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625222206116</t>
+    <t xml:space="preserve">2.32625246047974</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
@@ -383,22 +383,22 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239765167236</t>
+    <t xml:space="preserve">2.13239812850952</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616662502289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854343891144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805081367493</t>
+    <t xml:space="preserve">1.86805105209351</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
@@ -419,25 +419,25 @@
     <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575947761536</t>
+    <t xml:space="preserve">2.25575971603394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535316467285</t>
+    <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,49 +446,49 @@
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445363044739</t>
+    <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633793830872</t>
+    <t xml:space="preserve">2.69633769989014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929249763489</t>
+    <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740842819214</t>
+    <t xml:space="preserve">3.20740866661072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027798652649</t>
+    <t xml:space="preserve">3.26027750968933</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239252090454</t>
+    <t xml:space="preserve">3.26239275932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369161605835</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616830825806</t>
+    <t xml:space="preserve">3.31616806983948</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674734115601</t>
+    <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
     <t xml:space="preserve">3.60297203063965</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562651634216</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48130798339844</t>
+    <t xml:space="preserve">4.4813084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537424087524</t>
+    <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168262481689</t>
+    <t xml:space="preserve">4.39168214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753267288208</t>
+    <t xml:space="preserve">4.42753314971924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790636062622</t>
+    <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413105010986</t>
+    <t xml:space="preserve">4.28413057327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998205184937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056108474731</t>
+    <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317785263062</t>
+    <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902837753296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525211334229</t>
+    <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732685089111</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579414367676</t>
+    <t xml:space="preserve">3.40579438209534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334619522095</t>
+    <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147680282593</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -45633,9 +45633,11 @@
       <c r="E1697" t="n">
         <v>2.09999990463257</v>
       </c>
-      <c r="F1697"/>
+      <c r="F1697" t="n">
+        <v>2.11999988555908</v>
+      </c>
       <c r="G1697" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45643,27 +45645,51 @@
     </row>
     <row r="1698">
       <c r="A1698" s="1" t="n">
-        <v>46099.5688773148</v>
+        <v>46100.3333333333</v>
       </c>
       <c r="B1698" t="n">
-        <v>4750</v>
+        <v>750</v>
       </c>
       <c r="C1698" t="n">
         <v>2.11999988555908</v>
       </c>
       <c r="D1698" t="n">
-        <v>2.09999990463257</v>
+        <v>2.11999988555908</v>
       </c>
       <c r="E1698" t="n">
-        <v>2.09999990463257</v>
-      </c>
-      <c r="F1698" t="n">
         <v>2.11999988555908</v>
       </c>
+      <c r="F1698"/>
       <c r="G1698" t="s">
+        <v>390</v>
+      </c>
+      <c r="H1698" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="1" t="n">
+        <v>46100.3831365741</v>
+      </c>
+      <c r="B1699" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1699" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D1699" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1699" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F1699" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G1699" t="s">
         <v>384</v>
       </c>
-      <c r="H1698" t="s">
+      <c r="H1699" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="392">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,16 +53,16 @@
     <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526304244995</t>
+    <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
     <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
     <t xml:space="preserve">4.37999296188354</t>
@@ -71,19 +71,19 @@
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
     <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702301025391</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539842605591</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010549545288</t>
+    <t xml:space="preserve">4.13010454177856</t>
   </si>
   <si>
     <t xml:space="preserve">4.2255482673645</t>
@@ -107,22 +107,22 @@
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613555908203</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216514587402</t>
+    <t xml:space="preserve">4.18216466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819568634033</t>
+    <t xml:space="preserve">4.20819425582886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451049804688</t>
+    <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
     <t xml:space="preserve">3.93054103851318</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">3.99995470046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921780586243</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171419143677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
     <t xml:space="preserve">3.7743604183197</t>
@@ -167,61 +167,61 @@
     <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230005264282</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759322166443</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568388938904</t>
+    <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657110214233</t>
+    <t xml:space="preserve">3.9565703868866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392439842224</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201482772827</t>
+    <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583420753479</t>
+    <t xml:space="preserve">3.89583349227905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333686828613</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833035469055</t>
+    <t xml:space="preserve">3.74833059310913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273631095886</t>
+    <t xml:space="preserve">3.52273678779602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258623123169</t>
@@ -230,25 +230,25 @@
     <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714274406433</t>
+    <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596935272217</t>
+    <t xml:space="preserve">3.43596982955933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390946388245</t>
+    <t xml:space="preserve">3.38390970230103</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45413208007812</t>
+    <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363981246948</t>
+    <t xml:space="preserve">3.38363933563232</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650913238525</t>
+    <t xml:space="preserve">3.43650937080383</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216229438782</t>
+    <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
     <t xml:space="preserve">3.29552412033081</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -323,76 +323,76 @@
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068429946899</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0135543346405</t>
+    <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81969976425171</t>
+    <t xml:space="preserve">2.81970000267029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207681655884</t>
+    <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4672372341156</t>
+    <t xml:space="preserve">2.46723699569702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912130355835</t>
+    <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387564659119</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625246047974</t>
+    <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477470397949</t>
+    <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971519947052</t>
+    <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239765167236</t>
+    <t xml:space="preserve">2.13239812850952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854379653931</t>
+    <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567423820496</t>
@@ -404,28 +404,28 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
     <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002131462097</t>
+    <t xml:space="preserve">2.15002083778381</t>
   </si>
   <si>
     <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575947761536</t>
+    <t xml:space="preserve">2.25575995445251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53772974014282</t>
+    <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
     <t xml:space="preserve">2.73158407211304</t>
@@ -437,43 +437,43 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010679244995</t>
+    <t xml:space="preserve">2.52010631561279</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059929847717</t>
+    <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445339202881</t>
+    <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633769989014</t>
+    <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929249763489</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027798652649</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369161605835</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35201859474182</t>
+    <t xml:space="preserve">3.3520188331604</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297179222107</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48130798339844</t>
+    <t xml:space="preserve">4.4813084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537424087524</t>
+    <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
     <t xml:space="preserve">4.17657947540283</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
     <t xml:space="preserve">4.5709342956543</t>
@@ -572,22 +572,22 @@
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574745178223</t>
+    <t xml:space="preserve">4.61574792861938</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790636062622</t>
+    <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280416488647</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317785263062</t>
+    <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
     <t xml:space="preserve">3.97940158843994</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824304580688</t>
+    <t xml:space="preserve">3.29824280738831</t>
   </si>
   <si>
     <t xml:space="preserve">3.40579438209534</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147680282593</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -1183,6 +1183,12 @@
   <si>
     <t xml:space="preserve">2.20000004768372</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05999994277954</t>
+  </si>
 </sst>
 </file>
 
@@ -45718,6 +45724,82 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1701">
+      <c r="A1701" s="1" t="n">
+        <v>46105.3333333333</v>
+      </c>
+      <c r="B1701" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1701" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="D1701" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E1701" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F1701" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="G1701" t="s">
+        <v>388</v>
+      </c>
+      <c r="H1701" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="1" t="n">
+        <v>46106.3333333333</v>
+      </c>
+      <c r="B1702" t="n">
+        <v>6750</v>
+      </c>
+      <c r="C1702" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D1702" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E1702" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F1702"/>
+      <c r="G1702" t="s">
+        <v>390</v>
+      </c>
+      <c r="H1702" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="1" t="n">
+        <v>46106.6672337963</v>
+      </c>
+      <c r="B1703" t="n">
+        <v>6750</v>
+      </c>
+      <c r="C1703" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D1703" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="E1703" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F1703" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G1703" t="s">
+        <v>391</v>
+      </c>
+      <c r="H1703" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.4077582359314</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526256561279</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3730525970459</t>
+    <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.37999296188354</t>
@@ -71,19 +71,19 @@
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216872215271</t>
+    <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539842605591</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010454177856</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -104,64 +104,64 @@
     <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819425582886</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.93054151535034</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
     <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628540039062</t>
+    <t xml:space="preserve">4.28628492355347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0693678855896</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
     <t xml:space="preserve">3.99995470046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921756744385</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171419143677</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
     <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436065673828</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
@@ -185,22 +185,22 @@
     <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9565703868866</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392439842224</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672189712524</t>
+    <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598476409912</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
     <t xml:space="preserve">3.92186427116394</t>
@@ -209,19 +209,19 @@
     <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583349227905</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273678779602</t>
+    <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258623123169</t>
@@ -242,25 +242,25 @@
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714250564575</t>
+    <t xml:space="preserve">3.29714226722717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596982955933</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861605644226</t>
+    <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978920936584</t>
+    <t xml:space="preserve">3.27978897094727</t>
   </si>
   <si>
     <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390970230103</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363933563232</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650937080383</t>
+    <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -293,22 +293,22 @@
     <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216205596924</t>
+    <t xml:space="preserve">3.17216229438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
     <t xml:space="preserve">3.1016697883606</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81970000267029</t>
+    <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
     <t xml:space="preserve">2.85494589805603</t>
@@ -341,22 +341,22 @@
     <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207681655884</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46723699569702</t>
+    <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
     <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239812850952</t>
+    <t xml:space="preserve">2.13239765167236</t>
   </si>
   <si>
     <t xml:space="preserve">2.00903606414795</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -413,52 +413,52 @@
     <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002083778381</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
     <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575995445251</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010631561279</t>
+    <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059906005859</t>
+    <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.66109156608582</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929249763489</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027774810791</t>
+    <t xml:space="preserve">3.26027798652649</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3520188331604</t>
+    <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674757957458</t>
+    <t xml:space="preserve">3.65674734115601</t>
   </si>
   <si>
     <t xml:space="preserve">3.60297203063965</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.92562651634216</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.39168262481689</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.5709342956543</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574792861938</t>
+    <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056060791016</t>
+    <t xml:space="preserve">4.66056108474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035526275635</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525259017944</t>
+    <t xml:space="preserve">4.01525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732685089111</t>
   </si>
   <si>
     <t xml:space="preserve">3.97940158843994</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824280738831</t>
+    <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579438209534</t>
+    <t xml:space="preserve">3.40579414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334595680237</t>
+    <t xml:space="preserve">3.51334619522095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -1184,9 +1184,6 @@
     <t xml:space="preserve">2.20000004768372</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">2.05999994277954</t>
   </si>
 </sst>
@@ -45766,37 +45763,13 @@
       <c r="E1702" t="n">
         <v>2.03999996185303</v>
       </c>
-      <c r="F1702"/>
+      <c r="F1702" t="n">
+        <v>2.05999994277954</v>
+      </c>
       <c r="G1702" t="s">
         <v>390</v>
       </c>
       <c r="H1702" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="1703">
-      <c r="A1703" s="1" t="n">
-        <v>46106.6672337963</v>
-      </c>
-      <c r="B1703" t="n">
-        <v>6750</v>
-      </c>
-      <c r="C1703" t="n">
-        <v>2.07999992370605</v>
-      </c>
-      <c r="D1703" t="n">
-        <v>2.03999996185303</v>
-      </c>
-      <c r="E1703" t="n">
-        <v>2.03999996185303</v>
-      </c>
-      <c r="F1703" t="n">
-        <v>2.05999994277954</v>
-      </c>
-      <c r="G1703" t="s">
-        <v>391</v>
-      </c>
-      <c r="H1703" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775918960571</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526256561279</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214134216309</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
@@ -77,31 +77,31 @@
     <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834552764893</t>
+    <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539842605591</t>
+    <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.16481113433838</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275148391724</t>
@@ -110,25 +110,25 @@
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613508224487</t>
+    <t xml:space="preserve">4.15613555908203</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216562271118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451049804688</t>
+    <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9305408000946</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
@@ -137,46 +137,46 @@
     <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628587722778</t>
+    <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936883926392</t>
+    <t xml:space="preserve">4.06936740875244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127721786499</t>
+    <t xml:space="preserve">3.99127793312073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921732902527</t>
+    <t xml:space="preserve">3.93921756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789481163025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509731292725</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
     <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494675636292</t>
+    <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
     <t xml:space="preserve">3.60082697868347</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392439842224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524715423584</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583373069763</t>
+    <t xml:space="preserve">3.89583420753479</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333782196045</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258623123169</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345850944519</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596935272217</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302248954773</t>
+    <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
@@ -266,16 +266,13 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4541323184967</t>
+    <t xml:space="preserve">3.45413208007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363981246948</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40126252174377</t>
   </si>
   <si>
     <t xml:space="preserve">3.43650913238525</t>
@@ -299,19 +296,19 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216205596924</t>
+    <t xml:space="preserve">3.17216229438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
     <t xml:space="preserve">3.0664234161377</t>
@@ -320,13 +317,13 @@
     <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404636383057</t>
+    <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068429946899</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355409622192</t>
+    <t xml:space="preserve">3.0135543346405</t>
   </si>
   <si>
     <t xml:space="preserve">2.9783079624176</t>
@@ -338,16 +335,16 @@
     <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9430615901947</t>
+    <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207681655884</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
@@ -356,46 +353,46 @@
     <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912130355835</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387540817261</t>
+    <t xml:space="preserve">2.34387564659119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625222206116</t>
+    <t xml:space="preserve">2.32625246047974</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289039611816</t>
+    <t xml:space="preserve">2.20289015769958</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477494239807</t>
+    <t xml:space="preserve">2.11477470397949</t>
   </si>
   <si>
     <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903606414795</t>
+    <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854331970215</t>
+    <t xml:space="preserve">1.93854379653931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -404,31 +401,31 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518161296844</t>
+    <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042774677277</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002107620239</t>
+    <t xml:space="preserve">2.15002131462097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428243637085</t>
+    <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
     <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158407211304</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
@@ -437,10 +434,10 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010655403137</t>
+    <t xml:space="preserve">2.52010679244995</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
@@ -449,7 +446,7 @@
     <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
@@ -458,37 +455,37 @@
     <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059906005859</t>
+    <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633793830872</t>
+    <t xml:space="preserve">2.69633769989014</t>
   </si>
   <si>
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929249763489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740818977356</t>
+    <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027774810791</t>
+    <t xml:space="preserve">3.26027798652649</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,10 +494,13 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239252090454</t>
+    <t xml:space="preserve">3.26239275932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297226905823</t>
+    <t xml:space="preserve">3.60297179222107</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168262481689</t>
+    <t xml:space="preserve">4.39168214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545841217041</t>
+    <t xml:space="preserve">4.44545793533325</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -599,16 +599,16 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280368804932</t>
+    <t xml:space="preserve">4.12280416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620578765869</t>
+    <t xml:space="preserve">4.26620626449585</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -7102,7 +7102,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -7128,7 +7128,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -7154,7 +7154,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -7180,7 +7180,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -7206,7 +7206,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -7232,7 +7232,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7258,7 +7258,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -7284,7 +7284,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -7310,7 +7310,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G223" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -7336,7 +7336,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -7362,7 +7362,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -7388,7 +7388,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -7414,7 +7414,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -7440,7 +7440,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -7466,7 +7466,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7492,7 +7492,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -7518,7 +7518,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -7544,7 +7544,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -7570,7 +7570,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7596,7 +7596,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -7622,7 +7622,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7648,7 +7648,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -7674,7 +7674,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -7700,7 +7700,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -7726,7 +7726,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -7752,7 +7752,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -7778,7 +7778,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -7804,7 +7804,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -7830,7 +7830,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -7856,7 +7856,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -7882,7 +7882,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -7908,7 +7908,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -7960,7 +7960,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -7986,7 +7986,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8012,7 +8012,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8038,7 +8038,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8064,7 +8064,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G252" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -8116,7 +8116,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -8142,7 +8142,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -8168,7 +8168,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -8194,7 +8194,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -8220,7 +8220,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G258" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -8246,7 +8246,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -8272,7 +8272,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -8298,7 +8298,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -8324,7 +8324,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8350,7 +8350,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -8376,7 +8376,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8402,7 +8402,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -8428,7 +8428,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -8454,7 +8454,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8480,7 +8480,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8506,7 +8506,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -8532,7 +8532,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8558,7 +8558,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8584,7 +8584,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8610,7 +8610,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8636,7 +8636,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8662,7 +8662,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -8688,7 +8688,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -8714,7 +8714,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8740,7 +8740,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -8766,7 +8766,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8792,7 +8792,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8818,7 +8818,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -8844,7 +8844,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -8870,7 +8870,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -8896,7 +8896,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -8922,7 +8922,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -8948,7 +8948,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -8974,7 +8974,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -9000,7 +9000,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -9026,7 +9026,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -9052,7 +9052,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -9078,7 +9078,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -9104,7 +9104,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9130,7 +9130,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -9156,7 +9156,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9182,7 +9182,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -9208,7 +9208,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -9234,7 +9234,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -9260,7 +9260,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9286,7 +9286,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -9312,7 +9312,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -9338,7 +9338,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9364,7 +9364,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -9390,7 +9390,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -9416,7 +9416,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -9442,7 +9442,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9468,7 +9468,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -9494,7 +9494,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9520,7 +9520,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9546,7 +9546,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -9572,7 +9572,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9598,7 +9598,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -9624,7 +9624,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -9650,7 +9650,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -9676,7 +9676,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G314" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -9702,7 +9702,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G315" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -9728,7 +9728,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G316" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -9754,7 +9754,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9780,7 +9780,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -9806,7 +9806,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -9832,7 +9832,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -9858,7 +9858,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -9884,7 +9884,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -9910,7 +9910,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G323" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -9936,7 +9936,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -9962,7 +9962,7 @@
         <v>2.5</v>
       </c>
       <c r="G325" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9988,7 +9988,7 @@
         <v>2.5</v>
       </c>
       <c r="G326" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -10014,7 +10014,7 @@
         <v>2.5</v>
       </c>
       <c r="G327" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -10040,7 +10040,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -10066,7 +10066,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -10092,7 +10092,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -10118,7 +10118,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -10144,7 +10144,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -10170,7 +10170,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -10196,7 +10196,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -10222,7 +10222,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10248,7 +10248,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -10274,7 +10274,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10300,7 +10300,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10326,7 +10326,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -10352,7 +10352,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10378,7 +10378,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10404,7 +10404,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -10430,7 +10430,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10456,7 +10456,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10482,7 +10482,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10508,7 +10508,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G346" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10534,7 +10534,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10560,7 +10560,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G348" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10586,7 +10586,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10612,7 +10612,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G350" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10638,7 +10638,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10664,7 +10664,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -10690,7 +10690,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -10716,7 +10716,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -10742,7 +10742,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10768,7 +10768,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -10794,7 +10794,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10820,7 +10820,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -10846,7 +10846,7 @@
         <v>2.5</v>
       </c>
       <c r="G359" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10872,7 +10872,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -10898,7 +10898,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -10924,7 +10924,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -10950,7 +10950,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10976,7 +10976,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -11002,7 +11002,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11028,7 +11028,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11054,7 +11054,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11080,7 +11080,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11106,7 +11106,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G369" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11132,7 +11132,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11158,7 +11158,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11184,7 +11184,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11210,7 +11210,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11236,7 +11236,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G374" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11262,7 +11262,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11288,7 +11288,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11314,7 +11314,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11340,7 +11340,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11366,7 +11366,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G379" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11392,7 +11392,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G380" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11418,7 +11418,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G381" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11444,7 +11444,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G382" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11470,7 +11470,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G383" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11496,7 +11496,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11522,7 +11522,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G385" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11548,7 +11548,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11574,7 +11574,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G387" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11600,7 +11600,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G388" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11626,7 +11626,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G389" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11652,7 +11652,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G390" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11678,7 +11678,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11704,7 +11704,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11730,7 +11730,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G393" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11756,7 +11756,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11782,7 +11782,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G395" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -11808,7 +11808,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -11834,7 +11834,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -11860,7 +11860,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -11886,7 +11886,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -11912,7 +11912,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -11938,7 +11938,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -11964,7 +11964,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -11990,7 +11990,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12016,7 +12016,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12042,7 +12042,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12068,7 +12068,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12094,7 +12094,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12120,7 +12120,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12146,7 +12146,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12172,7 +12172,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12198,7 +12198,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12224,7 +12224,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G412" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12250,7 +12250,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G413" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12276,7 +12276,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G414" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12302,7 +12302,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G415" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12328,7 +12328,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G416" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12354,7 +12354,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12380,7 +12380,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12406,7 +12406,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G419" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12432,7 +12432,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G420" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12458,7 +12458,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12484,7 +12484,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12510,7 +12510,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12536,7 +12536,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12562,7 +12562,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12588,7 +12588,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12614,7 +12614,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12640,7 +12640,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12666,7 +12666,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12692,7 +12692,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G430" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12718,7 +12718,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G431" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12744,7 +12744,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12770,7 +12770,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -12796,7 +12796,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -12822,7 +12822,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -12848,7 +12848,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -12874,7 +12874,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -12900,7 +12900,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -12926,7 +12926,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -12952,7 +12952,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -12978,7 +12978,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -13004,7 +13004,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13030,7 +13030,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13056,7 +13056,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13082,7 +13082,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13134,7 +13134,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13160,7 +13160,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13186,7 +13186,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13212,7 +13212,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13238,7 +13238,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13264,7 +13264,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13290,7 +13290,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13316,7 +13316,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13342,7 +13342,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13368,7 +13368,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13394,7 +13394,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G457" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13420,7 +13420,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13446,7 +13446,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13472,7 +13472,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G460" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13498,7 +13498,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13524,7 +13524,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G462" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13550,7 +13550,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13576,7 +13576,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G464" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13602,7 +13602,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G465" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13628,7 +13628,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13654,7 +13654,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G467" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13680,7 +13680,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G468" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -45819,6 +45819,32 @@
         <v>385</v>
       </c>
       <c r="H1704" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="1" t="n">
+        <v>46111.2916666667</v>
+      </c>
+      <c r="B1705" t="n">
+        <v>21500</v>
+      </c>
+      <c r="C1705" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D1705" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E1705" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F1705" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G1705" t="s">
+        <v>383</v>
+      </c>
+      <c r="H1705" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415710449219</t>
+    <t xml:space="preserve">4.46415758132935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526256561279</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39213991165161</t>
   </si>
   <si>
     <t xml:space="preserve">4.3730525970459</t>
@@ -68,67 +68,67 @@
     <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
     <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539747238159</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23422527313232</t>
+    <t xml:space="preserve">4.23422574996948</t>
   </si>
   <si>
     <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275196075439</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290180206299</t>
+    <t xml:space="preserve">4.24290132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613555908203</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216562271118</t>
+    <t xml:space="preserve">4.18216466903687</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451073646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054056167603</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
@@ -143,55 +143,55 @@
     <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995422363281</t>
+    <t xml:space="preserve">3.99995470046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127817153931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921756744385</t>
+    <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789481163025</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.8350977897644</t>
   </si>
   <si>
     <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
     <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494723320007</t>
+    <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759322166443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657062530518</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392439842224</t>
+    <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524834632874</t>
+    <t xml:space="preserve">3.96524786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583373069763</t>
+    <t xml:space="preserve">3.89583420753479</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333734512329</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258599281311</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684186935425</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345850944519</t>
+    <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
     <t xml:space="preserve">3.21037554740906</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596935272217</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390946388245</t>
+    <t xml:space="preserve">3.38390922546387</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126299858093</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274003982544</t>
+    <t xml:space="preserve">3.61274027824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077025413513</t>
+    <t xml:space="preserve">3.33077049255371</t>
   </si>
   <si>
     <t xml:space="preserve">3.34839344024658</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216229438782</t>
+    <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552388191223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
     <t xml:space="preserve">3.1016697883606</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593091011047</t>
+    <t xml:space="preserve">2.99593114852905</t>
   </si>
   <si>
     <t xml:space="preserve">3.08404660224915</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355409622192</t>
+    <t xml:space="preserve">3.01355385780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783079624176</t>
+    <t xml:space="preserve">2.97830820083618</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
     <t xml:space="preserve">2.80207681655884</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912130355835</t>
+    <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100584983826</t>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">2.34387564659119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625222206116</t>
+    <t xml:space="preserve">2.32625246047974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22051382064819</t>
+    <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
@@ -383,31 +383,31 @@
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239812850952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616662502289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854379653931</t>
+    <t xml:space="preserve">1.93854343891144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805105209351</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952833175659</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575947761536</t>
+    <t xml:space="preserve">2.25575971603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822200775146</t>
+    <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
     <t xml:space="preserve">2.5024836063385</t>
@@ -449,13 +449,13 @@
     <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059929847717</t>
@@ -470,25 +470,25 @@
     <t xml:space="preserve">2.69633769989014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740842819214</t>
+    <t xml:space="preserve">3.20740866661072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027774810791</t>
+    <t xml:space="preserve">3.26027750968933</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369161605835</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616830825806</t>
+    <t xml:space="preserve">3.31616806983948</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297179222107</t>
+    <t xml:space="preserve">3.60297203063965</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48130798339844</t>
+    <t xml:space="preserve">4.4813084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537424087524</t>
+    <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.39168214797974</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753267288208</t>
+    <t xml:space="preserve">4.42753314971924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790636062622</t>
+    <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413105010986</t>
+    <t xml:space="preserve">4.28413057327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998157501221</t>
+    <t xml:space="preserve">4.31998205184937</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280416488647</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317785263062</t>
+    <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902837753296</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147680282593</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775918960571</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526304244995</t>
+    <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
     <t xml:space="preserve">4.51187944412231</t>
@@ -71,31 +71,31 @@
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216872215271</t>
+    <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702205657959</t>
+    <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539747238159</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745807647705</t>
+    <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -107,109 +107,109 @@
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216514587402</t>
+    <t xml:space="preserve">4.18216562271118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819473266602</t>
+    <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
     <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142848968506</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0693678855896</t>
+    <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921756744385</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171347618103</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509731292725</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
     <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627022743225</t>
+    <t xml:space="preserve">3.69627046585083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72229981422424</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421033859253</t>
+    <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
     <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568388938904</t>
+    <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392439842224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672142028809</t>
+    <t xml:space="preserve">4.08672189712524</t>
   </si>
   <si>
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.0259838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524810791016</t>
+    <t xml:space="preserve">3.96524739265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
     <t xml:space="preserve">4.04333734512329</t>
@@ -218,31 +218,31 @@
     <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273654937744</t>
+    <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258646965027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714250564575</t>
+    <t xml:space="preserve">3.29714274406433</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596935272217</t>
@@ -254,22 +254,22 @@
     <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978897094727</t>
+    <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
     <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390922546387</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126323699951</t>
+    <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45413255691528</t>
+    <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363981246948</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650889396667</t>
+    <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077001571655</t>
+    <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34839344024658</t>
+    <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.17216229438782</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -326,34 +326,34 @@
     <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355409622192</t>
+    <t xml:space="preserve">3.0135543346405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783079624176</t>
+    <t xml:space="preserve">2.97830772399902</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94306135177612</t>
+    <t xml:space="preserve">2.9430615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207681655884</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912154197693</t>
@@ -377,28 +377,28 @@
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477494239807</t>
+    <t xml:space="preserve">2.11477470397949</t>
   </si>
   <si>
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903606414795</t>
+    <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854379653931</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002107620239</t>
+    <t xml:space="preserve">2.15002131462097</t>
   </si>
   <si>
     <t xml:space="preserve">2.04428219795227</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53772974014282</t>
+    <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158407211304</t>
+    <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822200775146</t>
+    <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248312950134</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
     <t xml:space="preserve">2.44961428642273</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109132766724</t>
+    <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
     <t xml:space="preserve">2.78445363044739</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929249763489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740842819214</t>
+    <t xml:space="preserve">3.20740818977356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027774810791</t>
+    <t xml:space="preserve">3.26027798652649</t>
   </si>
   <si>
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239275932312</t>
+    <t xml:space="preserve">3.26239252090454</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
     <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31616806983948</t>
+    <t xml:space="preserve">3.31616830825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.58504676818848</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674757957458</t>
+    <t xml:space="preserve">3.65674734115601</t>
   </si>
   <si>
     <t xml:space="preserve">3.60297203063965</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.925626039505</t>
+    <t xml:space="preserve">3.92562651634216</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168214797974</t>
+    <t xml:space="preserve">4.39168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21242952346802</t>
+    <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19450426101685</t>
+    <t xml:space="preserve">4.194504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657899856567</t>
+    <t xml:space="preserve">4.17657947540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.08695316314697</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57093477249146</t>
+    <t xml:space="preserve">4.5709342956543</t>
   </si>
   <si>
     <t xml:space="preserve">4.52612161636353</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42753314971924</t>
+    <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28413057327271</t>
+    <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998205184937</t>
+    <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056060791016</t>
+    <t xml:space="preserve">4.66056108474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035478591919</t>
+    <t xml:space="preserve">4.23035526275635</t>
   </si>
   <si>
     <t xml:space="preserve">4.12280368804932</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902837753296</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525259017944</t>
+    <t xml:space="preserve">4.01525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732732772827</t>
+    <t xml:space="preserve">3.99732685089111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940182685852</t>
+    <t xml:space="preserve">3.97940158843994</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355130195618</t>
+    <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
     <t xml:space="preserve">3.90770125389099</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579438209534</t>
+    <t xml:space="preserve">3.40579414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334595680237</t>
+    <t xml:space="preserve">3.51334619522095</t>
   </si>
   <si>
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
     <t xml:space="preserve">4.34686946868896</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398017883301</t>
+    <t xml:space="preserve">4.23398065567017</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273334503174</t>
+    <t xml:space="preserve">4.13273286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443187713623</t>
+    <t xml:space="preserve">4.34443235397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25238943099976</t>
+    <t xml:space="preserve">4.2523889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830310821533</t>
+    <t xml:space="preserve">4.06830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -713,25 +713,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193773269653</t>
+    <t xml:space="preserve">4.14193725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989433288574</t>
+    <t xml:space="preserve">4.0498948097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04068994522095</t>
+    <t xml:space="preserve">4.04069042205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466848373413</t>
+    <t xml:space="preserve">3.99466896057129</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546409606934</t>
+    <t xml:space="preserve">3.98546433448792</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96705555915833</t>
+    <t xml:space="preserve">3.9670557975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93023824691772</t>
+    <t xml:space="preserve">3.9302384853363</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376532554626</t>
+    <t xml:space="preserve">3.77376508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739947319031</t>
+    <t xml:space="preserve">3.84739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421702384949</t>
+    <t xml:space="preserve">3.88421678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671188354492</t>
+    <t xml:space="preserve">4.08671140670776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86580801010132</t>
+    <t xml:space="preserve">3.8658082485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694801330566</t>
+    <t xml:space="preserve">3.73694825172424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615263938904</t>
+    <t xml:space="preserve">3.74615240097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89342141151428</t>
+    <t xml:space="preserve">3.8934211730957</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501287460327</t>
+    <t xml:space="preserve">3.87501263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864726066589</t>
+    <t xml:space="preserve">3.94864702224731</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716358184814</t>
+    <t xml:space="preserve">4.19716310501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795967102051</t>
+    <t xml:space="preserve">4.18795919418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -45934,7 +45934,7 @@
     </row>
     <row r="1709">
       <c r="A1709" s="1" t="n">
-        <v>46119.4081018518</v>
+        <v>46119.2916666667</v>
       </c>
       <c r="B1709" t="n">
         <v>2750</v>
@@ -45955,6 +45955,32 @@
         <v>391</v>
       </c>
       <c r="H1709" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="1" t="n">
+        <v>46120.2916666667</v>
+      </c>
+      <c r="B1710" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1710" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D1710" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="E1710" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="F1710" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G1710" t="s">
+        <v>389</v>
+      </c>
+      <c r="H1710" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -47,55 +47,55 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526304244995</t>
+    <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
     <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39214134216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999391555786</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
     <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702253341675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539842605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
@@ -113,52 +113,52 @@
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216514587402</t>
+    <t xml:space="preserve">4.18216562271118</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451121330261</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730823516846</t>
+    <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
     <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28628540039062</t>
+    <t xml:space="preserve">4.28628587722778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936836242676</t>
+    <t xml:space="preserve">4.06936883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995398521423</t>
+    <t xml:space="preserve">3.99995446205139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127745628357</t>
+    <t xml:space="preserve">3.99127721786499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921685218811</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789505004883</t>
+    <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171347618103</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
     <t xml:space="preserve">3.77436017990112</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72230076789856</t>
+    <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420962333679</t>
+    <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
     <t xml:space="preserve">3.68759369850159</t>
@@ -182,61 +182,61 @@
     <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568388938904</t>
+    <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657110214233</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201482772827</t>
+    <t xml:space="preserve">4.05201435089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186450958252</t>
+    <t xml:space="preserve">3.92186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.96524715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833011627197</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273631095886</t>
+    <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684163093567</t>
+    <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
     <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978944778442</t>
+    <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302225112915</t>
+    <t xml:space="preserve">3.19302248954773</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854343891144</t>
+    <t xml:space="preserve">1.93854331970215</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059906005859</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297226905823</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072942733765</t>
+    <t xml:space="preserve">4.14072895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">4.24828004837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21243000030518</t>
+    <t xml:space="preserve">4.21242952346802</t>
   </si>
   <si>
     <t xml:space="preserve">4.19450426101685</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695363998413</t>
+    <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612209320068</t>
+    <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
     <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44545793533325</t>
+    <t xml:space="preserve">4.44545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">4.35583209991455</t>
@@ -605,25 +605,25 @@
     <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280321121216</t>
+    <t xml:space="preserve">4.12280368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620626449585</t>
+    <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06902742385864</t>
+    <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9794020652771</t>
+    <t xml:space="preserve">3.97940182685852</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147656440735</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -46007,6 +46007,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1712">
+      <c r="A1712" s="1" t="n">
+        <v>46122.2916666667</v>
+      </c>
+      <c r="B1712" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1712" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1712" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E1712" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1712" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1712" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1712" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849536895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775918960571</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526256561279</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187944412231</t>
+    <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214038848877</t>
+    <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3296685218811</t>
+    <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
     <t xml:space="preserve">4.216872215271</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010501861572</t>
+    <t xml:space="preserve">4.13010549545288</t>
   </si>
   <si>
     <t xml:space="preserve">4.2255482673645</t>
@@ -104,37 +104,37 @@
     <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
     <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216562271118</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451049804688</t>
+    <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054127693176</t>
+    <t xml:space="preserve">3.9305408000946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01730728149414</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142848968506</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -143,76 +143,76 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995422363281</t>
+    <t xml:space="preserve">3.99995493888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127769470215</t>
+    <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
     <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789433479309</t>
+    <t xml:space="preserve">3.94789481163025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171371459961</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509755134583</t>
+    <t xml:space="preserve">3.83509731292725</t>
   </si>
   <si>
     <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
     <t xml:space="preserve">3.7223002910614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70494699478149</t>
+    <t xml:space="preserve">3.70494675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421010017395</t>
+    <t xml:space="preserve">3.64420986175537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082650184631</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
     <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657086372375</t>
+    <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672189712524</t>
+    <t xml:space="preserve">4.08672094345093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201482772827</t>
+    <t xml:space="preserve">4.05201530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0259838104248</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.96524810791016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583373069763</t>
+    <t xml:space="preserve">3.89583468437195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
     <t xml:space="preserve">3.74833035469055</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670672416687</t>
+    <t xml:space="preserve">3.49670648574829</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258623123169</t>
@@ -230,25 +230,25 @@
     <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375890731812</t>
+    <t xml:space="preserve">3.25375914573669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345850944519</t>
+    <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
     <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052586555481</t>
+    <t xml:space="preserve">3.34052610397339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714250564575</t>
+    <t xml:space="preserve">3.29714226722717</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41861629486084</t>
+    <t xml:space="preserve">3.41861605644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.50538325309753</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390970230103</t>
+    <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126276016235</t>
+    <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45413255691528</t>
+    <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
     <t xml:space="preserve">3.3836395740509</t>
@@ -275,19 +275,22 @@
     <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
+    <t xml:space="preserve">3.40126252174377</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.43650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47175526618958</t>
+    <t xml:space="preserve">3.471755027771</t>
   </si>
   <si>
     <t xml:space="preserve">3.61274027824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077049255371</t>
+    <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
     <t xml:space="preserve">3.348393201828</t>
@@ -308,31 +311,31 @@
     <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593114852905</t>
+    <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404684066772</t>
+    <t xml:space="preserve">3.08404636383057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97830772399902</t>
+    <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81969976425171</t>
+    <t xml:space="preserve">2.81970000267029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
     <t xml:space="preserve">2.9430615901947</t>
@@ -341,22 +344,22 @@
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346837997437</t>
+    <t xml:space="preserve">2.64346861839294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584543228149</t>
+    <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100608825684</t>
+    <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
     <t xml:space="preserve">2.34387540817261</t>
@@ -368,7 +371,7 @@
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
@@ -377,7 +380,7 @@
     <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09715175628662</t>
+    <t xml:space="preserve">2.0971519947052</t>
   </si>
   <si>
     <t xml:space="preserve">2.13239789009094</t>
@@ -386,34 +389,34 @@
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9561665058136</t>
+    <t xml:space="preserve">1.95616674423218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854343891144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805093288422</t>
+    <t xml:space="preserve">1.86805081367493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83280467987061</t>
+    <t xml:space="preserve">1.8328047990799</t>
   </si>
   <si>
     <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042774677277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04428219795227</t>
+    <t xml:space="preserve">2.04428243637085</t>
   </si>
   <si>
     <t xml:space="preserve">2.25575971603394</t>
@@ -422,7 +425,7 @@
     <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
     <t xml:space="preserve">2.73158383369446</t>
@@ -431,22 +434,22 @@
     <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822224617004</t>
+    <t xml:space="preserve">2.60822248458862</t>
   </si>
   <si>
     <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010631561279</t>
+    <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4319908618927</t>
+    <t xml:space="preserve">2.43199110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961428642273</t>
+    <t xml:space="preserve">2.44961404800415</t>
   </si>
   <si>
     <t xml:space="preserve">2.41436791419983</t>
@@ -461,16 +464,16 @@
     <t xml:space="preserve">2.66109156608582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445363044739</t>
+    <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
     <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929297447205</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
@@ -500,9 +503,6 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369161605835</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674734115601</t>
+    <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
     <t xml:space="preserve">3.60297203063965</t>
@@ -524,19 +524,19 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562651634216</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14072895050049</t>
+    <t xml:space="preserve">4.14072942733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48130798339844</t>
+    <t xml:space="preserve">4.4813084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537424087524</t>
+    <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.39168262481689</t>
@@ -551,25 +551,25 @@
     <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17657947540283</t>
+    <t xml:space="preserve">4.17657899856567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08695316314697</t>
+    <t xml:space="preserve">4.08695363998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5709342956543</t>
+    <t xml:space="preserve">4.57093477249146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52612161636353</t>
+    <t xml:space="preserve">4.52612209320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
     <t xml:space="preserve">4.61574745178223</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790636062622</t>
+    <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056108474731</t>
+    <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -599,40 +599,40 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280368804932</t>
+    <t xml:space="preserve">4.12280321121216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620578765869</t>
+    <t xml:space="preserve">4.26620626449585</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0690279006958</t>
+    <t xml:space="preserve">4.06902742385864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525211334229</t>
+    <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732685089111</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97940158843994</t>
+    <t xml:space="preserve">3.9794020652771</t>
   </si>
   <si>
     <t xml:space="preserve">3.85392546653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
@@ -641,19 +641,19 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579414367676</t>
+    <t xml:space="preserve">3.40579438209534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334619522095</t>
+    <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
     <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147680282593</t>
+    <t xml:space="preserve">3.96147656440735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">4.10512018203735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23398065567017</t>
+    <t xml:space="preserve">4.23398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">4.22477626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273286819458</t>
+    <t xml:space="preserve">4.13273334503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.20636796951294</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21557188034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34443235397339</t>
+    <t xml:space="preserve">4.34443187713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.37204504013062</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">4.27079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2523889541626</t>
+    <t xml:space="preserve">4.25238943099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.11432409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06830358505249</t>
+    <t xml:space="preserve">4.06830310821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.15114212036133</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.03148603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14193725585938</t>
+    <t xml:space="preserve">4.14193773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0498948097229</t>
+    <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04069042205811</t>
+    <t xml:space="preserve">4.04068994522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.00387287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99466896057129</t>
+    <t xml:space="preserve">3.99466848373413</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98546433448792</t>
+    <t xml:space="preserve">3.98546409606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.09591579437256</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">3.95785164833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9670557975769</t>
+    <t xml:space="preserve">3.96705555915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.93944311141968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9302384853363</t>
+    <t xml:space="preserve">3.93023824691772</t>
   </si>
   <si>
     <t xml:space="preserve">3.91182994842529</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">3.81978702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77376508712769</t>
+    <t xml:space="preserve">3.77376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84739971160889</t>
+    <t xml:space="preserve">3.84739947319031</t>
   </si>
   <si>
     <t xml:space="preserve">3.75535655021667</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">3.78296971321106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88421678543091</t>
+    <t xml:space="preserve">3.88421702384949</t>
   </si>
   <si>
     <t xml:space="preserve">4.07750749588013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08671140670776</t>
+    <t xml:space="preserve">4.08671188354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8658082485199</t>
+    <t xml:space="preserve">3.86580801010132</t>
   </si>
   <si>
     <t xml:space="preserve">3.79217386245728</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">3.76456117630005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73694825172424</t>
+    <t xml:space="preserve">3.73694801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74615240097046</t>
+    <t xml:space="preserve">3.74615263938904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8934211730957</t>
+    <t xml:space="preserve">3.89342141151428</t>
   </si>
   <si>
     <t xml:space="preserve">3.90262532234192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87501263618469</t>
+    <t xml:space="preserve">3.87501287460327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94864702224731</t>
+    <t xml:space="preserve">3.94864726066589</t>
   </si>
   <si>
     <t xml:space="preserve">4.12352895736694</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.05909872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19716310501099</t>
+    <t xml:space="preserve">4.19716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18795919418335</t>
+    <t xml:space="preserve">4.18795967102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.20543718338013</t>
@@ -7105,7 +7105,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -7131,7 +7131,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -7157,7 +7157,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -7183,7 +7183,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -7209,7 +7209,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -7235,7 +7235,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7261,7 +7261,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -7287,7 +7287,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -7313,7 +7313,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G223" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -7339,7 +7339,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -7365,7 +7365,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -7391,7 +7391,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -7417,7 +7417,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -7443,7 +7443,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -7469,7 +7469,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7495,7 +7495,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -7521,7 +7521,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -7547,7 +7547,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -7573,7 +7573,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7599,7 +7599,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -7625,7 +7625,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7651,7 +7651,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -7677,7 +7677,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -7703,7 +7703,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -7729,7 +7729,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -7755,7 +7755,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -7781,7 +7781,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -7807,7 +7807,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -7833,7 +7833,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -7859,7 +7859,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -7885,7 +7885,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -7911,7 +7911,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -7963,7 +7963,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -7989,7 +7989,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8015,7 +8015,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8041,7 +8041,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8067,7 +8067,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G252" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -8119,7 +8119,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -8145,7 +8145,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -8171,7 +8171,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -8197,7 +8197,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -8223,7 +8223,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G258" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -8249,7 +8249,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -8275,7 +8275,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -8301,7 +8301,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -8327,7 +8327,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8353,7 +8353,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -8379,7 +8379,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8405,7 +8405,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -8431,7 +8431,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -8457,7 +8457,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8483,7 +8483,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8509,7 +8509,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -8535,7 +8535,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8561,7 +8561,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8587,7 +8587,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8613,7 +8613,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8639,7 +8639,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8665,7 +8665,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -8691,7 +8691,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -8717,7 +8717,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8743,7 +8743,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -8769,7 +8769,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8795,7 +8795,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8821,7 +8821,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -8847,7 +8847,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -8873,7 +8873,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -8899,7 +8899,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -8925,7 +8925,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -8951,7 +8951,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -8977,7 +8977,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -9003,7 +9003,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -9029,7 +9029,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -9055,7 +9055,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -9081,7 +9081,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -9107,7 +9107,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9133,7 +9133,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -9159,7 +9159,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9185,7 +9185,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -9211,7 +9211,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -9237,7 +9237,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -9263,7 +9263,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9289,7 +9289,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -9315,7 +9315,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -9341,7 +9341,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9367,7 +9367,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -9393,7 +9393,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -9419,7 +9419,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -9445,7 +9445,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9471,7 +9471,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -9497,7 +9497,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9523,7 +9523,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9549,7 +9549,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -9575,7 +9575,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9601,7 +9601,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -9627,7 +9627,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -9653,7 +9653,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -9679,7 +9679,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G314" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -9705,7 +9705,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G315" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -9731,7 +9731,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G316" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -9757,7 +9757,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9783,7 +9783,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -9809,7 +9809,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -9835,7 +9835,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -9861,7 +9861,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -9887,7 +9887,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -9913,7 +9913,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G323" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -9939,7 +9939,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -9965,7 +9965,7 @@
         <v>2.5</v>
       </c>
       <c r="G325" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9991,7 +9991,7 @@
         <v>2.5</v>
       </c>
       <c r="G326" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -10017,7 +10017,7 @@
         <v>2.5</v>
       </c>
       <c r="G327" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -10043,7 +10043,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -10069,7 +10069,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -10095,7 +10095,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -10121,7 +10121,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -10147,7 +10147,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -10173,7 +10173,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -10199,7 +10199,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -10225,7 +10225,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10251,7 +10251,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -10277,7 +10277,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10303,7 +10303,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10329,7 +10329,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -10355,7 +10355,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10381,7 +10381,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10407,7 +10407,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -10433,7 +10433,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10459,7 +10459,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10485,7 +10485,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10511,7 +10511,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G346" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10537,7 +10537,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10563,7 +10563,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G348" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10589,7 +10589,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10615,7 +10615,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G350" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10641,7 +10641,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10667,7 +10667,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -10693,7 +10693,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -10719,7 +10719,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -10745,7 +10745,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10771,7 +10771,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -10797,7 +10797,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10823,7 +10823,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -10849,7 +10849,7 @@
         <v>2.5</v>
       </c>
       <c r="G359" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10875,7 +10875,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -10901,7 +10901,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -10927,7 +10927,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -10953,7 +10953,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10979,7 +10979,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -11005,7 +11005,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11031,7 +11031,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11057,7 +11057,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11083,7 +11083,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11109,7 +11109,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G369" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11135,7 +11135,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11161,7 +11161,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11187,7 +11187,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11213,7 +11213,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11239,7 +11239,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G374" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11265,7 +11265,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11291,7 +11291,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11317,7 +11317,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11343,7 +11343,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11369,7 +11369,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G379" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11395,7 +11395,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G380" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11421,7 +11421,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G381" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11447,7 +11447,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G382" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11473,7 +11473,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G383" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11499,7 +11499,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11525,7 +11525,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G385" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11551,7 +11551,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11577,7 +11577,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G387" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11603,7 +11603,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G388" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11629,7 +11629,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G389" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11655,7 +11655,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G390" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11681,7 +11681,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11707,7 +11707,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11733,7 +11733,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G393" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11759,7 +11759,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11785,7 +11785,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G395" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -11811,7 +11811,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -11837,7 +11837,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -11863,7 +11863,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -11889,7 +11889,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -11915,7 +11915,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -11941,7 +11941,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -11967,7 +11967,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -11993,7 +11993,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12019,7 +12019,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12045,7 +12045,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12071,7 +12071,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12097,7 +12097,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12123,7 +12123,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12149,7 +12149,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12175,7 +12175,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12201,7 +12201,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12227,7 +12227,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G412" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12253,7 +12253,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G413" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12279,7 +12279,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G414" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12305,7 +12305,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G415" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12331,7 +12331,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G416" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12357,7 +12357,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12383,7 +12383,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12409,7 +12409,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G419" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12435,7 +12435,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G420" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12461,7 +12461,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12487,7 +12487,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12513,7 +12513,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12539,7 +12539,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12565,7 +12565,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12591,7 +12591,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12617,7 +12617,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12643,7 +12643,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12669,7 +12669,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12695,7 +12695,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G430" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12721,7 +12721,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G431" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12747,7 +12747,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12773,7 +12773,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -12799,7 +12799,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -12825,7 +12825,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -12851,7 +12851,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -12877,7 +12877,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -12903,7 +12903,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -12929,7 +12929,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -12955,7 +12955,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -12981,7 +12981,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -13007,7 +13007,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13033,7 +13033,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13059,7 +13059,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13085,7 +13085,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13137,7 +13137,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13163,7 +13163,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13189,7 +13189,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13215,7 +13215,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13241,7 +13241,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13267,7 +13267,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13293,7 +13293,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13319,7 +13319,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13345,7 +13345,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13371,7 +13371,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13397,7 +13397,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G457" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13423,7 +13423,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13449,7 +13449,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13475,7 +13475,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G460" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13501,7 +13501,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13527,7 +13527,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G462" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13553,7 +13553,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13579,7 +13579,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G464" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13605,7 +13605,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G465" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13631,7 +13631,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13657,7 +13657,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G467" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13683,7 +13683,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G468" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -46082,6 +46082,32 @@
         <v>368</v>
       </c>
       <c r="H1714" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="1" t="n">
+        <v>46127.2916666667</v>
+      </c>
+      <c r="B1715" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C1715" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1715" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1715" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1715" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G1715" t="s">
+        <v>388</v>
+      </c>
+      <c r="H1715" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526351928711</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
     <t xml:space="preserve">4.51187896728516</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">4.39214086532593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
     <t xml:space="preserve">4.37999391555786</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702157974243</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
     <t xml:space="preserve">4.09539794921875</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745903015137</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
@@ -101,22 +101,22 @@
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613412857056</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819520950317</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -143,25 +143,25 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995398521423</t>
   </si>
   <si>
     <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789457321167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171419143677</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436065673828</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627046585083</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657110214233</t>
@@ -200,10 +200,10 @@
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598524093628</t>
+    <t xml:space="preserve">4.02598476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.9218635559082</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524786949158</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">3.89583396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833083152771</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273631095886</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684186935425</t>
+    <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
     <t xml:space="preserve">3.25375914573669</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714226722717</t>
+    <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596935272217</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">3.27978944778442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302225112915</t>
+    <t xml:space="preserve">3.19302248954773</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
@@ -46140,6 +46140,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1717">
+      <c r="A1717" s="1" t="n">
+        <v>46129.2916666667</v>
+      </c>
+      <c r="B1717" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C1717" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1717" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G1717" t="s">
+        <v>369</v>
+      </c>
+      <c r="H1717" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4077582359314</t>
+    <t xml:space="preserve">4.40775918960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.55526256561279</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.37305212020874</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">4.3799934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643619537354</t>
+    <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
     <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702253341675</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539747238159</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">4.14745855331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13010454177856</t>
+    <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22554874420166</t>
+    <t xml:space="preserve">4.2255482673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
@@ -107,34 +107,34 @@
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157833099365</t>
+    <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216514587402</t>
+    <t xml:space="preserve">4.18216562271118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819520950317</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863122940063</t>
+    <t xml:space="preserve">4.00863075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -143,22 +143,22 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127793312073</t>
+    <t xml:space="preserve">3.99127769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
     <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509731292725</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
     <t xml:space="preserve">3.77436017990112</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759369850159</t>
+    <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082650184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568388938904</t>
+    <t xml:space="preserve">3.76568365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657110214233</t>
+    <t xml:space="preserve">3.95657086372375</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804441452026</t>
+    <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.08672189712524</t>
@@ -200,28 +200,28 @@
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598428726196</t>
+    <t xml:space="preserve">4.0259838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186450958252</t>
+    <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524739265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833059310913</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273654937744</t>
+    <t xml:space="preserve">3.52273631095886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258623123169</t>
@@ -230,19 +230,19 @@
     <t xml:space="preserve">3.03684163093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375914573669</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052610397339</t>
+    <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714226722717</t>
+    <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596959114075</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
@@ -260,22 +260,19 @@
     <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38390946388245</t>
+    <t xml:space="preserve">3.38390970230103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126252174377</t>
+    <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45413208007812</t>
+    <t xml:space="preserve">3.45413255691528</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363933563232</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
     <t xml:space="preserve">3.22503161430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
     <t xml:space="preserve">3.43650913238525</t>
@@ -287,55 +284,55 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274003982544</t>
+    <t xml:space="preserve">3.61274027824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077025413513</t>
+    <t xml:space="preserve">3.33077049255371</t>
   </si>
   <si>
     <t xml:space="preserve">3.348393201828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27790069580078</t>
+    <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216229438782</t>
+    <t xml:space="preserve">3.17216205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552412033081</t>
+    <t xml:space="preserve">3.29552388191223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593091011047</t>
+    <t xml:space="preserve">2.99593114852905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404636383057</t>
+    <t xml:space="preserve">3.08404684066772</t>
   </si>
   <si>
     <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355385780334</t>
+    <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783079624176</t>
+    <t xml:space="preserve">2.97830772399902</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494613647461</t>
+    <t xml:space="preserve">2.85494589805603</t>
   </si>
   <si>
     <t xml:space="preserve">2.9430615901947</t>
@@ -344,16 +341,16 @@
     <t xml:space="preserve">2.80207657814026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64346861839294</t>
+    <t xml:space="preserve">2.64346837997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62584519386292</t>
+    <t xml:space="preserve">2.62584543228149</t>
   </si>
   <si>
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
     <t xml:space="preserve">2.37912178039551</t>
@@ -362,7 +359,7 @@
     <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387516975403</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
@@ -371,10 +368,10 @@
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289039611816</t>
+    <t xml:space="preserve">2.20289015769958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16764402389526</t>
+    <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
     <t xml:space="preserve">2.11477494239807</t>
@@ -389,28 +386,28 @@
     <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95616674423218</t>
+    <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854367733002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567435741425</t>
+    <t xml:space="preserve">1.88567423820496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86805081367493</t>
+    <t xml:space="preserve">1.86805093288422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952833175659</t>
+    <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
@@ -419,13 +416,13 @@
     <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575947761536</t>
+    <t xml:space="preserve">2.25575971603394</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53772974014282</t>
+    <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
     <t xml:space="preserve">2.73158383369446</t>
@@ -437,22 +434,22 @@
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010655403137</t>
+    <t xml:space="preserve">2.52010631561279</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43199110031128</t>
+    <t xml:space="preserve">2.4319908618927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44961404800415</t>
+    <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436767578125</t>
+    <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
     <t xml:space="preserve">2.39674472808838</t>
@@ -467,13 +464,13 @@
     <t xml:space="preserve">2.78445363044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633769989014</t>
+    <t xml:space="preserve">2.69633793830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880046844482</t>
+    <t xml:space="preserve">3.04880023002625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929297447205</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
     <t xml:space="preserve">3.20740842819214</t>
@@ -488,7 +485,7 @@
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -503,7 +500,10 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3520188331604</t>
+    <t xml:space="preserve">3.1369161605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674757957458</t>
+    <t xml:space="preserve">3.65674734115601</t>
   </si>
   <si>
     <t xml:space="preserve">3.60297203063965</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.92562651634216</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -533,10 +533,10 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.39168262481689</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.5709342956543</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574792861938</t>
+    <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056060791016</t>
+    <t xml:space="preserve">4.66056108474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035526275635</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525259017944</t>
+    <t xml:space="preserve">4.01525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732685089111</t>
   </si>
   <si>
     <t xml:space="preserve">3.97940158843994</t>
@@ -632,28 +632,28 @@
     <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824280738831</t>
+    <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579438209534</t>
+    <t xml:space="preserve">3.40579414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334595680237</t>
+    <t xml:space="preserve">3.51334619522095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -7105,7 +7105,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -7131,7 +7131,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -7157,7 +7157,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -7183,7 +7183,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -7209,7 +7209,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -7235,7 +7235,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7261,7 +7261,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -7287,7 +7287,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -7313,7 +7313,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G223" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -7339,7 +7339,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -7365,7 +7365,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -7391,7 +7391,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -7417,7 +7417,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -7443,7 +7443,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -7469,7 +7469,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7495,7 +7495,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -7521,7 +7521,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -7547,7 +7547,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -7573,7 +7573,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7599,7 +7599,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -7625,7 +7625,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7651,7 +7651,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -7677,7 +7677,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -7703,7 +7703,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -7729,7 +7729,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -7755,7 +7755,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -7781,7 +7781,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -7807,7 +7807,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -7833,7 +7833,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -7859,7 +7859,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -7885,7 +7885,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -7911,7 +7911,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -7963,7 +7963,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -7989,7 +7989,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -8015,7 +8015,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -8041,7 +8041,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8067,7 +8067,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G252" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -8119,7 +8119,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -8145,7 +8145,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -8171,7 +8171,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -8197,7 +8197,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -8223,7 +8223,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G258" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -8249,7 +8249,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -8275,7 +8275,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -8301,7 +8301,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -8327,7 +8327,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8353,7 +8353,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -8379,7 +8379,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8405,7 +8405,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -8431,7 +8431,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -8457,7 +8457,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8483,7 +8483,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8509,7 +8509,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -8535,7 +8535,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -8561,7 +8561,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8587,7 +8587,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8613,7 +8613,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -8639,7 +8639,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -8665,7 +8665,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -8691,7 +8691,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -8717,7 +8717,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8743,7 +8743,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -8769,7 +8769,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -8795,7 +8795,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8821,7 +8821,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -8847,7 +8847,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -8873,7 +8873,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -8899,7 +8899,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -8925,7 +8925,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -8951,7 +8951,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -8977,7 +8977,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -9003,7 +9003,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -9029,7 +9029,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -9055,7 +9055,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -9081,7 +9081,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -9107,7 +9107,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9133,7 +9133,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -9159,7 +9159,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9185,7 +9185,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -9211,7 +9211,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -9237,7 +9237,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -9263,7 +9263,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9289,7 +9289,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -9315,7 +9315,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -9341,7 +9341,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9367,7 +9367,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -9393,7 +9393,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -9419,7 +9419,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -9445,7 +9445,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9471,7 +9471,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -9497,7 +9497,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9523,7 +9523,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9549,7 +9549,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -9575,7 +9575,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9601,7 +9601,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -9627,7 +9627,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -9653,7 +9653,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -9679,7 +9679,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G314" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -9705,7 +9705,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G315" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -9731,7 +9731,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G316" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -9757,7 +9757,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9783,7 +9783,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -9809,7 +9809,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -9835,7 +9835,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -9861,7 +9861,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -9887,7 +9887,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -9913,7 +9913,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G323" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -9939,7 +9939,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -9965,7 +9965,7 @@
         <v>2.5</v>
       </c>
       <c r="G325" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9991,7 +9991,7 @@
         <v>2.5</v>
       </c>
       <c r="G326" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -10017,7 +10017,7 @@
         <v>2.5</v>
       </c>
       <c r="G327" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -10043,7 +10043,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -10069,7 +10069,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -10095,7 +10095,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -10121,7 +10121,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -10147,7 +10147,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -10173,7 +10173,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -10199,7 +10199,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -10225,7 +10225,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10251,7 +10251,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -10277,7 +10277,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10303,7 +10303,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10329,7 +10329,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -10355,7 +10355,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10381,7 +10381,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10407,7 +10407,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -10433,7 +10433,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -10459,7 +10459,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10485,7 +10485,7 @@
         <v>2.5</v>
       </c>
       <c r="G345" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10511,7 +10511,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G346" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10537,7 +10537,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10563,7 +10563,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G348" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10589,7 +10589,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10615,7 +10615,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G350" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10641,7 +10641,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -10667,7 +10667,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -10693,7 +10693,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -10719,7 +10719,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -10745,7 +10745,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10771,7 +10771,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -10797,7 +10797,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10823,7 +10823,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -10849,7 +10849,7 @@
         <v>2.5</v>
       </c>
       <c r="G359" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10875,7 +10875,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -10901,7 +10901,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -10927,7 +10927,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -10953,7 +10953,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10979,7 +10979,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -11005,7 +11005,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -11031,7 +11031,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -11057,7 +11057,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -11083,7 +11083,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11109,7 +11109,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G369" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11135,7 +11135,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -11161,7 +11161,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -11187,7 +11187,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11213,7 +11213,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -11239,7 +11239,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G374" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11265,7 +11265,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11291,7 +11291,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11317,7 +11317,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11343,7 +11343,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11369,7 +11369,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G379" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11395,7 +11395,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G380" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11421,7 +11421,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G381" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11447,7 +11447,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G382" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11473,7 +11473,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G383" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11499,7 +11499,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11525,7 +11525,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G385" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11551,7 +11551,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11577,7 +11577,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G387" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11603,7 +11603,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G388" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -11629,7 +11629,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G389" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11655,7 +11655,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G390" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -11681,7 +11681,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -11707,7 +11707,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -11733,7 +11733,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G393" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -11759,7 +11759,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -11785,7 +11785,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G395" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -11811,7 +11811,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -11837,7 +11837,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -11863,7 +11863,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -11889,7 +11889,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -11915,7 +11915,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -11941,7 +11941,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -11967,7 +11967,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -11993,7 +11993,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -12019,7 +12019,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -12045,7 +12045,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -12071,7 +12071,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -12097,7 +12097,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -12123,7 +12123,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -12149,7 +12149,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12175,7 +12175,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -12201,7 +12201,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -12227,7 +12227,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G412" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12253,7 +12253,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G413" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12279,7 +12279,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G414" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12305,7 +12305,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G415" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -12331,7 +12331,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G416" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -12357,7 +12357,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -12383,7 +12383,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -12409,7 +12409,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G419" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12435,7 +12435,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G420" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12461,7 +12461,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -12487,7 +12487,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12513,7 +12513,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12539,7 +12539,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12565,7 +12565,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12591,7 +12591,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12617,7 +12617,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -12643,7 +12643,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12669,7 +12669,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12695,7 +12695,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G430" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12721,7 +12721,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G431" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12747,7 +12747,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12773,7 +12773,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -12799,7 +12799,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -12825,7 +12825,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -12851,7 +12851,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -12877,7 +12877,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -12903,7 +12903,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -12929,7 +12929,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -12955,7 +12955,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G440" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -12981,7 +12981,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -13007,7 +13007,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -13033,7 +13033,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -13059,7 +13059,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -13085,7 +13085,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -13137,7 +13137,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -13163,7 +13163,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -13189,7 +13189,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13215,7 +13215,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13241,7 +13241,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -13267,7 +13267,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13293,7 +13293,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13319,7 +13319,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13345,7 +13345,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13371,7 +13371,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -13397,7 +13397,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G457" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -13423,7 +13423,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -13449,7 +13449,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -13475,7 +13475,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G460" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -13501,7 +13501,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -13527,7 +13527,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G462" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -13553,7 +13553,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -13579,7 +13579,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G464" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -13605,7 +13605,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G465" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -13631,7 +13631,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -13657,7 +13657,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G467" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13683,7 +13683,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G468" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -46186,6 +46186,58 @@
         <v>368</v>
       </c>
       <c r="H1718" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="1" t="n">
+        <v>46133.2916666667</v>
+      </c>
+      <c r="B1719" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1719" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D1719" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F1719" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G1719" t="s">
+        <v>368</v>
+      </c>
+      <c r="H1719" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="1" t="n">
+        <v>46134.2916666667</v>
+      </c>
+      <c r="B1720" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C1720" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1720" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E1720" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F1720" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="G1720" t="s">
+        <v>366</v>
+      </c>
+      <c r="H1720" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231546401978</t>
+    <t xml:space="preserve">4.31231498718262</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849632263184</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46415758132935</t>
+    <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775871276855</t>
+    <t xml:space="preserve">4.4077582359314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526351928711</t>
+    <t xml:space="preserve">4.55526304244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187896728516</t>
+    <t xml:space="preserve">4.51187944412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39214086532593</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">4.37305212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37999391555786</t>
+    <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
     <t xml:space="preserve">4.41643571853638</t>
@@ -80,52 +80,52 @@
     <t xml:space="preserve">4.33834505081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34702157974243</t>
+    <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539842605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817512512207</t>
+    <t xml:space="preserve">4.01817560195923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14745855331421</t>
+    <t xml:space="preserve">4.14745807647705</t>
   </si>
   <si>
     <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481161117554</t>
+    <t xml:space="preserve">4.16481113433838</t>
   </si>
   <si>
     <t xml:space="preserve">4.11275148391724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24290132522583</t>
+    <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
     <t xml:space="preserve">4.25157880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613412857056</t>
+    <t xml:space="preserve">4.15613508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451073646545</t>
+    <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054056167603</t>
+    <t xml:space="preserve">3.93054103851318</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863075256348</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">4.0173077583313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1214280128479</t>
+    <t xml:space="preserve">4.12142753601074</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995470046997</t>
   </si>
   <si>
     <t xml:space="preserve">3.99127745628357</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">3.93921780586243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789457321167</t>
+    <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171419143677</t>
+    <t xml:space="preserve">3.79171395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8350977897644</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
     <t xml:space="preserve">3.77436065673828</t>
@@ -173,22 +173,22 @@
     <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64420986175537</t>
+    <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
     <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76568412780762</t>
+    <t xml:space="preserve">3.7656843662262</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392463684082</t>
+    <t xml:space="preserve">3.97392439842224</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
@@ -200,28 +200,28 @@
     <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02598524093628</t>
+    <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186403274536</t>
+    <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524786949158</t>
+    <t xml:space="preserve">3.96524739265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583420753479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
     <t xml:space="preserve">3.74833083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52273631095886</t>
+    <t xml:space="preserve">3.52273654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49670648574829</t>
+    <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
     <t xml:space="preserve">3.39258623123169</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037554740906</t>
+    <t xml:space="preserve">3.21037578582764</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714226722717</t>
+    <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
     <t xml:space="preserve">3.43596935272217</t>
@@ -254,25 +254,25 @@
     <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978944778442</t>
+    <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302225112915</t>
+    <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126299858093</t>
+    <t xml:space="preserve">3.40126323699951</t>
   </si>
   <si>
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3836395740509</t>
+    <t xml:space="preserve">3.38363981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22503137588501</t>
+    <t xml:space="preserve">3.22503161430359</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126276016235</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314706802368</t>
+    <t xml:space="preserve">3.31314730644226</t>
   </si>
   <si>
     <t xml:space="preserve">3.17216229438782</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453886985779</t>
+    <t xml:space="preserve">3.15453910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1016697883606</t>
+    <t xml:space="preserve">3.10166954994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0664234161377</t>
+    <t xml:space="preserve">3.06642365455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01355385780334</t>
+    <t xml:space="preserve">3.0135543346405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9783079624176</t>
+    <t xml:space="preserve">2.97830772399902</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
@@ -350,49 +350,49 @@
     <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46723699569702</t>
+    <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149859428406</t>
+    <t xml:space="preserve">2.36149835586548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912154197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387516975403</t>
+    <t xml:space="preserve">2.34387540817261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625198364258</t>
+    <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289039611816</t>
+    <t xml:space="preserve">2.20289015769958</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477494239807</t>
+    <t xml:space="preserve">2.11477470397949</t>
   </si>
   <si>
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239789009094</t>
+    <t xml:space="preserve">2.13239765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903606414795</t>
+    <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
     <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854355812073</t>
+    <t xml:space="preserve">1.93854379653931</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518161296844</t>
+    <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002107620239</t>
+    <t xml:space="preserve">2.15002131462097</t>
   </si>
   <si>
     <t xml:space="preserve">2.04428219795227</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526721000671</t>
+    <t xml:space="preserve">2.18526744842529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53772974014282</t>
+    <t xml:space="preserve">2.5377299785614</t>
   </si>
   <si>
     <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535292625427</t>
+    <t xml:space="preserve">2.55535316467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024836063385</t>
+    <t xml:space="preserve">2.50248312950134</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059906005859</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929273605347</t>
+    <t xml:space="preserve">3.11929249763489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740842819214</t>
+    <t xml:space="preserve">3.20740818977356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027774810791</t>
+    <t xml:space="preserve">3.26027798652649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978548049927</t>
+    <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.1369161605835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3520188331604</t>
+    <t xml:space="preserve">3.35201859474182</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674757957458</t>
+    <t xml:space="preserve">3.65674734115601</t>
   </si>
   <si>
     <t xml:space="preserve">3.60297203063965</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562627792358</t>
+    <t xml:space="preserve">3.92562651634216</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4813084602356</t>
+    <t xml:space="preserve">4.48130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537376403809</t>
+    <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.39168262481689</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375688552856</t>
+    <t xml:space="preserve">4.37375736236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.5709342956543</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338367462158</t>
+    <t xml:space="preserve">4.46338319778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574792861938</t>
+    <t xml:space="preserve">4.61574745178223</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790683746338</t>
+    <t xml:space="preserve">4.33790636062622</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056060791016</t>
+    <t xml:space="preserve">4.66056108474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110263824463</t>
+    <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035526275635</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317737579346</t>
+    <t xml:space="preserve">4.03317785263062</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525259017944</t>
+    <t xml:space="preserve">4.01525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732708930969</t>
+    <t xml:space="preserve">3.99732685089111</t>
   </si>
   <si>
     <t xml:space="preserve">3.97940158843994</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770149230957</t>
+    <t xml:space="preserve">3.90770125389099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824280738831</t>
+    <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579438209534</t>
+    <t xml:space="preserve">3.40579414367676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334595680237</t>
+    <t xml:space="preserve">3.51334619522095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637389183044</t>
+    <t xml:space="preserve">3.74637365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147704124451</t>
+    <t xml:space="preserve">3.96147680282593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686899185181</t>
+    <t xml:space="preserve">4.34686946868896</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -46296,6 +46296,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1723">
+      <c r="A1723" s="1" t="n">
+        <v>46139.2916666667</v>
+      </c>
+      <c r="B1723" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1723" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1723" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1723" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G1723" t="s">
+        <v>373</v>
+      </c>
+      <c r="H1723" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="1" t="n">
+        <v>46140.2916666667</v>
+      </c>
+      <c r="B1724" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1724" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="D1724" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1724" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F1724" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G1724" t="s">
+        <v>382</v>
+      </c>
+      <c r="H1724" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849584579468</t>
+    <t xml:space="preserve">4.46849536895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4077582359314</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526304244995</t>
+    <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
     <t xml:space="preserve">4.51187944412231</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">4.37999296188354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41643571853638</t>
+    <t xml:space="preserve">4.41643524169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.32966899871826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21687173843384</t>
+    <t xml:space="preserve">4.216872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33834505081177</t>
+    <t xml:space="preserve">4.33834552764893</t>
   </si>
   <si>
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539842605591</t>
+    <t xml:space="preserve">4.09539794921875</t>
   </si>
   <si>
     <t xml:space="preserve">4.01817560195923</t>
@@ -101,40 +101,40 @@
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16481113433838</t>
+    <t xml:space="preserve">4.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275148391724</t>
+    <t xml:space="preserve">4.11275100708008</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613508224487</t>
+    <t xml:space="preserve">4.15613460540771</t>
   </si>
   <si>
     <t xml:space="preserve">4.18216514587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20819520950317</t>
+    <t xml:space="preserve">4.20819473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451097488403</t>
+    <t xml:space="preserve">3.90451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054103851318</t>
+    <t xml:space="preserve">3.93054127693176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00863075256348</t>
+    <t xml:space="preserve">4.00863122940063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0173077583313</t>
+    <t xml:space="preserve">4.01730823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12142753601074</t>
+    <t xml:space="preserve">4.1214280128479</t>
   </si>
   <si>
     <t xml:space="preserve">4.28628540039062</t>
@@ -143,28 +143,28 @@
     <t xml:space="preserve">4.06936836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995470046997</t>
+    <t xml:space="preserve">3.99995493888855</t>
   </si>
   <si>
     <t xml:space="preserve">3.99127745628357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921780586243</t>
+    <t xml:space="preserve">3.93921732902527</t>
   </si>
   <si>
     <t xml:space="preserve">3.94789433479309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
     <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77436065673828</t>
+    <t xml:space="preserve">3.7743604183197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69627046585083</t>
+    <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
     <t xml:space="preserve">3.7223002910614</t>
@@ -173,28 +173,28 @@
     <t xml:space="preserve">3.70494699478149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421010017395</t>
+    <t xml:space="preserve">3.64421033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68759346008301</t>
+    <t xml:space="preserve">3.68759369850159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082697868347</t>
+    <t xml:space="preserve">3.60082674026489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7656843662262</t>
+    <t xml:space="preserve">3.76568388938904</t>
   </si>
   <si>
     <t xml:space="preserve">3.95657110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392439842224</t>
+    <t xml:space="preserve">3.97392416000366</t>
   </si>
   <si>
     <t xml:space="preserve">4.07804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672189712524</t>
+    <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.05201482772827</t>
@@ -203,19 +203,19 @@
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186427116394</t>
+    <t xml:space="preserve">3.92186450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524739265442</t>
+    <t xml:space="preserve">3.965247631073</t>
   </si>
   <si>
     <t xml:space="preserve">3.89583420753479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333734512329</t>
+    <t xml:space="preserve">4.04333782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833083152771</t>
+    <t xml:space="preserve">3.74833059310913</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">3.49670672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39258623123169</t>
+    <t xml:space="preserve">3.39258646965027</t>
   </si>
   <si>
     <t xml:space="preserve">3.03684186935425</t>
@@ -236,43 +236,43 @@
     <t xml:space="preserve">2.99345827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21037578582764</t>
+    <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
     <t xml:space="preserve">3.34052586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714250564575</t>
+    <t xml:space="preserve">3.29714226722717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596935272217</t>
+    <t xml:space="preserve">3.43596959114075</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538301467896</t>
+    <t xml:space="preserve">3.50538325309753</t>
   </si>
   <si>
     <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302201271057</t>
+    <t xml:space="preserve">3.19302225112915</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126323699951</t>
+    <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
     <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38363981246948</t>
+    <t xml:space="preserve">3.3836395740509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22503161430359</t>
+    <t xml:space="preserve">3.22503137588501</t>
   </si>
   <si>
     <t xml:space="preserve">3.40126276016235</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
     <t xml:space="preserve">3.17216229438782</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">2.99593091011047</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068453788757</t>
+    <t xml:space="preserve">2.96068477630615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0135543346405</t>
+    <t xml:space="preserve">3.01355385780334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97830772399902</t>
+    <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
@@ -350,49 +350,49 @@
     <t xml:space="preserve">2.62584519386292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4672372341156</t>
+    <t xml:space="preserve">2.46723699569702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912154197693</t>
+    <t xml:space="preserve">2.37912178039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.29100608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387540817261</t>
+    <t xml:space="preserve">2.34387516975403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32625222206116</t>
+    <t xml:space="preserve">2.32625198364258</t>
   </si>
   <si>
     <t xml:space="preserve">2.22051358222961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20289015769958</t>
+    <t xml:space="preserve">2.20289039611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.16764426231384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11477470397949</t>
+    <t xml:space="preserve">2.11477494239807</t>
   </si>
   <si>
     <t xml:space="preserve">2.09715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13239765167236</t>
+    <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903582572937</t>
+    <t xml:space="preserve">2.00903606414795</t>
   </si>
   <si>
     <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854379653931</t>
+    <t xml:space="preserve">1.93854355812073</t>
   </si>
   <si>
     <t xml:space="preserve">1.88567435741425</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518173217773</t>
+    <t xml:space="preserve">1.81518161296844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042786598206</t>
+    <t xml:space="preserve">1.85042798519135</t>
   </si>
   <si>
     <t xml:space="preserve">2.07952857017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15002131462097</t>
+    <t xml:space="preserve">2.15002107620239</t>
   </si>
   <si>
     <t xml:space="preserve">2.04428219795227</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18526744842529</t>
+    <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
     <t xml:space="preserve">2.73158383369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55535316467285</t>
+    <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
     <t xml:space="preserve">2.60822224617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248312950134</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
     <t xml:space="preserve">2.52010655403137</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">2.41436791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674496650696</t>
+    <t xml:space="preserve">2.39674472808838</t>
   </si>
   <si>
     <t xml:space="preserve">2.59059906005859</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11929249763489</t>
+    <t xml:space="preserve">3.11929273605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20740818977356</t>
+    <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265456199646</t>
+    <t xml:space="preserve">3.24265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26027798652649</t>
+    <t xml:space="preserve">3.26027774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18978524208069</t>
+    <t xml:space="preserve">3.18978548049927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691592216492</t>
+    <t xml:space="preserve">3.13691568374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">3.2265419960022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1369161605835</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35201859474182</t>
+    <t xml:space="preserve">3.3520188331604</t>
   </si>
   <si>
     <t xml:space="preserve">3.31616830825806</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674734115601</t>
+    <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
     <t xml:space="preserve">3.60297203063965</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562651634216</t>
+    <t xml:space="preserve">3.92562627792358</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">4.30205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48130798339844</t>
+    <t xml:space="preserve">4.4813084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70537424087524</t>
+    <t xml:space="preserve">4.70537376403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.39168262481689</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.08695316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37375736236572</t>
+    <t xml:space="preserve">4.37375688552856</t>
   </si>
   <si>
     <t xml:space="preserve">4.5709342956543</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">4.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46338319778442</t>
+    <t xml:space="preserve">4.46338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61574745178223</t>
+    <t xml:space="preserve">4.61574792861938</t>
   </si>
   <si>
     <t xml:space="preserve">4.42753267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33790636062622</t>
+    <t xml:space="preserve">4.33790683746338</t>
   </si>
   <si>
     <t xml:space="preserve">4.28413105010986</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">4.31998109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056108474731</t>
+    <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">4.15865421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05110311508179</t>
+    <t xml:space="preserve">4.05110263824463</t>
   </si>
   <si>
     <t xml:space="preserve">4.23035526275635</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">4.26620578765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03317785263062</t>
+    <t xml:space="preserve">4.03317737579346</t>
   </si>
   <si>
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525211334229</t>
+    <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732685089111</t>
+    <t xml:space="preserve">3.99732708930969</t>
   </si>
   <si>
     <t xml:space="preserve">3.97940158843994</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.94355177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90770125389099</t>
+    <t xml:space="preserve">3.90770149230957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29824304580688</t>
+    <t xml:space="preserve">3.29824280738831</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579414367676</t>
+    <t xml:space="preserve">3.40579438209534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334619522095</t>
+    <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96147680282593</t>
+    <t xml:space="preserve">3.96147704124451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34686946868896</t>
+    <t xml:space="preserve">4.34686899185181</t>
   </si>
   <si>
     <t xml:space="preserve">4.25724267959595</t>
@@ -46348,6 +46348,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1725">
+      <c r="A1725" s="1" t="n">
+        <v>46141.2916666667</v>
+      </c>
+      <c r="B1725" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1725" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D1725" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1725" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1725" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G1725" t="s">
+        <v>389</v>
+      </c>
+      <c r="H1725" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31231498718262</t>
+    <t xml:space="preserve">4.31231546401978</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46849536895752</t>
+    <t xml:space="preserve">4.46849584579468</t>
   </si>
   <si>
     <t xml:space="preserve">4.46415710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40775918960571</t>
+    <t xml:space="preserve">4.40775871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55526304244995</t>
+    <t xml:space="preserve">4.55526256561279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51187944412231</t>
+    <t xml:space="preserve">4.51187896728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39214086532593</t>
+    <t xml:space="preserve">4.39214038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37305212020874</t>
+    <t xml:space="preserve">4.3730525970459</t>
   </si>
   <si>
     <t xml:space="preserve">4.37999296188354</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">4.41643571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32966899871826</t>
+    <t xml:space="preserve">4.3296685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216872215271</t>
+    <t xml:space="preserve">4.21687173843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.33834505081177</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">4.34702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09539794921875</t>
+    <t xml:space="preserve">4.09539747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01817560195923</t>
+    <t xml:space="preserve">4.01817512512207</t>
   </si>
   <si>
     <t xml:space="preserve">4.14745807647705</t>
@@ -95,37 +95,37 @@
     <t xml:space="preserve">4.13010501861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2255482673645</t>
+    <t xml:space="preserve">4.22554874420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.23422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1648120880127</t>
+    <t xml:space="preserve">4.16481161117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11275100708008</t>
+    <t xml:space="preserve">4.11275196075439</t>
   </si>
   <si>
     <t xml:space="preserve">4.24290180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25157880783081</t>
+    <t xml:space="preserve">4.25157833099365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15613460540771</t>
+    <t xml:space="preserve">4.15613555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18216466903687</t>
+    <t xml:space="preserve">4.18216562271118</t>
   </si>
   <si>
     <t xml:space="preserve">4.20819520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90451121330261</t>
+    <t xml:space="preserve">3.90451097488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93054127693176</t>
+    <t xml:space="preserve">3.93054056167603</t>
   </si>
   <si>
     <t xml:space="preserve">4.00863122940063</t>
@@ -140,82 +140,82 @@
     <t xml:space="preserve">4.28628540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06936836242676</t>
+    <t xml:space="preserve">4.0693678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99995446205139</t>
+    <t xml:space="preserve">3.99995422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99127745628357</t>
+    <t xml:space="preserve">3.99127793312073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93921732902527</t>
+    <t xml:space="preserve">3.93921756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94789433479309</t>
+    <t xml:space="preserve">3.94789481163025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79171395301819</t>
+    <t xml:space="preserve">3.79171371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83509731292725</t>
+    <t xml:space="preserve">3.83509755134583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7743604183197</t>
+    <t xml:space="preserve">3.77436017990112</t>
   </si>
   <si>
     <t xml:space="preserve">3.69627022743225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7223002910614</t>
+    <t xml:space="preserve">3.72230005264282</t>
   </si>
   <si>
     <t xml:space="preserve">3.70494723320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64421033859253</t>
+    <t xml:space="preserve">3.64421010017395</t>
   </si>
   <si>
     <t xml:space="preserve">3.68759346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60082674026489</t>
+    <t xml:space="preserve">3.60082697868347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7656843662262</t>
+    <t xml:space="preserve">3.76568412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95657110214233</t>
+    <t xml:space="preserve">3.95657062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392416000366</t>
+    <t xml:space="preserve">3.97392439842224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07804489135742</t>
+    <t xml:space="preserve">4.07804441452026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08672189712524</t>
+    <t xml:space="preserve">4.08672142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05201530456543</t>
+    <t xml:space="preserve">4.05201482772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.02598428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92186450958252</t>
+    <t xml:space="preserve">3.92186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96524810791016</t>
+    <t xml:space="preserve">3.96524834632874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89583396911621</t>
+    <t xml:space="preserve">3.89583373069763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04333782196045</t>
+    <t xml:space="preserve">4.04333734512329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74833083152771</t>
+    <t xml:space="preserve">3.74833035469055</t>
   </si>
   <si>
     <t xml:space="preserve">3.52273654937744</t>
@@ -227,46 +227,46 @@
     <t xml:space="preserve">3.39258623123169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03684210777283</t>
+    <t xml:space="preserve">3.03684186935425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25375938415527</t>
+    <t xml:space="preserve">3.25375890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99345827102661</t>
+    <t xml:space="preserve">2.99345850944519</t>
   </si>
   <si>
     <t xml:space="preserve">3.21037554740906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34052610397339</t>
+    <t xml:space="preserve">3.34052562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29714226722717</t>
+    <t xml:space="preserve">3.29714250564575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43596959114075</t>
+    <t xml:space="preserve">3.43596935272217</t>
   </si>
   <si>
     <t xml:space="preserve">3.41861629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50538325309753</t>
+    <t xml:space="preserve">3.50538301467896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27978944778442</t>
+    <t xml:space="preserve">3.27978920936584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19302225112915</t>
+    <t xml:space="preserve">3.19302201271057</t>
   </si>
   <si>
     <t xml:space="preserve">3.38390946388245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40126323699951</t>
+    <t xml:space="preserve">3.40126299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45413255691528</t>
+    <t xml:space="preserve">3.4541323184967</t>
   </si>
   <si>
     <t xml:space="preserve">3.3836395740509</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">3.40126276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43650913238525</t>
+    <t xml:space="preserve">3.43650889396667</t>
   </si>
   <si>
     <t xml:space="preserve">3.4188859462738</t>
@@ -287,61 +287,61 @@
     <t xml:space="preserve">3.47175526618958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61274027824402</t>
+    <t xml:space="preserve">3.61274003982544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33077049255371</t>
+    <t xml:space="preserve">3.33077025413513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.348393201828</t>
+    <t xml:space="preserve">3.34839344024658</t>
   </si>
   <si>
     <t xml:space="preserve">3.27790093421936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31314730644226</t>
+    <t xml:space="preserve">3.31314706802368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17216205596924</t>
+    <t xml:space="preserve">3.17216229438782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29552388191223</t>
+    <t xml:space="preserve">3.29552412033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15453910827637</t>
+    <t xml:space="preserve">3.15453886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10166954994202</t>
+    <t xml:space="preserve">3.1016697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06642365455627</t>
+    <t xml:space="preserve">3.0664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99593114852905</t>
+    <t xml:space="preserve">2.99593091011047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08404684066772</t>
+    <t xml:space="preserve">3.08404660224915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96068477630615</t>
+    <t xml:space="preserve">2.96068453788757</t>
   </si>
   <si>
     <t xml:space="preserve">3.01355409622192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97830772399902</t>
+    <t xml:space="preserve">2.9783079624176</t>
   </si>
   <si>
     <t xml:space="preserve">2.81969976425171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85494589805603</t>
+    <t xml:space="preserve">2.85494613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9430615901947</t>
+    <t xml:space="preserve">2.94306135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80207657814026</t>
+    <t xml:space="preserve">2.80207681655884</t>
   </si>
   <si>
     <t xml:space="preserve">2.64346837997437</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">2.4672372341156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36149835586548</t>
+    <t xml:space="preserve">2.36149859428406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37912178039551</t>
+    <t xml:space="preserve">2.37912130355835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29100608825684</t>
+    <t xml:space="preserve">2.29100584983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34387540817261</t>
+    <t xml:space="preserve">2.34387564659119</t>
   </si>
   <si>
     <t xml:space="preserve">2.32625222206116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22051358222961</t>
+    <t xml:space="preserve">2.22051382064819</t>
   </si>
   <si>
     <t xml:space="preserve">2.20289015769958</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">2.13239789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00903606414795</t>
+    <t xml:space="preserve">2.00903582572937</t>
   </si>
   <si>
     <t xml:space="preserve">1.9561665058136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93854367733002</t>
+    <t xml:space="preserve">1.93854379653931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88567423820496</t>
+    <t xml:space="preserve">1.88567435741425</t>
   </si>
   <si>
     <t xml:space="preserve">1.86805093288422</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">1.83280467987061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518161296844</t>
+    <t xml:space="preserve">1.81518173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85042798519135</t>
+    <t xml:space="preserve">1.85042786598206</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07952857017517</t>
+    <t xml:space="preserve">2.07952833175659</t>
   </si>
   <si>
     <t xml:space="preserve">2.15002107620239</t>
@@ -419,28 +419,28 @@
     <t xml:space="preserve">2.04428219795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25575971603394</t>
+    <t xml:space="preserve">2.25575947761536</t>
   </si>
   <si>
     <t xml:space="preserve">2.18526721000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5377299785614</t>
+    <t xml:space="preserve">2.53772974014282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73158383369446</t>
+    <t xml:space="preserve">2.73158431053162</t>
   </si>
   <si>
     <t xml:space="preserve">2.55535292625427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60822224617004</t>
+    <t xml:space="preserve">2.60822200775146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50248336791992</t>
+    <t xml:space="preserve">2.5024836063385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52010631561279</t>
+    <t xml:space="preserve">2.52010655403137</t>
   </si>
   <si>
     <t xml:space="preserve">2.48486018180847</t>
@@ -452,25 +452,25 @@
     <t xml:space="preserve">2.44961428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41436791419983</t>
+    <t xml:space="preserve">2.41436767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39674472808838</t>
+    <t xml:space="preserve">2.39674496650696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59059906005859</t>
+    <t xml:space="preserve">2.59059929847717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66109156608582</t>
+    <t xml:space="preserve">2.66109132766724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78445363044739</t>
+    <t xml:space="preserve">2.78445339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69633793830872</t>
+    <t xml:space="preserve">2.69633769989014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04880023002625</t>
+    <t xml:space="preserve">3.04880046844482</t>
   </si>
   <si>
     <t xml:space="preserve">3.11929273605347</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">3.20740842819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24265480041504</t>
+    <t xml:space="preserve">3.24265456199646</t>
   </si>
   <si>
     <t xml:space="preserve">3.26027774810791</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">3.18978524208069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13691568374634</t>
+    <t xml:space="preserve">3.13691592216492</t>
   </si>
   <si>
     <t xml:space="preserve">3.2086169719696</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">3.24446725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26239252090454</t>
+    <t xml:space="preserve">3.26239275932312</t>
   </si>
   <si>
     <t xml:space="preserve">3.2265419960022</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.62089729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65674734115601</t>
+    <t xml:space="preserve">3.65674757957458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60297203063965</t>
+    <t xml:space="preserve">3.60297179222107</t>
   </si>
   <si>
     <t xml:space="preserve">3.54919624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92562651634216</t>
+    <t xml:space="preserve">3.925626039505</t>
   </si>
   <si>
     <t xml:space="preserve">4.14072895050049</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.70537424087524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39168262481689</t>
+    <t xml:space="preserve">4.39168214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.40960788726807</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">4.21243000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.194504737854</t>
+    <t xml:space="preserve">4.19450426101685</t>
   </si>
   <si>
     <t xml:space="preserve">4.17657947540283</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">4.28413105010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31998109817505</t>
+    <t xml:space="preserve">4.31998157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66056108474731</t>
+    <t xml:space="preserve">4.66056060791016</t>
   </si>
   <si>
     <t xml:space="preserve">4.44545793533325</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">4.05110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23035526275635</t>
+    <t xml:space="preserve">4.23035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12280368804932</t>
+    <t xml:space="preserve">4.12280416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26620578765869</t>
+    <t xml:space="preserve">4.26620626449585</t>
   </si>
   <si>
     <t xml:space="preserve">4.03317785263062</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">4.0690279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01525211334229</t>
+    <t xml:space="preserve">4.01525259017944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99732685089111</t>
+    <t xml:space="preserve">3.99732732772827</t>
   </si>
   <si>
     <t xml:space="preserve">3.97940158843994</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">3.29824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40579414367676</t>
+    <t xml:space="preserve">3.40579438209534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51334619522095</t>
+    <t xml:space="preserve">3.51334595680237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74637365341187</t>
+    <t xml:space="preserve">3.74637389183044</t>
   </si>
   <si>
     <t xml:space="preserve">3.96147680282593</t>
@@ -46400,6 +46400,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1727">
+      <c r="A1727" s="1" t="n">
+        <v>46146.2916666667</v>
+      </c>
+      <c r="B1727" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C1727" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1727" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1727" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G1727" t="s">
+        <v>373</v>
+      </c>
+      <c r="H1727" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.197829246521</t>
+    <t xml:space="preserve">4.19782876968384</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34986352920532</t>
+    <t xml:space="preserve">4.34986305236816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34563970565796</t>
+    <t xml:space="preserve">4.34564018249512</t>
   </si>
   <si>
     <t xml:space="preserve">4.29073858261108</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">4.27553510665894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25695371627808</t>
+    <t xml:space="preserve">4.25695323944092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26371049880981</t>
+    <t xml:space="preserve">4.26371002197266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29918575286865</t>
+    <t xml:space="preserve">4.29918479919434</t>
   </si>
   <si>
     <t xml:space="preserve">4.2147216796875</t>
@@ -77,34 +77,34 @@
     <t xml:space="preserve">4.10491943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22316837310791</t>
+    <t xml:space="preserve">4.22316789627075</t>
   </si>
   <si>
     <t xml:space="preserve">4.23161458969116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98667097091675</t>
+    <t xml:space="preserve">3.98667073249817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91149830818176</t>
+    <t xml:space="preserve">3.91149806976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03734922409058</t>
+    <t xml:space="preserve">4.03734874725342</t>
   </si>
   <si>
     <t xml:space="preserve">4.02045679092407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11336612701416</t>
+    <t xml:space="preserve">4.11336517333984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12181234359741</t>
+    <t xml:space="preserve">4.12181186676025</t>
   </si>
   <si>
     <t xml:space="preserve">4.05424118041992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00356340408325</t>
+    <t xml:space="preserve">4.00356292724609</t>
   </si>
   <si>
     <t xml:space="preserve">4.13025856018066</t>
@@ -113,58 +113,58 @@
     <t xml:space="preserve">4.13870477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04579496383667</t>
+    <t xml:space="preserve">4.04579544067383</t>
   </si>
   <si>
     <t xml:space="preserve">4.07113409042358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09647369384766</t>
+    <t xml:space="preserve">4.09647274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8008508682251</t>
+    <t xml:space="preserve">3.80085158348083</t>
   </si>
   <si>
     <t xml:space="preserve">3.82619023323059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90220737457275</t>
+    <t xml:space="preserve">3.9022068977356</t>
   </si>
   <si>
     <t xml:space="preserve">3.91065359115601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01201009750366</t>
+    <t xml:space="preserve">4.01200914382935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17249011993408</t>
+    <t xml:space="preserve">4.17249059677124</t>
   </si>
   <si>
     <t xml:space="preserve">3.96133160591125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89376044273376</t>
+    <t xml:space="preserve">3.8937611579895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88531422615051</t>
+    <t xml:space="preserve">3.88531494140625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83463644981384</t>
+    <t xml:space="preserve">3.834636926651</t>
   </si>
   <si>
     <t xml:space="preserve">3.84308290481567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69104838371277</t>
+    <t xml:space="preserve">3.69104886054993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73328042030334</t>
+    <t xml:space="preserve">3.73328065872192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67415618896484</t>
+    <t xml:space="preserve">3.67415595054626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59813928604126</t>
+    <t xml:space="preserve">3.59813904762268</t>
   </si>
   <si>
     <t xml:space="preserve">3.62347793579102</t>
@@ -176,28 +176,28 @@
     <t xml:space="preserve">3.54746103286743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58969259262085</t>
+    <t xml:space="preserve">3.58969283103943</t>
   </si>
   <si>
     <t xml:space="preserve">3.50522971153259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66570997238159</t>
+    <t xml:space="preserve">3.66570973396301</t>
   </si>
   <si>
     <t xml:space="preserve">3.8515293598175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86842155456543</t>
+    <t xml:space="preserve">3.86842203140259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96977782249451</t>
+    <t xml:space="preserve">3.96977829933167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97822427749634</t>
+    <t xml:space="preserve">3.97822403907776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94443917274475</t>
+    <t xml:space="preserve">3.94443869590759</t>
   </si>
   <si>
     <t xml:space="preserve">3.91909980773926</t>
@@ -209,31 +209,31 @@
     <t xml:space="preserve">3.85997533798218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79240393638611</t>
+    <t xml:space="preserve">3.79240489006042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93599200248718</t>
+    <t xml:space="preserve">3.93599224090576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64881753921509</t>
+    <t xml:space="preserve">3.64881730079651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42921233177185</t>
+    <t xml:space="preserve">3.42921257019043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40387344360352</t>
+    <t xml:space="preserve">3.40387392044067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30251741409302</t>
+    <t xml:space="preserve">3.3025176525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.95621776580811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16737580299377</t>
+    <t xml:space="preserve">3.16737604141235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91398620605469</t>
+    <t xml:space="preserve">2.91398596763611</t>
   </si>
   <si>
     <t xml:space="preserve">3.12514448165894</t>
@@ -242,31 +242,31 @@
     <t xml:space="preserve">3.25183939933777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20960760116577</t>
+    <t xml:space="preserve">3.20960783958435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34474921226501</t>
+    <t xml:space="preserve">3.34474897384644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32785654067993</t>
+    <t xml:space="preserve">3.32785630226135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41231966018677</t>
+    <t xml:space="preserve">3.41231989860535</t>
   </si>
   <si>
     <t xml:space="preserve">3.19271516799927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10825204849243</t>
+    <t xml:space="preserve">3.10825157165527</t>
   </si>
   <si>
     <t xml:space="preserve">3.29407119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31096386909485</t>
+    <t xml:space="preserve">3.31096410751343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36242961883545</t>
+    <t xml:space="preserve">3.36242938041687</t>
   </si>
   <si>
     <t xml:space="preserve">3.2938084602356</t>
@@ -275,10 +275,10 @@
     <t xml:space="preserve">3.13941121101379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31096363067627</t>
+    <t xml:space="preserve">3.31096386909485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3452742099762</t>
+    <t xml:space="preserve">3.34527444839478</t>
   </si>
   <si>
     <t xml:space="preserve">3.32811903953552</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">3.242342710495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25949811935425</t>
+    <t xml:space="preserve">3.25949788093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19087696075439</t>
+    <t xml:space="preserve">3.19087719917297</t>
   </si>
   <si>
     <t xml:space="preserve">3.22518730163574</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">3.08794546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20803236961365</t>
+    <t xml:space="preserve">3.20803213119507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07079005241394</t>
+    <t xml:space="preserve">3.07079029083252</t>
   </si>
   <si>
     <t xml:space="preserve">3.01932454109192</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">3.00216913223267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88208222389221</t>
+    <t xml:space="preserve">2.88208198547363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93354821205139</t>
+    <t xml:space="preserve">2.93354845046997</t>
   </si>
   <si>
     <t xml:space="preserve">2.89923787117004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74484038352966</t>
+    <t xml:space="preserve">2.74484062194824</t>
   </si>
   <si>
     <t xml:space="preserve">2.77915096282959</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">2.86492705345154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72768545150757</t>
+    <t xml:space="preserve">2.72768521308899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57328772544861</t>
+    <t xml:space="preserve">2.57328796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55613279342651</t>
+    <t xml:space="preserve">2.55613255500793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40173530578613</t>
+    <t xml:space="preserve">2.40173506736755</t>
   </si>
   <si>
     <t xml:space="preserve">2.29880380630493</t>
@@ -359,31 +359,31 @@
     <t xml:space="preserve">2.31595873832703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23018264770508</t>
+    <t xml:space="preserve">2.23018288612366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28164887428284</t>
+    <t xml:space="preserve">2.28164863586426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.264493227005</t>
+    <t xml:space="preserve">2.26449370384216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16156220436096</t>
+    <t xml:space="preserve">2.1615617275238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14440631866455</t>
+    <t xml:space="preserve">2.14440655708313</t>
   </si>
   <si>
     <t xml:space="preserve">2.11009621620178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05863046646118</t>
+    <t xml:space="preserve">2.0586302280426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04147505760193</t>
+    <t xml:space="preserve">2.04147529602051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07578563690186</t>
+    <t xml:space="preserve">2.07578539848328</t>
   </si>
   <si>
     <t xml:space="preserve">1.95569860935211</t>
@@ -392,16 +392,16 @@
     <t xml:space="preserve">1.90423285961151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88707804679871</t>
+    <t xml:space="preserve">1.88707792758942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83561217784882</t>
+    <t xml:space="preserve">1.83561205863953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81845664978027</t>
+    <t xml:space="preserve">1.81845676898956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78414607048035</t>
+    <t xml:space="preserve">1.78414618968964</t>
   </si>
   <si>
     <t xml:space="preserve">1.76699101924896</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">2.02431964874268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09294080734253</t>
+    <t xml:space="preserve">2.09294104576111</t>
   </si>
   <si>
     <t xml:space="preserve">1.99000918865204</t>
@@ -422,25 +422,25 @@
     <t xml:space="preserve">2.19587206840515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12725114822388</t>
+    <t xml:space="preserve">2.12725138664246</t>
   </si>
   <si>
     <t xml:space="preserve">2.47035646438599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65906429290771</t>
+    <t xml:space="preserve">2.65906405448914</t>
   </si>
   <si>
     <t xml:space="preserve">2.48751163482666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53897714614868</t>
+    <t xml:space="preserve">2.53897738456726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43604588508606</t>
+    <t xml:space="preserve">2.43604564666748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45320105552673</t>
+    <t xml:space="preserve">2.45320129394531</t>
   </si>
   <si>
     <t xml:space="preserve">2.41889047622681</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">2.38458013534546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026931762695</t>
+    <t xml:space="preserve">2.35026979446411</t>
   </si>
   <si>
     <t xml:space="preserve">2.33311462402344</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">2.52182221412659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59044289588928</t>
+    <t xml:space="preserve">2.59044313430786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71052980422974</t>
+    <t xml:space="preserve">2.71053004264832</t>
   </si>
   <si>
     <t xml:space="preserve">2.62475347518921</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">2.96785879135132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03647971153259</t>
+    <t xml:space="preserve">3.03647947311401</t>
   </si>
   <si>
     <t xml:space="preserve">3.12225604057312</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">3.15656638145447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17372155189514</t>
+    <t xml:space="preserve">3.17372179031372</t>
   </si>
   <si>
     <t xml:space="preserve">3.10510063171387</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">3.52476716041565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55966567993164</t>
+    <t xml:space="preserve">3.55966591835022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50731754302979</t>
+    <t xml:space="preserve">3.50731778144836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45496964454651</t>
+    <t xml:space="preserve">3.45496988296509</t>
   </si>
   <si>
     <t xml:space="preserve">3.82140588760376</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">4.03079795837402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18784236907959</t>
+    <t xml:space="preserve">4.18784189224243</t>
   </si>
   <si>
     <t xml:space="preserve">4.36233520507812</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">4.27508878707886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2925386428833</t>
+    <t xml:space="preserve">4.29253816604614</t>
   </si>
   <si>
     <t xml:space="preserve">4.13549375534058</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">4.06569671630859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97844982147217</t>
+    <t xml:space="preserve">3.97845005989075</t>
   </si>
   <si>
     <t xml:space="preserve">4.25763988494873</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.49320554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30998754501343</t>
+    <t xml:space="preserve">4.30998802185059</t>
   </si>
   <si>
     <t xml:space="preserve">4.222740650177</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">4.1703929901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20529174804688</t>
+    <t xml:space="preserve">4.20529222488403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53682899475098</t>
+    <t xml:space="preserve">4.53682851791382</t>
   </si>
   <si>
     <t xml:space="preserve">4.32743692398071</t>
@@ -599,10 +599,10 @@
     <t xml:space="preserve">4.24019050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04824733734131</t>
+    <t xml:space="preserve">4.04824686050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94355177879333</t>
+    <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
     <t xml:space="preserve">4.11804437637329</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">4.0133490562439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15294408798218</t>
+    <t xml:space="preserve">4.15294361114502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92610239982605</t>
+    <t xml:space="preserve">3.92610216140747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96100068092346</t>
+    <t xml:space="preserve">3.96100091934204</t>
   </si>
   <si>
     <t xml:space="preserve">3.90865302085876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89120364189148</t>
+    <t xml:space="preserve">3.8912034034729</t>
   </si>
   <si>
     <t xml:space="preserve">3.87375378608704</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">3.80395698547363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43752026557922</t>
+    <t xml:space="preserve">3.4375205039978</t>
   </si>
   <si>
     <t xml:space="preserve">3.21067905426025</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">3.31537508964539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4200713634491</t>
+    <t xml:space="preserve">3.42007112503052</t>
   </si>
   <si>
     <t xml:space="preserve">3.64691257476807</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">4.14421844482422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05697202682495</t>
+    <t xml:space="preserve">4.05697250366211</t>
   </si>
   <si>
     <t xml:space="preserve">3.99589920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98717498779297</t>
+    <t xml:space="preserve">3.98717474937439</t>
   </si>
   <si>
     <t xml:space="preserve">3.99613475799561</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">4.02301406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0946946144104</t>
+    <t xml:space="preserve">4.09469413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10365390777588</t>
+    <t xml:space="preserve">4.10365438461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22909355163574</t>
+    <t xml:space="preserve">4.22909307479858</t>
   </si>
   <si>
     <t xml:space="preserve">4.25597286224365</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">4.15741348266602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13949346542358</t>
+    <t xml:space="preserve">4.13949394226074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00509405136108</t>
+    <t xml:space="preserve">4.00509452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96029543876648</t>
+    <t xml:space="preserve">3.9602952003479</t>
   </si>
   <si>
     <t xml:space="preserve">4.04093456268311</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">3.92445540428162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03197431564331</t>
+    <t xml:space="preserve">4.03197479248047</t>
   </si>
   <si>
     <t xml:space="preserve">3.94237542152405</t>
@@ -722,22 +722,22 @@
     <t xml:space="preserve">3.93341541290283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89757537841797</t>
+    <t xml:space="preserve">3.89757561683655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88861584663391</t>
+    <t xml:space="preserve">3.88861560821533</t>
   </si>
   <si>
     <t xml:space="preserve">3.87069582939148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87965559959412</t>
+    <t xml:space="preserve">3.87965536117554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98717451095581</t>
+    <t xml:space="preserve">3.98717427253723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85277581214905</t>
+    <t xml:space="preserve">3.85277605056763</t>
   </si>
   <si>
     <t xml:space="preserve">3.86173558235168</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">3.67357659339905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7452564239502</t>
+    <t xml:space="preserve">3.74525618553162</t>
   </si>
   <si>
     <t xml:space="preserve">3.6556568145752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9154953956604</t>
+    <t xml:space="preserve">3.91549515724182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58397722244263</t>
+    <t xml:space="preserve">3.58397746086121</t>
   </si>
   <si>
     <t xml:space="preserve">3.68253684043884</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">3.7810959815979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96925497055054</t>
+    <t xml:space="preserve">3.96925520896912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97821450233459</t>
+    <t xml:space="preserve">3.97821474075317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76317620277405</t>
+    <t xml:space="preserve">3.76317596435547</t>
   </si>
   <si>
     <t xml:space="preserve">3.69149661064148</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">3.66461706161499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63773727416992</t>
+    <t xml:space="preserve">3.63773703575134</t>
   </si>
   <si>
     <t xml:space="preserve">3.64669704437256</t>
@@ -809,13 +809,13 @@
     <t xml:space="preserve">3.84381556510925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01405477523804</t>
+    <t xml:space="preserve">4.01405429840088</t>
   </si>
   <si>
     <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13053417205811</t>
+    <t xml:space="preserve">4.13053369522095</t>
   </si>
   <si>
     <t xml:space="preserve">4.18429374694824</t>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.197829246521</t>
+    <t xml:space="preserve">4.19782876968384</t>
   </si>
   <si>
     <t xml:space="preserve">MARP.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34986352920532</t>
+    <t xml:space="preserve">4.34986305236816</t>
   </si>
   <si>
     <t xml:space="preserve">4.34564018249512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29073905944824</t>
+    <t xml:space="preserve">4.29073858261108</t>
   </si>
   <si>
     <t xml:space="preserve">4.43432664871216</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">4.25695371627808</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26371002197266</t>
+    <t xml:space="preserve">4.26371049880981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29918479919434</t>
+    <t xml:space="preserve">4.29918527603149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21472072601318</t>
+    <t xml:space="preserve">4.2147216796875</t>
   </si>
   <si>
     <t xml:space="preserve">4.10491943359375</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">3.98667025566101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9114978313446</t>
+    <t xml:space="preserve">3.91149854660034</t>
   </si>
   <si>
     <t xml:space="preserve">4.03734922409058</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">4.113365650177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12181234359741</t>
+    <t xml:space="preserve">4.12181186676025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05424165725708</t>
+    <t xml:space="preserve">4.05424118041992</t>
   </si>
   <si>
     <t xml:space="preserve">4.00356292724609</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">4.13025808334351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13870477676392</t>
+    <t xml:space="preserve">4.13870525360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.04579496383667</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">4.09647274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80085158348083</t>
+    <t xml:space="preserve">3.80085110664368</t>
   </si>
   <si>
     <t xml:space="preserve">3.82619023323059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90220737457275</t>
+    <t xml:space="preserve">3.90220761299133</t>
   </si>
   <si>
     <t xml:space="preserve">3.91065359115601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0120096206665</t>
+    <t xml:space="preserve">4.01200914382935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17249059677124</t>
+    <t xml:space="preserve">4.17249011993408</t>
   </si>
   <si>
     <t xml:space="preserve">3.96133160591125</t>
@@ -146,82 +146,82 @@
     <t xml:space="preserve">3.8937611579895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88531494140625</t>
+    <t xml:space="preserve">3.88531517982483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.834636926651</t>
+    <t xml:space="preserve">3.83463668823242</t>
   </si>
   <si>
     <t xml:space="preserve">3.84308290481567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69104886054993</t>
+    <t xml:space="preserve">3.69104862213135</t>
   </si>
   <si>
     <t xml:space="preserve">3.73328042030334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67415571212769</t>
+    <t xml:space="preserve">3.67415642738342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59813904762268</t>
+    <t xml:space="preserve">3.59813952445984</t>
   </si>
   <si>
     <t xml:space="preserve">3.62347769737244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60658574104309</t>
+    <t xml:space="preserve">3.60658526420593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54746103286743</t>
+    <t xml:space="preserve">3.54746055603027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58969259262085</t>
+    <t xml:space="preserve">3.58969283103943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50522971153259</t>
+    <t xml:space="preserve">3.50522947311401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66571021080017</t>
+    <t xml:space="preserve">3.66570997238159</t>
   </si>
   <si>
     <t xml:space="preserve">3.8515293598175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86842155456543</t>
+    <t xml:space="preserve">3.86842179298401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96977782249451</t>
+    <t xml:space="preserve">3.96977806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97822403907776</t>
+    <t xml:space="preserve">3.97822380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94443917274475</t>
+    <t xml:space="preserve">3.94443893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91909980773926</t>
+    <t xml:space="preserve">3.91910028457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81774353981018</t>
+    <t xml:space="preserve">3.81774401664734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85997629165649</t>
+    <t xml:space="preserve">3.85997581481934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79240441322327</t>
+    <t xml:space="preserve">3.79240465164185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93599224090576</t>
+    <t xml:space="preserve">3.9359929561615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64881730079651</t>
+    <t xml:space="preserve">3.64881753921509</t>
   </si>
   <si>
     <t xml:space="preserve">3.42921257019043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40387392044067</t>
+    <t xml:space="preserve">3.40387368202209</t>
   </si>
   <si>
     <t xml:space="preserve">3.3025176525116</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">3.16737580299377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91398620605469</t>
+    <t xml:space="preserve">2.91398596763611</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12514424324036</t>
+    <t xml:space="preserve">3.12514448165894</t>
   </si>
   <si>
     <t xml:space="preserve">3.25183939933777</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">3.32785630226135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41231989860535</t>
+    <t xml:space="preserve">3.41231966018677</t>
   </si>
   <si>
     <t xml:space="preserve">3.19271492958069</t>
@@ -260,34 +260,34 @@
     <t xml:space="preserve">3.10825181007385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29407095909119</t>
+    <t xml:space="preserve">3.29407119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31096410751343</t>
+    <t xml:space="preserve">3.31096386909485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36242961883545</t>
+    <t xml:space="preserve">3.36242938041687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29380822181702</t>
+    <t xml:space="preserve">3.2938084602356</t>
   </si>
   <si>
     <t xml:space="preserve">3.13941121101379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31096386909485</t>
+    <t xml:space="preserve">3.31096363067627</t>
   </si>
   <si>
     <t xml:space="preserve">3.3452742099762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32811903953552</t>
+    <t xml:space="preserve">3.32811880111694</t>
   </si>
   <si>
     <t xml:space="preserve">3.37958478927612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51682662963867</t>
+    <t xml:space="preserve">3.51682686805725</t>
   </si>
   <si>
     <t xml:space="preserve">3.242342710495</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">3.25949788093567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19087719917297</t>
+    <t xml:space="preserve">3.19087672233582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22518730163574</t>
+    <t xml:space="preserve">3.22518754005432</t>
   </si>
   <si>
     <t xml:space="preserve">3.08794546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20803213119507</t>
+    <t xml:space="preserve">3.20803236961365</t>
   </si>
   <si>
     <t xml:space="preserve">3.07079005241394</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">2.98501396179199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91639280319214</t>
+    <t xml:space="preserve">2.91639304161072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00216913223267</t>
+    <t xml:space="preserve">3.00216937065125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88208222389221</t>
+    <t xml:space="preserve">2.88208246231079</t>
   </si>
   <si>
     <t xml:space="preserve">2.93354821205139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89923787117004</t>
+    <t xml:space="preserve">2.89923763275146</t>
   </si>
   <si>
     <t xml:space="preserve">2.74484062194824</t>
@@ -338,31 +338,31 @@
     <t xml:space="preserve">2.77915096282959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86492705345154</t>
+    <t xml:space="preserve">2.86492729187012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72768521308899</t>
+    <t xml:space="preserve">2.72768545150757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57328772544861</t>
+    <t xml:space="preserve">2.57328796386719</t>
   </si>
   <si>
     <t xml:space="preserve">2.55613279342651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40173506736755</t>
+    <t xml:space="preserve">2.40173530578613</t>
   </si>
   <si>
     <t xml:space="preserve">2.29880404472351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31595873832703</t>
+    <t xml:space="preserve">2.31595897674561</t>
   </si>
   <si>
     <t xml:space="preserve">2.23018288612366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28164863586426</t>
+    <t xml:space="preserve">2.28164839744568</t>
   </si>
   <si>
     <t xml:space="preserve">2.26449346542358</t>
@@ -374,43 +374,43 @@
     <t xml:space="preserve">2.14440655708313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11009621620178</t>
+    <t xml:space="preserve">2.1100959777832</t>
   </si>
   <si>
     <t xml:space="preserve">2.05863046646118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04147505760193</t>
+    <t xml:space="preserve">2.04147529602051</t>
   </si>
   <si>
     <t xml:space="preserve">2.07578563690186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95569860935211</t>
+    <t xml:space="preserve">1.95569884777069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90423285961151</t>
+    <t xml:space="preserve">1.9042329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88707792758942</t>
+    <t xml:space="preserve">1.88707780838013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83561217784882</t>
+    <t xml:space="preserve">1.83561205863953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81845676898956</t>
+    <t xml:space="preserve">1.81845653057098</t>
   </si>
   <si>
     <t xml:space="preserve">1.78414607048035</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76699101924896</t>
+    <t xml:space="preserve">1.76699090003967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8013014793396</t>
+    <t xml:space="preserve">1.80130136013031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02431964874268</t>
+    <t xml:space="preserve">2.0243194103241</t>
   </si>
   <si>
     <t xml:space="preserve">2.09294080734253</t>
@@ -419,22 +419,22 @@
     <t xml:space="preserve">1.99000918865204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19587206840515</t>
+    <t xml:space="preserve">2.19587230682373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12725114822388</t>
+    <t xml:space="preserve">2.12725162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47035646438599</t>
+    <t xml:space="preserve">2.47035670280457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65906429290771</t>
+    <t xml:space="preserve">2.65906405448914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48751163482666</t>
+    <t xml:space="preserve">2.48751187324524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53897714614868</t>
+    <t xml:space="preserve">2.53897738456726</t>
   </si>
   <si>
     <t xml:space="preserve">2.43604588508606</t>
@@ -446,25 +446,25 @@
     <t xml:space="preserve">2.41889047622681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36742448806763</t>
+    <t xml:space="preserve">2.36742496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38458037376404</t>
+    <t xml:space="preserve">2.38458013534546</t>
   </si>
   <si>
     <t xml:space="preserve">2.35026955604553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33311462402344</t>
+    <t xml:space="preserve">2.33311438560486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52182221412659</t>
+    <t xml:space="preserve">2.52182197570801</t>
   </si>
   <si>
     <t xml:space="preserve">2.59044289588928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71053004264832</t>
+    <t xml:space="preserve">2.71053028106689</t>
   </si>
   <si>
     <t xml:space="preserve">2.62475347518921</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">2.96785879135132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03647947311401</t>
+    <t xml:space="preserve">3.03647971153259</t>
   </si>
   <si>
     <t xml:space="preserve">3.12225604057312</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">3.15656638145447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17372155189514</t>
+    <t xml:space="preserve">3.17372179031372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10510063171387</t>
+    <t xml:space="preserve">3.10510039329529</t>
   </si>
   <si>
     <t xml:space="preserve">3.05363488197327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12343239784241</t>
+    <t xml:space="preserve">3.12343215942383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1583309173584</t>
+    <t xml:space="preserve">3.15833067893982</t>
   </si>
   <si>
     <t xml:space="preserve">3.17578053474426</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">3.05363512039185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26302695274353</t>
+    <t xml:space="preserve">3.26302719116211</t>
   </si>
   <si>
     <t xml:space="preserve">3.22812843322754</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">3.52476716041565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55966591835022</t>
+    <t xml:space="preserve">3.55966567993164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50731778144836</t>
+    <t xml:space="preserve">3.50731801986694</t>
   </si>
   <si>
     <t xml:space="preserve">3.45496988296509</t>
@@ -530,25 +530,25 @@
     <t xml:space="preserve">3.82140588760376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03079795837402</t>
+    <t xml:space="preserve">4.03079748153687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18784189224243</t>
+    <t xml:space="preserve">4.18784236907959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36233520507812</t>
+    <t xml:space="preserve">4.36233568191528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58045291900635</t>
+    <t xml:space="preserve">4.58045244216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27508878707886</t>
+    <t xml:space="preserve">4.27508926391602</t>
   </si>
   <si>
     <t xml:space="preserve">4.29253816604614</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13549375534058</t>
+    <t xml:space="preserve">4.13549423217773</t>
   </si>
   <si>
     <t xml:space="preserve">4.10059547424316</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">4.06569671630859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97845005989075</t>
+    <t xml:space="preserve">3.97845029830933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25763988494873</t>
+    <t xml:space="preserve">4.25763940811157</t>
   </si>
   <si>
     <t xml:space="preserve">4.44958209991455</t>
@@ -572,67 +572,67 @@
     <t xml:space="preserve">4.4059591293335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.344886302948</t>
+    <t xml:space="preserve">4.34488582611084</t>
   </si>
   <si>
     <t xml:space="preserve">4.49320554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30998802185059</t>
+    <t xml:space="preserve">4.30998754501343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.222740650177</t>
+    <t xml:space="preserve">4.22274112701416</t>
   </si>
   <si>
     <t xml:space="preserve">4.1703929901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20529222488403</t>
+    <t xml:space="preserve">4.20529127120972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53682851791382</t>
+    <t xml:space="preserve">4.53682899475098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32743692398071</t>
+    <t xml:space="preserve">4.32743740081787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24019050598145</t>
+    <t xml:space="preserve">4.2401909828186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04824686050415</t>
+    <t xml:space="preserve">4.04824733734131</t>
   </si>
   <si>
     <t xml:space="preserve">3.94355130195618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11804437637329</t>
+    <t xml:space="preserve">4.11804389953613</t>
   </si>
   <si>
     <t xml:space="preserve">4.0133490562439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15294361114502</t>
+    <t xml:space="preserve">4.15294408798218</t>
   </si>
   <si>
     <t xml:space="preserve">3.92610216140747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96100091934204</t>
+    <t xml:space="preserve">3.96100068092346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90865302085876</t>
+    <t xml:space="preserve">3.90865278244019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8912034034729</t>
+    <t xml:space="preserve">3.89120364189148</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87375378608704</t>
+    <t xml:space="preserve">3.87375402450562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75160884857178</t>
+    <t xml:space="preserve">3.75160908699036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8388557434082</t>
+    <t xml:space="preserve">3.83885550498962</t>
   </si>
   <si>
     <t xml:space="preserve">3.80395698547363</t>
@@ -650,46 +650,46 @@
     <t xml:space="preserve">3.42007112503052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64691257476807</t>
+    <t xml:space="preserve">3.64691233634949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85630488395691</t>
+    <t xml:space="preserve">3.85630440711975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2314658164978</t>
+    <t xml:space="preserve">4.23146486282349</t>
   </si>
   <si>
     <t xml:space="preserve">4.14421844482422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05697250366211</t>
+    <t xml:space="preserve">4.05697202682495</t>
   </si>
   <si>
     <t xml:space="preserve">3.99589920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98717474937439</t>
+    <t xml:space="preserve">3.98717522621155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99613475799561</t>
+    <t xml:space="preserve">3.99613499641418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12157392501831</t>
+    <t xml:space="preserve">4.12157440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11261415481567</t>
+    <t xml:space="preserve">4.11261367797852</t>
   </si>
   <si>
     <t xml:space="preserve">4.02301406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09469413757324</t>
+    <t xml:space="preserve">4.0946946144104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10365438461304</t>
+    <t xml:space="preserve">4.10365390777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22909307479858</t>
+    <t xml:space="preserve">4.22909259796143</t>
   </si>
   <si>
     <t xml:space="preserve">4.25597286224365</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">4.15741348266602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13949394226074</t>
+    <t xml:space="preserve">4.13949346542358</t>
   </si>
   <si>
     <t xml:space="preserve">4.00509452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9602952003479</t>
+    <t xml:space="preserve">3.96029472351074</t>
   </si>
   <si>
     <t xml:space="preserve">4.04093456268311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92445540428162</t>
+    <t xml:space="preserve">3.92445516586304</t>
   </si>
   <si>
     <t xml:space="preserve">4.03197479248047</t>
@@ -719,25 +719,25 @@
     <t xml:space="preserve">3.94237542152405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93341541290283</t>
+    <t xml:space="preserve">3.93341493606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89757561683655</t>
+    <t xml:space="preserve">3.89757537841797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88861560821533</t>
+    <t xml:space="preserve">3.88861536979675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87069582939148</t>
+    <t xml:space="preserve">3.8706955909729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87965536117554</t>
+    <t xml:space="preserve">3.87965559959412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98717427253723</t>
+    <t xml:space="preserve">3.98717451095581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85277605056763</t>
+    <t xml:space="preserve">3.85277628898621</t>
   </si>
   <si>
     <t xml:space="preserve">3.86173558235168</t>
@@ -746,16 +746,16 @@
     <t xml:space="preserve">3.8348560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8258957862854</t>
+    <t xml:space="preserve">3.82589602470398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80797600746155</t>
+    <t xml:space="preserve">3.80797576904297</t>
   </si>
   <si>
     <t xml:space="preserve">3.71837663650513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67357659339905</t>
+    <t xml:space="preserve">3.67357683181763</t>
   </si>
   <si>
     <t xml:space="preserve">3.74525618553162</t>
@@ -767,19 +767,19 @@
     <t xml:space="preserve">3.91549515724182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58397746086121</t>
+    <t xml:space="preserve">3.58397722244263</t>
   </si>
   <si>
     <t xml:space="preserve">3.68253684043884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7810959815979</t>
+    <t xml:space="preserve">3.78109622001648</t>
   </si>
   <si>
     <t xml:space="preserve">3.96925520896912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97821474075317</t>
+    <t xml:space="preserve">3.97821497917175</t>
   </si>
   <si>
     <t xml:space="preserve">3.76317596435547</t>
@@ -794,28 +794,28 @@
     <t xml:space="preserve">3.63773703575134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64669704437256</t>
+    <t xml:space="preserve">3.64669728279114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79005599021912</t>
+    <t xml:space="preserve">3.7900562286377</t>
   </si>
   <si>
     <t xml:space="preserve">3.79901576042175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77213621139526</t>
+    <t xml:space="preserve">3.77213597297668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84381556510925</t>
+    <t xml:space="preserve">3.84381532669067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01405429840088</t>
+    <t xml:space="preserve">4.01405477523804</t>
   </si>
   <si>
     <t xml:space="preserve">4.04989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13053369522095</t>
+    <t xml:space="preserve">4.13053417205811</t>
   </si>
   <si>
     <t xml:space="preserve">4.18429374694824</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">3.95133495330811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08573389053345</t>
+    <t xml:space="preserve">4.08573436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07677459716797</t>
+    <t xml:space="preserve">4.07677412033081</t>
   </si>
   <si>
     <t xml:space="preserve">4.09378814697266</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">4.01969242095947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11231184005737</t>
+    <t xml:space="preserve">4.11231231689453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90854859352112</t>
+    <t xml:space="preserve">3.9085488319397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87150073051453</t>
+    <t xml:space="preserve">3.87150096893311</t>
   </si>
   <si>
     <t xml:space="preserve">3.85297679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77888107299805</t>
+    <t xml:space="preserve">3.77888131141663</t>
   </si>
   <si>
     <t xml:space="preserve">3.72330951690674</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">3.74183344841003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83445286750793</t>
+    <t xml:space="preserve">3.83445310592651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79740500450134</t>
+    <t xml:space="preserve">3.79740524291992</t>
   </si>
   <si>
     <t xml:space="preserve">3.89002466201782</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.64921379089355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61216616630554</t>
+    <t xml:space="preserve">3.61216592788696</t>
   </si>
   <si>
     <t xml:space="preserve">3.4639744758606</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">3.50102233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57511806488037</t>
+    <t xml:space="preserve">3.57511782646179</t>
   </si>
   <si>
     <t xml:space="preserve">3.48249840736389</t>
@@ -905,19 +905,19 @@
     <t xml:space="preserve">3.40840268135071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37135481834412</t>
+    <t xml:space="preserve">3.3713550567627</t>
   </si>
   <si>
     <t xml:space="preserve">3.33430695533752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26021122932434</t>
+    <t xml:space="preserve">3.26021146774292</t>
   </si>
   <si>
     <t xml:space="preserve">3.35283088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59364223480225</t>
+    <t xml:space="preserve">3.59364199638367</t>
   </si>
   <si>
     <t xml:space="preserve">3.51954627037048</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">3.68626165390015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63069009780884</t>
+    <t xml:space="preserve">3.63068985939026</t>
   </si>
   <si>
     <t xml:space="preserve">3.76035737991333</t>
@@ -46666,6 +46666,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1737">
+      <c r="A1737" s="1" t="n">
+        <v>46160.2916666667</v>
+      </c>
+      <c r="B1737" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C1737" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G1737" t="s">
+        <v>373</v>
+      </c>
+      <c r="H1737" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2" t="n">
-        <v>4.19782829284668</v>
+        <v>4.19782876968384</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G5" t="n">
-        <v>4.29073858261108</v>
+        <v>4.29073905944824</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4.43432664871216</v>
+        <v>4.434326171875</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39209508895874</v>
+        <v>4.39209461212158</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>4.25695371627808</v>
+        <v>4.25695323944092</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.0479998588562</v>
       </c>
       <c r="G10" t="n">
-        <v>4.26371049880981</v>
+        <v>4.26371002197266</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2147216796875</v>
+        <v>4.21472120285034</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>4.25695371627808</v>
+        <v>4.25695323944092</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.23161506652832</v>
+        <v>4.23161458969116</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>4.25695371627808</v>
+        <v>4.25695323944092</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G23" t="n">
-        <v>3.98667025566101</v>
+        <v>3.98667001724243</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>3.91149806976318</v>
+        <v>3.9114978313446</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G26" t="n">
-        <v>4.03734827041626</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G27" t="n">
-        <v>4.03734827041626</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G28" t="n">
-        <v>4.03734827041626</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045631408691</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G30" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045631408691</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G31" t="n">
-        <v>4.113365650177</v>
+        <v>4.11336612701416</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>4.03734827041626</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>4.03734827041626</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>4.03734827041626</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G38" t="n">
-        <v>4.03734827041626</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G40" t="n">
-        <v>4.13025760650635</v>
+        <v>4.13025808334351</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G42" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>4.04579496383667</v>
+        <v>4.04579448699951</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G50" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G52" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045631408691</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G53" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045631408691</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>4.0964732170105</v>
+        <v>4.09647274017334</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G56" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045631408691</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.5</v>
       </c>
       <c r="G57" t="n">
-        <v>3.80085062980652</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>3.90220713615417</v>
+        <v>3.9022068977356</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G60" t="n">
-        <v>3.91065335273743</v>
+        <v>3.91065359115601</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>3.91065335273743</v>
+        <v>3.91065359115601</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>4.19782829284668</v>
+        <v>4.19782876968384</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.75</v>
       </c>
       <c r="G65" t="n">
-        <v>4.01201009750366</v>
+        <v>4.0120096206665</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G66" t="n">
-        <v>3.98667025566101</v>
+        <v>3.98667001724243</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G67" t="n">
-        <v>3.98667025566101</v>
+        <v>3.98667001724243</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G68" t="n">
-        <v>3.98667025566101</v>
+        <v>3.98667001724243</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G69" t="n">
-        <v>4.17249011993408</v>
+        <v>4.17248964309692</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5</v>
       </c>
       <c r="G70" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0964732170105</v>
+        <v>4.09647274017334</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G75" t="n">
-        <v>4.0964732170105</v>
+        <v>4.09647274017334</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G76" t="n">
-        <v>4.0964732170105</v>
+        <v>4.09647274017334</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>4.0964732170105</v>
+        <v>4.09647274017334</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>3.96133160591125</v>
+        <v>3.96133208274841</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.75</v>
       </c>
       <c r="G82" t="n">
-        <v>4.01201009750366</v>
+        <v>4.0120096206665</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G85" t="n">
-        <v>3.96133160591125</v>
+        <v>3.96133208274841</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96133160591125</v>
+        <v>3.96133208274841</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96133160591125</v>
+        <v>3.96133208274841</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.88531422615051</v>
+        <v>3.88531446456909</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>3.834636926651</v>
+        <v>3.83463668823242</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>3.69104909896851</v>
+        <v>3.69104886054993</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G93" t="n">
-        <v>3.73328113555908</v>
+        <v>3.73328042030334</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>3.73328113555908</v>
+        <v>3.73328042030334</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>3.67415595054626</v>
+        <v>3.67415618896484</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>3.62347793579102</v>
+        <v>3.62347817420959</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>3.60658550262451</v>
+        <v>3.60658574104309</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.25</v>
       </c>
       <c r="G100" t="n">
-        <v>3.58969283103943</v>
+        <v>3.58969306945801</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.25</v>
       </c>
       <c r="G101" t="n">
-        <v>3.58969283103943</v>
+        <v>3.58969306945801</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.25</v>
       </c>
       <c r="G102" t="n">
-        <v>3.58969283103943</v>
+        <v>3.58969306945801</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>3.60658550262451</v>
+        <v>3.60658574104309</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>3.50522994995117</v>
+        <v>3.50522947311401</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>3.50522994995117</v>
+        <v>3.50522947311401</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>3.66571021080017</v>
+        <v>3.66571044921875</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>3.86842203140259</v>
+        <v>3.86842226982117</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96977734565735</v>
+        <v>3.96977782249451</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>3.9782247543335</v>
+        <v>3.97822427749634</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G112" t="n">
-        <v>3.96133160591125</v>
+        <v>3.96133208274841</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>3.86842203140259</v>
+        <v>3.86842226982117</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86842203140259</v>
+        <v>3.86842226982117</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.75</v>
       </c>
       <c r="G117" t="n">
-        <v>4.01201009750366</v>
+        <v>4.0120096206665</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.75</v>
       </c>
       <c r="G118" t="n">
-        <v>4.01201009750366</v>
+        <v>4.0120096206665</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G123" t="n">
-        <v>3.81774425506592</v>
+        <v>3.81774377822876</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G124" t="n">
-        <v>3.81774425506592</v>
+        <v>3.81774377822876</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G126" t="n">
-        <v>3.85997581481934</v>
+        <v>3.85997557640076</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G127" t="n">
-        <v>3.79240465164185</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.80085062980652</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.5</v>
       </c>
       <c r="G129" t="n">
-        <v>3.80085062980652</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.5</v>
       </c>
       <c r="G130" t="n">
-        <v>3.80085062980652</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>3.80085062980652</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>3.93599200248718</v>
+        <v>3.93599247932434</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>3.93599200248718</v>
+        <v>3.93599247932434</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>3.93599200248718</v>
+        <v>3.93599247932434</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>3.93599200248718</v>
+        <v>3.93599247932434</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.79240465164185</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>3.79240465164185</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G148" t="n">
-        <v>3.88531422615051</v>
+        <v>3.88531446456909</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>3.79240465164185</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G150" t="n">
-        <v>3.79240465164185</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G151" t="n">
-        <v>3.81774425506592</v>
+        <v>3.81774377822876</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.834636926651</v>
+        <v>3.83463668823242</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G153" t="n">
-        <v>3.73328113555908</v>
+        <v>3.73328042030334</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>3.73328113555908</v>
+        <v>3.73328042030334</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G155" t="n">
-        <v>3.64881730079651</v>
+        <v>3.64881753921509</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G156" t="n">
-        <v>3.64881730079651</v>
+        <v>3.64881753921509</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G157" t="n">
-        <v>3.64881730079651</v>
+        <v>3.64881753921509</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40387368202209</v>
+        <v>3.40387344360352</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G165" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G167" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.5</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95621752738953</v>
+        <v>2.95621776580811</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.75</v>
       </c>
       <c r="G169" t="n">
-        <v>3.16737580299377</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.75</v>
       </c>
       <c r="G170" t="n">
-        <v>3.16737580299377</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.75</v>
       </c>
       <c r="G171" t="n">
-        <v>3.16737580299377</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.75</v>
       </c>
       <c r="G172" t="n">
-        <v>3.16737580299377</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75</v>
       </c>
       <c r="G173" t="n">
-        <v>3.16737580299377</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G174" t="n">
-        <v>2.91398596763611</v>
+        <v>2.91398620605469</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G175" t="n">
-        <v>2.91398596763611</v>
+        <v>2.91398620605469</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12514424324036</v>
+        <v>3.12514400482178</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G177" t="n">
-        <v>3.25183939933777</v>
+        <v>3.25183963775635</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>3.25183939933777</v>
+        <v>3.25183963775635</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25183939933777</v>
+        <v>3.25183963775635</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G180" t="n">
-        <v>3.20960736274719</v>
+        <v>3.20960760116577</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G181" t="n">
-        <v>3.20960736274719</v>
+        <v>3.20960760116577</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.20960736274719</v>
+        <v>3.20960760116577</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>3.20960736274719</v>
+        <v>3.20960760116577</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.20960736274719</v>
+        <v>3.20960760116577</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G185" t="n">
-        <v>3.20960736274719</v>
+        <v>3.20960760116577</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.34474873542786</v>
+        <v>3.34474921226501</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G187" t="n">
-        <v>3.34474873542786</v>
+        <v>3.34474921226501</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.32785630226135</v>
+        <v>3.32785654067993</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G190" t="n">
-        <v>3.20960736274719</v>
+        <v>3.20960760116577</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G191" t="n">
-        <v>3.20960736274719</v>
+        <v>3.20960760116577</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G192" t="n">
-        <v>3.20960736274719</v>
+        <v>3.20960760116577</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>3.20960736274719</v>
+        <v>3.20960760116577</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G195" t="n">
-        <v>3.10825157165527</v>
+        <v>3.10825181007385</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G196" t="n">
-        <v>3.10825157165527</v>
+        <v>3.10825181007385</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G197" t="n">
-        <v>3.10825157165527</v>
+        <v>3.10825181007385</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>3.10825157165527</v>
+        <v>3.10825181007385</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>3.29407095909119</v>
+        <v>3.29407119750977</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G202" t="n">
-        <v>3.36242938041687</v>
+        <v>3.36242961883545</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>3.36242938041687</v>
+        <v>3.36242961883545</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>3.36242938041687</v>
+        <v>3.36242961883545</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G205" t="n">
-        <v>3.36242938041687</v>
+        <v>3.36242961883545</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G206" t="n">
-        <v>3.2938084602356</v>
+        <v>3.29380822181702</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G207" t="n">
-        <v>3.2938084602356</v>
+        <v>3.29380822181702</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G208" t="n">
-        <v>3.2938084602356</v>
+        <v>3.29380822181702</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G209" t="n">
-        <v>3.2938084602356</v>
+        <v>3.29380822181702</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G210" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G211" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G212" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G213" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.3452742099762</v>
+        <v>3.34527444839478</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="n">
-        <v>3.37958455085754</v>
+        <v>3.37958478927612</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="n">
-        <v>3.37958455085754</v>
+        <v>3.37958478927612</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.37958455085754</v>
+        <v>3.37958478927612</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682639122009</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682639122009</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682639122009</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682639122009</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>3.3452742099762</v>
+        <v>3.34527444839478</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>3.242342710495</v>
+        <v>3.24234247207642</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="n">
-        <v>3.25949764251709</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="n">
-        <v>3.242342710495</v>
+        <v>3.24234247207642</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>3.242342710495</v>
+        <v>3.24234247207642</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>3.242342710495</v>
+        <v>3.24234247207642</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G252" t="n">
-        <v>3.20803213119507</v>
+        <v>3.20803236961365</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>3.07079029083252</v>
+        <v>3.07079005241394</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>3.07079029083252</v>
+        <v>3.07079005241394</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>3.07079029083252</v>
+        <v>3.07079005241394</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>3.0193247795105</v>
+        <v>3.01932454109192</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="n">
-        <v>3.00216913223267</v>
+        <v>3.00216889381409</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.74484062194824</v>
+        <v>2.74484038352966</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>2.77915120124817</v>
+        <v>2.77915096282959</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86492705345154</v>
+        <v>2.86492729187012</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="n">
-        <v>2.74484062194824</v>
+        <v>2.74484038352966</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>2.72768521308899</v>
+        <v>2.72768497467041</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>2.74484062194824</v>
+        <v>2.74484038352966</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="n">
-        <v>2.74484062194824</v>
+        <v>2.74484038352966</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.74484062194824</v>
+        <v>2.74484038352966</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="n">
-        <v>2.31595897674561</v>
+        <v>2.31595921516418</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.31595897674561</v>
+        <v>2.31595921516418</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>2.28164863586426</v>
+        <v>2.28164839744568</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G316" t="n">
-        <v>2.28164863586426</v>
+        <v>2.28164839744568</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>2.26449346542358</v>
+        <v>2.264493227005</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.26449346542358</v>
+        <v>2.264493227005</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="n">
-        <v>2.26449346542358</v>
+        <v>2.264493227005</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="n">
-        <v>2.26449346542358</v>
+        <v>2.264493227005</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="n">
-        <v>2.26449346542358</v>
+        <v>2.264493227005</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="n">
-        <v>2.26449346542358</v>
+        <v>2.264493227005</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>2.16156196594238</v>
+        <v>2.1615617275238</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>2.11009621620178</v>
+        <v>2.1100959777832</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>1.9556987285614</v>
+        <v>1.95569884777069</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="n">
-        <v>1.9042329788208</v>
+        <v>1.90423309803009</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>1.88707768917084</v>
+        <v>1.88707780838013</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>1.81845653057098</v>
+        <v>1.81845664978027</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>1.78414618968964</v>
+        <v>1.78414607048035</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="n">
-        <v>1.78414618968964</v>
+        <v>1.78414607048035</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>1.78414618968964</v>
+        <v>1.78414607048035</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76699090003967</v>
+        <v>1.76699101924896</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="n">
-        <v>1.8013014793396</v>
+        <v>1.80130159854889</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>2.09294104576111</v>
+        <v>2.09294080734253</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>2.16156196594238</v>
+        <v>2.1615617275238</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>2.19587230682373</v>
+        <v>2.19587206840515</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>2.11009621620178</v>
+        <v>2.1100959777832</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="n">
-        <v>2.65906429290771</v>
+        <v>2.65906381607056</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="n">
-        <v>2.43604588508606</v>
+        <v>2.43604564666748</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="n">
-        <v>2.45320081710815</v>
+        <v>2.45320105552673</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.41889047622681</v>
+        <v>2.41889071464539</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="n">
-        <v>2.43604588508606</v>
+        <v>2.43604564666748</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="n">
-        <v>2.31595897674561</v>
+        <v>2.31595921516418</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="n">
-        <v>2.43604588508606</v>
+        <v>2.43604564666748</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="n">
-        <v>2.41889047622681</v>
+        <v>2.41889071464539</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.41889047622681</v>
+        <v>2.41889071464539</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="n">
-        <v>2.31595897674561</v>
+        <v>2.31595921516418</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="n">
-        <v>2.45320081710815</v>
+        <v>2.45320105552673</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="n">
-        <v>2.45320081710815</v>
+        <v>2.45320105552673</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="n">
-        <v>2.52182221412659</v>
+        <v>2.52182197570801</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="n">
-        <v>2.52182221412659</v>
+        <v>2.52182197570801</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="n">
-        <v>2.52182221412659</v>
+        <v>2.52182197570801</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="n">
-        <v>2.43604588508606</v>
+        <v>2.43604564666748</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="n">
-        <v>2.45320081710815</v>
+        <v>2.45320105552673</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>2.31595897674561</v>
+        <v>2.31595921516418</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="n">
-        <v>2.40173554420471</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="n">
-        <v>2.52182221412659</v>
+        <v>2.52182197570801</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="n">
-        <v>2.59044289588928</v>
+        <v>2.59044313430786</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>2.59044289588928</v>
+        <v>2.59044313430786</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G430" t="n">
-        <v>2.71052980422974</v>
+        <v>2.71053004264832</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G431" t="n">
-        <v>2.71052980422974</v>
+        <v>2.71053004264832</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="n">
-        <v>2.72768521308899</v>
+        <v>2.72768497467041</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="n">
-        <v>3.00216913223267</v>
+        <v>3.00216889381409</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>2.96785855293274</v>
+        <v>2.96785879135132</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.96785855293274</v>
+        <v>2.96785879135132</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>3.03647971153259</v>
+        <v>3.03647994995117</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="n">
-        <v>3.15656638145447</v>
+        <v>3.15656661987305</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.25949764251709</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="n">
-        <v>3.25949764251709</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G446" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="n">
-        <v>3.15656638145447</v>
+        <v>3.15656661987305</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="n">
-        <v>3.15656638145447</v>
+        <v>3.15656661987305</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="n">
-        <v>3.15656638145447</v>
+        <v>3.15656661987305</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>3.15656638145447</v>
+        <v>3.15656661987305</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="n">
-        <v>3.25949764251709</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G499" t="n">
-        <v>3.97845005989075</v>
+        <v>3.97844982147217</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G512" t="n">
-        <v>4.20529174804688</v>
+        <v>4.20529222488403</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G513" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G518" t="n">
-        <v>4.20529174804688</v>
+        <v>4.20529222488403</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G547" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G549" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G562" t="n">
-        <v>4.20529174804688</v>
+        <v>4.20529222488403</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G563" t="n">
-        <v>4.20529174804688</v>
+        <v>4.20529222488403</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G565" t="n">
-        <v>4.20529174804688</v>
+        <v>4.20529222488403</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G592" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G595" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G596" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G599" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G603" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G604" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.5</v>
       </c>
       <c r="G617" t="n">
-        <v>3.92610144615173</v>
+        <v>3.92610192298889</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>4.5</v>
       </c>
       <c r="G618" t="n">
-        <v>3.92610144615173</v>
+        <v>3.92610192298889</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>4.5</v>
       </c>
       <c r="G624" t="n">
-        <v>3.92610144615173</v>
+        <v>3.92610192298889</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>3.96100115776062</v>
+        <v>3.96100091934204</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>3.90865254402161</v>
+        <v>3.90865302085876</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>3.96100115776062</v>
+        <v>3.96100091934204</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>3.96100115776062</v>
+        <v>3.96100091934204</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>3.97845005989075</v>
+        <v>3.97844982147217</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>3.97845005989075</v>
+        <v>3.97844982147217</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.5</v>
       </c>
       <c r="G654" t="n">
-        <v>3.92610144615173</v>
+        <v>3.92610192298889</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>3.8912034034729</v>
+        <v>3.89120364189148</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>3.8912034034729</v>
+        <v>3.89120364189148</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G660" t="n">
-        <v>3.97845005989075</v>
+        <v>3.97844982147217</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G666" t="n">
-        <v>3.96100115776062</v>
+        <v>3.96100091934204</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.5</v>
       </c>
       <c r="G667" t="n">
-        <v>3.92610144615173</v>
+        <v>3.92610192298889</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.5</v>
       </c>
       <c r="G668" t="n">
-        <v>3.92610144615173</v>
+        <v>3.92610192298889</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.5</v>
       </c>
       <c r="G671" t="n">
-        <v>3.92610144615173</v>
+        <v>3.92610192298889</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G675" t="n">
-        <v>3.31537485122681</v>
+        <v>3.31537508964539</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>3.42007112503052</v>
+        <v>3.4200713634491</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>3.42007112503052</v>
+        <v>3.4200713634491</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>3.42007112503052</v>
+        <v>3.4200713634491</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G680" t="n">
-        <v>3.42007112503052</v>
+        <v>3.4200713634491</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G681" t="n">
-        <v>3.64691257476807</v>
+        <v>3.64691233634949</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G682" t="n">
-        <v>3.64691257476807</v>
+        <v>3.64691233634949</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64691257476807</v>
+        <v>3.64691233634949</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G684" t="n">
-        <v>3.64691257476807</v>
+        <v>3.64691233634949</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G685" t="n">
-        <v>3.64691257476807</v>
+        <v>3.64691233634949</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.5</v>
       </c>
       <c r="G690" t="n">
-        <v>3.92610144615173</v>
+        <v>3.92610192298889</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>3.96100115776062</v>
+        <v>3.96100091934204</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G694" t="n">
-        <v>4.18784189224243</v>
+        <v>4.18784236907959</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.75</v>
       </c>
       <c r="G701" t="n">
-        <v>4.14421892166138</v>
+        <v>4.14421844482422</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.75</v>
       </c>
       <c r="G702" t="n">
-        <v>4.14421892166138</v>
+        <v>4.14421844482422</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.75</v>
       </c>
       <c r="G704" t="n">
-        <v>4.14421892166138</v>
+        <v>4.14421844482422</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.75</v>
       </c>
       <c r="G705" t="n">
-        <v>4.14421892166138</v>
+        <v>4.14421844482422</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.75</v>
       </c>
       <c r="G706" t="n">
-        <v>4.14421892166138</v>
+        <v>4.14421844482422</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>3.99589943885803</v>
+        <v>3.99589920043945</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.75</v>
       </c>
       <c r="G713" t="n">
-        <v>4.14421892166138</v>
+        <v>4.14421844482422</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>3.99589943885803</v>
+        <v>3.99589920043945</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G715" t="n">
-        <v>3.99589943885803</v>
+        <v>3.99589920043945</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>3.99613499641418</v>
+        <v>3.99613475799561</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G718" t="n">
-        <v>3.99613499641418</v>
+        <v>3.99613475799561</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.12157392501831</v>
+        <v>4.12157344818115</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G739" t="n">
-        <v>4.15741395950317</v>
+        <v>4.15741348266602</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G741" t="n">
-        <v>4.00509452819824</v>
+        <v>4.00509405136108</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G742" t="n">
-        <v>4.00509452819824</v>
+        <v>4.00509405136108</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G745" t="n">
-        <v>4.04093503952026</v>
+        <v>4.04093456268311</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G746" t="n">
-        <v>3.92445516586304</v>
+        <v>3.92445540428162</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G747" t="n">
-        <v>3.92445516586304</v>
+        <v>3.92445540428162</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G748" t="n">
-        <v>3.92445516586304</v>
+        <v>3.92445540428162</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G757" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G770" t="n">
-        <v>3.8706955909729</v>
+        <v>3.87069582939148</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G771" t="n">
-        <v>3.8706955909729</v>
+        <v>3.87069582939148</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G772" t="n">
-        <v>3.8706955909729</v>
+        <v>3.87069582939148</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G773" t="n">
-        <v>3.87965559959412</v>
+        <v>3.87965536117554</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G782" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G790" t="n">
-        <v>3.83485627174377</v>
+        <v>3.8348560333252</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G791" t="n">
-        <v>3.83485627174377</v>
+        <v>3.8348560333252</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G792" t="n">
-        <v>3.83485627174377</v>
+        <v>3.8348560333252</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G793" t="n">
-        <v>3.83485627174377</v>
+        <v>3.8348560333252</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G794" t="n">
-        <v>3.83485627174377</v>
+        <v>3.8348560333252</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G795" t="n">
-        <v>3.83485627174377</v>
+        <v>3.8348560333252</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G796" t="n">
-        <v>3.83485627174377</v>
+        <v>3.8348560333252</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.25</v>
       </c>
       <c r="G807" t="n">
-        <v>3.80797576904297</v>
+        <v>3.80797600746155</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.25</v>
       </c>
       <c r="G808" t="n">
-        <v>3.80797576904297</v>
+        <v>3.80797600746155</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.25</v>
       </c>
       <c r="G809" t="n">
-        <v>3.80797576904297</v>
+        <v>3.80797600746155</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G810" t="n">
-        <v>3.71837687492371</v>
+        <v>3.71837663650513</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G822" t="n">
-        <v>3.91549515724182</v>
+        <v>3.9154953956604</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>3.91549515724182</v>
+        <v>3.9154953956604</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>3.91549515724182</v>
+        <v>3.9154953956604</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G825" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G826" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G827" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G828" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>3.71837687492371</v>
+        <v>3.71837663650513</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G834" t="n">
-        <v>3.7810959815979</v>
+        <v>3.78109622001648</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G836" t="n">
-        <v>3.7810959815979</v>
+        <v>3.78109622001648</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G837" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G838" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.96925473213196</v>
+        <v>3.96925497055054</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>4.00509452819824</v>
+        <v>4.00509405136108</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G851" t="n">
-        <v>3.8706955909729</v>
+        <v>3.87069582939148</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G852" t="n">
-        <v>3.8706955909729</v>
+        <v>3.87069582939148</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G853" t="n">
-        <v>3.8706955909729</v>
+        <v>3.87069582939148</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G854" t="n">
-        <v>3.8706955909729</v>
+        <v>3.87069582939148</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.8706955909729</v>
+        <v>3.87069582939148</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G859" t="n">
-        <v>3.7810959815979</v>
+        <v>3.78109622001648</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G872" t="n">
-        <v>3.69149684906006</v>
+        <v>3.69149661064148</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G873" t="n">
-        <v>3.8706955909729</v>
+        <v>3.87069582939148</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G874" t="n">
-        <v>3.83485627174377</v>
+        <v>3.8348560333252</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G875" t="n">
-        <v>3.83485627174377</v>
+        <v>3.8348560333252</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>3.69149684906006</v>
+        <v>3.69149661064148</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.25</v>
       </c>
       <c r="G911" t="n">
-        <v>3.80797576904297</v>
+        <v>3.80797600746155</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.25</v>
       </c>
       <c r="G912" t="n">
-        <v>3.80797576904297</v>
+        <v>3.80797600746155</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.25</v>
       </c>
       <c r="G913" t="n">
-        <v>3.80797576904297</v>
+        <v>3.80797600746155</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87965559959412</v>
+        <v>3.87965536117554</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G918" t="n">
-        <v>3.92445516586304</v>
+        <v>3.92445540428162</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G919" t="n">
-        <v>3.92445516586304</v>
+        <v>3.92445540428162</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G920" t="n">
-        <v>3.92445516586304</v>
+        <v>3.92445540428162</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>4.13053369522095</v>
+        <v>4.13053417205811</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G937" t="n">
-        <v>3.95133543014526</v>
+        <v>3.95133495330811</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G949" t="n">
-        <v>4.07677459716797</v>
+        <v>4.07677507400513</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G950" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G951" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G959" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G960" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>3.9602952003479</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.12157392501831</v>
+        <v>4.12157344818115</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G980" t="n">
-        <v>4.11231231689453</v>
+        <v>4.11231184005737</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G981" t="n">
-        <v>4.11231231689453</v>
+        <v>4.11231184005737</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>4.11231231689453</v>
+        <v>4.11231184005737</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G983" t="n">
-        <v>4.11231231689453</v>
+        <v>4.11231184005737</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G984" t="n">
-        <v>4.11231231689453</v>
+        <v>4.11231184005737</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G985" t="n">
-        <v>4.11231231689453</v>
+        <v>4.11231184005737</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G986" t="n">
-        <v>4.11231231689453</v>
+        <v>4.11231184005737</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>4.11231231689453</v>
+        <v>4.11231184005737</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G992" t="n">
-        <v>3.9085488319397</v>
+        <v>3.90854859352112</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G993" t="n">
-        <v>3.87150096893311</v>
+        <v>3.87150073051453</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G998" t="n">
-        <v>3.77888131141663</v>
+        <v>3.77888107299805</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G999" t="n">
-        <v>3.87150096893311</v>
+        <v>3.87150073051453</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.87150096893311</v>
+        <v>3.87150073051453</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.83445310592651</v>
+        <v>3.83445286750793</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.77888131141663</v>
+        <v>3.77888107299805</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.77888131141663</v>
+        <v>3.77888107299805</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.83445310592651</v>
+        <v>3.83445286750793</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.61216592788696</v>
+        <v>3.61216616630554</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.61216592788696</v>
+        <v>3.61216616630554</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.57511782646179</v>
+        <v>3.57511806488037</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.3713550567627</v>
+        <v>3.37135481834412</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.26021146774292</v>
+        <v>3.26021122932434</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.61216592788696</v>
+        <v>3.61216616630554</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.57511782646179</v>
+        <v>3.57511806488037</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.57511782646179</v>
+        <v>3.57511806488037</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.57511782646179</v>
+        <v>3.57511806488037</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.63068985939026</v>
+        <v>3.63069009780884</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.61216592788696</v>
+        <v>3.61216616630554</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.61216592788696</v>
+        <v>3.61216616630554</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.61216592788696</v>
+        <v>3.61216616630554</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.77888131141663</v>
+        <v>3.77888107299805</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.77888131141663</v>
+        <v>3.77888107299805</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.77888131141663</v>
+        <v>3.77888107299805</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.77888131141663</v>
+        <v>3.77888107299805</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.83445310592651</v>
+        <v>3.83445286750793</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.77888131141663</v>
+        <v>3.77888107299805</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.83445310592651</v>
+        <v>3.83445286750793</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.83445310592651</v>
+        <v>3.83445286750793</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.83445310592651</v>
+        <v>3.83445286750793</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.79740524291992</v>
+        <v>3.79740500450134</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.63068985939026</v>
+        <v>3.63069009780884</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.61216592788696</v>
+        <v>3.61216616630554</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.57511782646179</v>
+        <v>3.57511806488037</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.63068985939026</v>
+        <v>3.63069009780884</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.57511782646179</v>
+        <v>3.57511806488037</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.63068985939026</v>
+        <v>3.63069009780884</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.59364199638367</v>
+        <v>3.59364223480225</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.61216592788696</v>
+        <v>3.61216616630554</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.61216592788696</v>
+        <v>3.61216616630554</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.61216592788696</v>
+        <v>3.61216616630554</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.57511782646179</v>
+        <v>3.57511806488037</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.63068985939026</v>
+        <v>3.63069009780884</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.63068985939026</v>
+        <v>3.63069009780884</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.63068985939026</v>
+        <v>3.63069009780884</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.63068985939026</v>
+        <v>3.63069009780884</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.77888131141663</v>
+        <v>3.77888107299805</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.77888131141663</v>
+        <v>3.77888107299805</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -45638,6 +45638,32 @@
         <v>2.24000000953674</v>
       </c>
       <c r="H1741" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="1" t="n">
+        <v>46167.2916666667</v>
+      </c>
+      <c r="B1742" t="n">
+        <v>10750</v>
+      </c>
+      <c r="C1742" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G1742" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H1742" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2" t="n">
-        <v>4.19782781600952</v>
+        <v>4.19782829284668</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4.434326171875</v>
+        <v>4.43432664871216</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39209508895874</v>
+        <v>4.39209461212158</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>4.25695323944092</v>
+        <v>4.25695371627808</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>4.25695323944092</v>
+        <v>4.25695371627808</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.23161458969116</v>
+        <v>4.23161506652832</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>4.25695323944092</v>
+        <v>4.25695371627808</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G42" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>3.90220713615417</v>
+        <v>3.90220665931702</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>4.19782781600952</v>
+        <v>4.19782829284668</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>3.67415642738342</v>
+        <v>3.67415595054626</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G96" t="n">
-        <v>3.59813928604126</v>
+        <v>3.59813904762268</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>3.60658526420593</v>
+        <v>3.60658550262451</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.25</v>
       </c>
       <c r="G100" t="n">
-        <v>3.58969259262085</v>
+        <v>3.58969306945801</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.25</v>
       </c>
       <c r="G101" t="n">
-        <v>3.58969259262085</v>
+        <v>3.58969306945801</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.25</v>
       </c>
       <c r="G102" t="n">
-        <v>3.58969259262085</v>
+        <v>3.58969306945801</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>3.60658526420593</v>
+        <v>3.60658550262451</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>3.50522947311401</v>
+        <v>3.50522971153259</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>3.50522947311401</v>
+        <v>3.50522971153259</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>3.93599271774292</v>
+        <v>3.93599224090576</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>3.93599271774292</v>
+        <v>3.93599224090576</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>3.93599271774292</v>
+        <v>3.93599224090576</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>3.93599271774292</v>
+        <v>3.93599224090576</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G158" t="n">
-        <v>3.59813928604126</v>
+        <v>3.59813904762268</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40387344360352</v>
+        <v>3.40387368202209</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G174" t="n">
-        <v>2.91398596763611</v>
+        <v>2.91398620605469</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G175" t="n">
-        <v>2.91398596763611</v>
+        <v>2.91398620605469</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.32785654067993</v>
+        <v>3.32785630226135</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>3.19271516799927</v>
+        <v>3.19271492958069</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -45716,6 +45716,32 @@
         <v>2.22000002861023</v>
       </c>
       <c r="H1744" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="1" t="n">
+        <v>46170.2916666667</v>
+      </c>
+      <c r="B1745" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1745" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="D1745" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G1745" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="H1745" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -473,7 +473,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3456392288208</v>
+        <v>4.34563970565796</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G5" t="n">
-        <v>4.29073810577393</v>
+        <v>4.29073858261108</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4.434326171875</v>
+        <v>4.43432664871216</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39209508895874</v>
+        <v>4.39209461212158</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.0479998588562</v>
       </c>
       <c r="G10" t="n">
-        <v>4.26371049880981</v>
+        <v>4.26371002197266</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G14" t="n">
-        <v>4.10491991043091</v>
+        <v>4.10491943359375</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G15" t="n">
-        <v>4.10491991043091</v>
+        <v>4.10491943359375</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>4.10491991043091</v>
+        <v>4.10491943359375</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>3.91149854660034</v>
+        <v>3.91149830818176</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G25" t="n">
-        <v>4.10491991043091</v>
+        <v>4.10491943359375</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G26" t="n">
-        <v>4.03734874725342</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G27" t="n">
-        <v>4.03734874725342</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G28" t="n">
-        <v>4.03734874725342</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045679092407</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G30" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045679092407</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G32" t="n">
-        <v>4.12181186676025</v>
+        <v>4.12181234359741</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.05424165725708</v>
+        <v>4.05424118041992</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>4.03734874725342</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>4.03734874725342</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>4.03734874725342</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G38" t="n">
-        <v>4.03734874725342</v>
+        <v>4.03734922409058</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>4.05424165725708</v>
+        <v>4.05424118041992</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G40" t="n">
-        <v>4.13025808334351</v>
+        <v>4.13025856018066</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G42" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>4.05424165725708</v>
+        <v>4.05424118041992</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>4.04579448699951</v>
+        <v>4.04579544067383</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G50" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G52" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045679092407</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G53" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045679092407</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G56" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045679092407</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.5</v>
       </c>
       <c r="G57" t="n">
-        <v>3.80085110664368</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G58" t="n">
-        <v>3.82619047164917</v>
+        <v>3.82619023323059</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>3.90220713615417</v>
+        <v>3.90220642089844</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G60" t="n">
-        <v>3.91065406799316</v>
+        <v>3.91065311431885</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>3.91065406799316</v>
+        <v>3.91065311431885</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>4.12181186676025</v>
+        <v>4.12181234359741</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.75</v>
       </c>
       <c r="G65" t="n">
-        <v>4.0120096206665</v>
+        <v>4.01201009750366</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5</v>
       </c>
       <c r="G70" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G72" t="n">
-        <v>4.12181186676025</v>
+        <v>4.12181234359741</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>4.05424165725708</v>
+        <v>4.05424118041992</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>4.05424165725708</v>
+        <v>4.05424118041992</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>4.13870477676392</v>
+        <v>4.13870429992676</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>3.96133232116699</v>
+        <v>3.96133208274841</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.75</v>
       </c>
       <c r="G82" t="n">
-        <v>4.0120096206665</v>
+        <v>4.01201009750366</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>4.05424165725708</v>
+        <v>4.05424118041992</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>4.05424165725708</v>
+        <v>4.05424118041992</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G85" t="n">
-        <v>3.96133232116699</v>
+        <v>3.96133208274841</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96133232116699</v>
+        <v>3.96133208274841</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96133232116699</v>
+        <v>3.96133208274841</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.88531422615051</v>
+        <v>3.88531398773193</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>3.83463644981384</v>
+        <v>3.83463621139526</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.84308290481567</v>
+        <v>3.84308314323425</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>3.69104886054993</v>
+        <v>3.69104838371277</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G93" t="n">
-        <v>3.7332808971405</v>
+        <v>3.73328042030334</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>3.7332808971405</v>
+        <v>3.73328042030334</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>3.67415642738342</v>
+        <v>3.67415618896484</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G96" t="n">
-        <v>3.59813928604126</v>
+        <v>3.59813904762268</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G99" t="n">
-        <v>3.54746150970459</v>
+        <v>3.54746079444885</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.25</v>
       </c>
       <c r="G100" t="n">
-        <v>3.58969283103943</v>
+        <v>3.58969259262085</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.25</v>
       </c>
       <c r="G101" t="n">
-        <v>3.58969283103943</v>
+        <v>3.58969259262085</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.25</v>
       </c>
       <c r="G102" t="n">
-        <v>3.58969283103943</v>
+        <v>3.58969259262085</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>3.66570973396301</v>
+        <v>3.66570997238159</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G107" t="n">
-        <v>3.8515293598175</v>
+        <v>3.85152912139893</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>3.86842203140259</v>
+        <v>3.86842226982117</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96977782249451</v>
+        <v>3.96977806091309</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>3.97822451591492</v>
+        <v>3.97822427749634</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82619047164917</v>
+        <v>3.82619023323059</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G112" t="n">
-        <v>3.96133232116699</v>
+        <v>3.96133208274841</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G113" t="n">
-        <v>3.8515293598175</v>
+        <v>3.85152912139893</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G114" t="n">
-        <v>3.8515293598175</v>
+        <v>3.85152912139893</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>3.86842203140259</v>
+        <v>3.86842226982117</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86842203140259</v>
+        <v>3.86842226982117</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.75</v>
       </c>
       <c r="G117" t="n">
-        <v>4.0120096206665</v>
+        <v>4.01201009750366</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.75</v>
       </c>
       <c r="G118" t="n">
-        <v>4.0120096206665</v>
+        <v>4.01201009750366</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.94443893432617</v>
+        <v>3.94443917274475</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>3.94443893432617</v>
+        <v>3.94443917274475</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G121" t="n">
-        <v>3.91909956932068</v>
+        <v>3.91909980773926</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.91909956932068</v>
+        <v>3.91909980773926</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G123" t="n">
-        <v>3.81774401664734</v>
+        <v>3.81774377822876</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G124" t="n">
-        <v>3.81774401664734</v>
+        <v>3.81774377822876</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G125" t="n">
-        <v>3.91909956932068</v>
+        <v>3.91909980773926</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G126" t="n">
-        <v>3.85997533798218</v>
+        <v>3.85997557640076</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G127" t="n">
-        <v>3.79240465164185</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.80085110664368</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.5</v>
       </c>
       <c r="G129" t="n">
-        <v>3.80085110664368</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.5</v>
       </c>
       <c r="G130" t="n">
-        <v>3.80085110664368</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>3.80085110664368</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>3.93599271774292</v>
+        <v>3.93599247932434</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>3.93599271774292</v>
+        <v>3.93599247932434</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>3.93599271774292</v>
+        <v>3.93599247932434</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>3.93599271774292</v>
+        <v>3.93599247932434</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.79240465164185</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>3.79240465164185</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>3.84308290481567</v>
+        <v>3.84308314323425</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G142" t="n">
-        <v>3.84308290481567</v>
+        <v>3.84308314323425</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G143" t="n">
-        <v>3.84308290481567</v>
+        <v>3.84308314323425</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>3.84308290481567</v>
+        <v>3.84308314323425</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G145" t="n">
-        <v>3.84308290481567</v>
+        <v>3.84308314323425</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>3.84308290481567</v>
+        <v>3.84308314323425</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>3.84308290481567</v>
+        <v>3.84308314323425</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G148" t="n">
-        <v>3.88531422615051</v>
+        <v>3.88531398773193</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>3.79240465164185</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G150" t="n">
-        <v>3.79240465164185</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G151" t="n">
-        <v>3.81774401664734</v>
+        <v>3.81774377822876</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.83463644981384</v>
+        <v>3.83463621139526</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G153" t="n">
-        <v>3.7332808971405</v>
+        <v>3.73328042030334</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>3.7332808971405</v>
+        <v>3.73328042030334</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G158" t="n">
-        <v>3.59813928604126</v>
+        <v>3.59813904762268</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>3.54746150970459</v>
+        <v>3.54746079444885</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>3.42921257019043</v>
+        <v>3.42921233177185</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>3.42921257019043</v>
+        <v>3.42921233177185</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G162" t="n">
-        <v>3.42921257019043</v>
+        <v>3.42921233177185</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40387368202209</v>
+        <v>3.40387344360352</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G165" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G167" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.75</v>
       </c>
       <c r="G169" t="n">
-        <v>3.16737604141235</v>
+        <v>3.16737580299377</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.75</v>
       </c>
       <c r="G170" t="n">
-        <v>3.16737604141235</v>
+        <v>3.16737580299377</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.75</v>
       </c>
       <c r="G171" t="n">
-        <v>3.16737604141235</v>
+        <v>3.16737580299377</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.75</v>
       </c>
       <c r="G172" t="n">
-        <v>3.16737604141235</v>
+        <v>3.16737580299377</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75</v>
       </c>
       <c r="G173" t="n">
-        <v>3.16737604141235</v>
+        <v>3.16737580299377</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G174" t="n">
-        <v>2.91398596763611</v>
+        <v>2.91398620605469</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G175" t="n">
-        <v>2.91398596763611</v>
+        <v>2.91398620605469</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.32785654067993</v>
+        <v>3.32785630226135</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>3.41231989860535</v>
+        <v>3.41231966018677</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>3.19271492958069</v>
+        <v>3.19271516799927</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G195" t="n">
-        <v>3.10825181007385</v>
+        <v>3.10825204849243</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G196" t="n">
-        <v>3.10825181007385</v>
+        <v>3.10825204849243</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G197" t="n">
-        <v>3.10825181007385</v>
+        <v>3.10825204849243</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>3.10825181007385</v>
+        <v>3.10825204849243</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G210" t="n">
-        <v>3.13941097259521</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G211" t="n">
-        <v>3.13941097259521</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G212" t="n">
-        <v>3.13941097259521</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G213" t="n">
-        <v>3.13941097259521</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13941097259521</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>3.31096386909485</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.3452742099762</v>
+        <v>3.34527444839478</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682639122009</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682639122009</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682639122009</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682639122009</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>3.3452742099762</v>
+        <v>3.34527444839478</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>3.242342710495</v>
+        <v>3.24234247207642</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="n">
-        <v>3.25949788093567</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="n">
-        <v>3.242342710495</v>
+        <v>3.24234247207642</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>3.242342710495</v>
+        <v>3.24234247207642</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>3.242342710495</v>
+        <v>3.24234247207642</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>3.13941097259521</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>3.13941097259521</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="n">
-        <v>3.00216937065125</v>
+        <v>3.00216889381409</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>2.91639304161072</v>
+        <v>2.91639280319214</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="n">
-        <v>2.88208246231079</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>2.77915072441101</v>
+        <v>2.77915096282959</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>2.72768545150757</v>
+        <v>2.72768497467041</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="n">
-        <v>2.57328772544861</v>
+        <v>2.57328796386719</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>2.16156196594238</v>
+        <v>2.1615617275238</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>2.11009621620178</v>
+        <v>2.1100959777832</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>2.07578539848328</v>
+        <v>2.07578563690186</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>1.95569896697998</v>
+        <v>1.95569884777069</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="n">
-        <v>1.90423285961151</v>
+        <v>1.90423309803009</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="n">
-        <v>1.83561217784882</v>
+        <v>1.83561193943024</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>1.81845653057098</v>
+        <v>1.81845664978027</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>1.78414618968964</v>
+        <v>1.78414607048035</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="n">
-        <v>1.78414618968964</v>
+        <v>1.78414607048035</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>1.78414618968964</v>
+        <v>1.78414607048035</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76699090003967</v>
+        <v>1.76699101924896</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>1.99000906944275</v>
+        <v>1.99000918865204</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="n">
-        <v>2.07578539848328</v>
+        <v>2.07578563690186</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>2.07578539848328</v>
+        <v>2.07578563690186</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>2.16156196594238</v>
+        <v>2.1615617275238</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>2.11009621620178</v>
+        <v>2.1100959777832</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="n">
-        <v>2.12725114822388</v>
+        <v>2.12725138664246</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="n">
-        <v>2.65906405448914</v>
+        <v>2.65906381607056</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="n">
-        <v>2.57328772544861</v>
+        <v>2.57328796386719</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="n">
-        <v>2.43604588508606</v>
+        <v>2.43604564666748</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.41889047622681</v>
+        <v>2.41889071464539</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="n">
-        <v>2.43604588508606</v>
+        <v>2.43604564666748</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="n">
-        <v>2.43604588508606</v>
+        <v>2.43604564666748</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="n">
-        <v>2.41889047622681</v>
+        <v>2.41889071464539</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.41889047622681</v>
+        <v>2.41889071464539</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="n">
-        <v>2.43604588508606</v>
+        <v>2.43604564666748</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.62475347518921</v>
+        <v>2.62475371360779</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="n">
-        <v>2.72768545150757</v>
+        <v>2.72768497467041</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="n">
-        <v>3.00216937065125</v>
+        <v>3.00216889381409</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>3.03647947311401</v>
+        <v>3.03647994995117</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G440" t="n">
-        <v>3.12225580215454</v>
+        <v>3.12225604057312</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.25949788093567</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="n">
-        <v>3.25949788093567</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>3.17372179031372</v>
+        <v>3.17372155189514</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G446" t="n">
-        <v>3.13941097259521</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="n">
-        <v>3.25949788093567</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>3.17372179031372</v>
+        <v>3.17372155189514</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G457" t="n">
-        <v>3.10510087013245</v>
+        <v>3.10510063171387</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="n">
-        <v>2.93354797363281</v>
+        <v>2.93354821205139</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>3.12343215942383</v>
+        <v>3.12343239784241</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05363512039185</v>
+        <v>3.05363488197327</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G469" t="n">
-        <v>3.26302719116211</v>
+        <v>3.26302695274353</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G470" t="n">
-        <v>3.22812843322754</v>
+        <v>3.22812819480896</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>3.22812843322754</v>
+        <v>3.22812819480896</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G478" t="n">
-        <v>3.45496988296509</v>
+        <v>3.45496964454651</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>3.82140612602234</v>
+        <v>3.82140588760376</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.03079748153687</v>
+        <v>4.03079795837402</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G489" t="n">
-        <v>4.29253816604614</v>
+        <v>4.2925386428833</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G490" t="n">
-        <v>4.13549423217773</v>
+        <v>4.13549375534058</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>4.03079748153687</v>
+        <v>4.03079795837402</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G494" t="n">
-        <v>4.13549423217773</v>
+        <v>4.13549375534058</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G495" t="n">
-        <v>4.03079748153687</v>
+        <v>4.03079795837402</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G496" t="n">
-        <v>4.08314657211304</v>
+        <v>4.08314561843872</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G498" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G500" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G502" t="n">
-        <v>4.44958209991455</v>
+        <v>4.44958257675171</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G503" t="n">
-        <v>4.44958209991455</v>
+        <v>4.44958257675171</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G504" t="n">
-        <v>4.40595865249634</v>
+        <v>4.4059591293335</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G505" t="n">
-        <v>4.34488677978516</v>
+        <v>4.344886302948</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>4.49320602416992</v>
+        <v>4.49320554733276</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G507" t="n">
-        <v>4.30998754501343</v>
+        <v>4.30998802185059</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>4.1703929901123</v>
+        <v>4.17039251327515</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G510" t="n">
-        <v>4.1703929901123</v>
+        <v>4.17039251327515</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G511" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G512" t="n">
-        <v>4.20529127120972</v>
+        <v>4.20529222488403</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G514" t="n">
-        <v>4.53682851791382</v>
+        <v>4.53682899475098</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G515" t="n">
-        <v>4.44958209991455</v>
+        <v>4.44958257675171</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>4.32743740081787</v>
+        <v>4.32743692398071</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G518" t="n">
-        <v>4.20529127120972</v>
+        <v>4.20529222488403</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>4.29253816604614</v>
+        <v>4.2925386428833</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G523" t="n">
-        <v>4.13549423217773</v>
+        <v>4.13549375534058</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G525" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>4.03079748153687</v>
+        <v>4.03079795837402</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>3.94355130195618</v>
+        <v>3.94355177879333</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G530" t="n">
-        <v>4.08314657211304</v>
+        <v>4.08314561843872</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.03079748153687</v>
+        <v>4.03079795837402</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G532" t="n">
-        <v>4.11804485321045</v>
+        <v>4.11804437637329</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G534" t="n">
-        <v>4.11804485321045</v>
+        <v>4.11804437637329</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>4.03079748153687</v>
+        <v>4.03079795837402</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G538" t="n">
-        <v>4.03079748153687</v>
+        <v>4.03079795837402</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G543" t="n">
-        <v>4.1703929901123</v>
+        <v>4.17039251327515</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.11804485321045</v>
+        <v>4.11804437637329</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G560" t="n">
-        <v>4.1703929901123</v>
+        <v>4.17039251327515</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G562" t="n">
-        <v>4.20529127120972</v>
+        <v>4.20529222488403</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G563" t="n">
-        <v>4.20529127120972</v>
+        <v>4.20529222488403</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G565" t="n">
-        <v>4.20529127120972</v>
+        <v>4.20529222488403</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G566" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G567" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G573" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>4.30998754501343</v>
+        <v>4.30998802185059</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>4.29253816604614</v>
+        <v>4.2925386428833</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>4.29253816604614</v>
+        <v>4.2925386428833</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G579" t="n">
-        <v>4.32743740081787</v>
+        <v>4.32743692398071</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>4.32743740081787</v>
+        <v>4.32743692398071</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>4.29253816604614</v>
+        <v>4.2925386428833</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G584" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G585" t="n">
-        <v>4.13549423217773</v>
+        <v>4.13549375534058</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>4.34488677978516</v>
+        <v>4.344886302948</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G590" t="n">
-        <v>4.29253816604614</v>
+        <v>4.2925386428833</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G594" t="n">
-        <v>4.1703929901123</v>
+        <v>4.17039251327515</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.25763940811157</v>
+        <v>4.25763988494873</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G600" t="n">
-        <v>4.13549423217773</v>
+        <v>4.13549375534058</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G602" t="n">
-        <v>4.1703929901123</v>
+        <v>4.17039251327515</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>4.08314657211304</v>
+        <v>4.08314561843872</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>4.03079748153687</v>
+        <v>4.03079795837402</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G610" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.03079748153687</v>
+        <v>4.03079795837402</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G613" t="n">
-        <v>4.08314657211304</v>
+        <v>4.08314561843872</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G615" t="n">
-        <v>4.11804485321045</v>
+        <v>4.11804437637329</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>3.94355130195618</v>
+        <v>3.94355177879333</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G623" t="n">
-        <v>3.94355130195618</v>
+        <v>3.94355177879333</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>3.96100068092346</v>
+        <v>3.96100091934204</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>3.90865278244019</v>
+        <v>3.90865302085876</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>3.96100068092346</v>
+        <v>3.96100091934204</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>3.96100068092346</v>
+        <v>3.96100091934204</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G632" t="n">
-        <v>4.11804485321045</v>
+        <v>4.11804437637329</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G633" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G634" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G637" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.08314657211304</v>
+        <v>4.08314561843872</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G644" t="n">
-        <v>4.03079748153687</v>
+        <v>4.03079795837402</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G645" t="n">
-        <v>4.1703929901123</v>
+        <v>4.17039251327515</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G648" t="n">
-        <v>4.11804485321045</v>
+        <v>4.11804437637329</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G649" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G650" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G651" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>3.8912034034729</v>
+        <v>3.89120364189148</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>3.8912034034729</v>
+        <v>3.89120364189148</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G661" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G664" t="n">
-        <v>3.87375354766846</v>
+        <v>3.87375402450562</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>3.87375354766846</v>
+        <v>3.87375402450562</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G666" t="n">
-        <v>3.96100068092346</v>
+        <v>3.96100091934204</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>3.83885550498962</v>
+        <v>3.83885526657104</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G672" t="n">
-        <v>3.80395722389221</v>
+        <v>3.80395698547363</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G674" t="n">
-        <v>3.21067881584167</v>
+        <v>3.21067905426025</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G681" t="n">
-        <v>3.64691257476807</v>
+        <v>3.64691233634949</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G682" t="n">
-        <v>3.64691257476807</v>
+        <v>3.64691233634949</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64691257476807</v>
+        <v>3.64691233634949</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G684" t="n">
-        <v>3.64691257476807</v>
+        <v>3.64691233634949</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G685" t="n">
-        <v>3.64691257476807</v>
+        <v>3.64691233634949</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G686" t="n">
-        <v>3.82140612602234</v>
+        <v>3.82140588760376</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G687" t="n">
-        <v>3.82140612602234</v>
+        <v>3.82140588760376</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>3.87375354766846</v>
+        <v>3.87375402450562</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>3.96100068092346</v>
+        <v>3.96100091934204</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>3.94355130195618</v>
+        <v>3.94355177879333</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>3.94355130195618</v>
+        <v>3.94355177879333</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>4.23146533966064</v>
+        <v>4.2314658164978</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G696" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G698" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G699" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G703" t="n">
-        <v>4.11804485321045</v>
+        <v>4.11804437637329</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G708" t="n">
-        <v>4.06569671630859</v>
+        <v>4.06569623947144</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G716" t="n">
-        <v>3.98717522621155</v>
+        <v>3.98717498779297</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.12157392501831</v>
+        <v>4.12157344818115</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G726" t="n">
-        <v>4.02301406860352</v>
+        <v>4.02301454544067</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G737" t="n">
-        <v>4.22909355163574</v>
+        <v>4.22909307479858</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>4.13949346542358</v>
+        <v>4.13949394226074</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.5</v>
       </c>
       <c r="G749" t="n">
-        <v>4.03197431564331</v>
+        <v>4.03197479248047</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G750" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G751" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G752" t="n">
-        <v>3.93341541290283</v>
+        <v>3.93341493606567</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G753" t="n">
-        <v>3.93341541290283</v>
+        <v>3.93341493606567</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G754" t="n">
-        <v>3.93341541290283</v>
+        <v>3.93341493606567</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G755" t="n">
-        <v>3.93341541290283</v>
+        <v>3.93341493606567</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G757" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G758" t="n">
-        <v>3.93341541290283</v>
+        <v>3.93341493606567</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G760" t="n">
-        <v>3.88861584663391</v>
+        <v>3.88861536979675</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G761" t="n">
-        <v>3.88861584663391</v>
+        <v>3.88861536979675</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G762" t="n">
-        <v>3.88861584663391</v>
+        <v>3.88861536979675</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G763" t="n">
-        <v>3.88861584663391</v>
+        <v>3.88861536979675</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G764" t="n">
-        <v>3.88861584663391</v>
+        <v>3.88861536979675</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G765" t="n">
-        <v>3.88861584663391</v>
+        <v>3.88861536979675</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G773" t="n">
-        <v>3.87965559959412</v>
+        <v>3.87965536117554</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G779" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G782" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.5</v>
       </c>
       <c r="G786" t="n">
-        <v>4.03197431564331</v>
+        <v>4.03197479248047</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.5</v>
       </c>
       <c r="G787" t="n">
-        <v>4.03197431564331</v>
+        <v>4.03197479248047</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.5</v>
       </c>
       <c r="G788" t="n">
-        <v>4.03197431564331</v>
+        <v>4.03197479248047</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.5</v>
       </c>
       <c r="G789" t="n">
-        <v>4.03197431564331</v>
+        <v>4.03197479248047</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G797" t="n">
-        <v>3.8258957862854</v>
+        <v>3.82589554786682</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G811" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G813" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G820" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G825" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G826" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G827" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G828" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G834" t="n">
-        <v>3.7810959815979</v>
+        <v>3.78109622001648</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G836" t="n">
-        <v>3.7810959815979</v>
+        <v>3.78109622001648</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G837" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G838" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G843" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G844" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G846" t="n">
-        <v>3.97821450233459</v>
+        <v>3.97821497917175</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G847" t="n">
-        <v>3.97821450233459</v>
+        <v>3.97821497917175</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G848" t="n">
-        <v>3.97821450233459</v>
+        <v>3.97821497917175</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G849" t="n">
-        <v>3.97821450233459</v>
+        <v>3.97821497917175</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G856" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G859" t="n">
-        <v>3.7810959815979</v>
+        <v>3.78109622001648</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G860" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G861" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G862" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>3.76317620277405</v>
+        <v>3.76317596435547</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>3.76317620277405</v>
+        <v>3.76317596435547</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G865" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G866" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G867" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G868" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G869" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G870" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G876" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G877" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G878" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G880" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G881" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G882" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G883" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G884" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G886" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G887" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G891" t="n">
-        <v>3.63773727416992</v>
+        <v>3.63773703575134</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G892" t="n">
-        <v>3.63773727416992</v>
+        <v>3.63773703575134</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G893" t="n">
-        <v>3.64669704437256</v>
+        <v>3.64669728279114</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G894" t="n">
-        <v>3.64669704437256</v>
+        <v>3.64669728279114</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G897" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G900" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G901" t="n">
-        <v>3.76317620277405</v>
+        <v>3.76317596435547</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G902" t="n">
-        <v>3.7452564239502</v>
+        <v>3.74525618553162</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G906" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>3.79005599021912</v>
+        <v>3.7900562286377</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G909" t="n">
-        <v>3.76317620277405</v>
+        <v>3.76317596435547</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.77213621139526</v>
+        <v>3.77213644981384</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87965559959412</v>
+        <v>3.87965536117554</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>3.84381556510925</v>
+        <v>3.84381580352783</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G923" t="n">
-        <v>3.88861584663391</v>
+        <v>3.88861536979675</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G938" t="n">
-        <v>3.88861584663391</v>
+        <v>3.88861536979675</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173534393311</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G949" t="n">
-        <v>4.07677459716797</v>
+        <v>4.07677507400513</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G950" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G951" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.5</v>
       </c>
       <c r="G956" t="n">
-        <v>4.03197431564331</v>
+        <v>4.03197479248047</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G957" t="n">
-        <v>3.97821450233459</v>
+        <v>3.97821497917175</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.5</v>
       </c>
       <c r="G958" t="n">
-        <v>4.03197431564331</v>
+        <v>4.03197479248047</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G959" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G960" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G961" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.5</v>
       </c>
       <c r="G965" t="n">
-        <v>4.03197431564331</v>
+        <v>4.03197479248047</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.5</v>
       </c>
       <c r="G966" t="n">
-        <v>4.03197431564331</v>
+        <v>4.03197479248047</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.5</v>
       </c>
       <c r="G967" t="n">
-        <v>4.03197431564331</v>
+        <v>4.03197479248047</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>3.96029543876648</v>
+        <v>3.96029496192932</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G969" t="n">
-        <v>3.94237542152405</v>
+        <v>3.94237494468689</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.12157392501831</v>
+        <v>4.12157344818115</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -45794,6 +45794,32 @@
         <v>2.24000000953674</v>
       </c>
       <c r="H1747" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="n">
+        <v>46175.2916666667</v>
+      </c>
+      <c r="B1748" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C1748" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G1748" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="H1748" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -473,7 +473,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>4.34563970565796</v>
+        <v>4.3456392288208</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G8" t="n">
-        <v>4.27553510665894</v>
+        <v>4.27553558349609</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.0479998588562</v>
       </c>
       <c r="G10" t="n">
-        <v>4.26371002197266</v>
+        <v>4.26371049880981</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>4.29918479919434</v>
+        <v>4.29918527603149</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>4.22316837310791</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>4.22316837310791</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>4.22316837310791</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>4.22316837310791</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G23" t="n">
-        <v>3.98667049407959</v>
+        <v>3.98667025566101</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>3.91149830818176</v>
+        <v>3.91149806976318</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.02045679092407</v>
+        <v>4.02045583724976</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G30" t="n">
-        <v>4.02045679092407</v>
+        <v>4.02045583724976</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G31" t="n">
-        <v>4.11336612701416</v>
+        <v>4.113365650177</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G32" t="n">
-        <v>4.12181234359741</v>
+        <v>4.12181186676025</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.00356340408325</v>
+        <v>4.00356292724609</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G40" t="n">
-        <v>4.13025856018066</v>
+        <v>4.13025808334351</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>4.13870429992676</v>
+        <v>4.13870525360107</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G42" t="n">
-        <v>4.13870429992676</v>
+        <v>4.13870525360107</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>4.13870429992676</v>
+        <v>4.13870525360107</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>4.13870429992676</v>
+        <v>4.13870525360107</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>4.13870429992676</v>
+        <v>4.13870525360107</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13870429992676</v>
+        <v>4.13870525360107</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>4.13870429992676</v>
+        <v>4.13870525360107</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>4.04579544067383</v>
+        <v>4.04579448699951</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G50" t="n">
-        <v>4.00356340408325</v>
+        <v>4.00356292724609</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>4.00356340408325</v>
+        <v>4.00356292724609</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G52" t="n">
-        <v>4.02045679092407</v>
+        <v>4.02045583724976</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G53" t="n">
-        <v>4.02045679092407</v>
+        <v>4.02045583724976</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G54" t="n">
-        <v>4.07113409042358</v>
+        <v>4.07113361358643</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G56" t="n">
-        <v>4.02045679092407</v>
+        <v>4.02045583724976</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G58" t="n">
-        <v>3.82619023323059</v>
+        <v>3.82618999481201</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>3.90220642089844</v>
+        <v>3.90220713615417</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G60" t="n">
-        <v>3.91065311431885</v>
+        <v>3.91065359115601</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>3.91065311431885</v>
+        <v>3.91065359115601</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G62" t="n">
-        <v>4.12181234359741</v>
+        <v>4.12181186676025</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>4.13870429992676</v>
+        <v>4.13870525360107</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.75</v>
       </c>
       <c r="G65" t="n">
-        <v>4.01201009750366</v>
+        <v>4.0120096206665</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G66" t="n">
-        <v>3.98667049407959</v>
+        <v>3.98667025566101</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G67" t="n">
-        <v>3.98667049407959</v>
+        <v>3.98667025566101</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G68" t="n">
-        <v>3.98667049407959</v>
+        <v>3.98667025566101</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5</v>
       </c>
       <c r="G70" t="n">
-        <v>4.22316837310791</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.22316837310791</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G72" t="n">
-        <v>4.12181234359741</v>
+        <v>4.12181186676025</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>4.13870429992676</v>
+        <v>4.13870525360107</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>4.13870429992676</v>
+        <v>4.13870525360107</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.75</v>
       </c>
       <c r="G82" t="n">
-        <v>4.01201009750366</v>
+        <v>4.0120096206665</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89376091957092</v>
+        <v>3.8937611579895</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.88531398773193</v>
+        <v>3.88531422615051</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>3.83463621139526</v>
+        <v>3.834636926651</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.84308314323425</v>
+        <v>3.84308338165283</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>3.69104838371277</v>
+        <v>3.69104862213135</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>3.67415618896484</v>
+        <v>3.67415642738342</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G96" t="n">
-        <v>3.59813904762268</v>
+        <v>3.59813952445984</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>3.62347817420959</v>
+        <v>3.62347793579102</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.25</v>
       </c>
       <c r="G100" t="n">
-        <v>3.58969259262085</v>
+        <v>3.58969283103943</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.25</v>
       </c>
       <c r="G101" t="n">
-        <v>3.58969259262085</v>
+        <v>3.58969283103943</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.25</v>
       </c>
       <c r="G102" t="n">
-        <v>3.58969259262085</v>
+        <v>3.58969283103943</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>3.50522947311401</v>
+        <v>3.50522971153259</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>3.50522947311401</v>
+        <v>3.50522971153259</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>3.66570997238159</v>
+        <v>3.66571021080017</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G107" t="n">
-        <v>3.85152912139893</v>
+        <v>3.85152888298035</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96977806091309</v>
+        <v>3.96977853775024</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>3.97822427749634</v>
+        <v>3.9782247543335</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82619023323059</v>
+        <v>3.82618999481201</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G113" t="n">
-        <v>3.85152912139893</v>
+        <v>3.85152888298035</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G114" t="n">
-        <v>3.85152912139893</v>
+        <v>3.85152888298035</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.75</v>
       </c>
       <c r="G117" t="n">
-        <v>4.01201009750366</v>
+        <v>4.0120096206665</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.75</v>
       </c>
       <c r="G118" t="n">
-        <v>4.01201009750366</v>
+        <v>4.0120096206665</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.94443917274475</v>
+        <v>3.94443941116333</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>3.94443917274475</v>
+        <v>3.94443941116333</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G121" t="n">
-        <v>3.91909980773926</v>
+        <v>3.91910028457642</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.91909980773926</v>
+        <v>3.91910028457642</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G123" t="n">
-        <v>3.81774377822876</v>
+        <v>3.81774353981018</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G124" t="n">
-        <v>3.81774377822876</v>
+        <v>3.81774353981018</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G125" t="n">
-        <v>3.91909980773926</v>
+        <v>3.91910028457642</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G126" t="n">
-        <v>3.85997557640076</v>
+        <v>3.85997533798218</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G127" t="n">
-        <v>3.79240489006042</v>
+        <v>3.79240417480469</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>3.89376091957092</v>
+        <v>3.8937611579895</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G133" t="n">
-        <v>3.89376091957092</v>
+        <v>3.8937611579895</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G134" t="n">
-        <v>3.89376091957092</v>
+        <v>3.8937611579895</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.79240489006042</v>
+        <v>3.79240417480469</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>3.79240489006042</v>
+        <v>3.79240417480469</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>3.84308314323425</v>
+        <v>3.84308338165283</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G142" t="n">
-        <v>3.84308314323425</v>
+        <v>3.84308338165283</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G143" t="n">
-        <v>3.84308314323425</v>
+        <v>3.84308338165283</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>3.84308314323425</v>
+        <v>3.84308338165283</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G145" t="n">
-        <v>3.84308314323425</v>
+        <v>3.84308338165283</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>3.84308314323425</v>
+        <v>3.84308338165283</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>3.84308314323425</v>
+        <v>3.84308338165283</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G148" t="n">
-        <v>3.88531398773193</v>
+        <v>3.88531422615051</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>3.79240489006042</v>
+        <v>3.79240417480469</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G150" t="n">
-        <v>3.79240489006042</v>
+        <v>3.79240417480469</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G151" t="n">
-        <v>3.81774377822876</v>
+        <v>3.81774353981018</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.83463621139526</v>
+        <v>3.834636926651</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G158" t="n">
-        <v>3.59813904762268</v>
+        <v>3.59813952445984</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>3.42921233177185</v>
+        <v>3.42921257019043</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>3.42921233177185</v>
+        <v>3.42921257019043</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G162" t="n">
-        <v>3.42921233177185</v>
+        <v>3.42921257019043</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40387344360352</v>
+        <v>3.40387368202209</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.30251741409302</v>
+        <v>3.3025176525116</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G165" t="n">
-        <v>3.30251741409302</v>
+        <v>3.3025176525116</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.30251741409302</v>
+        <v>3.3025176525116</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G167" t="n">
-        <v>3.30251741409302</v>
+        <v>3.3025176525116</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.75</v>
       </c>
       <c r="G169" t="n">
-        <v>3.16737580299377</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.75</v>
       </c>
       <c r="G170" t="n">
-        <v>3.16737580299377</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.75</v>
       </c>
       <c r="G171" t="n">
-        <v>3.16737580299377</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.75</v>
       </c>
       <c r="G172" t="n">
-        <v>3.16737580299377</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75</v>
       </c>
       <c r="G173" t="n">
-        <v>3.16737580299377</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12514448165894</v>
+        <v>3.12514424324036</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G177" t="n">
-        <v>3.25183939933777</v>
+        <v>3.25183916091919</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>3.25183939933777</v>
+        <v>3.25183916091919</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25183939933777</v>
+        <v>3.25183916091919</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.34474897384644</v>
+        <v>3.34474921226501</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G187" t="n">
-        <v>3.34474897384644</v>
+        <v>3.34474921226501</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G195" t="n">
-        <v>3.10825204849243</v>
+        <v>3.10825157165527</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G196" t="n">
-        <v>3.10825204849243</v>
+        <v>3.10825157165527</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G197" t="n">
-        <v>3.10825204849243</v>
+        <v>3.10825157165527</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>3.10825204849243</v>
+        <v>3.10825157165527</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G206" t="n">
-        <v>3.29380822181702</v>
+        <v>3.2938084602356</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G207" t="n">
-        <v>3.29380822181702</v>
+        <v>3.2938084602356</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G208" t="n">
-        <v>3.29380822181702</v>
+        <v>3.2938084602356</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G209" t="n">
-        <v>3.29380822181702</v>
+        <v>3.2938084602356</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G210" t="n">
-        <v>3.13941144943237</v>
+        <v>3.13941121101379</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G211" t="n">
-        <v>3.13941144943237</v>
+        <v>3.13941121101379</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G212" t="n">
-        <v>3.13941144943237</v>
+        <v>3.13941121101379</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G213" t="n">
-        <v>3.13941144943237</v>
+        <v>3.13941121101379</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13941144943237</v>
+        <v>3.13941121101379</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="n">
-        <v>3.37958478927612</v>
+        <v>3.37958455085754</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="n">
-        <v>3.37958478927612</v>
+        <v>3.37958455085754</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.37958478927612</v>
+        <v>3.37958455085754</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.51682639122009</v>
+        <v>3.51682662963867</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.51682639122009</v>
+        <v>3.51682662963867</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.51682639122009</v>
+        <v>3.51682662963867</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>3.51682639122009</v>
+        <v>3.51682662963867</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G232" t="n">
-        <v>3.24234247207642</v>
+        <v>3.242342710495</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="n">
-        <v>3.25949811935425</v>
+        <v>3.25949788093567</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G234" t="n">
-        <v>3.24234247207642</v>
+        <v>3.242342710495</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>3.24234247207642</v>
+        <v>3.242342710495</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>3.24234247207642</v>
+        <v>3.242342710495</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19087696075439</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>3.13941144943237</v>
+        <v>3.13941121101379</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="n">
-        <v>3.19087696075439</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>3.19087696075439</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="n">
-        <v>3.19087696075439</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.08794522285461</v>
+        <v>3.08794546127319</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>3.13941144943237</v>
+        <v>3.13941121101379</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>3.01932454109192</v>
+        <v>3.01932430267334</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="n">
-        <v>3.00216889381409</v>
+        <v>3.00216937065125</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="n">
-        <v>2.88208222389221</v>
+        <v>2.88208270072937</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="n">
-        <v>2.88208222389221</v>
+        <v>2.88208270072937</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="n">
-        <v>2.88208222389221</v>
+        <v>2.88208270072937</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>2.88208222389221</v>
+        <v>2.88208270072937</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.74484038352966</v>
+        <v>2.74484062194824</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>2.91639280319214</v>
+        <v>2.9163932800293</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="n">
-        <v>2.88208222389221</v>
+        <v>2.88208270072937</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>2.88208222389221</v>
+        <v>2.88208270072937</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="n">
-        <v>2.88208222389221</v>
+        <v>2.88208270072937</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="n">
-        <v>2.89923787117004</v>
+        <v>2.89923763275146</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="n">
-        <v>2.74484038352966</v>
+        <v>2.74484062194824</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>2.72768497467041</v>
+        <v>2.72768521308899</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>2.74484038352966</v>
+        <v>2.74484062194824</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="n">
-        <v>2.74484038352966</v>
+        <v>2.74484062194824</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.74484038352966</v>
+        <v>2.74484062194824</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>2.55613255500793</v>
+        <v>2.55613279342651</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="n">
-        <v>2.29880380630493</v>
+        <v>2.29880404472351</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="n">
-        <v>2.29880380630493</v>
+        <v>2.29880404472351</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="n">
-        <v>2.31595921516418</v>
+        <v>2.31595897674561</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.31595921516418</v>
+        <v>2.31595897674561</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>2.1615617275238</v>
+        <v>2.16156196594238</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>2.1100959777832</v>
+        <v>2.11009621620178</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>2.05863046646118</v>
+        <v>2.0586302280426</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.05863046646118</v>
+        <v>2.0586302280426</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>1.95569884777069</v>
+        <v>1.95569860935211</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="n">
-        <v>1.90423309803009</v>
+        <v>1.90423285961151</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="n">
-        <v>1.83561193943024</v>
+        <v>1.83561205863953</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>1.81845664978027</v>
+        <v>1.81845653057098</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76699101924896</v>
+        <v>1.76699090003967</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80130159854889</v>
+        <v>1.80130136013031</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>2.05863046646118</v>
+        <v>2.0586302280426</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>2.05863046646118</v>
+        <v>2.0586302280426</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="n">
-        <v>2.05863046646118</v>
+        <v>2.0586302280426</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>2.05863046646118</v>
+        <v>2.0586302280426</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.05863046646118</v>
+        <v>2.0586302280426</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>2.1615617275238</v>
+        <v>2.16156196594238</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>2.19587206840515</v>
+        <v>2.19587230682373</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>2.1100959777832</v>
+        <v>2.11009621620178</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="n">
-        <v>2.12725138664246</v>
+        <v>2.12725162506104</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="n">
-        <v>2.05863046646118</v>
+        <v>2.0586302280426</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>2.05863046646118</v>
+        <v>2.0586302280426</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G365" t="n">
-        <v>2.65906381607056</v>
+        <v>2.65906405448914</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="n">
-        <v>2.55613255500793</v>
+        <v>2.55613279342651</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="n">
-        <v>2.48751163482666</v>
+        <v>2.48751187324524</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="n">
-        <v>2.48751163482666</v>
+        <v>2.48751187324524</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G371" t="n">
-        <v>2.43604564666748</v>
+        <v>2.43604588508606</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G372" t="n">
-        <v>2.45320105552673</v>
+        <v>2.45320081710815</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.41889071464539</v>
+        <v>2.41889023780823</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G375" t="n">
-        <v>2.43604564666748</v>
+        <v>2.43604588508606</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="n">
-        <v>2.31595921516418</v>
+        <v>2.31595897674561</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G386" t="n">
-        <v>2.43604564666748</v>
+        <v>2.43604588508606</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="n">
-        <v>2.41889071464539</v>
+        <v>2.41889023780823</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.41889071464539</v>
+        <v>2.41889023780823</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="n">
-        <v>2.31595921516418</v>
+        <v>2.31595897674561</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G398" t="n">
-        <v>2.45320105552673</v>
+        <v>2.45320081710815</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G399" t="n">
-        <v>2.45320105552673</v>
+        <v>2.45320081710815</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G400" t="n">
-        <v>2.52182197570801</v>
+        <v>2.52182221412659</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G401" t="n">
-        <v>2.52182197570801</v>
+        <v>2.52182221412659</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G402" t="n">
-        <v>2.52182197570801</v>
+        <v>2.52182221412659</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="n">
-        <v>2.48751163482666</v>
+        <v>2.48751187324524</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.48751163482666</v>
+        <v>2.48751187324524</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G405" t="n">
-        <v>2.43604564666748</v>
+        <v>2.43604588508606</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.48751163482666</v>
+        <v>2.48751187324524</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.48751163482666</v>
+        <v>2.48751187324524</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="n">
-        <v>2.55613255500793</v>
+        <v>2.55613279342651</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G411" t="n">
-        <v>2.45320105552673</v>
+        <v>2.45320081710815</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>2.31595921516418</v>
+        <v>2.31595897674561</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>2.48751163482666</v>
+        <v>2.48751187324524</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G426" t="n">
-        <v>2.52182197570801</v>
+        <v>2.52182221412659</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="n">
-        <v>2.48751163482666</v>
+        <v>2.48751187324524</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>2.55613255500793</v>
+        <v>2.55613279342651</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="n">
-        <v>2.72768497467041</v>
+        <v>2.72768521308899</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="n">
-        <v>3.00216889381409</v>
+        <v>3.00216937065125</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>3.03647994995117</v>
+        <v>3.03647971153259</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>3.08794522285461</v>
+        <v>3.08794546127319</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="n">
-        <v>3.15656661987305</v>
+        <v>3.15656638145447</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.25949811935425</v>
+        <v>3.25949788093567</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="n">
-        <v>3.25949811935425</v>
+        <v>3.25949788093567</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="n">
-        <v>3.19087696075439</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>3.17372155189514</v>
+        <v>3.17372179031372</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G446" t="n">
-        <v>3.13941144943237</v>
+        <v>3.13941121101379</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="n">
-        <v>3.15656661987305</v>
+        <v>3.15656638145447</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="n">
-        <v>3.15656661987305</v>
+        <v>3.15656638145447</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="n">
-        <v>3.15656661987305</v>
+        <v>3.15656638145447</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>3.15656661987305</v>
+        <v>3.15656638145447</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="n">
-        <v>3.25949811935425</v>
+        <v>3.25949788093567</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="n">
-        <v>3.19087696075439</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="n">
-        <v>3.19087696075439</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>3.17372155189514</v>
+        <v>3.17372179031372</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>3.08794522285461</v>
+        <v>3.08794546127319</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>3.12343239784241</v>
+        <v>3.12343215942383</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="n">
-        <v>3.17578053474426</v>
+        <v>3.17578029632568</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.5</v>
       </c>
       <c r="G466" t="n">
-        <v>3.05363488197327</v>
+        <v>3.05363512039185</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G469" t="n">
-        <v>3.26302695274353</v>
+        <v>3.26302719116211</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G470" t="n">
-        <v>3.22812819480896</v>
+        <v>3.22812843322754</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>3.22812819480896</v>
+        <v>3.22812843322754</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4</v>
       </c>
       <c r="G472" t="n">
-        <v>3.48986840248108</v>
+        <v>3.48986864089966</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4</v>
       </c>
       <c r="G477" t="n">
-        <v>3.48986840248108</v>
+        <v>3.48986864089966</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G478" t="n">
-        <v>3.45496964454651</v>
+        <v>3.45496988296509</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4</v>
       </c>
       <c r="G479" t="n">
-        <v>3.48986840248108</v>
+        <v>3.48986864089966</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4</v>
       </c>
       <c r="G480" t="n">
-        <v>3.48986840248108</v>
+        <v>3.48986864089966</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>3.82140588760376</v>
+        <v>3.82140612602234</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G484" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G490" t="n">
-        <v>4.13549375534058</v>
+        <v>4.13549423217773</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G494" t="n">
-        <v>4.13549375534058</v>
+        <v>4.13549423217773</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G496" t="n">
-        <v>4.08314561843872</v>
+        <v>4.08314609527588</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G498" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G500" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G502" t="n">
-        <v>4.44958257675171</v>
+        <v>4.44958209991455</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G503" t="n">
-        <v>4.44958257675171</v>
+        <v>4.44958209991455</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>4.49320554733276</v>
+        <v>4.49320602416992</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>4.17039251327515</v>
+        <v>4.1703929901123</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G510" t="n">
-        <v>4.17039251327515</v>
+        <v>4.1703929901123</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G511" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G512" t="n">
-        <v>4.20529222488403</v>
+        <v>4.20529127120972</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G513" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G515" t="n">
-        <v>4.44958257675171</v>
+        <v>4.44958209991455</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>4.32743692398071</v>
+        <v>4.32743740081787</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G518" t="n">
-        <v>4.20529222488403</v>
+        <v>4.20529127120972</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G523" t="n">
-        <v>4.13549375534058</v>
+        <v>4.13549423217773</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G525" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>3.94355177879333</v>
+        <v>3.94355130195618</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G530" t="n">
-        <v>4.08314561843872</v>
+        <v>4.08314609527588</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G543" t="n">
-        <v>4.17039251327515</v>
+        <v>4.1703929901123</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G547" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G549" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G560" t="n">
-        <v>4.17039251327515</v>
+        <v>4.1703929901123</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G562" t="n">
-        <v>4.20529222488403</v>
+        <v>4.20529127120972</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G563" t="n">
-        <v>4.20529222488403</v>
+        <v>4.20529127120972</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G565" t="n">
-        <v>4.20529222488403</v>
+        <v>4.20529127120972</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G566" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G567" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G573" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G579" t="n">
-        <v>4.32743692398071</v>
+        <v>4.32743740081787</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>4.32743692398071</v>
+        <v>4.32743740081787</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G584" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G585" t="n">
-        <v>4.13549375534058</v>
+        <v>4.13549423217773</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G592" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G594" t="n">
-        <v>4.17039251327515</v>
+        <v>4.1703929901123</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G595" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G596" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.25763988494873</v>
+        <v>4.25763940811157</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G599" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G600" t="n">
-        <v>4.13549375534058</v>
+        <v>4.13549423217773</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G602" t="n">
-        <v>4.17039251327515</v>
+        <v>4.1703929901123</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G603" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G604" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>4.08314561843872</v>
+        <v>4.08314609527588</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G610" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G613" t="n">
-        <v>4.08314561843872</v>
+        <v>4.08314609527588</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.5</v>
       </c>
       <c r="G617" t="n">
-        <v>3.92610192298889</v>
+        <v>3.92610216140747</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>4.5</v>
       </c>
       <c r="G618" t="n">
-        <v>3.92610192298889</v>
+        <v>3.92610216140747</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>3.94355177879333</v>
+        <v>3.94355130195618</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G623" t="n">
-        <v>3.94355177879333</v>
+        <v>3.94355130195618</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>4.5</v>
       </c>
       <c r="G624" t="n">
-        <v>3.92610192298889</v>
+        <v>3.92610216140747</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>3.96100091934204</v>
+        <v>3.96100068092346</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>3.90865302085876</v>
+        <v>3.90865230560303</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>3.96100091934204</v>
+        <v>3.96100068092346</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>3.96100091934204</v>
+        <v>3.96100068092346</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G633" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G634" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G636" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G637" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>4.08314561843872</v>
+        <v>4.08314609527588</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G645" t="n">
-        <v>4.17039251327515</v>
+        <v>4.1703929901123</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G649" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G650" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G651" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.5</v>
       </c>
       <c r="G654" t="n">
-        <v>3.92610192298889</v>
+        <v>3.92610216140747</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>3.89120364189148</v>
+        <v>3.8912034034729</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>3.89120364189148</v>
+        <v>3.8912034034729</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G661" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G664" t="n">
-        <v>3.87375402450562</v>
+        <v>3.87375378608704</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>3.87375402450562</v>
+        <v>3.87375378608704</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G666" t="n">
-        <v>3.96100091934204</v>
+        <v>3.96100068092346</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.5</v>
       </c>
       <c r="G667" t="n">
-        <v>3.92610192298889</v>
+        <v>3.92610216140747</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.5</v>
       </c>
       <c r="G668" t="n">
-        <v>3.92610192298889</v>
+        <v>3.92610216140747</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>3.75160884857178</v>
+        <v>3.75160908699036</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>3.83885526657104</v>
+        <v>3.83885550498962</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.5</v>
       </c>
       <c r="G671" t="n">
-        <v>3.92610192298889</v>
+        <v>3.92610216140747</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G674" t="n">
-        <v>3.21067905426025</v>
+        <v>3.21067881584167</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G686" t="n">
-        <v>3.82140588760376</v>
+        <v>3.82140612602234</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G687" t="n">
-        <v>3.82140588760376</v>
+        <v>3.82140612602234</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G688" t="n">
-        <v>3.85630512237549</v>
+        <v>3.85630488395691</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>3.87375402450562</v>
+        <v>3.87375378608704</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.5</v>
       </c>
       <c r="G690" t="n">
-        <v>3.92610192298889</v>
+        <v>3.92610216140747</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>3.96100091934204</v>
+        <v>3.96100068092346</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>3.94355177879333</v>
+        <v>3.94355130195618</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>3.94355177879333</v>
+        <v>3.94355130195618</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G694" t="n">
-        <v>4.18784236907959</v>
+        <v>4.18784189224243</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>4.2314658164978</v>
+        <v>4.23146533966064</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G696" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G698" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G699" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>4.10059499740601</v>
+        <v>4.10059547424316</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G708" t="n">
-        <v>4.06569623947144</v>
+        <v>4.06569719314575</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>3.99589920043945</v>
+        <v>3.99589967727661</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>3.99589920043945</v>
+        <v>3.99589967727661</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G715" t="n">
-        <v>3.99589920043945</v>
+        <v>3.99589967727661</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G716" t="n">
-        <v>3.98717498779297</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.12157344818115</v>
+        <v>4.12157392501831</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G726" t="n">
-        <v>4.02301454544067</v>
+        <v>4.02301406860352</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G730" t="n">
-        <v>4.0946946144104</v>
+        <v>4.09469413757324</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G731" t="n">
-        <v>4.0946946144104</v>
+        <v>4.09469413757324</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>4.10365390777588</v>
+        <v>4.10365438461304</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>4.10365390777588</v>
+        <v>4.10365438461304</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>4.10365390777588</v>
+        <v>4.10365438461304</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>4.10365390777588</v>
+        <v>4.10365438461304</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>4.10365390777588</v>
+        <v>4.10365438461304</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G741" t="n">
-        <v>4.00509405136108</v>
+        <v>4.00509452819824</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G742" t="n">
-        <v>4.00509405136108</v>
+        <v>4.00509452819824</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G744" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G750" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G751" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G752" t="n">
-        <v>3.93341493606567</v>
+        <v>3.93341541290283</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G753" t="n">
-        <v>3.93341493606567</v>
+        <v>3.93341541290283</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G754" t="n">
-        <v>3.93341493606567</v>
+        <v>3.93341541290283</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G755" t="n">
-        <v>3.93341493606567</v>
+        <v>3.93341541290283</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G757" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G758" t="n">
-        <v>3.93341493606567</v>
+        <v>3.93341541290283</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G759" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G760" t="n">
-        <v>3.88861536979675</v>
+        <v>3.88861560821533</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G761" t="n">
-        <v>3.88861536979675</v>
+        <v>3.88861560821533</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G762" t="n">
-        <v>3.88861536979675</v>
+        <v>3.88861560821533</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G763" t="n">
-        <v>3.88861536979675</v>
+        <v>3.88861560821533</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G764" t="n">
-        <v>3.88861536979675</v>
+        <v>3.88861560821533</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G765" t="n">
-        <v>3.88861536979675</v>
+        <v>3.88861560821533</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G768" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G774" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G775" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G777" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G779" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G780" t="n">
-        <v>3.85277581214905</v>
+        <v>3.85277605056763</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G781" t="n">
-        <v>3.85277581214905</v>
+        <v>3.85277605056763</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G782" t="n">
-        <v>3.86173534393311</v>
+        <v>3.86173558235168</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G784" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G785" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G797" t="n">
-        <v>3.82589554786682</v>
+        <v>3.8258957862854</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G799" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G800" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G801" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G802" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G811" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G822" t="n">
-        <v>3.9154953956604</v>
+        <v>3.91549515724182</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>3.9154953956604</v>
+        <v>3.91549515724182</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>3.9154953956604</v>
+        <v>3.91549515724182</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G825" t="n">
-        <v>3.86173534393311</v>
+        <v>3.86173558235168</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G826" t="n">
-        <v>3.86173534393311</v>
+        <v>3.86173558235168</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G827" t="n">
-        <v>3.86173534393311</v>
+        <v>3.86173558235168</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G828" t="n">
-        <v>3.86173534393311</v>
+        <v>3.86173558235168</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>3.86173534393311</v>
+        <v>3.86173558235168</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="n">
-        <v>3.58397722244263</v>
+        <v>3.58397746086121</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G834" t="n">
-        <v>3.78109622001648</v>
+        <v>3.7810959815979</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G836" t="n">
-        <v>3.78109622001648</v>
+        <v>3.7810959815979</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G837" t="n">
-        <v>3.86173534393311</v>
+        <v>3.86173558235168</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G838" t="n">
-        <v>3.86173534393311</v>
+        <v>3.86173558235168</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G839" t="n">
-        <v>3.85277581214905</v>
+        <v>3.85277605056763</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G840" t="n">
-        <v>3.85277581214905</v>
+        <v>3.85277605056763</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G841" t="n">
-        <v>3.85277581214905</v>
+        <v>3.85277605056763</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G842" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G843" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G844" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.96925497055054</v>
+        <v>3.96925520896912</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G846" t="n">
-        <v>3.97821497917175</v>
+        <v>3.97821474075317</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G847" t="n">
-        <v>3.97821497917175</v>
+        <v>3.97821474075317</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G848" t="n">
-        <v>3.97821497917175</v>
+        <v>3.97821474075317</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G849" t="n">
-        <v>3.97821497917175</v>
+        <v>3.97821474075317</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>4.00509405136108</v>
+        <v>4.00509452819824</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G856" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G857" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G859" t="n">
-        <v>3.78109622001648</v>
+        <v>3.7810959815979</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G865" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G866" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G867" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G868" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G869" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G870" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G886" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G887" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G893" t="n">
-        <v>3.64669728279114</v>
+        <v>3.64669704437256</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G894" t="n">
-        <v>3.64669728279114</v>
+        <v>3.64669704437256</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G897" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G900" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G906" t="n">
-        <v>3.67357683181763</v>
+        <v>3.67357659339905</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>3.7900562286377</v>
+        <v>3.79005599021912</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G914" t="n">
-        <v>3.85277581214905</v>
+        <v>3.85277605056763</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G915" t="n">
-        <v>3.85277581214905</v>
+        <v>3.85277605056763</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.77213644981384</v>
+        <v>3.77213621139526</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>3.84381580352783</v>
+        <v>3.84381556510925</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G923" t="n">
-        <v>3.88861536979675</v>
+        <v>3.88861560821533</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G924" t="n">
-        <v>4.01405477523804</v>
+        <v>4.01405429840088</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>4.01405477523804</v>
+        <v>4.01405429840088</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G927" t="n">
-        <v>4.0946946144104</v>
+        <v>4.09469413757324</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>4.13053417205811</v>
+        <v>4.13053369522095</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G930" t="n">
-        <v>4.10365390777588</v>
+        <v>4.10365438461304</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>4.10365390777588</v>
+        <v>4.10365438461304</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>4.10365390777588</v>
+        <v>4.10365438461304</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G934" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G938" t="n">
-        <v>3.88861536979675</v>
+        <v>3.88861560821533</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G940" t="n">
-        <v>3.98717451095581</v>
+        <v>3.98717427253723</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.08573436737061</v>
+        <v>4.08573389053345</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>4.08573436737061</v>
+        <v>4.08573389053345</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G944" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G945" t="n">
-        <v>3.89757537841797</v>
+        <v>3.89757561683655</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>3.86173534393311</v>
+        <v>3.86173558235168</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.86173534393311</v>
+        <v>3.86173558235168</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G949" t="n">
-        <v>4.07677507400513</v>
+        <v>4.07677459716797</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G950" t="n">
-        <v>4.08573436737061</v>
+        <v>4.08573389053345</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G951" t="n">
-        <v>4.08573436737061</v>
+        <v>4.08573389053345</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>4.08573436737061</v>
+        <v>4.08573389053345</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>4.08573436737061</v>
+        <v>4.08573389053345</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G954" t="n">
-        <v>4.01405477523804</v>
+        <v>4.01405429840088</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G955" t="n">
-        <v>4.01405477523804</v>
+        <v>4.01405429840088</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G957" t="n">
-        <v>3.97821497917175</v>
+        <v>3.97821474075317</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G959" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G960" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G961" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>3.96029496192932</v>
+        <v>3.9602952003479</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G969" t="n">
-        <v>3.94237494468689</v>
+        <v>3.94237542152405</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>4.08573436737061</v>
+        <v>4.08573389053345</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.12157344818115</v>
+        <v>4.12157392501831</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -45820,6 +45820,32 @@
         <v>2.3199999332428</v>
       </c>
       <c r="H1748" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="1" t="n">
+        <v>46176.2916666667</v>
+      </c>
+      <c r="B1749" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1749" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G1749" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="H1749" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2" t="n">
-        <v>4.197829246521</v>
+        <v>4.19782876968384</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3456392288208</v>
+        <v>4.34564018249512</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4.43432664871216</v>
+        <v>4.434326171875</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G8" t="n">
-        <v>4.27553558349609</v>
+        <v>4.27553510665894</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>4.25695371627808</v>
+        <v>4.25695323944092</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.0479998588562</v>
       </c>
       <c r="G10" t="n">
-        <v>4.26371049880981</v>
+        <v>4.26371002197266</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>4.29918527603149</v>
+        <v>4.29918479919434</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2147216796875</v>
+        <v>4.21472120285034</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>4.25695371627808</v>
+        <v>4.25695323944092</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>4.25695371627808</v>
+        <v>4.25695323944092</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G23" t="n">
-        <v>3.98667025566101</v>
+        <v>3.98667049407959</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G26" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G27" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G28" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045631408691</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G30" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045631408691</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G31" t="n">
-        <v>4.113365650177</v>
+        <v>4.11336612701416</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G38" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G40" t="n">
-        <v>4.13025808334351</v>
+        <v>4.13025856018066</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G42" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G50" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G52" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045631408691</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G53" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045631408691</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G54" t="n">
-        <v>4.07113361358643</v>
+        <v>4.07113456726074</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G56" t="n">
-        <v>4.02045583724976</v>
+        <v>4.02045631408691</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.5</v>
       </c>
       <c r="G57" t="n">
-        <v>3.80085134506226</v>
+        <v>3.8008508682251</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G58" t="n">
-        <v>3.82618999481201</v>
+        <v>3.82619023323059</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G60" t="n">
-        <v>3.91065359115601</v>
+        <v>3.91065311431885</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>3.91065359115601</v>
+        <v>3.91065311431885</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>4.197829246521</v>
+        <v>4.19782876968384</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G66" t="n">
-        <v>3.98667025566101</v>
+        <v>3.98667049407959</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G67" t="n">
-        <v>3.98667025566101</v>
+        <v>3.98667049407959</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G68" t="n">
-        <v>3.98667025566101</v>
+        <v>3.98667049407959</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G69" t="n">
-        <v>4.17249011993408</v>
+        <v>4.17248964309692</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5</v>
       </c>
       <c r="G70" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.22316789627075</v>
+        <v>4.22316837310791</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>3.96133208274841</v>
+        <v>3.96133184432983</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G85" t="n">
-        <v>3.96133208274841</v>
+        <v>3.96133184432983</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96133208274841</v>
+        <v>3.96133184432983</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G87" t="n">
-        <v>3.8937611579895</v>
+        <v>3.89376091957092</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96133208274841</v>
+        <v>3.96133184432983</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.88531422615051</v>
+        <v>3.88531470298767</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>3.834636926651</v>
+        <v>3.83463668823242</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.84308338165283</v>
+        <v>3.84308266639709</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>3.69104862213135</v>
+        <v>3.69104886054993</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G93" t="n">
-        <v>3.73328042030334</v>
+        <v>3.7332808971405</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>3.73328042030334</v>
+        <v>3.7332808971405</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G95" t="n">
-        <v>3.67415642738342</v>
+        <v>3.67415618896484</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G96" t="n">
-        <v>3.59813952445984</v>
+        <v>3.59813928604126</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>3.60658526420593</v>
+        <v>3.60658574104309</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G99" t="n">
-        <v>3.54746079444885</v>
+        <v>3.54746103286743</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>3.60658526420593</v>
+        <v>3.60658574104309</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>3.50522971153259</v>
+        <v>3.50522923469543</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>3.50522971153259</v>
+        <v>3.50522923469543</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>3.66571021080017</v>
+        <v>3.66570997238159</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G107" t="n">
-        <v>3.85152888298035</v>
+        <v>3.85152959823608</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>3.86842226982117</v>
+        <v>3.86842155456543</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96977853775024</v>
+        <v>3.96977782249451</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>3.9782247543335</v>
+        <v>3.97822451591492</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82618999481201</v>
+        <v>3.82619023323059</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G112" t="n">
-        <v>3.96133208274841</v>
+        <v>3.96133184432983</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G113" t="n">
-        <v>3.85152888298035</v>
+        <v>3.85152959823608</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G114" t="n">
-        <v>3.85152888298035</v>
+        <v>3.85152959823608</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>3.86842226982117</v>
+        <v>3.86842155456543</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86842226982117</v>
+        <v>3.86842155456543</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.94443941116333</v>
+        <v>3.94443893432617</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>3.94443941116333</v>
+        <v>3.94443893432617</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G121" t="n">
-        <v>3.91910028457642</v>
+        <v>3.91909980773926</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G122" t="n">
-        <v>3.91910028457642</v>
+        <v>3.91909980773926</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G123" t="n">
-        <v>3.81774353981018</v>
+        <v>3.81774377822876</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G124" t="n">
-        <v>3.81774353981018</v>
+        <v>3.81774377822876</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G125" t="n">
-        <v>3.91910028457642</v>
+        <v>3.91909980773926</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G126" t="n">
-        <v>3.85997533798218</v>
+        <v>3.85997605323792</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G127" t="n">
-        <v>3.79240417480469</v>
+        <v>3.79240441322327</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.80085134506226</v>
+        <v>3.8008508682251</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.5</v>
       </c>
       <c r="G129" t="n">
-        <v>3.80085134506226</v>
+        <v>3.8008508682251</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.5</v>
       </c>
       <c r="G130" t="n">
-        <v>3.80085134506226</v>
+        <v>3.8008508682251</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>3.80085134506226</v>
+        <v>3.8008508682251</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>3.8937611579895</v>
+        <v>3.89376091957092</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G133" t="n">
-        <v>3.8937611579895</v>
+        <v>3.89376091957092</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G134" t="n">
-        <v>3.8937611579895</v>
+        <v>3.89376091957092</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>3.93599247932434</v>
+        <v>3.93599271774292</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>3.93599247932434</v>
+        <v>3.93599271774292</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>3.93599247932434</v>
+        <v>3.93599271774292</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>3.93599247932434</v>
+        <v>3.93599271774292</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.79240417480469</v>
+        <v>3.79240441322327</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>3.79240417480469</v>
+        <v>3.79240441322327</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>3.84308338165283</v>
+        <v>3.84308266639709</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G142" t="n">
-        <v>3.84308338165283</v>
+        <v>3.84308266639709</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G143" t="n">
-        <v>3.84308338165283</v>
+        <v>3.84308266639709</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>3.84308338165283</v>
+        <v>3.84308266639709</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G145" t="n">
-        <v>3.84308338165283</v>
+        <v>3.84308266639709</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>3.84308338165283</v>
+        <v>3.84308266639709</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>3.84308338165283</v>
+        <v>3.84308266639709</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G148" t="n">
-        <v>3.88531422615051</v>
+        <v>3.88531470298767</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>3.79240417480469</v>
+        <v>3.79240441322327</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G150" t="n">
-        <v>3.79240417480469</v>
+        <v>3.79240441322327</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G151" t="n">
-        <v>3.81774353981018</v>
+        <v>3.81774377822876</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.834636926651</v>
+        <v>3.83463668823242</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G153" t="n">
-        <v>3.73328042030334</v>
+        <v>3.7332808971405</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>3.73328042030334</v>
+        <v>3.7332808971405</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G155" t="n">
-        <v>3.64881753921509</v>
+        <v>3.64881777763367</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G156" t="n">
-        <v>3.64881753921509</v>
+        <v>3.64881777763367</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G157" t="n">
-        <v>3.64881753921509</v>
+        <v>3.64881777763367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G158" t="n">
-        <v>3.59813952445984</v>
+        <v>3.59813928604126</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>3.54746079444885</v>
+        <v>3.54746103286743</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>3.42921257019043</v>
+        <v>3.42921233177185</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>3.42921257019043</v>
+        <v>3.42921233177185</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G162" t="n">
-        <v>3.42921257019043</v>
+        <v>3.42921233177185</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G165" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G167" t="n">
-        <v>3.3025176525116</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.5</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95621776580811</v>
+        <v>2.95621728897095</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G174" t="n">
-        <v>2.91398620605469</v>
+        <v>2.91398596763611</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G175" t="n">
-        <v>2.91398620605469</v>
+        <v>2.91398596763611</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12514424324036</v>
+        <v>3.12514448165894</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G177" t="n">
-        <v>3.25183916091919</v>
+        <v>3.25183939933777</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>3.25183916091919</v>
+        <v>3.25183939933777</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25183916091919</v>
+        <v>3.25183939933777</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G180" t="n">
-        <v>3.20960760116577</v>
+        <v>3.20960783958435</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G181" t="n">
-        <v>3.20960760116577</v>
+        <v>3.20960783958435</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.20960760116577</v>
+        <v>3.20960783958435</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>3.20960760116577</v>
+        <v>3.20960783958435</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.20960760116577</v>
+        <v>3.20960783958435</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G185" t="n">
-        <v>3.20960760116577</v>
+        <v>3.20960783958435</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.34474921226501</v>
+        <v>3.34474897384644</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G187" t="n">
-        <v>3.34474921226501</v>
+        <v>3.34474897384644</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>3.32785630226135</v>
+        <v>3.32785654067993</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G190" t="n">
-        <v>3.20960760116577</v>
+        <v>3.20960783958435</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G191" t="n">
-        <v>3.20960760116577</v>
+        <v>3.20960783958435</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G192" t="n">
-        <v>3.20960760116577</v>
+        <v>3.20960783958435</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>3.20960760116577</v>
+        <v>3.20960783958435</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>3.19271516799927</v>
+        <v>3.19271492958069</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G206" t="n">
-        <v>3.2938084602356</v>
+        <v>3.29380822181702</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G207" t="n">
-        <v>3.2938084602356</v>
+        <v>3.29380822181702</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G208" t="n">
-        <v>3.2938084602356</v>
+        <v>3.29380822181702</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G209" t="n">
-        <v>3.2938084602356</v>
+        <v>3.29380822181702</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G210" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G211" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G212" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G213" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>3.31096363067627</v>
+        <v>3.31096386909485</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="n">
-        <v>3.31096363067627</v>
+        <v>3.31096386909485</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="n">
-        <v>3.31096363067627</v>
+        <v>3.31096386909485</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.31096363067627</v>
+        <v>3.31096386909485</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="n">
-        <v>3.31096363067627</v>
+        <v>3.31096386909485</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="n">
-        <v>3.31096363067627</v>
+        <v>3.31096386909485</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>3.31096363067627</v>
+        <v>3.31096386909485</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G224" t="n">
-        <v>3.37958455085754</v>
+        <v>3.37958478927612</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G225" t="n">
-        <v>3.37958455085754</v>
+        <v>3.37958478927612</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.37958455085754</v>
+        <v>3.37958478927612</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>3.01932430267334</v>
+        <v>3.01932454109192</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.5</v>
       </c>
       <c r="G260" t="n">
-        <v>3.00216937065125</v>
+        <v>3.00216913223267</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G261" t="n">
-        <v>2.88208270072937</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G262" t="n">
-        <v>2.88208270072937</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="n">
-        <v>2.88208270072937</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>2.88208270072937</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G269" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G270" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93354821205139</v>
+        <v>2.93354797363281</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.93354821205139</v>
+        <v>2.93354797363281</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93354821205139</v>
+        <v>2.93354797363281</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.93354821205139</v>
+        <v>2.93354797363281</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.74484062194824</v>
+        <v>2.74484038352966</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G279" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G283" t="n">
-        <v>2.93354821205139</v>
+        <v>2.93354797363281</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>2.9163932800293</v>
+        <v>2.91639304161072</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G293" t="n">
-        <v>2.88208270072937</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>2.88208270072937</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G295" t="n">
-        <v>2.88208270072937</v>
+        <v>2.88208222389221</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>2.77915096282959</v>
+        <v>2.77915072441101</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86492729187012</v>
+        <v>2.86492705345154</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G300" t="n">
-        <v>2.74484062194824</v>
+        <v>2.74484038352966</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>2.74484062194824</v>
+        <v>2.74484038352966</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="n">
-        <v>2.74484062194824</v>
+        <v>2.74484038352966</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.74484062194824</v>
+        <v>2.74484038352966</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="n">
-        <v>2.57328796386719</v>
+        <v>2.57328748703003</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>2.55613279342651</v>
+        <v>2.55613255500793</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G310" t="n">
-        <v>2.29880404472351</v>
+        <v>2.29880380630493</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G311" t="n">
-        <v>2.29880404472351</v>
+        <v>2.29880380630493</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G312" t="n">
-        <v>2.31595897674561</v>
+        <v>2.31595921516418</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.31595897674561</v>
+        <v>2.31595921516418</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G314" t="n">
-        <v>2.23018288612366</v>
+        <v>2.23018264770508</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G323" t="n">
-        <v>2.23018288612366</v>
+        <v>2.23018264770508</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>2.16156196594238</v>
+        <v>2.1615617275238</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="n">
-        <v>2.04147505760193</v>
+        <v>2.04147529602051</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>2.07578563690186</v>
+        <v>2.07578539848328</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.04147505760193</v>
+        <v>2.04147529602051</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>2.04147505760193</v>
+        <v>2.04147529602051</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>1.95569860935211</v>
+        <v>1.95569896697998</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="n">
-        <v>1.90423285961151</v>
+        <v>1.90423309803009</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>1.88707780838013</v>
+        <v>1.88707792758942</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="n">
-        <v>1.83561205863953</v>
+        <v>1.83561193943024</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>1.81845653057098</v>
+        <v>1.81845664978027</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>1.78414607048035</v>
+        <v>1.78414630889893</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G341" t="n">
-        <v>1.78414607048035</v>
+        <v>1.78414630889893</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>1.78414607048035</v>
+        <v>1.78414630889893</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>1.76699090003967</v>
+        <v>1.76699113845825</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G346" t="n">
-        <v>2.02431964874268</v>
+        <v>2.0243194103241</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>1.99000918865204</v>
+        <v>1.99000930786133</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G350" t="n">
-        <v>2.02431964874268</v>
+        <v>2.0243194103241</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="n">
-        <v>2.07578563690186</v>
+        <v>2.07578539848328</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>2.07578563690186</v>
+        <v>2.07578539848328</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>2.16156196594238</v>
+        <v>2.1615617275238</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="n">
-        <v>2.12725162506104</v>
+        <v>2.12725138664246</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="n">
-        <v>2.55613279342651</v>
+        <v>2.55613255500793</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="n">
-        <v>2.57328796386719</v>
+        <v>2.57328748703003</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.41889023780823</v>
+        <v>2.41889071464539</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G379" t="n">
-        <v>2.38458013534546</v>
+        <v>2.3845796585083</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G380" t="n">
-        <v>2.38458013534546</v>
+        <v>2.3845796585083</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G381" t="n">
-        <v>2.38458013534546</v>
+        <v>2.3845796585083</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G384" t="n">
-        <v>2.31595897674561</v>
+        <v>2.31595921516418</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G387" t="n">
-        <v>2.38458013534546</v>
+        <v>2.3845796585083</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G388" t="n">
-        <v>2.38458013534546</v>
+        <v>2.3845796585083</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G391" t="n">
-        <v>2.41889023780823</v>
+        <v>2.41889071464539</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.41889023780823</v>
+        <v>2.41889071464539</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G394" t="n">
-        <v>2.31595897674561</v>
+        <v>2.31595921516418</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="n">
-        <v>2.55613279342651</v>
+        <v>2.55613255500793</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G412" t="n">
-        <v>2.38458013534546</v>
+        <v>2.3845796585083</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G413" t="n">
-        <v>2.38458013534546</v>
+        <v>2.3845796585083</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G414" t="n">
-        <v>2.38458013534546</v>
+        <v>2.3845796585083</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>2.31595897674561</v>
+        <v>2.31595921516418</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G419" t="n">
-        <v>2.38458013534546</v>
+        <v>2.3845796585083</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="n">
-        <v>2.40173530578613</v>
+        <v>2.40173554420471</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G432" t="n">
-        <v>2.62475371360779</v>
+        <v>2.62475347518921</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>2.55613279342651</v>
+        <v>2.55613255500793</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.5</v>
       </c>
       <c r="G435" t="n">
-        <v>3.00216937065125</v>
+        <v>3.00216913223267</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>3.17372179031372</v>
+        <v>3.17372155189514</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G446" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="n">
-        <v>3.22518730163574</v>
+        <v>3.22518754005432</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>3.17372179031372</v>
+        <v>3.17372155189514</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G458" t="n">
-        <v>2.93354821205139</v>
+        <v>2.93354797363281</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G460" t="n">
-        <v>3.05363488197327</v>
+        <v>3.05363512039185</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G463" t="n">
-        <v>3.17578029632568</v>
+        <v>3.17578053474426</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G474" t="n">
-        <v>3.55966567993164</v>
+        <v>3.55966591835022</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>3.55966567993164</v>
+        <v>3.55966591835022</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G489" t="n">
-        <v>4.2925386428833</v>
+        <v>4.29253816604614</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G493" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G499" t="n">
-        <v>3.97844982147217</v>
+        <v>3.97845029830933</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G505" t="n">
-        <v>4.344886302948</v>
+        <v>4.34488582611084</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>4.49320602416992</v>
+        <v>4.49320554733276</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G507" t="n">
-        <v>4.30998802185059</v>
+        <v>4.30998754501343</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>4.32743740081787</v>
+        <v>4.32743692398071</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>4.2925386428833</v>
+        <v>4.29253816604614</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G527" t="n">
-        <v>3.94355130195618</v>
+        <v>3.94355177879333</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G532" t="n">
-        <v>4.11804437637329</v>
+        <v>4.11804389953613</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G534" t="n">
-        <v>4.11804437637329</v>
+        <v>4.11804389953613</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G539" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.11804437637329</v>
+        <v>4.11804389953613</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>4.30998802185059</v>
+        <v>4.30998754501343</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>4.2925386428833</v>
+        <v>4.29253816604614</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>4.2925386428833</v>
+        <v>4.29253816604614</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G579" t="n">
-        <v>4.32743740081787</v>
+        <v>4.32743692398071</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>4.32743740081787</v>
+        <v>4.32743692398071</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>4.2925386428833</v>
+        <v>4.29253816604614</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>4.344886302948</v>
+        <v>4.34488582611084</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G590" t="n">
-        <v>4.2925386428833</v>
+        <v>4.29253816604614</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G606" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G610" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G615" t="n">
-        <v>4.11804437637329</v>
+        <v>4.11804389953613</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G621" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>3.94355130195618</v>
+        <v>3.94355177879333</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G623" t="n">
-        <v>3.94355130195618</v>
+        <v>3.94355177879333</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>3.90865230560303</v>
+        <v>3.90865278244019</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G632" t="n">
-        <v>4.11804437637329</v>
+        <v>4.11804389953613</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G633" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G648" t="n">
-        <v>4.11804437637329</v>
+        <v>4.11804389953613</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>3.97844982147217</v>
+        <v>3.97845029830933</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>3.97844982147217</v>
+        <v>3.97845029830933</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G656" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G657" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G660" t="n">
-        <v>3.97844982147217</v>
+        <v>3.97845029830933</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G661" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G662" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G663" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G664" t="n">
-        <v>3.87375378608704</v>
+        <v>3.87375426292419</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>3.87375378608704</v>
+        <v>3.87375426292419</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>3.4200713634491</v>
+        <v>3.42007112503052</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>3.4200713634491</v>
+        <v>3.42007112503052</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G679" t="n">
-        <v>3.4200713634491</v>
+        <v>3.42007112503052</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G680" t="n">
-        <v>3.4200713634491</v>
+        <v>3.42007112503052</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G681" t="n">
-        <v>3.64691233634949</v>
+        <v>3.64691257476807</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G682" t="n">
-        <v>3.64691233634949</v>
+        <v>3.64691257476807</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64691233634949</v>
+        <v>3.64691257476807</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G684" t="n">
-        <v>3.64691233634949</v>
+        <v>3.64691257476807</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G685" t="n">
-        <v>3.64691233634949</v>
+        <v>3.64691257476807</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G689" t="n">
-        <v>3.87375378608704</v>
+        <v>3.87375426292419</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>3.94355130195618</v>
+        <v>3.94355177879333</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>3.94355130195618</v>
+        <v>3.94355177879333</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>4.23146533966064</v>
+        <v>4.23146486282349</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G696" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.01334857940674</v>
+        <v>4.0133490562439</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G698" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G699" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>4.10059547424316</v>
+        <v>4.10059499740601</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G703" t="n">
-        <v>4.11804437637329</v>
+        <v>4.11804389953613</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G716" t="n">
-        <v>3.98717474937439</v>
+        <v>3.98717522621155</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.12157392501831</v>
+        <v>4.12157440185547</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G726" t="n">
-        <v>4.02301406860352</v>
+        <v>4.02301454544067</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G730" t="n">
-        <v>4.09469413757324</v>
+        <v>4.0946946144104</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G731" t="n">
-        <v>4.09469413757324</v>
+        <v>4.0946946144104</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G737" t="n">
-        <v>4.22909307479858</v>
+        <v>4.22909259796143</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G774" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G775" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G777" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G782" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173582077026</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G783" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G784" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G785" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G797" t="n">
-        <v>3.8258957862854</v>
+        <v>3.82589602470398</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G811" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G813" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G815" t="n">
-        <v>3.6556568145752</v>
+        <v>3.65565705299377</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>3.6556568145752</v>
+        <v>3.65565705299377</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>3.6556568145752</v>
+        <v>3.65565705299377</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.6556568145752</v>
+        <v>3.65565705299377</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>3.6556568145752</v>
+        <v>3.65565705299377</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G820" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G821" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G825" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173582077026</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G826" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173582077026</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G827" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173582077026</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G828" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173582077026</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173582077026</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G834" t="n">
-        <v>3.7810959815979</v>
+        <v>3.78109622001648</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G836" t="n">
-        <v>3.7810959815979</v>
+        <v>3.78109622001648</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G837" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173582077026</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G838" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173582077026</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G846" t="n">
-        <v>3.97821474075317</v>
+        <v>3.97821521759033</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G847" t="n">
-        <v>3.97821474075317</v>
+        <v>3.97821521759033</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G848" t="n">
-        <v>3.97821474075317</v>
+        <v>3.97821521759033</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G849" t="n">
-        <v>3.97821474075317</v>
+        <v>3.97821521759033</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G859" t="n">
-        <v>3.7810959815979</v>
+        <v>3.78109622001648</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G860" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G861" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G862" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G865" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G866" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G867" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G868" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G869" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G870" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G876" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G877" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G878" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G879" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G880" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G881" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G882" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G883" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G884" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G886" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G887" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>3.6556568145752</v>
+        <v>3.65565705299377</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G897" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G900" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G902" t="n">
-        <v>3.74525618553162</v>
+        <v>3.7452564239502</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>3.6556568145752</v>
+        <v>3.65565705299377</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G906" t="n">
-        <v>3.67357659339905</v>
+        <v>3.67357683181763</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G907" t="n">
-        <v>3.6556568145752</v>
+        <v>3.65565705299377</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G908" t="n">
-        <v>3.79005599021912</v>
+        <v>3.7900562286377</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G924" t="n">
-        <v>4.01405429840088</v>
+        <v>4.01405477523804</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>4.01405429840088</v>
+        <v>4.01405477523804</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G926" t="n">
-        <v>4.04989433288574</v>
+        <v>4.0498948097229</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G927" t="n">
-        <v>4.09469413757324</v>
+        <v>4.0946946144104</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>4.13053369522095</v>
+        <v>4.13053417205811</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G933" t="n">
-        <v>4.18429374694824</v>
+        <v>4.18429327011108</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G934" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G936" t="n">
-        <v>4.05885457992554</v>
+        <v>4.0588550567627</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G939" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G940" t="n">
-        <v>3.98717427253723</v>
+        <v>3.98717474937439</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G941" t="n">
-        <v>4.04989433288574</v>
+        <v>4.0498948097229</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173582077026</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G947" t="n">
-        <v>3.86173558235168</v>
+        <v>3.86173582077026</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G948" t="n">
-        <v>4.04989433288574</v>
+        <v>4.0498948097229</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G950" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G951" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G953" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G954" t="n">
-        <v>4.01405429840088</v>
+        <v>4.01405477523804</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G955" t="n">
-        <v>4.01405429840088</v>
+        <v>4.01405477523804</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G957" t="n">
-        <v>3.97821474075317</v>
+        <v>3.97821521759033</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G963" t="n">
-        <v>4.04989433288574</v>
+        <v>4.0498948097229</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G964" t="n">
-        <v>4.04989433288574</v>
+        <v>4.0498948097229</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>4.08573389053345</v>
+        <v>4.08573436737061</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.12157392501831</v>
+        <v>4.12157440185547</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G980" t="n">
-        <v>4.11231184005737</v>
+        <v>4.11231231689453</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G981" t="n">
-        <v>4.11231184005737</v>
+        <v>4.11231231689453</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G982" t="n">
-        <v>4.11231184005737</v>
+        <v>4.11231231689453</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G983" t="n">
-        <v>4.11231184005737</v>
+        <v>4.11231231689453</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G984" t="n">
-        <v>4.11231184005737</v>
+        <v>4.11231231689453</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G985" t="n">
-        <v>4.11231184005737</v>
+        <v>4.11231231689453</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G986" t="n">
-        <v>4.11231184005737</v>
+        <v>4.11231231689453</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G987" t="n">
-        <v>4.11231184005737</v>
+        <v>4.11231231689453</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G992" t="n">
-        <v>3.90854859352112</v>
+        <v>3.9085488319397</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G993" t="n">
-        <v>3.87150073051453</v>
+        <v>3.87150096893311</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G998" t="n">
-        <v>3.77888107299805</v>
+        <v>3.77888131141663</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G999" t="n">
-        <v>3.87150073051453</v>
+        <v>3.87150096893311</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.87150073051453</v>
+        <v>3.87150096893311</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.83445286750793</v>
+        <v>3.83445310592651</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.77888107299805</v>
+        <v>3.77888131141663</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.77888107299805</v>
+        <v>3.77888131141663</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.83445286750793</v>
+        <v>3.83445310592651</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.61216616630554</v>
+        <v>3.61216592788696</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.61216616630554</v>
+        <v>3.61216592788696</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.57511806488037</v>
+        <v>3.57511782646179</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.37135481834412</v>
+        <v>3.3713550567627</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.26021122932434</v>
+        <v>3.26021146774292</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.61216616630554</v>
+        <v>3.61216592788696</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.57511806488037</v>
+        <v>3.57511782646179</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.57511806488037</v>
+        <v>3.57511782646179</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.57511806488037</v>
+        <v>3.57511782646179</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.63069009780884</v>
+        <v>3.63068985939026</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.61216616630554</v>
+        <v>3.61216592788696</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.61216616630554</v>
+        <v>3.61216592788696</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.61216616630554</v>
+        <v>3.61216592788696</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.77888107299805</v>
+        <v>3.77888131141663</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.77888107299805</v>
+        <v>3.77888131141663</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.77888107299805</v>
+        <v>3.77888131141663</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.77888107299805</v>
+        <v>3.77888131141663</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.83445286750793</v>
+        <v>3.83445310592651</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.77888107299805</v>
+        <v>3.77888131141663</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.83445286750793</v>
+        <v>3.83445310592651</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.83445286750793</v>
+        <v>3.83445310592651</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.83445286750793</v>
+        <v>3.83445310592651</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.79740500450134</v>
+        <v>3.79740524291992</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.63069009780884</v>
+        <v>3.63068985939026</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.61216616630554</v>
+        <v>3.61216592788696</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.57511806488037</v>
+        <v>3.57511782646179</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.63069009780884</v>
+        <v>3.63068985939026</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.57511806488037</v>
+        <v>3.57511782646179</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.63069009780884</v>
+        <v>3.63068985939026</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.59364223480225</v>
+        <v>3.59364199638367</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.61216616630554</v>
+        <v>3.61216592788696</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.61216616630554</v>
+        <v>3.61216592788696</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.61216616630554</v>
+        <v>3.61216592788696</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.57511806488037</v>
+        <v>3.57511782646179</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.63069009780884</v>
+        <v>3.63068985939026</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.63069009780884</v>
+        <v>3.63068985939026</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.63069009780884</v>
+        <v>3.63068985939026</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.63069009780884</v>
+        <v>3.63068985939026</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.77888107299805</v>
+        <v>3.77888131141663</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.77888107299805</v>
+        <v>3.77888131141663</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -45846,6 +45846,32 @@
         <v>2.3199999332428</v>
       </c>
       <c r="H1749" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="1" t="n">
+        <v>46177.2916666667</v>
+      </c>
+      <c r="B1750" t="n">
+        <v>250</v>
+      </c>
+      <c r="C1750" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1750" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="H1750" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -40622,6 +40622,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1751">
+      <c r="A1751" s="1" t="n">
+        <v>46178.2916666667</v>
+      </c>
+      <c r="B1751" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1751" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MARP.MI.xlsx
+++ b/data/MARP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2" t="n">
-        <v>4.197829246521</v>
+        <v>4.19782829284668</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.25</v>
       </c>
       <c r="G6" t="n">
-        <v>4.43432664871216</v>
+        <v>4.434326171875</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G7" t="n">
-        <v>4.39209461212158</v>
+        <v>4.39209413528442</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G8" t="n">
-        <v>4.27553462982178</v>
+        <v>4.27553510665894</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>4.25695323944092</v>
+        <v>4.25695371627808</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.0479998588562</v>
       </c>
       <c r="G10" t="n">
-        <v>4.26371002197266</v>
+        <v>4.26371049880981</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G11" t="n">
-        <v>4.29918527603149</v>
+        <v>4.29918479919434</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G12" t="n">
-        <v>4.21472120285034</v>
+        <v>4.21472072601318</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>4.25695323944092</v>
+        <v>4.25695371627808</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G14" t="n">
-        <v>4.10491943359375</v>
+        <v>4.10491991043091</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G15" t="n">
-        <v>4.10491943359375</v>
+        <v>4.10491991043091</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>4.10491943359375</v>
+        <v>4.10491991043091</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>4.22316741943359</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>4.22316741943359</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>4.22316741943359</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>4.22316741943359</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>4.25695323944092</v>
+        <v>4.25695371627808</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G24" t="n">
-        <v>3.91149830818176</v>
+        <v>3.91149806976318</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G25" t="n">
-        <v>4.10491943359375</v>
+        <v>4.10491991043091</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G26" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G27" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G28" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G31" t="n">
-        <v>4.11336517333984</v>
+        <v>4.113365650177</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G34" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G36" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G37" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G38" t="n">
-        <v>4.03734922409058</v>
+        <v>4.03734874725342</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G41" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G42" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G43" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G46" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G48" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G49" t="n">
-        <v>4.04579496383667</v>
+        <v>4.04579448699951</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G50" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>4.00356292724609</v>
+        <v>4.00356340408325</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G54" t="n">
-        <v>4.07113409042358</v>
+        <v>4.07113361358643</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>4.09647274017334</v>
+        <v>4.09647226333618</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.5</v>
       </c>
       <c r="G57" t="n">
-        <v>3.80085110664368</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G58" t="n">
-        <v>3.82618999481201</v>
+        <v>3.82619023323059</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>3.90220761299133</v>
+        <v>3.90220713615417</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G60" t="n">
-        <v>3.91065382957458</v>
+        <v>3.91065406799316</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>3.91065382957458</v>
+        <v>3.91065406799316</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G63" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>4.197829246521</v>
+        <v>4.19782829284668</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5</v>
       </c>
       <c r="G70" t="n">
-        <v>4.22316741943359</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>4.22316741943359</v>
+        <v>4.22316789627075</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G74" t="n">
-        <v>4.09647274017334</v>
+        <v>4.09647226333618</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G75" t="n">
-        <v>4.09647274017334</v>
+        <v>4.09647226333618</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G76" t="n">
-        <v>4.09647274017334</v>
+        <v>4.09647226333618</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G77" t="n">
-        <v>4.09647274017334</v>
+        <v>4.09647226333618</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G78" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G80" t="n">
-        <v>4.13870525360107</v>
+        <v>4.13870477676392</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G81" t="n">
-        <v>3.96133184432983</v>
+        <v>3.96133136749268</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G83" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G84" t="n">
-        <v>4.05424118041992</v>
+        <v>4.05424165725708</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G85" t="n">
-        <v>3.96133184432983</v>
+        <v>3.96133136749268</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G86" t="n">
-        <v>3.96133184432983</v>
+        <v>3.96133136749268</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G87" t="n">
-        <v>3.89376068115234</v>
+        <v>3.89376091957092</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96133184432983</v>
+        <v>3.96133136749268</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>3.88531446456909</v>
+        <v>3.88531470298767</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G90" t="n">
-        <v>3.83463644981384</v>
+        <v>3.83463668823242</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.84308362007141</v>
+        <v>3.84308290481567</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>3.69104886054993</v>
+        <v>3.69104862213135</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G96" t="n">
-        <v>3.59813928604126</v>
+        <v>3.59813904762268</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>3.62347793579102</v>
+        <v>3.62347841262817</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>3.60658526420593</v>
+        <v>3.60658502578735</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G99" t="n">
-        <v>3.54746079444885</v>
+        <v>3.54746103286743</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.25</v>
       </c>
       <c r="G100" t="n">
-        <v>3.58969235420227</v>
+        <v>3.58969259262085</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.25</v>
       </c>
       <c r="G101" t="n">
-        <v>3.58969235420227</v>
+        <v>3.58969259262085</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.25</v>
       </c>
       <c r="G102" t="n">
-        <v>3.58969235420227</v>
+        <v>3.58969259262085</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>3.60658526420593</v>
+        <v>3.60658502578735</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G107" t="n">
-        <v>3.85152912139893</v>
+        <v>3.8515293598175</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>3.86842179298401</v>
+        <v>3.86842131614685</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>3.97822451591492</v>
+        <v>3.97822403907776</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>3.82618999481201</v>
+        <v>3.82619023323059</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G112" t="n">
-        <v>3.96133184432983</v>
+        <v>3.96133136749268</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G113" t="n">
-        <v>3.85152912139893</v>
+        <v>3.8515293598175</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G114" t="n">
-        <v>3.85152912139893</v>
+        <v>3.8515293598175</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>3.86842179298401</v>
+        <v>3.86842131614685</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86842179298401</v>
+        <v>3.86842131614685</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>3.94443869590759</v>
+        <v>3.94443893432617</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>3.94443869590759</v>
+        <v>3.94443893432617</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G123" t="n">
-        <v>3.81774377822876</v>
+        <v>3.81774401664734</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G124" t="n">
-        <v>3.81774377822876</v>
+        <v>3.81774401664734</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G126" t="n">
-        <v>3.85997581481934</v>
+        <v>3.85997557640076</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G127" t="n">
-        <v>3.792405128479</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.80085110664368</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.5</v>
       </c>
       <c r="G129" t="n">
-        <v>3.80085110664368</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.5</v>
       </c>
       <c r="G130" t="n">
-        <v>3.80085110664368</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.5</v>
       </c>
       <c r="G131" t="n">
-        <v>3.80085110664368</v>
+        <v>3.80085134506226</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>3.89376068115234</v>
+        <v>3.89376091957092</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G133" t="n">
-        <v>3.89376068115234</v>
+        <v>3.89376091957092</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G134" t="n">
-        <v>3.89376068115234</v>
+        <v>3.89376091957092</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>3.93599200248718</v>
+        <v>3.93599271774292</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>3.93599200248718</v>
+        <v>3.93599271774292</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G137" t="n">
-        <v>3.93599200248718</v>
+        <v>3.93599271774292</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G138" t="n">
-        <v>3.93599200248718</v>
+        <v>3.93599271774292</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G139" t="n">
-        <v>3.792405128479</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>3.792405128479</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>3.84308362007141</v>
+        <v>3.84308290481567</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G142" t="n">
-        <v>3.84308362007141</v>
+        <v>3.84308290481567</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G143" t="n">
-        <v>3.84308362007141</v>
+        <v>3.84308290481567</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>3.84308362007141</v>
+        <v>3.84308290481567</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G145" t="n">
-        <v>3.84308362007141</v>
+        <v>3.84308290481567</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>3.84308362007141</v>
+        <v>3.84308290481567</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>3.84308362007141</v>
+        <v>3.84308290481567</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G148" t="n">
-        <v>3.88531446456909</v>
+        <v>3.88531470298767</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>3.792405128479</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G150" t="n">
-        <v>3.792405128479</v>
+        <v>3.79240489006042</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G151" t="n">
-        <v>3.81774377822876</v>
+        <v>3.81774401664734</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.83463644981384</v>
+        <v>3.83463668823242</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G155" t="n">
-        <v>3.64881706237793</v>
+        <v>3.64881753921509</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G156" t="n">
-        <v>3.64881706237793</v>
+        <v>3.64881753921509</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G157" t="n">
-        <v>3.64881706237793</v>
+        <v>3.64881753921509</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G158" t="n">
-        <v>3.59813928604126</v>
+        <v>3.59813904762268</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G159" t="n">
-        <v>3.54746079444885</v>
+        <v>3.54746103286743</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40387392044067</v>
+        <v>3.40387368202209</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.30251717567444</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G165" t="n">
-        <v>3.30251717567444</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G166" t="n">
-        <v>3.30251717567444</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G167" t="n">
-        <v>3.30251717567444</v>
+        <v>3.30251741409302</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.75</v>
       </c>
       <c r="G169" t="n">
-        <v>3.16737627983093</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.75</v>
       </c>
       <c r="G170" t="n">
-        <v>3.16737627983093</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.75</v>
       </c>
       <c r="G171" t="n">
-        <v>3.16737627983093</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.75</v>
       </c>
       <c r="G172" t="n">
-        <v>3.16737627983093</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75</v>
       </c>
       <c r="G173" t="n">
-        <v>3.16737627983093</v>
+        <v>3.16737604141235</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12514448165894</v>
+        <v>3.12514424324036</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G177" t="n">
-        <v>3.25183939933777</v>
+        <v>3.25183916091919</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G178" t="n">
-        <v>3.25183939933777</v>
+        <v>3.25183916091919</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25183939933777</v>
+        <v>3.25183916091919</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>3.41231942176819</v>
+        <v>3.41231966018677</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G194" t="n">
-        <v>3.19271516799927</v>
+        <v>3.19271492958069</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G195" t="n">
-        <v>3.10825157165527</v>
+        <v>3.10825181007385</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G196" t="n">
-        <v>3.10825157165527</v>
+        <v>3.10825181007385</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G197" t="n">
-        <v>3.10825157165527</v>
+        <v>3.10825181007385</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G198" t="n">
-        <v>3.10825157165527</v>
+        <v>3.10825181007385</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>3.29407143592834</v>
+        <v>3.29407095909119</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G210" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G211" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G212" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G213" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>3.31096339225769</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G216" t="n">
-        <v>3.31096339225769</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G217" t="n">
-        <v>3.31096339225769</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.31096339225769</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G219" t="n">
-        <v>3.31096339225769</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G220" t="n">
-        <v>3.31096339225769</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G221" t="n">
-        <v>3.31096339225769</v>
+        <v>3.31096363067627</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.34527468681335</v>
+        <v>3.3452742099762</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G223" t="n">
-        <v>3.32811903953552</v>
+        <v>3.32811880111694</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682686805725</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G228" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682686805725</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682686805725</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>3.51682662963867</v>
+        <v>3.51682686805725</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>3.34527468681335</v>
+        <v>3.3452742099762</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G233" t="n">
-        <v>3.25949788093567</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19087719917297</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G238" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G239" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G240" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G241" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G242" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G243" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G245" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G246" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G248" t="n">
-        <v>3.19087719917297</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>3.19087719917297</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G250" t="n">
-        <v>3.19087719917297</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G253" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>3.07079029083252</v>
+        <v>3.07079005241394</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>3.07079029083252</v>
+        <v>3.07079005241394</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>3.07079029083252</v>
+        <v>3.07079005241394</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G257" t="n">
-        <v>3.01932430267334</v>
+        <v>3.01932454109192</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>2.98501420021057</v>
+        <v>2.98501396179199</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G276" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G277" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G285" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G286" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G288" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G289" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G291" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G292" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G297" t="n">
-        <v>2.89923763275146</v>
+        <v>2.89923787117004</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G301" t="n">
-        <v>2.72768545150757</v>
+        <v>2.72768521308899</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3</v>
       </c>
       <c r="G305" t="n">
-        <v>2.57328796386719</v>
+        <v>2.57328772544861</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>2.55613255500793</v>
+        <v>2.55613279342651</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G307" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G309" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G317" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G319" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G320" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G321" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G322" t="n">
-        <v>2.264493227005</v>
+        <v>2.26449346542358</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>2.1615617275238</v>
+        <v>2.16156196594238</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>2.1100959777832</v>
+        <v>2.11009621620178</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G331" t="n">
-        <v>2.04147505760193</v>
+        <v>2.04147529602051</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G332" t="n">
-        <v>2.07578563690186</v>
+        <v>2.07578539848328</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G333" t="n">
-        <v>2.04147505760193</v>
+        <v>2.04147529602051</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>2.04147505760193</v>
+        <v>2.04147529602051</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G336" t="n">
-        <v>1.90423309803009</v>
+        <v>1.9042329788208</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G338" t="n">
-        <v>1.83561229705811</v>
+        <v>1.83561217784882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G344" t="n">
-        <v>1.80130136013031</v>
+        <v>1.80130124092102</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>1.99000918865204</v>
+        <v>1.99000930786133</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G352" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G353" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G354" t="n">
-        <v>2.07578563690186</v>
+        <v>2.07578539848328</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>2.07578563690186</v>
+        <v>2.07578539848328</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G357" t="n">
-        <v>2.1615617275238</v>
+        <v>2.16156196594238</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>2.1100959777832</v>
+        <v>2.11009621620178</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G361" t="n">
-        <v>2.12725162506104</v>
+        <v>2.12725138664246</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G362" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>2.0586302280426</v>
+        <v>2.05863046646118</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G366" t="n">
-        <v>2.55613255500793</v>
+        <v>2.55613279342651</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3</v>
       </c>
       <c r="G368" t="n">
-        <v>2.57328796386719</v>
+        <v>2.57328772544861</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G370" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G376" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G378" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G385" t="n">
-        <v>2.33311462402344</v>
+        <v>2.33311438560486</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G395" t="n">
-        <v>2.33311462402344</v>
+        <v>2.33311438560486</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G403" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G408" t="n">
-        <v>2.55613255500793</v>
+        <v>2.55613279342651</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G410" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G418" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G421" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G422" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G423" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G424" t="n">
-        <v>2.40173506736755</v>
+        <v>2.40173530578613</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G427" t="n">
-        <v>2.59044313430786</v>
+        <v>2.59044289588928</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>2.59044313430786</v>
+        <v>2.59044289588928</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G429" t="n">
-        <v>2.48751187324524</v>
+        <v>2.48751163482666</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G433" t="n">
-        <v>2.55613255500793</v>
+        <v>2.55613279342651</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G434" t="n">
-        <v>2.72768545150757</v>
+        <v>2.72768521308899</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G436" t="n">
-        <v>2.96785855293274</v>
+        <v>2.96785879135132</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>2.96785855293274</v>
+        <v>2.96785879135132</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>3.08794546127319</v>
+        <v>3.08794522285461</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G441" t="n">
-        <v>3.15656638145447</v>
+        <v>3.15656685829163</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.25949788093567</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G443" t="n">
-        <v>3.25949788093567</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G444" t="n">
-        <v>3.19087719917297</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>3.17372179031372</v>
+        <v>3.17372155189514</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G446" t="n">
-        <v>3.13941121101379</v>
+        <v>3.13941144943237</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G447" t="n">
-        <v>3.15656638145447</v>
+        <v>3.15656685829163</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G448" t="n">
-        <v>3.15656638145447</v>
+        <v>3.15656685829163</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G449" t="n">
-        <v>3.15656638145447</v>
+        <v>3.15656685829163</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>3.15656638145447</v>
+        <v>3.15656685829163</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G451" t="n">
-        <v>3.25949788093567</v>
+        <v>3.25949811935425</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G452" t="n">
-        <v>3.22518754005432</v>
+        <v>3.22518730163574</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="n">
-        <v>3.19087719917297</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G454" t="n">
-        <v>3.19087719917297</v>
+        <v>3.19087672233582</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>3.17372179031372</v>
+        <v>3.17372155189514</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>3.08794546127319</v>
+        <v>3.087945